--- a/TunnelDataProcessing/BoundaryLayerComparison/BoundaryLayerComparison.xlsx
+++ b/TunnelDataProcessing/BoundaryLayerComparison/BoundaryLayerComparison.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="12" uniqueCount="3">
   <si>
-    <t>Y_cm</t>
+    <t>Y_over_D</t>
   </si>
   <si>
     <t>Mach</t>
@@ -74,7 +74,7 @@
   <dimension ref="A1:C102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.5546875" customWidth="true"/>
+    <col min="1" max="1" width="13.5546875" customWidth="true"/>
     <col min="2" max="2" width="11.5546875" customWidth="true"/>
     <col min="3" max="3" width="12.5546875" customWidth="true"/>
   </cols>
@@ -103,7 +103,7 @@
     </row>
     <row r="3">
       <c r="A3" s="0">
-        <v>0.025399999999999999</v>
+        <v>0.013661055235841445</v>
       </c>
       <c r="B3" s="0">
         <v>1.1801272893808017</v>
@@ -114,7 +114,7 @@
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>0.050800000000000005</v>
+        <v>0.027322110471682894</v>
       </c>
       <c r="B4" s="0">
         <v>1.2703880532489977</v>
@@ -125,7 +125,7 @@
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>0.076200000000000018</v>
+        <v>0.040983165707524347</v>
       </c>
       <c r="B5" s="0">
         <v>1.3199692774267098</v>
@@ -136,7 +136,7 @@
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>0.1016</v>
+        <v>0.054644220943365782</v>
       </c>
       <c r="B6" s="0">
         <v>1.3649038953773749</v>
@@ -147,7 +147,7 @@
     </row>
     <row r="7">
       <c r="A7" s="0">
-        <v>0.127</v>
+        <v>0.06830527617920723</v>
       </c>
       <c r="B7" s="0">
         <v>1.4069184970061013</v>
@@ -158,7 +158,7 @@
     </row>
     <row r="8">
       <c r="A8" s="0">
-        <v>0.15240000000000001</v>
+        <v>0.081966331415048679</v>
       </c>
       <c r="B8" s="0">
         <v>1.433074383134163</v>
@@ -169,7 +169,7 @@
     </row>
     <row r="9">
       <c r="A9" s="0">
-        <v>0.17780000000000001</v>
+        <v>0.095627386650890128</v>
       </c>
       <c r="B9" s="0">
         <v>1.4653548246463237</v>
@@ -180,7 +180,7 @@
     </row>
     <row r="10">
       <c r="A10" s="0">
-        <v>0.20320000000000002</v>
+        <v>0.10928844188673158</v>
       </c>
       <c r="B10" s="0">
         <v>1.4833701477140482</v>
@@ -191,7 +191,7 @@
     </row>
     <row r="11">
       <c r="A11" s="0">
-        <v>0.2286</v>
+        <v>0.12294949712257301</v>
       </c>
       <c r="B11" s="0">
         <v>1.5122113345495833</v>
@@ -202,7 +202,7 @@
     </row>
     <row r="12">
       <c r="A12" s="0">
-        <v>0.25400000000000006</v>
+        <v>0.13661055235841449</v>
       </c>
       <c r="B12" s="0">
         <v>1.5270056304221185</v>
@@ -213,7 +213,7 @@
     </row>
     <row r="13">
       <c r="A13" s="0">
-        <v>0.27940000000000004</v>
+        <v>0.15027160759425592</v>
       </c>
       <c r="B13" s="0">
         <v>1.5512238889731131</v>
@@ -224,7 +224,7 @@
     </row>
     <row r="14">
       <c r="A14" s="0">
-        <v>0.30480000000000002</v>
+        <v>0.16393266283009736</v>
       </c>
       <c r="B14" s="0">
         <v>1.5709300764159524</v>
@@ -235,7 +235,7 @@
     </row>
     <row r="15">
       <c r="A15" s="0">
-        <v>0.33019999999999999</v>
+        <v>0.17759371806593879</v>
       </c>
       <c r="B15" s="0">
         <v>1.5907753810842402</v>
@@ -246,7 +246,7 @@
     </row>
     <row r="16">
       <c r="A16" s="0">
-        <v>0.35560000000000003</v>
+        <v>0.19125477330178026</v>
       </c>
       <c r="B16" s="0">
         <v>1.6125544390281139</v>
@@ -257,7 +257,7 @@
     </row>
     <row r="17">
       <c r="A17" s="0">
-        <v>0.38100000000000001</v>
+        <v>0.20491582853762169</v>
       </c>
       <c r="B17" s="0">
         <v>1.6303697885348365</v>
@@ -268,7 +268,7 @@
     </row>
     <row r="18">
       <c r="A18" s="0">
-        <v>0.40639999999999998</v>
+        <v>0.21857688377346313</v>
       </c>
       <c r="B18" s="0">
         <v>1.6447327293663507</v>
@@ -279,7 +279,7 @@
     </row>
     <row r="19">
       <c r="A19" s="0">
-        <v>0.43180000000000002</v>
+        <v>0.23223793900930459</v>
       </c>
       <c r="B19" s="0">
         <v>1.6598148970147137</v>
@@ -290,7 +290,7 @@
     </row>
     <row r="20">
       <c r="A20" s="0">
-        <v>0.45719999999999994</v>
+        <v>0.245898994245146</v>
       </c>
       <c r="B20" s="0">
         <v>1.6697415726619329</v>
@@ -301,7 +301,7 @@
     </row>
     <row r="21">
       <c r="A21" s="0">
-        <v>0.48260000000000003</v>
+        <v>0.25956004948098749</v>
       </c>
       <c r="B21" s="0">
         <v>1.6843850017447239</v>
@@ -312,7 +312,7 @@
     </row>
     <row r="22">
       <c r="A22" s="0">
-        <v>0.50800000000000001</v>
+        <v>0.27322110471682892</v>
       </c>
       <c r="B22" s="0">
         <v>1.7002614123723407</v>
@@ -323,7 +323,7 @@
     </row>
     <row r="23">
       <c r="A23" s="0">
-        <v>0.53339999999999999</v>
+        <v>0.28688215995267036</v>
       </c>
       <c r="B23" s="0">
         <v>1.713833150061147</v>
@@ -334,7 +334,7 @@
     </row>
     <row r="24">
       <c r="A24" s="0">
-        <v>0.55879999999999996</v>
+        <v>0.30054321518851179</v>
       </c>
       <c r="B24" s="0">
         <v>1.7239702300810447</v>
@@ -345,7 +345,7 @@
     </row>
     <row r="25">
       <c r="A25" s="0">
-        <v>0.58420000000000005</v>
+        <v>0.31420427042435328</v>
       </c>
       <c r="B25" s="0">
         <v>1.7363621535622578</v>
@@ -356,7 +356,7 @@
     </row>
     <row r="26">
       <c r="A26" s="0">
-        <v>0.60960000000000003</v>
+        <v>0.32786532566019472</v>
       </c>
       <c r="B26" s="0">
         <v>1.7504585312760839</v>
@@ -367,7 +367,7 @@
     </row>
     <row r="27">
       <c r="A27" s="0">
-        <v>0.63500000000000012</v>
+        <v>0.34152638089603621</v>
       </c>
       <c r="B27" s="0">
         <v>1.7637787746447846</v>
@@ -378,7 +378,7 @@
     </row>
     <row r="28">
       <c r="A28" s="0">
-        <v>0.6604000000000001</v>
+        <v>0.35518743613187764</v>
       </c>
       <c r="B28" s="0">
         <v>1.7699116970299644</v>
@@ -389,7 +389,7 @@
     </row>
     <row r="29">
       <c r="A29" s="0">
-        <v>0.68580000000000008</v>
+        <v>0.36884849136771908</v>
       </c>
       <c r="B29" s="0">
         <v>1.7845186480742063</v>
@@ -400,7 +400,7 @@
     </row>
     <row r="30">
       <c r="A30" s="0">
-        <v>0.71120000000000017</v>
+        <v>0.38250954660356057</v>
       </c>
       <c r="B30" s="0">
         <v>1.7996559313864116</v>
@@ -411,7 +411,7 @@
     </row>
     <row r="31">
       <c r="A31" s="0">
-        <v>0.73660000000000003</v>
+        <v>0.39617060183940195</v>
       </c>
       <c r="B31" s="0">
         <v>1.8042467104192472</v>
@@ -422,7 +422,7 @@
     </row>
     <row r="32">
       <c r="A32" s="0">
-        <v>0.76200000000000001</v>
+        <v>0.40983165707524338</v>
       </c>
       <c r="B32" s="0">
         <v>1.8182353825519313</v>
@@ -433,7 +433,7 @@
     </row>
     <row r="33">
       <c r="A33" s="0">
-        <v>0.7874000000000001</v>
+        <v>0.42349271231108487</v>
       </c>
       <c r="B33" s="0">
         <v>1.8302739876195666</v>
@@ -444,7 +444,7 @@
     </row>
     <row r="34">
       <c r="A34" s="0">
-        <v>0.81280000000000008</v>
+        <v>0.43715376754692631</v>
       </c>
       <c r="B34" s="0">
         <v>1.8361021708613796</v>
@@ -455,7 +455,7 @@
     </row>
     <row r="35">
       <c r="A35" s="0">
-        <v>0.83820000000000017</v>
+        <v>0.4508148227827678</v>
       </c>
       <c r="B35" s="0">
         <v>1.8446464361359243</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="36">
       <c r="A36" s="0">
-        <v>0.86360000000000015</v>
+        <v>0.46447587801860923</v>
       </c>
       <c r="B36" s="0">
         <v>1.8573114680691525</v>
@@ -477,7 +477,7 @@
     </row>
     <row r="37">
       <c r="A37" s="0">
-        <v>0.88900000000000001</v>
+        <v>0.47813693325445061</v>
       </c>
       <c r="B37" s="0">
         <v>1.8677466904890905</v>
@@ -488,7 +488,7 @@
     </row>
     <row r="38">
       <c r="A38" s="0">
-        <v>0.91439999999999999</v>
+        <v>0.49179798849029205</v>
       </c>
       <c r="B38" s="0">
         <v>1.8856764809010658</v>
@@ -499,7 +499,7 @@
     </row>
     <row r="39">
       <c r="A39" s="0">
-        <v>0.93980000000000008</v>
+        <v>0.50545904372613359</v>
       </c>
       <c r="B39" s="0">
         <v>1.891474820100556</v>
@@ -510,7 +510,7 @@
     </row>
     <row r="40">
       <c r="A40" s="0">
-        <v>0.96520000000000017</v>
+        <v>0.51912009896197508</v>
       </c>
       <c r="B40" s="0">
         <v>1.8944542398949935</v>
@@ -521,7 +521,7 @@
     </row>
     <row r="41">
       <c r="A41" s="0">
-        <v>0.99060000000000004</v>
+        <v>0.53278115419781646</v>
       </c>
       <c r="B41" s="0">
         <v>1.9007403611013853</v>
@@ -532,7 +532,7 @@
     </row>
     <row r="42">
       <c r="A42" s="0">
-        <v>1.016</v>
+        <v>0.54644220943365784</v>
       </c>
       <c r="B42" s="0">
         <v>1.9214539861382809</v>
@@ -543,7 +543,7 @@
     </row>
     <row r="43">
       <c r="A43" s="0">
-        <v>1.0413999999999999</v>
+        <v>0.56010326466949922</v>
       </c>
       <c r="B43" s="0">
         <v>1.9202791787202922</v>
@@ -554,7 +554,7 @@
     </row>
     <row r="44">
       <c r="A44" s="0">
-        <v>1.0668</v>
+        <v>0.57376431990534071</v>
       </c>
       <c r="B44" s="0">
         <v>1.9274830250897403</v>
@@ -565,7 +565,7 @@
     </row>
     <row r="45">
       <c r="A45" s="0">
-        <v>1.0922000000000001</v>
+        <v>0.5874253751411822</v>
       </c>
       <c r="B45" s="0">
         <v>1.9421778035683002</v>
@@ -576,7 +576,7 @@
     </row>
     <row r="46">
       <c r="A46" s="0">
-        <v>1.1175999999999999</v>
+        <v>0.60108643037702358</v>
       </c>
       <c r="B46" s="0">
         <v>1.946322054454416</v>
@@ -587,7 +587,7 @@
     </row>
     <row r="47">
       <c r="A47" s="0">
-        <v>1.143</v>
+        <v>0.61474748561286507</v>
       </c>
       <c r="B47" s="0">
         <v>1.9509668650917373</v>
@@ -598,7 +598,7 @@
     </row>
     <row r="48">
       <c r="A48" s="0">
-        <v>1.1684000000000001</v>
+        <v>0.62840854084870656</v>
       </c>
       <c r="B48" s="0">
         <v>1.9618850638946261</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="49">
       <c r="A49" s="0">
-        <v>1.1938</v>
+        <v>0.64206959608454794</v>
       </c>
       <c r="B49" s="0">
         <v>1.9645366119856296</v>
@@ -620,7 +620,7 @@
     </row>
     <row r="50">
       <c r="A50" s="0">
-        <v>1.2191999999999998</v>
+        <v>0.65573065132038932</v>
       </c>
       <c r="B50" s="0">
         <v>1.9810922636585904</v>
@@ -631,7 +631,7 @@
     </row>
     <row r="51">
       <c r="A51" s="0">
-        <v>1.2445999999999997</v>
+        <v>0.6693917065562307</v>
       </c>
       <c r="B51" s="0">
         <v>1.9820735124647584</v>
@@ -642,7 +642,7 @@
     </row>
     <row r="52">
       <c r="A52" s="0">
-        <v>1.2699999999999998</v>
+        <v>0.68305276179207219</v>
       </c>
       <c r="B52" s="0">
         <v>1.994247223365694</v>
@@ -653,7 +653,7 @@
     </row>
     <row r="53">
       <c r="A53" s="0">
-        <v>1.2953999999999999</v>
+        <v>0.69671381702791368</v>
       </c>
       <c r="B53" s="0">
         <v>2.0011858588976827</v>
@@ -664,7 +664,7 @@
     </row>
     <row r="54">
       <c r="A54" s="0">
-        <v>1.3208</v>
+        <v>0.71037487226375517</v>
       </c>
       <c r="B54" s="0">
         <v>2.0074550896397381</v>
@@ -675,7 +675,7 @@
     </row>
     <row r="55">
       <c r="A55" s="0">
-        <v>1.3461999999999998</v>
+        <v>0.72403592749959655</v>
       </c>
       <c r="B55" s="0">
         <v>2.0107211883721829</v>
@@ -686,7 +686,7 @@
     </row>
     <row r="56">
       <c r="A56" s="0">
-        <v>1.3715999999999999</v>
+        <v>0.73769698273543804</v>
       </c>
       <c r="B56" s="0">
         <v>2.0160358106010925</v>
@@ -697,7 +697,7 @@
     </row>
     <row r="57">
       <c r="A57" s="0">
-        <v>1.397</v>
+        <v>0.75135803797127954</v>
       </c>
       <c r="B57" s="0">
         <v>2.0233812552390535</v>
@@ -708,7 +708,7 @@
     </row>
     <row r="58">
       <c r="A58" s="0">
-        <v>1.4223999999999999</v>
+        <v>0.76501909320712091</v>
       </c>
       <c r="B58" s="0">
         <v>2.0239860635023876</v>
@@ -719,7 +719,7 @@
     </row>
     <row r="59">
       <c r="A59" s="0">
-        <v>1.4477999999999998</v>
+        <v>0.77868014844296229</v>
       </c>
       <c r="B59" s="0">
         <v>2.0332162962056923</v>
@@ -730,7 +730,7 @@
     </row>
     <row r="60">
       <c r="A60" s="0">
-        <v>1.4731999999999998</v>
+        <v>0.79234120367880378</v>
       </c>
       <c r="B60" s="0">
         <v>2.0377894248150561</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="61">
       <c r="A61" s="0">
-        <v>1.4985999999999997</v>
+        <v>0.80600225891464516</v>
       </c>
       <c r="B61" s="0">
         <v>2.0388522053156368</v>
@@ -752,7 +752,7 @@
     </row>
     <row r="62">
       <c r="A62" s="0">
-        <v>1.5239999999999998</v>
+        <v>0.81966331415048665</v>
       </c>
       <c r="B62" s="0">
         <v>2.0425296624780596</v>
@@ -763,7 +763,7 @@
     </row>
     <row r="63">
       <c r="A63" s="0">
-        <v>1.5493999999999999</v>
+        <v>0.83332436938632815</v>
       </c>
       <c r="B63" s="0">
         <v>2.0537170209256859</v>
@@ -774,7 +774,7 @@
     </row>
     <row r="64">
       <c r="A64" s="0">
-        <v>1.5747999999999998</v>
+        <v>0.84698542462216952</v>
       </c>
       <c r="B64" s="0">
         <v>2.0511956404237117</v>
@@ -785,7 +785,7 @@
     </row>
     <row r="65">
       <c r="A65" s="0">
-        <v>1.6001999999999998</v>
+        <v>0.86064647985801102</v>
       </c>
       <c r="B65" s="0">
         <v>2.0579376104521154</v>
@@ -796,7 +796,7 @@
     </row>
     <row r="66">
       <c r="A66" s="0">
-        <v>1.6255999999999999</v>
+        <v>0.87430753509385251</v>
       </c>
       <c r="B66" s="0">
         <v>2.0619459568027794</v>
@@ -807,7 +807,7 @@
     </row>
     <row r="67">
       <c r="A67" s="0">
-        <v>1.6509999999999998</v>
+        <v>0.88796859032969389</v>
       </c>
       <c r="B67" s="0">
         <v>2.0698774625552594</v>
@@ -818,7 +818,7 @@
     </row>
     <row r="68">
       <c r="A68" s="0">
-        <v>1.6763999999999999</v>
+        <v>0.90162964556553538</v>
       </c>
       <c r="B68" s="0">
         <v>2.062958675367776</v>
@@ -829,7 +829,7 @@
     </row>
     <row r="69">
       <c r="A69" s="0">
-        <v>1.7018</v>
+        <v>0.91529070080137687</v>
       </c>
       <c r="B69" s="0">
         <v>2.0762866300865377</v>
@@ -840,7 +840,7 @@
     </row>
     <row r="70">
       <c r="A70" s="0">
-        <v>1.7272000000000001</v>
+        <v>0.92895175603721836</v>
       </c>
       <c r="B70" s="0">
         <v>2.077034608690715</v>
@@ -851,7 +851,7 @@
     </row>
     <row r="71">
       <c r="A71" s="0">
-        <v>1.7525999999999997</v>
+        <v>0.94261281127305963</v>
       </c>
       <c r="B71" s="0">
         <v>2.0789740542092456</v>
@@ -862,7 +862,7 @@
     </row>
     <row r="72">
       <c r="A72" s="0">
-        <v>1.7779999999999998</v>
+        <v>0.95627386650890112</v>
       </c>
       <c r="B72" s="0">
         <v>2.0812543488510515</v>
@@ -873,7 +873,7 @@
     </row>
     <row r="73">
       <c r="A73" s="0">
-        <v>1.8033999999999997</v>
+        <v>0.9699349217447425</v>
       </c>
       <c r="B73" s="0">
         <v>2.0804089539163932</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="74">
       <c r="A74" s="0">
-        <v>1.8287999999999998</v>
+        <v>0.98359597698058399</v>
       </c>
       <c r="B74" s="0">
         <v>2.0790038267260029</v>
@@ -895,7 +895,7 @@
     </row>
     <row r="75">
       <c r="A75" s="0">
-        <v>1.8541999999999998</v>
+        <v>0.99725703221642548</v>
       </c>
       <c r="B75" s="0">
         <v>2.0790301123714281</v>
@@ -906,7 +906,7 @@
     </row>
     <row r="76">
       <c r="A76" s="0">
-        <v>1.8795999999999997</v>
+        <v>1.0109180874522667</v>
       </c>
       <c r="B76" s="0">
         <v>2.0786896581288801</v>
@@ -917,7 +917,7 @@
     </row>
     <row r="77">
       <c r="A77" s="0">
-        <v>1.9049999999999998</v>
+        <v>1.0245791426881083</v>
       </c>
       <c r="B77" s="0">
         <v>2.076683596976634</v>
@@ -928,7 +928,7 @@
     </row>
     <row r="78">
       <c r="A78" s="0">
-        <v>1.9303999999999999</v>
+        <v>1.0382401979239499</v>
       </c>
       <c r="B78" s="0">
         <v>2.0749784870930008</v>
@@ -939,7 +939,7 @@
     </row>
     <row r="79">
       <c r="A79" s="0">
-        <v>1.9558</v>
+        <v>1.0519012531597913</v>
       </c>
       <c r="B79" s="0">
         <v>2.0762344313246754</v>
@@ -950,7 +950,7 @@
     </row>
     <row r="80">
       <c r="A80" s="0">
-        <v>1.9811999999999999</v>
+        <v>1.0655623083956327</v>
       </c>
       <c r="B80" s="0">
         <v>2.0782855312316246</v>
@@ -961,7 +961,7 @@
     </row>
     <row r="81">
       <c r="A81" s="0">
-        <v>2.0065999999999997</v>
+        <v>1.0792233636314741</v>
       </c>
       <c r="B81" s="0">
         <v>2.0774722259440317</v>
@@ -972,7 +972,7 @@
     </row>
     <row r="82">
       <c r="A82" s="0">
-        <v>2.032</v>
+        <v>1.0928844188673157</v>
       </c>
       <c r="B82" s="0">
         <v>2.0789847234394747</v>
@@ -983,7 +983,7 @@
     </row>
     <row r="83">
       <c r="A83" s="0">
-        <v>2.0573999999999999</v>
+        <v>1.1065454741031571</v>
       </c>
       <c r="B83" s="0">
         <v>2.0810170329842466</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="84">
       <c r="A84" s="0">
-        <v>2.0827999999999998</v>
+        <v>1.1202065293389984</v>
       </c>
       <c r="B84" s="0">
         <v>2.0806476034369767</v>
@@ -1005,7 +1005,7 @@
     </row>
     <row r="85">
       <c r="A85" s="0">
-        <v>2.1081999999999996</v>
+        <v>1.1338675845748398</v>
       </c>
       <c r="B85" s="0">
         <v>2.0812655843253434</v>
@@ -1016,7 +1016,7 @@
     </row>
     <row r="86">
       <c r="A86" s="0">
-        <v>2.1335999999999999</v>
+        <v>1.1475286398106814</v>
       </c>
       <c r="B86" s="0">
         <v>2.083783165031635</v>
@@ -1027,7 +1027,7 @@
     </row>
     <row r="87">
       <c r="A87" s="0">
-        <v>2.1589999999999998</v>
+        <v>1.1611896950465228</v>
       </c>
       <c r="B87" s="0">
         <v>2.084183588990745</v>
@@ -1038,7 +1038,7 @@
     </row>
     <row r="88">
       <c r="A88" s="0">
-        <v>2.1843999999999997</v>
+        <v>1.1748507502823642</v>
       </c>
       <c r="B88" s="0">
         <v>2.0847598317312452</v>
@@ -1049,7 +1049,7 @@
     </row>
     <row r="89">
       <c r="A89" s="0">
-        <v>2.2098</v>
+        <v>1.1885118055182058</v>
       </c>
       <c r="B89" s="0">
         <v>2.0863662512352565</v>
@@ -1060,7 +1060,7 @@
     </row>
     <row r="90">
       <c r="A90" s="0">
-        <v>2.2351999999999999</v>
+        <v>1.2021728607540472</v>
       </c>
       <c r="B90" s="0">
         <v>2.0866615922173031</v>
@@ -1071,7 +1071,7 @@
     </row>
     <row r="91">
       <c r="A91" s="0">
-        <v>2.2605999999999997</v>
+        <v>1.2158339159898885</v>
       </c>
       <c r="B91" s="0">
         <v>2.0872585326684021</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="92">
       <c r="A92" s="0">
-        <v>2.286</v>
+        <v>1.2294949712257301</v>
       </c>
       <c r="B92" s="0">
         <v>2.0889936832896634</v>
@@ -1093,7 +1093,7 @@
     </row>
     <row r="93">
       <c r="A93" s="0">
-        <v>2.3113999999999999</v>
+        <v>1.2431560264615715</v>
       </c>
       <c r="B93" s="0">
         <v>2.0895626095608311</v>
@@ -1104,7 +1104,7 @@
     </row>
     <row r="94">
       <c r="A94" s="0">
-        <v>2.3367999999999998</v>
+        <v>1.2568170816974129</v>
       </c>
       <c r="B94" s="0">
         <v>2.0900664475671347</v>
@@ -1115,7 +1115,7 @@
     </row>
     <row r="95">
       <c r="A95" s="0">
-        <v>2.3622000000000001</v>
+        <v>1.2704781369332545</v>
       </c>
       <c r="B95" s="0">
         <v>2.0899826434458921</v>
@@ -1126,7 +1126,7 @@
     </row>
     <row r="96">
       <c r="A96" s="0">
-        <v>2.3875999999999995</v>
+        <v>1.2841391921690957</v>
       </c>
       <c r="B96" s="0">
         <v>2.0882875471414692</v>
@@ -1137,7 +1137,7 @@
     </row>
     <row r="97">
       <c r="A97" s="0">
-        <v>2.4129999999999998</v>
+        <v>1.2978002474049373</v>
       </c>
       <c r="B97" s="0">
         <v>2.0891972778324335</v>
@@ -1148,7 +1148,7 @@
     </row>
     <row r="98">
       <c r="A98" s="0">
-        <v>2.4383999999999997</v>
+        <v>1.3114613026407786</v>
       </c>
       <c r="B98" s="0">
         <v>2.0890097169373272</v>
@@ -1159,7 +1159,7 @@
     </row>
     <row r="99">
       <c r="A99" s="0">
-        <v>2.4638</v>
+        <v>1.3251223578766202</v>
       </c>
       <c r="B99" s="0">
         <v>2.0908557023832333</v>
@@ -1170,7 +1170,7 @@
     </row>
     <row r="100">
       <c r="A100" s="0">
-        <v>2.4891999999999999</v>
+        <v>1.3387834131124616</v>
       </c>
       <c r="B100" s="0">
         <v>2.0913515235657063</v>
@@ -1181,7 +1181,7 @@
     </row>
     <row r="101">
       <c r="A101" s="0">
-        <v>2.5145999999999997</v>
+        <v>1.352444468348303</v>
       </c>
       <c r="B101" s="0">
         <v>2.0930225097939967</v>
@@ -1192,7 +1192,7 @@
     </row>
     <row r="102">
       <c r="A102" s="0">
-        <v>2.54</v>
+        <v>1.3661055235841446</v>
       </c>
       <c r="B102" s="0">
         <v>2.093151881661107</v>
@@ -1210,7 +1210,7 @@
   <dimension ref="A1:C102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.5546875" customWidth="true"/>
+    <col min="1" max="1" width="13.5546875" customWidth="true"/>
     <col min="2" max="2" width="12.5546875" customWidth="true"/>
     <col min="3" max="3" width="12.5546875" customWidth="true"/>
   </cols>
@@ -1239,7 +1239,7 @@
     </row>
     <row r="3">
       <c r="A3" s="0">
-        <v>0.025400000000000002</v>
+        <v>0.013661055235841447</v>
       </c>
       <c r="B3" s="0">
         <v>0.54342481564007938</v>
@@ -1250,7 +1250,7 @@
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>0.050800000000000005</v>
+        <v>0.027322110471682894</v>
       </c>
       <c r="B4" s="0">
         <v>0.95787796605385633</v>
@@ -1261,7 +1261,7 @@
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>0.076200000000000004</v>
+        <v>0.04098316570752434</v>
       </c>
       <c r="B5" s="0">
         <v>1.1442788844265042</v>
@@ -1272,7 +1272,7 @@
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>0.10160000000000001</v>
+        <v>0.054644220943365789</v>
       </c>
       <c r="B6" s="0">
         <v>1.2153701708161071</v>
@@ -1283,7 +1283,7 @@
     </row>
     <row r="7">
       <c r="A7" s="0">
-        <v>0.127</v>
+        <v>0.06830527617920723</v>
       </c>
       <c r="B7" s="0">
         <v>1.2684796319446261</v>
@@ -1294,7 +1294,7 @@
     </row>
     <row r="8">
       <c r="A8" s="0">
-        <v>0.15240000000000001</v>
+        <v>0.081966331415048679</v>
       </c>
       <c r="B8" s="0">
         <v>1.3162243217368683</v>
@@ -1305,7 +1305,7 @@
     </row>
     <row r="9">
       <c r="A9" s="0">
-        <v>0.17780000000000001</v>
+        <v>0.095627386650890128</v>
       </c>
       <c r="B9" s="0">
         <v>1.3574896818881461</v>
@@ -1316,7 +1316,7 @@
     </row>
     <row r="10">
       <c r="A10" s="0">
-        <v>0.20320000000000002</v>
+        <v>0.10928844188673158</v>
       </c>
       <c r="B10" s="0">
         <v>1.3960349284979801</v>
@@ -1327,7 +1327,7 @@
     </row>
     <row r="11">
       <c r="A11" s="0">
-        <v>0.2286</v>
+        <v>0.12294949712257301</v>
       </c>
       <c r="B11" s="0">
         <v>1.4266616169728561</v>
@@ -1338,7 +1338,7 @@
     </row>
     <row r="12">
       <c r="A12" s="0">
-        <v>0.254</v>
+        <v>0.13661055235841446</v>
       </c>
       <c r="B12" s="0">
         <v>1.4547397750330797</v>
@@ -1349,7 +1349,7 @@
     </row>
     <row r="13">
       <c r="A13" s="0">
-        <v>0.27939999999999998</v>
+        <v>0.1502716075942559</v>
       </c>
       <c r="B13" s="0">
         <v>1.4797212709756193</v>
@@ -1360,7 +1360,7 @@
     </row>
     <row r="14">
       <c r="A14" s="0">
-        <v>0.30480000000000002</v>
+        <v>0.16393266283009736</v>
       </c>
       <c r="B14" s="0">
         <v>1.5051348409401275</v>
@@ -1371,7 +1371,7 @@
     </row>
     <row r="15">
       <c r="A15" s="0">
-        <v>0.33019999999999999</v>
+        <v>0.17759371806593879</v>
       </c>
       <c r="B15" s="0">
         <v>1.5199390535343353</v>
@@ -1382,7 +1382,7 @@
     </row>
     <row r="16">
       <c r="A16" s="0">
-        <v>0.35560000000000003</v>
+        <v>0.19125477330178026</v>
       </c>
       <c r="B16" s="0">
         <v>1.5477706346571014</v>
@@ -1393,7 +1393,7 @@
     </row>
     <row r="17">
       <c r="A17" s="0">
-        <v>0.38100000000000001</v>
+        <v>0.20491582853762169</v>
       </c>
       <c r="B17" s="0">
         <v>1.5641142860431971</v>
@@ -1404,7 +1404,7 @@
     </row>
     <row r="18">
       <c r="A18" s="0">
-        <v>0.40640000000000004</v>
+        <v>0.21857688377346315</v>
       </c>
       <c r="B18" s="0">
         <v>1.5837147348579532</v>
@@ -1415,7 +1415,7 @@
     </row>
     <row r="19">
       <c r="A19" s="0">
-        <v>0.43180000000000002</v>
+        <v>0.23223793900930459</v>
       </c>
       <c r="B19" s="0">
         <v>1.596412437583469</v>
@@ -1426,7 +1426,7 @@
     </row>
     <row r="20">
       <c r="A20" s="0">
-        <v>0.4572</v>
+        <v>0.24589899424514602</v>
       </c>
       <c r="B20" s="0">
         <v>1.6146002490234277</v>
@@ -1437,7 +1437,7 @@
     </row>
     <row r="21">
       <c r="A21" s="0">
-        <v>0.48260000000000003</v>
+        <v>0.25956004948098749</v>
       </c>
       <c r="B21" s="0">
         <v>1.6362267190936306</v>
@@ -1448,7 +1448,7 @@
     </row>
     <row r="22">
       <c r="A22" s="0">
-        <v>0.50800000000000001</v>
+        <v>0.27322110471682892</v>
       </c>
       <c r="B22" s="0">
         <v>1.6434510694586038</v>
@@ -1459,7 +1459,7 @@
     </row>
     <row r="23">
       <c r="A23" s="0">
-        <v>0.53339999999999999</v>
+        <v>0.28688215995267036</v>
       </c>
       <c r="B23" s="0">
         <v>1.6689867395243676</v>
@@ -1470,7 +1470,7 @@
     </row>
     <row r="24">
       <c r="A24" s="0">
-        <v>0.55879999999999996</v>
+        <v>0.30054321518851179</v>
       </c>
       <c r="B24" s="0">
         <v>1.676201284926365</v>
@@ -1481,7 +1481,7 @@
     </row>
     <row r="25">
       <c r="A25" s="0">
-        <v>0.58420000000000005</v>
+        <v>0.31420427042435328</v>
       </c>
       <c r="B25" s="0">
         <v>1.6874219921690372</v>
@@ -1492,7 +1492,7 @@
     </row>
     <row r="26">
       <c r="A26" s="0">
-        <v>0.60960000000000003</v>
+        <v>0.32786532566019472</v>
       </c>
       <c r="B26" s="0">
         <v>1.701661435915589</v>
@@ -1503,7 +1503,7 @@
     </row>
     <row r="27">
       <c r="A27" s="0">
-        <v>0.63500000000000001</v>
+        <v>0.34152638089603615</v>
       </c>
       <c r="B27" s="0">
         <v>1.7157523002003863</v>
@@ -1514,7 +1514,7 @@
     </row>
     <row r="28">
       <c r="A28" s="0">
-        <v>0.66039999999999999</v>
+        <v>0.35518743613187759</v>
       </c>
       <c r="B28" s="0">
         <v>1.7268351046621127</v>
@@ -1525,7 +1525,7 @@
     </row>
     <row r="29">
       <c r="A29" s="0">
-        <v>0.68580000000000008</v>
+        <v>0.36884849136771908</v>
       </c>
       <c r="B29" s="0">
         <v>1.7339042370987565</v>
@@ -1536,7 +1536,7 @@
     </row>
     <row r="30">
       <c r="A30" s="0">
-        <v>0.71120000000000005</v>
+        <v>0.38250954660356051</v>
       </c>
       <c r="B30" s="0">
         <v>1.7536929322619588</v>
@@ -1547,7 +1547,7 @@
     </row>
     <row r="31">
       <c r="A31" s="0">
-        <v>0.73659999999999992</v>
+        <v>0.39617060183940189</v>
       </c>
       <c r="B31" s="0">
         <v>1.7680875566839407</v>
@@ -1558,7 +1558,7 @@
     </row>
     <row r="32">
       <c r="A32" s="0">
-        <v>0.76200000000000001</v>
+        <v>0.40983165707524338</v>
       </c>
       <c r="B32" s="0">
         <v>1.7794782787063641</v>
@@ -1569,7 +1569,7 @@
     </row>
     <row r="33">
       <c r="A33" s="0">
-        <v>0.78739999999999999</v>
+        <v>0.42349271231108482</v>
       </c>
       <c r="B33" s="0">
         <v>1.7876330500223203</v>
@@ -1580,7 +1580,7 @@
     </row>
     <row r="34">
       <c r="A34" s="0">
-        <v>0.81280000000000008</v>
+        <v>0.43715376754692631</v>
       </c>
       <c r="B34" s="0">
         <v>1.7953218844312575</v>
@@ -1591,7 +1591,7 @@
     </row>
     <row r="35">
       <c r="A35" s="0">
-        <v>0.83820000000000006</v>
+        <v>0.45081482278276774</v>
       </c>
       <c r="B35" s="0">
         <v>1.8059876724927291</v>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="36">
       <c r="A36" s="0">
-        <v>0.86360000000000003</v>
+        <v>0.46447587801860918</v>
       </c>
       <c r="B36" s="0">
         <v>1.8135998702381615</v>
@@ -1613,7 +1613,7 @@
     </row>
     <row r="37">
       <c r="A37" s="0">
-        <v>0.8889999999999999</v>
+        <v>0.47813693325445056</v>
       </c>
       <c r="B37" s="0">
         <v>1.8251284801403713</v>
@@ -1624,7 +1624,7 @@
     </row>
     <row r="38">
       <c r="A38" s="0">
-        <v>0.91439999999999999</v>
+        <v>0.49179798849029205</v>
       </c>
       <c r="B38" s="0">
         <v>1.8330010011429358</v>
@@ -1635,7 +1635,7 @@
     </row>
     <row r="39">
       <c r="A39" s="0">
-        <v>0.93979999999999997</v>
+        <v>0.50545904372613348</v>
       </c>
       <c r="B39" s="0">
         <v>1.8517029845433384</v>
@@ -1646,7 +1646,7 @@
     </row>
     <row r="40">
       <c r="A40" s="0">
-        <v>0.96520000000000006</v>
+        <v>0.51912009896197497</v>
       </c>
       <c r="B40" s="0">
         <v>1.8539005330462288</v>
@@ -1657,7 +1657,7 @@
     </row>
     <row r="41">
       <c r="A41" s="0">
-        <v>0.99060000000000004</v>
+        <v>0.53278115419781646</v>
       </c>
       <c r="B41" s="0">
         <v>1.8673111593981089</v>
@@ -1668,7 +1668,7 @@
     </row>
     <row r="42">
       <c r="A42" s="0">
-        <v>1.016</v>
+        <v>0.54644220943365784</v>
       </c>
       <c r="B42" s="0">
         <v>1.8781528854502467</v>
@@ -1679,7 +1679,7 @@
     </row>
     <row r="43">
       <c r="A43" s="0">
-        <v>1.0413999999999999</v>
+        <v>0.56010326466949922</v>
       </c>
       <c r="B43" s="0">
         <v>1.881763369351126</v>
@@ -1690,7 +1690,7 @@
     </row>
     <row r="44">
       <c r="A44" s="0">
-        <v>1.0668</v>
+        <v>0.57376431990534071</v>
       </c>
       <c r="B44" s="0">
         <v>1.8930050499758488</v>
@@ -1701,7 +1701,7 @@
     </row>
     <row r="45">
       <c r="A45" s="0">
-        <v>1.0922000000000001</v>
+        <v>0.5874253751411822</v>
       </c>
       <c r="B45" s="0">
         <v>1.9034270327155363</v>
@@ -1712,7 +1712,7 @@
     </row>
     <row r="46">
       <c r="A46" s="0">
-        <v>1.1175999999999999</v>
+        <v>0.60108643037702358</v>
       </c>
       <c r="B46" s="0">
         <v>1.9142516596871049</v>
@@ -1723,7 +1723,7 @@
     </row>
     <row r="47">
       <c r="A47" s="0">
-        <v>1.143</v>
+        <v>0.61474748561286507</v>
       </c>
       <c r="B47" s="0">
         <v>1.9173841218405794</v>
@@ -1734,7 +1734,7 @@
     </row>
     <row r="48">
       <c r="A48" s="0">
-        <v>1.1684000000000001</v>
+        <v>0.62840854084870656</v>
       </c>
       <c r="B48" s="0">
         <v>1.9297464739706887</v>
@@ -1745,7 +1745,7 @@
     </row>
     <row r="49">
       <c r="A49" s="0">
-        <v>1.1938</v>
+        <v>0.64206959608454794</v>
       </c>
       <c r="B49" s="0">
         <v>1.9329769335998661</v>
@@ -1756,7 +1756,7 @@
     </row>
     <row r="50">
       <c r="A50" s="0">
-        <v>1.2192000000000001</v>
+        <v>0.65573065132038943</v>
       </c>
       <c r="B50" s="0">
         <v>1.9428356525090114</v>
@@ -1767,7 +1767,7 @@
     </row>
     <row r="51">
       <c r="A51" s="0">
-        <v>1.2445999999999999</v>
+        <v>0.66939170655623081</v>
       </c>
       <c r="B51" s="0">
         <v>1.9517599346046777</v>
@@ -1778,7 +1778,7 @@
     </row>
     <row r="52">
       <c r="A52" s="0">
-        <v>1.27</v>
+        <v>0.6830527617920723</v>
       </c>
       <c r="B52" s="0">
         <v>1.9531201422496405</v>
@@ -1789,7 +1789,7 @@
     </row>
     <row r="53">
       <c r="A53" s="0">
-        <v>1.2954000000000001</v>
+        <v>0.6967138170279138</v>
       </c>
       <c r="B53" s="0">
         <v>1.9654175029724239</v>
@@ -1800,7 +1800,7 @@
     </row>
     <row r="54">
       <c r="A54" s="0">
-        <v>1.3208</v>
+        <v>0.71037487226375517</v>
       </c>
       <c r="B54" s="0">
         <v>1.9759989057674308</v>
@@ -1811,7 +1811,7 @@
     </row>
     <row r="55">
       <c r="A55" s="0">
-        <v>1.3462000000000001</v>
+        <v>0.72403592749959667</v>
       </c>
       <c r="B55" s="0">
         <v>1.9771480086852162</v>
@@ -1822,7 +1822,7 @@
     </row>
     <row r="56">
       <c r="A56" s="0">
-        <v>1.3716000000000002</v>
+        <v>0.73769698273543816</v>
       </c>
       <c r="B56" s="0">
         <v>1.978694287109332</v>
@@ -1833,7 +1833,7 @@
     </row>
     <row r="57">
       <c r="A57" s="0">
-        <v>1.3970000000000002</v>
+        <v>0.75135803797127965</v>
       </c>
       <c r="B57" s="0">
         <v>1.9906113553395421</v>
@@ -1844,7 +1844,7 @@
     </row>
     <row r="58">
       <c r="A58" s="0">
-        <v>1.4224000000000001</v>
+        <v>0.76501909320712103</v>
       </c>
       <c r="B58" s="0">
         <v>1.9975749726654961</v>
@@ -1855,7 +1855,7 @@
     </row>
     <row r="59">
       <c r="A59" s="0">
-        <v>1.4478</v>
+        <v>0.77868014844296241</v>
       </c>
       <c r="B59" s="0">
         <v>2.0033787731399566</v>
@@ -1866,7 +1866,7 @@
     </row>
     <row r="60">
       <c r="A60" s="0">
-        <v>1.4731999999999998</v>
+        <v>0.79234120367880378</v>
       </c>
       <c r="B60" s="0">
         <v>2.0064809784889892</v>
@@ -1877,7 +1877,7 @@
     </row>
     <row r="61">
       <c r="A61" s="0">
-        <v>1.4985999999999999</v>
+        <v>0.80600225891464528</v>
       </c>
       <c r="B61" s="0">
         <v>2.0079171298935381</v>
@@ -1888,7 +1888,7 @@
     </row>
     <row r="62">
       <c r="A62" s="0">
-        <v>1.524</v>
+        <v>0.81966331415048677</v>
       </c>
       <c r="B62" s="0">
         <v>2.0206405743721558</v>
@@ -1899,7 +1899,7 @@
     </row>
     <row r="63">
       <c r="A63" s="0">
-        <v>1.5493999999999999</v>
+        <v>0.83332436938632815</v>
       </c>
       <c r="B63" s="0">
         <v>2.0223844980510957</v>
@@ -1910,7 +1910,7 @@
     </row>
     <row r="64">
       <c r="A64" s="0">
-        <v>1.5748</v>
+        <v>0.84698542462216964</v>
       </c>
       <c r="B64" s="0">
         <v>2.0243615727227504</v>
@@ -1921,7 +1921,7 @@
     </row>
     <row r="65">
       <c r="A65" s="0">
-        <v>1.6002000000000001</v>
+        <v>0.86064647985801113</v>
       </c>
       <c r="B65" s="0">
         <v>2.0300084416355344</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="66">
       <c r="A66" s="0">
-        <v>1.6256000000000002</v>
+        <v>0.87430753509385262</v>
       </c>
       <c r="B66" s="0">
         <v>2.0342028945281339</v>
@@ -1943,7 +1943,7 @@
     </row>
     <row r="67">
       <c r="A67" s="0">
-        <v>1.651</v>
+        <v>0.887968590329694</v>
       </c>
       <c r="B67" s="0">
         <v>2.0371051635690631</v>
@@ -1954,7 +1954,7 @@
     </row>
     <row r="68">
       <c r="A68" s="0">
-        <v>1.6764000000000001</v>
+        <v>0.90162964556553549</v>
       </c>
       <c r="B68" s="0">
         <v>2.0445219475083123</v>
@@ -1965,7 +1965,7 @@
     </row>
     <row r="69">
       <c r="A69" s="0">
-        <v>1.7018000000000002</v>
+        <v>0.91529070080137698</v>
       </c>
       <c r="B69" s="0">
         <v>2.0474547043216558</v>
@@ -1976,7 +1976,7 @@
     </row>
     <row r="70">
       <c r="A70" s="0">
-        <v>1.7272000000000001</v>
+        <v>0.92895175603721836</v>
       </c>
       <c r="B70" s="0">
         <v>2.0535524674209058</v>
@@ -1987,7 +1987,7 @@
     </row>
     <row r="71">
       <c r="A71" s="0">
-        <v>1.7525999999999999</v>
+        <v>0.94261281127305974</v>
       </c>
       <c r="B71" s="0">
         <v>2.0517316649346187</v>
@@ -1998,7 +1998,7 @@
     </row>
     <row r="72">
       <c r="A72" s="0">
-        <v>1.7779999999999998</v>
+        <v>0.95627386650890112</v>
       </c>
       <c r="B72" s="0">
         <v>2.0598859333364405</v>
@@ -2009,7 +2009,7 @@
     </row>
     <row r="73">
       <c r="A73" s="0">
-        <v>1.8033999999999999</v>
+        <v>0.96993492174474261</v>
       </c>
       <c r="B73" s="0">
         <v>2.0578476372508243</v>
@@ -2020,7 +2020,7 @@
     </row>
     <row r="74">
       <c r="A74" s="0">
-        <v>1.8288</v>
+        <v>0.9835959769805841</v>
       </c>
       <c r="B74" s="0">
         <v>2.0650769646030835</v>
@@ -2031,7 +2031,7 @@
     </row>
     <row r="75">
       <c r="A75" s="0">
-        <v>1.8542000000000001</v>
+        <v>0.99725703221642559</v>
       </c>
       <c r="B75" s="0">
         <v>2.0644988294153213</v>
@@ -2042,7 +2042,7 @@
     </row>
     <row r="76">
       <c r="A76" s="0">
-        <v>1.8795999999999999</v>
+        <v>1.010918087452267</v>
       </c>
       <c r="B76" s="0">
         <v>2.0650897870508658</v>
@@ -2053,7 +2053,7 @@
     </row>
     <row r="77">
       <c r="A77" s="0">
-        <v>1.905</v>
+        <v>1.0245791426881086</v>
       </c>
       <c r="B77" s="0">
         <v>2.0647331054455802</v>
@@ -2064,7 +2064,7 @@
     </row>
     <row r="78">
       <c r="A78" s="0">
-        <v>1.9304000000000001</v>
+        <v>1.0382401979239499</v>
       </c>
       <c r="B78" s="0">
         <v>2.069428282002141</v>
@@ -2075,7 +2075,7 @@
     </row>
     <row r="79">
       <c r="A79" s="0">
-        <v>1.9558</v>
+        <v>1.0519012531597913</v>
       </c>
       <c r="B79" s="0">
         <v>2.0660035485054853</v>
@@ -2086,7 +2086,7 @@
     </row>
     <row r="80">
       <c r="A80" s="0">
-        <v>1.9812000000000001</v>
+        <v>1.0655623083956329</v>
       </c>
       <c r="B80" s="0">
         <v>2.0653133565979962</v>
@@ -2097,7 +2097,7 @@
     </row>
     <row r="81">
       <c r="A81" s="0">
-        <v>2.0066000000000002</v>
+        <v>1.0792233636314743</v>
       </c>
       <c r="B81" s="0">
         <v>2.0659131580717265</v>
@@ -2108,7 +2108,7 @@
     </row>
     <row r="82">
       <c r="A82" s="0">
-        <v>2.032</v>
+        <v>1.0928844188673157</v>
       </c>
       <c r="B82" s="0">
         <v>2.0664753490187824</v>
@@ -2119,7 +2119,7 @@
     </row>
     <row r="83">
       <c r="A83" s="0">
-        <v>2.0574000000000003</v>
+        <v>1.1065454741031573</v>
       </c>
       <c r="B83" s="0">
         <v>2.0672910757448002</v>
@@ -2130,7 +2130,7 @@
     </row>
     <row r="84">
       <c r="A84" s="0">
-        <v>2.0827999999999998</v>
+        <v>1.1202065293389984</v>
       </c>
       <c r="B84" s="0">
         <v>2.0692764391864471</v>
@@ -2141,7 +2141,7 @@
     </row>
     <row r="85">
       <c r="A85" s="0">
-        <v>2.1082000000000001</v>
+        <v>1.13386758457484</v>
       </c>
       <c r="B85" s="0">
         <v>2.0684558919353186</v>
@@ -2152,7 +2152,7 @@
     </row>
     <row r="86">
       <c r="A86" s="0">
-        <v>2.1335999999999999</v>
+        <v>1.1475286398106814</v>
       </c>
       <c r="B86" s="0">
         <v>2.0701221395948761</v>
@@ -2163,7 +2163,7 @@
     </row>
     <row r="87">
       <c r="A87" s="0">
-        <v>2.1589999999999998</v>
+        <v>1.1611896950465228</v>
       </c>
       <c r="B87" s="0">
         <v>2.0729183123798931</v>
@@ -2174,7 +2174,7 @@
     </row>
     <row r="88">
       <c r="A88" s="0">
-        <v>2.1844000000000001</v>
+        <v>1.1748507502823644</v>
       </c>
       <c r="B88" s="0">
         <v>2.0704643298225101</v>
@@ -2185,7 +2185,7 @@
     </row>
     <row r="89">
       <c r="A89" s="0">
-        <v>2.2098</v>
+        <v>1.1885118055182058</v>
       </c>
       <c r="B89" s="0">
         <v>2.071367220881247</v>
@@ -2196,7 +2196,7 @@
     </row>
     <row r="90">
       <c r="A90" s="0">
-        <v>2.2351999999999999</v>
+        <v>1.2021728607540472</v>
       </c>
       <c r="B90" s="0">
         <v>2.0765510660637023</v>
@@ -2207,7 +2207,7 @@
     </row>
     <row r="91">
       <c r="A91" s="0">
-        <v>2.2606000000000002</v>
+        <v>1.2158339159898888</v>
       </c>
       <c r="B91" s="0">
         <v>2.0775355260697501</v>
@@ -2218,7 +2218,7 @@
     </row>
     <row r="92">
       <c r="A92" s="0">
-        <v>2.286</v>
+        <v>1.2294949712257301</v>
       </c>
       <c r="B92" s="0">
         <v>2.0776246871578468</v>
@@ -2229,7 +2229,7 @@
     </row>
     <row r="93">
       <c r="A93" s="0">
-        <v>2.3113999999999999</v>
+        <v>1.2431560264615715</v>
       </c>
       <c r="B93" s="0">
         <v>2.0786311785282723</v>
@@ -2240,7 +2240,7 @@
     </row>
     <row r="94">
       <c r="A94" s="0">
-        <v>2.3368000000000002</v>
+        <v>1.2568170816974131</v>
       </c>
       <c r="B94" s="0">
         <v>2.0801140823208719</v>
@@ -2251,7 +2251,7 @@
     </row>
     <row r="95">
       <c r="A95" s="0">
-        <v>2.3622000000000001</v>
+        <v>1.2704781369332545</v>
       </c>
       <c r="B95" s="0">
         <v>2.0811707011919842</v>
@@ -2262,7 +2262,7 @@
     </row>
     <row r="96">
       <c r="A96" s="0">
-        <v>2.3875999999999999</v>
+        <v>1.2841391921690959</v>
       </c>
       <c r="B96" s="0">
         <v>2.0822410738333499</v>
@@ -2273,7 +2273,7 @@
     </row>
     <row r="97">
       <c r="A97" s="0">
-        <v>2.4129999999999998</v>
+        <v>1.2978002474049373</v>
       </c>
       <c r="B97" s="0">
         <v>2.0840956497977299</v>
@@ -2284,7 +2284,7 @@
     </row>
     <row r="98">
       <c r="A98" s="0">
-        <v>2.4384000000000001</v>
+        <v>1.3114613026407789</v>
       </c>
       <c r="B98" s="0">
         <v>2.08491970627193</v>
@@ -2295,7 +2295,7 @@
     </row>
     <row r="99">
       <c r="A99" s="0">
-        <v>2.4638</v>
+        <v>1.3251223578766202</v>
       </c>
       <c r="B99" s="0">
         <v>2.0868185312295591</v>
@@ -2306,7 +2306,7 @@
     </row>
     <row r="100">
       <c r="A100" s="0">
-        <v>2.4891999999999999</v>
+        <v>1.3387834131124616</v>
       </c>
       <c r="B100" s="0">
         <v>2.0875521451159416</v>
@@ -2317,7 +2317,7 @@
     </row>
     <row r="101">
       <c r="A101" s="0">
-        <v>2.5146000000000002</v>
+        <v>1.3524444683483032</v>
       </c>
       <c r="B101" s="0">
         <v>2.0884255393293722</v>
@@ -2328,7 +2328,7 @@
     </row>
     <row r="102">
       <c r="A102" s="0">
-        <v>2.54</v>
+        <v>1.3661055235841446</v>
       </c>
       <c r="B102" s="0">
         <v>2.0892172006827363</v>
@@ -2346,7 +2346,7 @@
   <dimension ref="A1:C102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.5546875" customWidth="true"/>
+    <col min="1" max="1" width="13.5546875" customWidth="true"/>
     <col min="2" max="2" width="12.5546875" customWidth="true"/>
     <col min="3" max="3" width="12.5546875" customWidth="true"/>
   </cols>
@@ -2375,7 +2375,7 @@
     </row>
     <row r="3">
       <c r="A3" s="0">
-        <v>0.025400000000000002</v>
+        <v>0.013661055235841447</v>
       </c>
       <c r="B3" s="0">
         <v>0.55022162793262885</v>
@@ -2386,7 +2386,7 @@
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>0.050800000000000005</v>
+        <v>0.027322110471682894</v>
       </c>
       <c r="B4" s="0">
         <v>0.97345960599107384</v>
@@ -2397,7 +2397,7 @@
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>0.076200000000000004</v>
+        <v>0.04098316570752434</v>
       </c>
       <c r="B5" s="0">
         <v>1.1396262655815841</v>
@@ -2408,7 +2408,7 @@
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>0.10160000000000001</v>
+        <v>0.054644220943365789</v>
       </c>
       <c r="B6" s="0">
         <v>1.2203277269898152</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="7">
       <c r="A7" s="0">
-        <v>0.127</v>
+        <v>0.06830527617920723</v>
       </c>
       <c r="B7" s="0">
         <v>1.271283732146518</v>
@@ -2430,7 +2430,7 @@
     </row>
     <row r="8">
       <c r="A8" s="0">
-        <v>0.15240000000000001</v>
+        <v>0.081966331415048679</v>
       </c>
       <c r="B8" s="0">
         <v>1.3163319118340238</v>
@@ -2441,7 +2441,7 @@
     </row>
     <row r="9">
       <c r="A9" s="0">
-        <v>0.17780000000000001</v>
+        <v>0.095627386650890128</v>
       </c>
       <c r="B9" s="0">
         <v>1.3606932970784156</v>
@@ -2452,7 +2452,7 @@
     </row>
     <row r="10">
       <c r="A10" s="0">
-        <v>0.20320000000000002</v>
+        <v>0.10928844188673158</v>
       </c>
       <c r="B10" s="0">
         <v>1.3916707364970806</v>
@@ -2463,7 +2463,7 @@
     </row>
     <row r="11">
       <c r="A11" s="0">
-        <v>0.2286</v>
+        <v>0.12294949712257301</v>
       </c>
       <c r="B11" s="0">
         <v>1.4265856769385599</v>
@@ -2474,7 +2474,7 @@
     </row>
     <row r="12">
       <c r="A12" s="0">
-        <v>0.254</v>
+        <v>0.13661055235841446</v>
       </c>
       <c r="B12" s="0">
         <v>1.4531586129944851</v>
@@ -2485,7 +2485,7 @@
     </row>
     <row r="13">
       <c r="A13" s="0">
-        <v>0.27939999999999998</v>
+        <v>0.1502716075942559</v>
       </c>
       <c r="B13" s="0">
         <v>1.4804802764378551</v>
@@ -2496,7 +2496,7 @@
     </row>
     <row r="14">
       <c r="A14" s="0">
-        <v>0.30480000000000002</v>
+        <v>0.16393266283009736</v>
       </c>
       <c r="B14" s="0">
         <v>1.5060787325393334</v>
@@ -2507,7 +2507,7 @@
     </row>
     <row r="15">
       <c r="A15" s="0">
-        <v>0.33019999999999999</v>
+        <v>0.17759371806593879</v>
       </c>
       <c r="B15" s="0">
         <v>1.5245716154185167</v>
@@ -2518,7 +2518,7 @@
     </row>
     <row r="16">
       <c r="A16" s="0">
-        <v>0.35560000000000003</v>
+        <v>0.19125477330178026</v>
       </c>
       <c r="B16" s="0">
         <v>1.5469238427387362</v>
@@ -2529,7 +2529,7 @@
     </row>
     <row r="17">
       <c r="A17" s="0">
-        <v>0.38100000000000001</v>
+        <v>0.20491582853762169</v>
       </c>
       <c r="B17" s="0">
         <v>1.5669150781876708</v>
@@ -2540,7 +2540,7 @@
     </row>
     <row r="18">
       <c r="A18" s="0">
-        <v>0.40640000000000004</v>
+        <v>0.21857688377346315</v>
       </c>
       <c r="B18" s="0">
         <v>1.5799461235773449</v>
@@ -2551,7 +2551,7 @@
     </row>
     <row r="19">
       <c r="A19" s="0">
-        <v>0.43180000000000002</v>
+        <v>0.23223793900930459</v>
       </c>
       <c r="B19" s="0">
         <v>1.5965470472081567</v>
@@ -2562,7 +2562,7 @@
     </row>
     <row r="20">
       <c r="A20" s="0">
-        <v>0.4572</v>
+        <v>0.24589899424514602</v>
       </c>
       <c r="B20" s="0">
         <v>1.6154303702695589</v>
@@ -2573,7 +2573,7 @@
     </row>
     <row r="21">
       <c r="A21" s="0">
-        <v>0.48260000000000003</v>
+        <v>0.25956004948098749</v>
       </c>
       <c r="B21" s="0">
         <v>1.6310848057741159</v>
@@ -2584,7 +2584,7 @@
     </row>
     <row r="22">
       <c r="A22" s="0">
-        <v>0.50800000000000001</v>
+        <v>0.27322110471682892</v>
       </c>
       <c r="B22" s="0">
         <v>1.6474247616726454</v>
@@ -2595,7 +2595,7 @@
     </row>
     <row r="23">
       <c r="A23" s="0">
-        <v>0.53339999999999999</v>
+        <v>0.28688215995267036</v>
       </c>
       <c r="B23" s="0">
         <v>1.6601031599459797</v>
@@ -2606,7 +2606,7 @@
     </row>
     <row r="24">
       <c r="A24" s="0">
-        <v>0.55879999999999996</v>
+        <v>0.30054321518851179</v>
       </c>
       <c r="B24" s="0">
         <v>1.6750050794432789</v>
@@ -2617,7 +2617,7 @@
     </row>
     <row r="25">
       <c r="A25" s="0">
-        <v>0.58420000000000005</v>
+        <v>0.31420427042435328</v>
       </c>
       <c r="B25" s="0">
         <v>1.6852363943960962</v>
@@ -2628,7 +2628,7 @@
     </row>
     <row r="26">
       <c r="A26" s="0">
-        <v>0.60960000000000003</v>
+        <v>0.32786532566019472</v>
       </c>
       <c r="B26" s="0">
         <v>1.7013384085791208</v>
@@ -2639,7 +2639,7 @@
     </row>
     <row r="27">
       <c r="A27" s="0">
-        <v>0.63500000000000001</v>
+        <v>0.34152638089603615</v>
       </c>
       <c r="B27" s="0">
         <v>1.709802408757813</v>
@@ -2650,7 +2650,7 @@
     </row>
     <row r="28">
       <c r="A28" s="0">
-        <v>0.66039999999999999</v>
+        <v>0.35518743613187759</v>
       </c>
       <c r="B28" s="0">
         <v>1.7302111635211372</v>
@@ -2661,7 +2661,7 @@
     </row>
     <row r="29">
       <c r="A29" s="0">
-        <v>0.68580000000000008</v>
+        <v>0.36884849136771908</v>
       </c>
       <c r="B29" s="0">
         <v>1.7310128459042906</v>
@@ -2672,7 +2672,7 @@
     </row>
     <row r="30">
       <c r="A30" s="0">
-        <v>0.71120000000000005</v>
+        <v>0.38250954660356051</v>
       </c>
       <c r="B30" s="0">
         <v>1.7523860856693019</v>
@@ -2683,7 +2683,7 @@
     </row>
     <row r="31">
       <c r="A31" s="0">
-        <v>0.73659999999999992</v>
+        <v>0.39617060183940189</v>
       </c>
       <c r="B31" s="0">
         <v>1.7594101346477633</v>
@@ -2694,7 +2694,7 @@
     </row>
     <row r="32">
       <c r="A32" s="0">
-        <v>0.76200000000000001</v>
+        <v>0.40983165707524338</v>
       </c>
       <c r="B32" s="0">
         <v>1.7783119873010516</v>
@@ -2705,7 +2705,7 @@
     </row>
     <row r="33">
       <c r="A33" s="0">
-        <v>0.78739999999999999</v>
+        <v>0.42349271231108482</v>
       </c>
       <c r="B33" s="0">
         <v>1.7856148369744718</v>
@@ -2716,7 +2716,7 @@
     </row>
     <row r="34">
       <c r="A34" s="0">
-        <v>0.81280000000000008</v>
+        <v>0.43715376754692631</v>
       </c>
       <c r="B34" s="0">
         <v>1.7976888293157787</v>
@@ -2727,7 +2727,7 @@
     </row>
     <row r="35">
       <c r="A35" s="0">
-        <v>0.83820000000000006</v>
+        <v>0.45081482278276774</v>
       </c>
       <c r="B35" s="0">
         <v>1.8035087230425404</v>
@@ -2738,7 +2738,7 @@
     </row>
     <row r="36">
       <c r="A36" s="0">
-        <v>0.86360000000000003</v>
+        <v>0.46447587801860918</v>
       </c>
       <c r="B36" s="0">
         <v>1.8142976617370148</v>
@@ -2749,7 +2749,7 @@
     </row>
     <row r="37">
       <c r="A37" s="0">
-        <v>0.8889999999999999</v>
+        <v>0.47813693325445056</v>
       </c>
       <c r="B37" s="0">
         <v>1.8263740159121082</v>
@@ -2760,7 +2760,7 @@
     </row>
     <row r="38">
       <c r="A38" s="0">
-        <v>0.91439999999999999</v>
+        <v>0.49179798849029205</v>
       </c>
       <c r="B38" s="0">
         <v>1.8302218752844301</v>
@@ -2771,7 +2771,7 @@
     </row>
     <row r="39">
       <c r="A39" s="0">
-        <v>0.93979999999999997</v>
+        <v>0.50545904372613348</v>
       </c>
       <c r="B39" s="0">
         <v>1.8440214219002558</v>
@@ -2782,7 +2782,7 @@
     </row>
     <row r="40">
       <c r="A40" s="0">
-        <v>0.96520000000000006</v>
+        <v>0.51912009896197497</v>
       </c>
       <c r="B40" s="0">
         <v>1.8534210137322913</v>
@@ -2793,7 +2793,7 @@
     </row>
     <row r="41">
       <c r="A41" s="0">
-        <v>0.99060000000000004</v>
+        <v>0.53278115419781646</v>
       </c>
       <c r="B41" s="0">
         <v>1.8662127278733327</v>
@@ -2804,7 +2804,7 @@
     </row>
     <row r="42">
       <c r="A42" s="0">
-        <v>1.016</v>
+        <v>0.54644220943365784</v>
       </c>
       <c r="B42" s="0">
         <v>1.8796019338083763</v>
@@ -2815,7 +2815,7 @@
     </row>
     <row r="43">
       <c r="A43" s="0">
-        <v>1.0413999999999999</v>
+        <v>0.56010326466949922</v>
       </c>
       <c r="B43" s="0">
         <v>1.8871007933343615</v>
@@ -2826,7 +2826,7 @@
     </row>
     <row r="44">
       <c r="A44" s="0">
-        <v>1.0668</v>
+        <v>0.57376431990534071</v>
       </c>
       <c r="B44" s="0">
         <v>1.8938611513936354</v>
@@ -2837,7 +2837,7 @@
     </row>
     <row r="45">
       <c r="A45" s="0">
-        <v>1.0922000000000001</v>
+        <v>0.5874253751411822</v>
       </c>
       <c r="B45" s="0">
         <v>1.9034126828989011</v>
@@ -2848,7 +2848,7 @@
     </row>
     <row r="46">
       <c r="A46" s="0">
-        <v>1.1175999999999999</v>
+        <v>0.60108643037702358</v>
       </c>
       <c r="B46" s="0">
         <v>1.9102777588568298</v>
@@ -2859,7 +2859,7 @@
     </row>
     <row r="47">
       <c r="A47" s="0">
-        <v>1.143</v>
+        <v>0.61474748561286507</v>
       </c>
       <c r="B47" s="0">
         <v>1.9227301810457671</v>
@@ -2870,7 +2870,7 @@
     </row>
     <row r="48">
       <c r="A48" s="0">
-        <v>1.1684000000000001</v>
+        <v>0.62840854084870656</v>
       </c>
       <c r="B48" s="0">
         <v>1.9168388139072805</v>
@@ -2881,7 +2881,7 @@
     </row>
     <row r="49">
       <c r="A49" s="0">
-        <v>1.1938</v>
+        <v>0.64206959608454794</v>
       </c>
       <c r="B49" s="0">
         <v>1.927327009949376</v>
@@ -2892,7 +2892,7 @@
     </row>
     <row r="50">
       <c r="A50" s="0">
-        <v>1.2192000000000001</v>
+        <v>0.65573065132038943</v>
       </c>
       <c r="B50" s="0">
         <v>1.9363025147809552</v>
@@ -2903,7 +2903,7 @@
     </row>
     <row r="51">
       <c r="A51" s="0">
-        <v>1.2445999999999999</v>
+        <v>0.66939170655623081</v>
       </c>
       <c r="B51" s="0">
         <v>1.9451553607177954</v>
@@ -2914,7 +2914,7 @@
     </row>
     <row r="52">
       <c r="A52" s="0">
-        <v>1.27</v>
+        <v>0.6830527617920723</v>
       </c>
       <c r="B52" s="0">
         <v>1.9500108066957691</v>
@@ -2925,7 +2925,7 @@
     </row>
     <row r="53">
       <c r="A53" s="0">
-        <v>1.2954000000000001</v>
+        <v>0.6967138170279138</v>
       </c>
       <c r="B53" s="0">
         <v>1.9578644926326771</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="54">
       <c r="A54" s="0">
-        <v>1.3208</v>
+        <v>0.71037487226375517</v>
       </c>
       <c r="B54" s="0">
         <v>1.9729131363973691</v>
@@ -2947,7 +2947,7 @@
     </row>
     <row r="55">
       <c r="A55" s="0">
-        <v>1.3462000000000001</v>
+        <v>0.72403592749959667</v>
       </c>
       <c r="B55" s="0">
         <v>1.9749017631929549</v>
@@ -2958,7 +2958,7 @@
     </row>
     <row r="56">
       <c r="A56" s="0">
-        <v>1.3716000000000002</v>
+        <v>0.73769698273543816</v>
       </c>
       <c r="B56" s="0">
         <v>1.9858528637561035</v>
@@ -2969,7 +2969,7 @@
     </row>
     <row r="57">
       <c r="A57" s="0">
-        <v>1.3970000000000002</v>
+        <v>0.75135803797127965</v>
       </c>
       <c r="B57" s="0">
         <v>1.9913987847635966</v>
@@ -2980,7 +2980,7 @@
     </row>
     <row r="58">
       <c r="A58" s="0">
-        <v>1.4224000000000001</v>
+        <v>0.76501909320712103</v>
       </c>
       <c r="B58" s="0">
         <v>1.9893710871277019</v>
@@ -2991,7 +2991,7 @@
     </row>
     <row r="59">
       <c r="A59" s="0">
-        <v>1.4478</v>
+        <v>0.77868014844296241</v>
       </c>
       <c r="B59" s="0">
         <v>1.9997050412674184</v>
@@ -3002,7 +3002,7 @@
     </row>
     <row r="60">
       <c r="A60" s="0">
-        <v>1.4731999999999998</v>
+        <v>0.79234120367880378</v>
       </c>
       <c r="B60" s="0">
         <v>2.003141360415615</v>
@@ -3013,7 +3013,7 @@
     </row>
     <row r="61">
       <c r="A61" s="0">
-        <v>1.4985999999999999</v>
+        <v>0.80600225891464528</v>
       </c>
       <c r="B61" s="0">
         <v>2.0136767260782289</v>
@@ -3024,7 +3024,7 @@
     </row>
     <row r="62">
       <c r="A62" s="0">
-        <v>1.524</v>
+        <v>0.81966331415048677</v>
       </c>
       <c r="B62" s="0">
         <v>2.0195381269848847</v>
@@ -3035,7 +3035,7 @@
     </row>
     <row r="63">
       <c r="A63" s="0">
-        <v>1.5493999999999999</v>
+        <v>0.83332436938632815</v>
       </c>
       <c r="B63" s="0">
         <v>2.021898314193554</v>
@@ -3046,7 +3046,7 @@
     </row>
     <row r="64">
       <c r="A64" s="0">
-        <v>1.5748</v>
+        <v>0.84698542462216964</v>
       </c>
       <c r="B64" s="0">
         <v>2.0256200650527045</v>
@@ -3057,7 +3057,7 @@
     </row>
     <row r="65">
       <c r="A65" s="0">
-        <v>1.6002000000000001</v>
+        <v>0.86064647985801113</v>
       </c>
       <c r="B65" s="0">
         <v>2.0305655810895065</v>
@@ -3068,7 +3068,7 @@
     </row>
     <row r="66">
       <c r="A66" s="0">
-        <v>1.6256000000000002</v>
+        <v>0.87430753509385262</v>
       </c>
       <c r="B66" s="0">
         <v>2.0337027818117144</v>
@@ -3079,7 +3079,7 @@
     </row>
     <row r="67">
       <c r="A67" s="0">
-        <v>1.651</v>
+        <v>0.887968590329694</v>
       </c>
       <c r="B67" s="0">
         <v>2.0342729895826017</v>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="68">
       <c r="A68" s="0">
-        <v>1.6764000000000001</v>
+        <v>0.90162964556553549</v>
       </c>
       <c r="B68" s="0">
         <v>2.042405207993597</v>
@@ -3101,7 +3101,7 @@
     </row>
     <row r="69">
       <c r="A69" s="0">
-        <v>1.7018000000000002</v>
+        <v>0.91529070080137698</v>
       </c>
       <c r="B69" s="0">
         <v>2.0454120980756429</v>
@@ -3112,7 +3112,7 @@
     </row>
     <row r="70">
       <c r="A70" s="0">
-        <v>1.7272000000000001</v>
+        <v>0.92895175603721836</v>
       </c>
       <c r="B70" s="0">
         <v>2.0502461981425788</v>
@@ -3123,7 +3123,7 @@
     </row>
     <row r="71">
       <c r="A71" s="0">
-        <v>1.7525999999999999</v>
+        <v>0.94261281127305974</v>
       </c>
       <c r="B71" s="0">
         <v>2.0543554536555186</v>
@@ -3134,7 +3134,7 @@
     </row>
     <row r="72">
       <c r="A72" s="0">
-        <v>1.7779999999999998</v>
+        <v>0.95627386650890112</v>
       </c>
       <c r="B72" s="0">
         <v>2.0531331487915017</v>
@@ -3145,7 +3145,7 @@
     </row>
     <row r="73">
       <c r="A73" s="0">
-        <v>1.8033999999999999</v>
+        <v>0.96993492174474261</v>
       </c>
       <c r="B73" s="0">
         <v>2.0615400849797427</v>
@@ -3156,7 +3156,7 @@
     </row>
     <row r="74">
       <c r="A74" s="0">
-        <v>1.8288</v>
+        <v>0.9835959769805841</v>
       </c>
       <c r="B74" s="0">
         <v>2.0637579363125038</v>
@@ -3167,7 +3167,7 @@
     </row>
     <row r="75">
       <c r="A75" s="0">
-        <v>1.8542000000000001</v>
+        <v>0.99725703221642559</v>
       </c>
       <c r="B75" s="0">
         <v>2.065171080326726</v>
@@ -3178,7 +3178,7 @@
     </row>
     <row r="76">
       <c r="A76" s="0">
-        <v>1.8795999999999999</v>
+        <v>1.010918087452267</v>
       </c>
       <c r="B76" s="0">
         <v>2.0624133525333175</v>
@@ -3189,7 +3189,7 @@
     </row>
     <row r="77">
       <c r="A77" s="0">
-        <v>1.905</v>
+        <v>1.0245791426881086</v>
       </c>
       <c r="B77" s="0">
         <v>2.0625081611608787</v>
@@ -3200,7 +3200,7 @@
     </row>
     <row r="78">
       <c r="A78" s="0">
-        <v>1.9304000000000001</v>
+        <v>1.0382401979239499</v>
       </c>
       <c r="B78" s="0">
         <v>2.0652875179873575</v>
@@ -3211,7 +3211,7 @@
     </row>
     <row r="79">
       <c r="A79" s="0">
-        <v>1.9558</v>
+        <v>1.0519012531597913</v>
       </c>
       <c r="B79" s="0">
         <v>2.0674265943402204</v>
@@ -3222,7 +3222,7 @@
     </row>
     <row r="80">
       <c r="A80" s="0">
-        <v>1.9812000000000001</v>
+        <v>1.0655623083956329</v>
       </c>
       <c r="B80" s="0">
         <v>2.0670009948720707</v>
@@ -3233,7 +3233,7 @@
     </row>
     <row r="81">
       <c r="A81" s="0">
-        <v>2.0066000000000002</v>
+        <v>1.0792233636314743</v>
       </c>
       <c r="B81" s="0">
         <v>2.0665671699638559</v>
@@ -3244,7 +3244,7 @@
     </row>
     <row r="82">
       <c r="A82" s="0">
-        <v>2.032</v>
+        <v>1.0928844188673157</v>
       </c>
       <c r="B82" s="0">
         <v>2.0635460082962624</v>
@@ -3255,7 +3255,7 @@
     </row>
     <row r="83">
       <c r="A83" s="0">
-        <v>2.0574000000000003</v>
+        <v>1.1065454741031573</v>
       </c>
       <c r="B83" s="0">
         <v>2.0637208100735145</v>
@@ -3266,7 +3266,7 @@
     </row>
     <row r="84">
       <c r="A84" s="0">
-        <v>2.0827999999999998</v>
+        <v>1.1202065293389984</v>
       </c>
       <c r="B84" s="0">
         <v>2.0669297151754202</v>
@@ -3277,7 +3277,7 @@
     </row>
     <row r="85">
       <c r="A85" s="0">
-        <v>2.1082000000000001</v>
+        <v>1.13386758457484</v>
       </c>
       <c r="B85" s="0">
         <v>2.0682162216853066</v>
@@ -3288,7 +3288,7 @@
     </row>
     <row r="86">
       <c r="A86" s="0">
-        <v>2.1335999999999999</v>
+        <v>1.1475286398106814</v>
       </c>
       <c r="B86" s="0">
         <v>2.0690265318398326</v>
@@ -3299,7 +3299,7 @@
     </row>
     <row r="87">
       <c r="A87" s="0">
-        <v>2.1589999999999998</v>
+        <v>1.1611896950465228</v>
       </c>
       <c r="B87" s="0">
         <v>2.0695056488224632</v>
@@ -3310,7 +3310,7 @@
     </row>
     <row r="88">
       <c r="A88" s="0">
-        <v>2.1844000000000001</v>
+        <v>1.1748507502823644</v>
       </c>
       <c r="B88" s="0">
         <v>2.0730494425838288</v>
@@ -3321,7 +3321,7 @@
     </row>
     <row r="89">
       <c r="A89" s="0">
-        <v>2.2098</v>
+        <v>1.1885118055182058</v>
       </c>
       <c r="B89" s="0">
         <v>2.0723771618701052</v>
@@ -3332,7 +3332,7 @@
     </row>
     <row r="90">
       <c r="A90" s="0">
-        <v>2.2351999999999999</v>
+        <v>1.2021728607540472</v>
       </c>
       <c r="B90" s="0">
         <v>2.0710651445750892</v>
@@ -3343,7 +3343,7 @@
     </row>
     <row r="91">
       <c r="A91" s="0">
-        <v>2.2606000000000002</v>
+        <v>1.2158339159898888</v>
       </c>
       <c r="B91" s="0">
         <v>2.0752023919162217</v>
@@ -3354,7 +3354,7 @@
     </row>
     <row r="92">
       <c r="A92" s="0">
-        <v>2.286</v>
+        <v>1.2294949712257301</v>
       </c>
       <c r="B92" s="0">
         <v>2.0778049986388383</v>
@@ -3365,7 +3365,7 @@
     </row>
     <row r="93">
       <c r="A93" s="0">
-        <v>2.3113999999999999</v>
+        <v>1.2431560264615715</v>
       </c>
       <c r="B93" s="0">
         <v>2.0797469177498513</v>
@@ -3376,7 +3376,7 @@
     </row>
     <row r="94">
       <c r="A94" s="0">
-        <v>2.3368000000000002</v>
+        <v>1.2568170816974131</v>
       </c>
       <c r="B94" s="0">
         <v>2.0786398212008041</v>
@@ -3387,7 +3387,7 @@
     </row>
     <row r="95">
       <c r="A95" s="0">
-        <v>2.3622000000000001</v>
+        <v>1.2704781369332545</v>
       </c>
       <c r="B95" s="0">
         <v>2.0794829213568939</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="96">
       <c r="A96" s="0">
-        <v>2.3875999999999999</v>
+        <v>1.2841391921690959</v>
       </c>
       <c r="B96" s="0">
         <v>2.0823110496785411</v>
@@ -3409,7 +3409,7 @@
     </row>
     <row r="97">
       <c r="A97" s="0">
-        <v>2.4129999999999998</v>
+        <v>1.2978002474049373</v>
       </c>
       <c r="B97" s="0">
         <v>2.0813744149440301</v>
@@ -3420,7 +3420,7 @@
     </row>
     <row r="98">
       <c r="A98" s="0">
-        <v>2.4384000000000001</v>
+        <v>1.3114613026407789</v>
       </c>
       <c r="B98" s="0">
         <v>2.082433775628497</v>
@@ -3431,7 +3431,7 @@
     </row>
     <row r="99">
       <c r="A99" s="0">
-        <v>2.4638</v>
+        <v>1.3251223578766202</v>
       </c>
       <c r="B99" s="0">
         <v>2.0855004566131905</v>
@@ -3442,7 +3442,7 @@
     </row>
     <row r="100">
       <c r="A100" s="0">
-        <v>2.4891999999999999</v>
+        <v>1.3387834131124616</v>
       </c>
       <c r="B100" s="0">
         <v>2.0846662077458666</v>
@@ -3453,7 +3453,7 @@
     </row>
     <row r="101">
       <c r="A101" s="0">
-        <v>2.5146000000000002</v>
+        <v>1.3524444683483032</v>
       </c>
       <c r="B101" s="0">
         <v>2.0866882354905574</v>
@@ -3464,7 +3464,7 @@
     </row>
     <row r="102">
       <c r="A102" s="0">
-        <v>2.54</v>
+        <v>1.3661055235841446</v>
       </c>
       <c r="B102" s="0">
         <v>2.0880638434839023</v>
@@ -3511,7 +3511,7 @@
     </row>
     <row r="3">
       <c r="A3" s="0">
-        <v>0.0079628428093645488</v>
+        <v>0.0042827100572067709</v>
       </c>
       <c r="B3" s="0">
         <v>0.98544772386602164</v>
@@ -3522,7 +3522,7 @@
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>0.015925685618729098</v>
+        <v>0.0085654201144135418</v>
       </c>
       <c r="B4" s="0">
         <v>1.0754073156353341</v>
@@ -3533,7 +3533,7 @@
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>0.023888528428093646</v>
+        <v>0.012848130171620313</v>
       </c>
       <c r="B5" s="0">
         <v>1.1405801993434901</v>
@@ -3544,7 +3544,7 @@
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>0.031851371237458195</v>
+        <v>0.017130840228827084</v>
       </c>
       <c r="B6" s="0">
         <v>1.1756363078411047</v>
@@ -3555,7 +3555,7 @@
     </row>
     <row r="7">
       <c r="A7" s="0">
-        <v>0.039814214046822748</v>
+        <v>0.021413550286033856</v>
       </c>
       <c r="B7" s="0">
         <v>1.1882246666541769</v>
@@ -3566,7 +3566,7 @@
     </row>
     <row r="8">
       <c r="A8" s="0">
-        <v>0.047777056856187293</v>
+        <v>0.025696260343240625</v>
       </c>
       <c r="B8" s="0">
         <v>1.1989258770929192</v>
@@ -3577,7 +3577,7 @@
     </row>
     <row r="9">
       <c r="A9" s="0">
-        <v>0.055739899665551838</v>
+        <v>0.029978970400447395</v>
       </c>
       <c r="B9" s="0">
         <v>1.2161768923540177</v>
@@ -3588,7 +3588,7 @@
     </row>
     <row r="10">
       <c r="A10" s="0">
-        <v>0.063702742474916391</v>
+        <v>0.034261680457654167</v>
       </c>
       <c r="B10" s="0">
         <v>1.2372276289176045</v>
@@ -3599,7 +3599,7 @@
     </row>
     <row r="11">
       <c r="A11" s="0">
-        <v>0.071665585284280936</v>
+        <v>0.038544390514860936</v>
       </c>
       <c r="B11" s="0">
         <v>1.2596903805621178</v>
@@ -3610,7 +3610,7 @@
     </row>
     <row r="12">
       <c r="A12" s="0">
-        <v>0.079628428093645495</v>
+        <v>0.042827100572067713</v>
       </c>
       <c r="B12" s="0">
         <v>1.2811818809192341</v>
@@ -3621,7 +3621,7 @@
     </row>
     <row r="13">
       <c r="A13" s="0">
-        <v>0.087591270903010027</v>
+        <v>0.047109810629274475</v>
       </c>
       <c r="B13" s="0">
         <v>1.3027791017068797</v>
@@ -3632,7 +3632,7 @@
     </row>
     <row r="14">
       <c r="A14" s="0">
-        <v>0.095554113712374586</v>
+        <v>0.051392520686481251</v>
       </c>
       <c r="B14" s="0">
         <v>1.3212218633896358</v>
@@ -3643,7 +3643,7 @@
     </row>
     <row r="15">
       <c r="A15" s="0">
-        <v>0.10351695652173913</v>
+        <v>0.05567523074368802</v>
       </c>
       <c r="B15" s="0">
         <v>1.3335465841302176</v>
@@ -3654,7 +3654,7 @@
     </row>
     <row r="16">
       <c r="A16" s="0">
-        <v>0.11147979933110368</v>
+        <v>0.059957940800894789</v>
       </c>
       <c r="B16" s="0">
         <v>1.34330917042303</v>
@@ -3665,7 +3665,7 @@
     </row>
     <row r="17">
       <c r="A17" s="0">
-        <v>0.11944264214046822</v>
+        <v>0.064240650858101558</v>
       </c>
       <c r="B17" s="0">
         <v>1.3528885770730126</v>
@@ -3676,7 +3676,7 @@
     </row>
     <row r="18">
       <c r="A18" s="0">
-        <v>0.12740548494983278</v>
+        <v>0.068523360915308335</v>
       </c>
       <c r="B18" s="0">
         <v>1.3646748555964048</v>
@@ -3687,7 +3687,7 @@
     </row>
     <row r="19">
       <c r="A19" s="0">
-        <v>0.13536832775919733</v>
+        <v>0.072806070972515097</v>
       </c>
       <c r="B19" s="0">
         <v>1.3822774607054451</v>
@@ -3698,7 +3698,7 @@
     </row>
     <row r="20">
       <c r="A20" s="0">
-        <v>0.14333117056856187</v>
+        <v>0.077088781029721873</v>
       </c>
       <c r="B20" s="0">
         <v>1.3975555116290648</v>
@@ -3709,7 +3709,7 @@
     </row>
     <row r="21">
       <c r="A21" s="0">
-        <v>0.15129401337792642</v>
+        <v>0.081371491086928635</v>
       </c>
       <c r="B21" s="0">
         <v>1.4062997747264605</v>
@@ -3720,7 +3720,7 @@
     </row>
     <row r="22">
       <c r="A22" s="0">
-        <v>0.15925685618729099</v>
+        <v>0.085654201144135425</v>
       </c>
       <c r="B22" s="0">
         <v>1.4130616913692964</v>
@@ -3731,7 +3731,7 @@
     </row>
     <row r="23">
       <c r="A23" s="0">
-        <v>0.16721969899665551</v>
+        <v>0.089936911201342173</v>
       </c>
       <c r="B23" s="0">
         <v>1.4190493379174101</v>
@@ -3742,7 +3742,7 @@
     </row>
     <row r="24">
       <c r="A24" s="0">
-        <v>0.17518254180602005</v>
+        <v>0.09421962125854895</v>
       </c>
       <c r="B24" s="0">
         <v>1.4254640386677579</v>
@@ -3753,7 +3753,7 @@
     </row>
     <row r="25">
       <c r="A25" s="0">
-        <v>0.1831453846153846</v>
+        <v>0.098502331315755712</v>
       </c>
       <c r="B25" s="0">
         <v>1.4319802569440785</v>
@@ -3764,7 +3764,7 @@
     </row>
     <row r="26">
       <c r="A26" s="0">
-        <v>0.19110822742474917</v>
+        <v>0.1027850413729625</v>
       </c>
       <c r="B26" s="0">
         <v>1.4382717422584212</v>
@@ -3775,7 +3775,7 @@
     </row>
     <row r="27">
       <c r="A27" s="0">
-        <v>0.19907107023411372</v>
+        <v>0.10706775143016926</v>
       </c>
       <c r="B27" s="0">
         <v>1.4450207081516659</v>
@@ -3786,7 +3786,7 @@
     </row>
     <row r="28">
       <c r="A28" s="0">
-        <v>0.20703391304347826</v>
+        <v>0.11135046148737604</v>
       </c>
       <c r="B28" s="0">
         <v>1.4529318416461383</v>
@@ -3797,7 +3797,7 @@
     </row>
     <row r="29">
       <c r="A29" s="0">
-        <v>0.21499675585284281</v>
+        <v>0.1156331715445828</v>
       </c>
       <c r="B29" s="0">
         <v>1.4643058380160126</v>
@@ -3808,7 +3808,7 @@
     </row>
     <row r="30">
       <c r="A30" s="0">
-        <v>0.22295959866220735</v>
+        <v>0.11991588160178958</v>
       </c>
       <c r="B30" s="0">
         <v>1.474049151810628</v>
@@ -3819,7 +3819,7 @@
     </row>
     <row r="31">
       <c r="A31" s="0">
-        <v>0.23092244147157193</v>
+        <v>0.12419859165899635</v>
       </c>
       <c r="B31" s="0">
         <v>1.4791447358590264</v>
@@ -3830,7 +3830,7 @@
     </row>
     <row r="32">
       <c r="A32" s="0">
-        <v>0.23888528428093644</v>
+        <v>0.12848130171620312</v>
       </c>
       <c r="B32" s="0">
         <v>1.4827199143060805</v>
@@ -3841,7 +3841,7 @@
     </row>
     <row r="33">
       <c r="A33" s="0">
-        <v>0.24684812709030102</v>
+        <v>0.13276401177340991</v>
       </c>
       <c r="B33" s="0">
         <v>1.4867149836946894</v>
@@ -3852,7 +3852,7 @@
     </row>
     <row r="34">
       <c r="A34" s="0">
-        <v>0.25481096989966556</v>
+        <v>0.13704672183061667</v>
       </c>
       <c r="B34" s="0">
         <v>1.4931734883575623</v>
@@ -3863,7 +3863,7 @@
     </row>
     <row r="35">
       <c r="A35" s="0">
-        <v>0.26277381270903005</v>
+        <v>0.1413294318878234</v>
       </c>
       <c r="B35" s="0">
         <v>1.509833339997235</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="36">
       <c r="A36" s="0">
-        <v>0.27073665551839465</v>
+        <v>0.14561214194503019</v>
       </c>
       <c r="B36" s="0">
         <v>1.5248789902532451</v>
@@ -3885,7 +3885,7 @@
     </row>
     <row r="37">
       <c r="A37" s="0">
-        <v>0.2786994983277592</v>
+        <v>0.14989485200223698</v>
       </c>
       <c r="B37" s="0">
         <v>1.5329642254314313</v>
@@ -3896,7 +3896,7 @@
     </row>
     <row r="38">
       <c r="A38" s="0">
-        <v>0.28666234113712374</v>
+        <v>0.15417756205944375</v>
       </c>
       <c r="B38" s="0">
         <v>1.5395805702127974</v>
@@ -3907,7 +3907,7 @@
     </row>
     <row r="39">
       <c r="A39" s="0">
-        <v>0.29462518394648829</v>
+        <v>0.15846027211665051</v>
       </c>
       <c r="B39" s="0">
         <v>1.5451029243134944</v>
@@ -3918,7 +3918,7 @@
     </row>
     <row r="40">
       <c r="A40" s="0">
-        <v>0.30258802675585283</v>
+        <v>0.16274298217385727</v>
       </c>
       <c r="B40" s="0">
         <v>1.5499061874496738</v>
@@ -3929,7 +3929,7 @@
     </row>
     <row r="41">
       <c r="A41" s="0">
-        <v>0.31055086956521738</v>
+        <v>0.16702569223106406</v>
       </c>
       <c r="B41" s="0">
         <v>1.5543652593374868</v>
@@ -3940,7 +3940,7 @@
     </row>
     <row r="42">
       <c r="A42" s="0">
-        <v>0.31851371237458198</v>
+        <v>0.17130840228827085</v>
       </c>
       <c r="B42" s="0">
         <v>1.5588473185845522</v>
@@ -3951,7 +3951,7 @@
     </row>
     <row r="43">
       <c r="A43" s="0">
-        <v>0.32647655518394647</v>
+        <v>0.17559111234547758</v>
       </c>
       <c r="B43" s="0">
         <v>1.5631373236617419</v>
@@ -3962,7 +3962,7 @@
     </row>
     <row r="44">
       <c r="A44" s="0">
-        <v>0.33443939799331102</v>
+        <v>0.17987382240268435</v>
       </c>
       <c r="B44" s="0">
         <v>1.567052100027293</v>
@@ -3973,7 +3973,7 @@
     </row>
     <row r="45">
       <c r="A45" s="0">
-        <v>0.34240224080267556</v>
+        <v>0.18415653245989114</v>
       </c>
       <c r="B45" s="0">
         <v>1.570699917277663</v>
@@ -3984,7 +3984,7 @@
     </row>
     <row r="46">
       <c r="A46" s="0">
-        <v>0.35036508361204011</v>
+        <v>0.1884392425170979</v>
       </c>
       <c r="B46" s="0">
         <v>1.574189045009309</v>
@@ -3995,7 +3995,7 @@
     </row>
     <row r="47">
       <c r="A47" s="0">
-        <v>0.35832792642140471</v>
+        <v>0.19272195257430469</v>
       </c>
       <c r="B47" s="0">
         <v>1.5776277528186882</v>
@@ -4006,7 +4006,7 @@
     </row>
     <row r="48">
       <c r="A48" s="0">
-        <v>0.3662907692307692</v>
+        <v>0.19700466263151142</v>
       </c>
       <c r="B48" s="0">
         <v>1.5811243103022576</v>
@@ -4017,7 +4017,7 @@
     </row>
     <row r="49">
       <c r="A49" s="0">
-        <v>0.3742536120401338</v>
+        <v>0.20128737268871824</v>
       </c>
       <c r="B49" s="0">
         <v>1.5847869870564746</v>
@@ -4028,7 +4028,7 @@
     </row>
     <row r="50">
       <c r="A50" s="0">
-        <v>0.38221645484949834</v>
+        <v>0.205570082745925</v>
       </c>
       <c r="B50" s="0">
         <v>1.5887237996240766</v>
@@ -4039,7 +4039,7 @@
     </row>
     <row r="51">
       <c r="A51" s="0">
-        <v>0.39017929765886283</v>
+        <v>0.20985279280313174</v>
       </c>
       <c r="B51" s="0">
         <v>1.592978308038639</v>
@@ -4050,7 +4050,7 @@
     </row>
     <row r="52">
       <c r="A52" s="0">
-        <v>0.39814214046822743</v>
+        <v>0.21413550286033853</v>
       </c>
       <c r="B52" s="0">
         <v>1.5974464971735054</v>
@@ -4061,7 +4061,7 @@
     </row>
     <row r="53">
       <c r="A53" s="0">
-        <v>0.40610498327759192</v>
+        <v>0.21841821291754529</v>
       </c>
       <c r="B53" s="0">
         <v>1.6020039513511992</v>
@@ -4072,7 +4072,7 @@
     </row>
     <row r="54">
       <c r="A54" s="0">
-        <v>0.41406782608695653</v>
+        <v>0.22270092297475208</v>
       </c>
       <c r="B54" s="0">
         <v>1.6065262548942443</v>
@@ -4083,7 +4083,7 @@
     </row>
     <row r="55">
       <c r="A55" s="0">
-        <v>0.42203066889632107</v>
+        <v>0.22698363303195884</v>
       </c>
       <c r="B55" s="0">
         <v>1.6108889921251641</v>
@@ -4094,7 +4094,7 @@
     </row>
     <row r="56">
       <c r="A56" s="0">
-        <v>0.42999351170568562</v>
+        <v>0.2312663430891656</v>
       </c>
       <c r="B56" s="0">
         <v>1.614971500463384</v>
@@ -4105,7 +4105,7 @@
     </row>
     <row r="57">
       <c r="A57" s="0">
-        <v>0.43795635451505016</v>
+        <v>0.23554905314637239</v>
       </c>
       <c r="B57" s="0">
         <v>1.6188339488628898</v>
@@ -4116,7 +4116,7 @@
     </row>
     <row r="58">
       <c r="A58" s="0">
-        <v>0.44591919732441471</v>
+        <v>0.23983176320357916</v>
       </c>
       <c r="B58" s="0">
         <v>1.6225621330925475</v>
@@ -4127,7 +4127,7 @@
     </row>
     <row r="59">
       <c r="A59" s="0">
-        <v>0.4538820401337792</v>
+        <v>0.24411447326078589</v>
       </c>
       <c r="B59" s="0">
         <v>1.6261806898596503</v>
@@ -4138,7 +4138,7 @@
     </row>
     <row r="60">
       <c r="A60" s="0">
-        <v>0.46184488294314385</v>
+        <v>0.24839718331799271</v>
       </c>
       <c r="B60" s="0">
         <v>1.6297142558714908</v>
@@ -4149,7 +4149,7 @@
     </row>
     <row r="61">
       <c r="A61" s="0">
-        <v>0.46980772575250834</v>
+        <v>0.25267989337519947</v>
       </c>
       <c r="B61" s="0">
         <v>1.6331874678353617</v>
@@ -4160,7 +4160,7 @@
     </row>
     <row r="62">
       <c r="A62" s="0">
-        <v>0.47777056856187289</v>
+        <v>0.25696260343240623</v>
       </c>
       <c r="B62" s="0">
         <v>1.636627982686762</v>
@@ -4171,7 +4171,7 @@
     </row>
     <row r="63">
       <c r="A63" s="0">
-        <v>0.48573341137123743</v>
+        <v>0.261245313489613</v>
       </c>
       <c r="B63" s="0">
         <v>1.6401300810629214</v>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="64">
       <c r="A64" s="0">
-        <v>0.49369625418060203</v>
+        <v>0.26552802354681981</v>
       </c>
       <c r="B64" s="0">
         <v>1.6436542335389974</v>
@@ -4193,7 +4193,7 @@
     </row>
     <row r="65">
       <c r="A65" s="0">
-        <v>0.50165909698996658</v>
+        <v>0.26981073360402658</v>
       </c>
       <c r="B65" s="0">
         <v>1.6470989757883827</v>
@@ -4204,7 +4204,7 @@
     </row>
     <row r="66">
       <c r="A66" s="0">
-        <v>0.50962193979933113</v>
+        <v>0.27409344366123334</v>
       </c>
       <c r="B66" s="0">
         <v>1.6503628434844706</v>
@@ -4215,7 +4215,7 @@
     </row>
     <row r="67">
       <c r="A67" s="0">
-        <v>0.51758478260869567</v>
+        <v>0.2783761537184401</v>
       </c>
       <c r="B67" s="0">
         <v>1.6533443723006538</v>
@@ -4226,7 +4226,7 @@
     </row>
     <row r="68">
       <c r="A68" s="0">
-        <v>0.5255476254180601</v>
+        <v>0.28265886377564681</v>
       </c>
       <c r="B68" s="0">
         <v>1.655942381895193</v>
@@ -4237,7 +4237,7 @@
     </row>
     <row r="69">
       <c r="A69" s="0">
-        <v>0.53351046822742476</v>
+        <v>0.28694157383285362</v>
       </c>
       <c r="B69" s="0">
         <v>1.6581065539638267</v>
@@ -4248,7 +4248,7 @@
     </row>
     <row r="70">
       <c r="A70" s="0">
-        <v>0.54147331103678931</v>
+        <v>0.29122428389006039</v>
       </c>
       <c r="B70" s="0">
         <v>1.6598957259701834</v>
@@ -4259,7 +4259,7 @@
     </row>
     <row r="71">
       <c r="A71" s="0">
-        <v>0.54943615384615385</v>
+        <v>0.2955069939472672</v>
       </c>
       <c r="B71" s="0">
         <v>1.6613828537146031</v>
@@ -4270,7 +4270,7 @@
     </row>
     <row r="72">
       <c r="A72" s="0">
-        <v>0.5573989966555184</v>
+        <v>0.29978970400447397</v>
       </c>
       <c r="B72" s="0">
         <v>1.6626408929974259</v>
@@ -4281,7 +4281,7 @@
     </row>
     <row r="73">
       <c r="A73" s="0">
-        <v>0.56536183946488294</v>
+        <v>0.30407241406168073</v>
       </c>
       <c r="B73" s="0">
         <v>1.6637427996189922</v>
@@ -4292,7 +4292,7 @@
     </row>
     <row r="74">
       <c r="A74" s="0">
-        <v>0.57332468227424749</v>
+        <v>0.30835512411888749</v>
       </c>
       <c r="B74" s="0">
         <v>1.6647615293796418</v>
@@ -4303,7 +4303,7 @@
     </row>
     <row r="75">
       <c r="A75" s="0">
-        <v>0.58128752508361203</v>
+        <v>0.31263783417609425</v>
       </c>
       <c r="B75" s="0">
         <v>1.6657700380797149</v>
@@ -4314,7 +4314,7 @@
     </row>
     <row r="76">
       <c r="A76" s="0">
-        <v>0.58925036789297658</v>
+        <v>0.31692054423330102</v>
       </c>
       <c r="B76" s="0">
         <v>1.6668412815195519</v>
@@ -4325,7 +4325,7 @@
     </row>
     <row r="77">
       <c r="A77" s="0">
-        <v>0.59721321070234112</v>
+        <v>0.32120325429050778</v>
       </c>
       <c r="B77" s="0">
         <v>1.6680482154994924</v>
@@ -4336,7 +4336,7 @@
     </row>
     <row r="78">
       <c r="A78" s="0">
-        <v>0.60517605351170567</v>
+        <v>0.32548596434771454</v>
       </c>
       <c r="B78" s="0">
         <v>1.6694637958198768</v>
@@ -4347,7 +4347,7 @@
     </row>
     <row r="79">
       <c r="A79" s="0">
-        <v>0.61313889632107021</v>
+        <v>0.32976867440492136</v>
       </c>
       <c r="B79" s="0">
         <v>1.6711609782810453</v>
@@ -4358,7 +4358,7 @@
     </row>
     <row r="80">
       <c r="A80" s="0">
-        <v>0.62110173913043476</v>
+        <v>0.33405138446212812</v>
       </c>
       <c r="B80" s="0">
         <v>1.6732127186833377</v>
@@ -4369,7 +4369,7 @@
     </row>
     <row r="81">
       <c r="A81" s="0">
-        <v>0.62906458193979931</v>
+        <v>0.33833409451933488</v>
       </c>
       <c r="B81" s="0">
         <v>1.6756919728270945</v>
@@ -4380,7 +4380,7 @@
     </row>
     <row r="82">
       <c r="A82" s="0">
-        <v>0.63702742474916396</v>
+        <v>0.3426168045765417</v>
       </c>
       <c r="B82" s="0">
         <v>1.6786716965126554</v>
@@ -4391,7 +4391,7 @@
     </row>
     <row r="83">
       <c r="A83" s="0">
-        <v>0.6449902675585284</v>
+        <v>0.34689951463374841</v>
       </c>
       <c r="B83" s="0">
         <v>1.6822248455403608</v>
@@ -4402,7 +4402,7 @@
     </row>
     <row r="84">
       <c r="A84" s="0">
-        <v>0.65295311036789294</v>
+        <v>0.35118222469095517</v>
       </c>
       <c r="B84" s="0">
         <v>1.687953584151594</v>
@@ -4413,7 +4413,7 @@
     </row>
     <row r="85">
       <c r="A85" s="0">
-        <v>0.66091595317725749</v>
+        <v>0.35546493474816193</v>
       </c>
       <c r="B85" s="0">
         <v>1.712304110600176</v>
@@ -4424,7 +4424,7 @@
     </row>
     <row r="86">
       <c r="A86" s="0">
-        <v>0.66887879598662203</v>
+        <v>0.35974764480536869</v>
       </c>
       <c r="B86" s="0">
         <v>1.7265298847914845</v>
@@ -4435,7 +4435,7 @@
     </row>
     <row r="87">
       <c r="A87" s="0">
-        <v>0.67684163879598669</v>
+        <v>0.36403035486257557</v>
       </c>
       <c r="B87" s="0">
         <v>1.7313470261748305</v>
@@ -4446,7 +4446,7 @@
     </row>
     <row r="88">
       <c r="A88" s="0">
-        <v>0.68480448160535112</v>
+        <v>0.36831306491978227</v>
       </c>
       <c r="B88" s="0">
         <v>1.7353945125776127</v>
@@ -4457,7 +4457,7 @@
     </row>
     <row r="89">
       <c r="A89" s="0">
-        <v>0.69276732441471567</v>
+        <v>0.37259577497698904</v>
       </c>
       <c r="B89" s="0">
         <v>1.7387730393685694</v>
@@ -4468,7 +4468,7 @@
     </row>
     <row r="90">
       <c r="A90" s="0">
-        <v>0.70073016722408021</v>
+        <v>0.3768784850341958</v>
       </c>
       <c r="B90" s="0">
         <v>1.7415833019164395</v>
@@ -4479,7 +4479,7 @@
     </row>
     <row r="91">
       <c r="A91" s="0">
-        <v>0.70869301003344476</v>
+        <v>0.38116119509140256</v>
       </c>
       <c r="B91" s="0">
         <v>1.7439259955899609</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="92">
       <c r="A92" s="0">
-        <v>0.71665585284280942</v>
+        <v>0.38544390514860938</v>
       </c>
       <c r="B92" s="0">
         <v>1.7459018157578723</v>
@@ -4501,7 +4501,7 @@
     </row>
     <row r="93">
       <c r="A93" s="0">
-        <v>0.72461869565217396</v>
+        <v>0.38972661520581614</v>
       </c>
       <c r="B93" s="0">
         <v>1.7476114577889119</v>
@@ -4512,7 +4512,7 @@
     </row>
     <row r="94">
       <c r="A94" s="0">
-        <v>0.7325815384615384</v>
+        <v>0.39400932526302285</v>
       </c>
       <c r="B94" s="0">
         <v>1.7491556170518183</v>
@@ -4523,7 +4523,7 @@
     </row>
     <row r="95">
       <c r="A95" s="0">
-        <v>0.74054438127090294</v>
+        <v>0.39829203532022961</v>
       </c>
       <c r="B95" s="0">
         <v>1.7506349889153299</v>
@@ -4534,7 +4534,7 @@
     </row>
     <row r="96">
       <c r="A96" s="0">
-        <v>0.7485072240802676</v>
+        <v>0.40257474537743648</v>
       </c>
       <c r="B96" s="0">
         <v>1.7521502687481851</v>
@@ -4545,7 +4545,7 @@
     </row>
     <row r="97">
       <c r="A97" s="0">
-        <v>0.75647006688963214</v>
+        <v>0.40685745543464324</v>
       </c>
       <c r="B97" s="0">
         <v>1.7538021519191223</v>
@@ -4556,7 +4556,7 @@
     </row>
     <row r="98">
       <c r="A98" s="0">
-        <v>0.76443290969899669</v>
+        <v>0.41114016549185001</v>
       </c>
       <c r="B98" s="0">
         <v>1.7556913337968798</v>
@@ -4567,7 +4567,7 @@
     </row>
     <row r="99">
       <c r="A99" s="0">
-        <v>0.77239575250836112</v>
+        <v>0.41542287554905671</v>
       </c>
       <c r="B99" s="0">
         <v>1.7579185097501961</v>
@@ -4578,7 +4578,7 @@
     </row>
     <row r="100">
       <c r="A100" s="0">
-        <v>0.78035859531772567</v>
+        <v>0.41970558560626348</v>
       </c>
       <c r="B100" s="0">
         <v>1.7605655683309591</v>
@@ -4589,7 +4589,7 @@
     </row>
     <row r="101">
       <c r="A101" s="0">
-        <v>0.78832143812709032</v>
+        <v>0.42398829566347029</v>
       </c>
       <c r="B101" s="0">
         <v>1.763440965390344</v>
@@ -4600,7 +4600,7 @@
     </row>
     <row r="102">
       <c r="A102" s="0">
-        <v>0.79628428093645487</v>
+        <v>0.42827100572067706</v>
       </c>
       <c r="B102" s="0">
         <v>1.7664454494121249</v>
@@ -4611,7 +4611,7 @@
     </row>
     <row r="103">
       <c r="A103" s="0">
-        <v>0.80424712374581941</v>
+        <v>0.43255371577788387</v>
       </c>
       <c r="B103" s="0">
         <v>1.7695501069065942</v>
@@ -4622,7 +4622,7 @@
     </row>
     <row r="104">
       <c r="A104" s="0">
-        <v>0.81220996655518385</v>
+        <v>0.43683642583509058</v>
       </c>
       <c r="B104" s="0">
         <v>1.7727260243840448</v>
@@ -4633,7 +4633,7 @@
     </row>
     <row r="105">
       <c r="A105" s="0">
-        <v>0.82017280936454851</v>
+        <v>0.4411191358922974</v>
       </c>
       <c r="B105" s="0">
         <v>1.7759442883547691</v>
@@ -4644,7 +4644,7 @@
     </row>
     <row r="106">
       <c r="A106" s="0">
-        <v>0.82813565217391305</v>
+        <v>0.44540184594950416</v>
       </c>
       <c r="B106" s="0">
         <v>1.7791759853290601</v>
@@ -4655,7 +4655,7 @@
     </row>
     <row r="107">
       <c r="A107" s="0">
-        <v>0.8360984949832776</v>
+        <v>0.44968455600671092</v>
       </c>
       <c r="B107" s="0">
         <v>1.7823922018172103</v>
@@ -4666,7 +4666,7 @@
     </row>
     <row r="108">
       <c r="A108" s="0">
-        <v>0.84406133779264214</v>
+        <v>0.45396726606391768</v>
       </c>
       <c r="B108" s="0">
         <v>1.7855640243295121</v>
@@ -4677,7 +4677,7 @@
     </row>
     <row r="109">
       <c r="A109" s="0">
-        <v>0.85202418060200669</v>
+        <v>0.45824997612112445</v>
       </c>
       <c r="B109" s="0">
         <v>1.7886625393762585</v>
@@ -4688,7 +4688,7 @@
     </row>
     <row r="110">
       <c r="A110" s="0">
-        <v>0.85998702341137123</v>
+        <v>0.46253268617833121</v>
       </c>
       <c r="B110" s="0">
         <v>1.7916588334677419</v>
@@ -4699,7 +4699,7 @@
     </row>
     <row r="111">
       <c r="A111" s="0">
-        <v>0.86794986622073567</v>
+        <v>0.46681539623553792</v>
       </c>
       <c r="B111" s="0">
         <v>1.7945239931142551</v>
@@ -4710,7 +4710,7 @@
     </row>
     <row r="112">
       <c r="A112" s="0">
-        <v>0.87591270903010032</v>
+        <v>0.47109810629274479</v>
       </c>
       <c r="B112" s="0">
         <v>1.7972360437806132</v>
@@ -4721,7 +4721,7 @@
     </row>
     <row r="113">
       <c r="A113" s="0">
-        <v>0.88387555183946498</v>
+        <v>0.47538081634995161</v>
       </c>
       <c r="B113" s="0">
         <v>1.7998533110661301</v>
@@ -4732,7 +4732,7 @@
     </row>
     <row r="114">
       <c r="A114" s="0">
-        <v>0.89183839464882941</v>
+        <v>0.47966352640715831</v>
       </c>
       <c r="B114" s="0">
         <v>1.8024017013484004</v>
@@ -4743,7 +4743,7 @@
     </row>
     <row r="115">
       <c r="A115" s="0">
-        <v>0.89980123745819396</v>
+        <v>0.48394623646436508</v>
       </c>
       <c r="B115" s="0">
         <v>1.8048887016228576</v>
@@ -4754,7 +4754,7 @@
     </row>
     <row r="116">
       <c r="A116" s="0">
-        <v>0.90776408026755839</v>
+        <v>0.48822894652157178</v>
       </c>
       <c r="B116" s="0">
         <v>1.8073217988849353</v>
@@ -4765,7 +4765,7 @@
     </row>
     <row r="117">
       <c r="A117" s="0">
-        <v>0.91572692307692305</v>
+        <v>0.4925116565787786</v>
       </c>
       <c r="B117" s="0">
         <v>1.8097084801300671</v>
@@ -4776,7 +4776,7 @@
     </row>
     <row r="118">
       <c r="A118" s="0">
-        <v>0.92368976588628771</v>
+        <v>0.49679436663598542</v>
       </c>
       <c r="B118" s="0">
         <v>1.8120562323536868</v>
@@ -4787,7 +4787,7 @@
     </row>
     <row r="119">
       <c r="A119" s="0">
-        <v>0.93165260869565214</v>
+        <v>0.50107707669319212</v>
       </c>
       <c r="B119" s="0">
         <v>1.814372542551228</v>
@@ -4798,7 +4798,7 @@
     </row>
     <row r="120">
       <c r="A120" s="0">
-        <v>0.93961545150501669</v>
+        <v>0.50535978675039894</v>
       </c>
       <c r="B120" s="0">
         <v>1.8166648977181241</v>
@@ -4809,7 +4809,7 @@
     </row>
     <row r="121">
       <c r="A121" s="0">
-        <v>0.94757829431438134</v>
+        <v>0.50964249680760576</v>
       </c>
       <c r="B121" s="0">
         <v>1.8189407848498091</v>
@@ -4820,7 +4820,7 @@
     </row>
     <row r="122">
       <c r="A122" s="0">
-        <v>0.95554113712374578</v>
+        <v>0.51392520686481247</v>
       </c>
       <c r="B122" s="0">
         <v>1.8212076909417161</v>
@@ -4831,7 +4831,7 @@
     </row>
     <row r="123">
       <c r="A123" s="0">
-        <v>0.96350397993311043</v>
+        <v>0.51820791692201928</v>
       </c>
       <c r="B123" s="0">
         <v>1.8234731029892792</v>
@@ -4842,7 +4842,7 @@
     </row>
     <row r="124">
       <c r="A124" s="0">
-        <v>0.97146682274247487</v>
+        <v>0.52249062697922599</v>
       </c>
       <c r="B124" s="0">
         <v>1.8257439720725368</v>
@@ -4853,7 +4853,7 @@
     </row>
     <row r="125">
       <c r="A125" s="0">
-        <v>0.97942966555183941</v>
+        <v>0.52677333703643281</v>
       </c>
       <c r="B125" s="0">
         <v>1.8280189886946592</v>
@@ -4864,7 +4864,7 @@
     </row>
     <row r="126">
       <c r="A126" s="0">
-        <v>0.98739250836120407</v>
+        <v>0.53105604709363963</v>
       </c>
       <c r="B126" s="0">
         <v>1.8302931112465</v>
@@ -4875,7 +4875,7 @@
     </row>
     <row r="127">
       <c r="A127" s="0">
-        <v>0.9953553511705685</v>
+        <v>0.53533875715084633</v>
       </c>
       <c r="B127" s="0">
         <v>1.8325617304425572</v>
@@ -4886,7 +4886,7 @@
     </row>
     <row r="128">
       <c r="A128" s="0">
-        <v>1.0033181939799332</v>
+        <v>0.53962146720805315</v>
       </c>
       <c r="B128" s="0">
         <v>1.8348202369973285</v>
@@ -4897,7 +4897,7 @@
     </row>
     <row r="129">
       <c r="A129" s="0">
-        <v>1.0112810367892975</v>
+        <v>0.54390417726525975</v>
       </c>
       <c r="B129" s="0">
         <v>1.8370640216253116</v>
@@ -4908,7 +4908,7 @@
     </row>
     <row r="130">
       <c r="A130" s="0">
-        <v>1.0192438795986623</v>
+        <v>0.54818688732246668</v>
       </c>
       <c r="B130" s="0">
         <v>1.8392884750410048</v>
@@ -4919,7 +4919,7 @@
     </row>
     <row r="131">
       <c r="A131" s="0">
-        <v>1.0272067224080268</v>
+        <v>0.55246959737967338</v>
       </c>
       <c r="B131" s="0">
         <v>1.8414889879589054</v>
@@ -4930,7 +4930,7 @@
     </row>
     <row r="132">
       <c r="A132" s="0">
-        <v>1.0351695652173913</v>
+        <v>0.5567523074368802</v>
       </c>
       <c r="B132" s="0">
         <v>1.8436609510935114</v>
@@ -4941,7 +4941,7 @@
     </row>
     <row r="133">
       <c r="A133" s="0">
-        <v>1.0431324080267559</v>
+        <v>0.56103501749408702</v>
       </c>
       <c r="B133" s="0">
         <v>1.8457997551593206</v>
@@ -4952,7 +4952,7 @@
     </row>
     <row r="134">
       <c r="A134" s="0">
-        <v>1.0510952508361202</v>
+        <v>0.56531772755129361</v>
       </c>
       <c r="B134" s="0">
         <v>1.8479007908708309</v>
@@ -4963,7 +4963,7 @@
     </row>
     <row r="135">
       <c r="A135" s="0">
-        <v>1.059058093645485</v>
+        <v>0.56960043760850054</v>
       </c>
       <c r="B135" s="0">
         <v>1.8499594489425402</v>
@@ -4974,7 +4974,7 @@
     </row>
     <row r="136">
       <c r="A136" s="0">
-        <v>1.0670209364548495</v>
+        <v>0.57388314766570725</v>
       </c>
       <c r="B136" s="0">
         <v>1.8519711200889462</v>
@@ -4985,7 +4985,7 @@
     </row>
     <row r="137">
       <c r="A137" s="0">
-        <v>1.0749837792642141</v>
+        <v>0.57816585772291407</v>
       </c>
       <c r="B137" s="0">
         <v>1.8539311950245467</v>
@@ -4996,7 +4996,7 @@
     </row>
     <row r="138">
       <c r="A138" s="0">
-        <v>1.0829466220735786</v>
+        <v>0.58244856778012077</v>
       </c>
       <c r="B138" s="0">
         <v>1.8558295795140607</v>
@@ -5007,7 +5007,7 @@
     </row>
     <row r="139">
       <c r="A139" s="0">
-        <v>1.0909094648829429</v>
+        <v>0.58673127783732748</v>
       </c>
       <c r="B139" s="0">
         <v>1.8576271996324851</v>
@@ -5018,7 +5018,7 @@
     </row>
     <row r="140">
       <c r="A140" s="0">
-        <v>1.0988723076923077</v>
+        <v>0.59101398789453441</v>
       </c>
       <c r="B140" s="0">
         <v>1.8593263560315336</v>
@@ -5029,7 +5029,7 @@
     </row>
     <row r="141">
       <c r="A141" s="0">
-        <v>1.1068351505016722</v>
+        <v>0.59529669795174112</v>
       </c>
       <c r="B141" s="0">
         <v>1.8609381340865101</v>
@@ -5040,7 +5040,7 @@
     </row>
     <row r="142">
       <c r="A142" s="0">
-        <v>1.1147979933110368</v>
+        <v>0.59957940800894793</v>
       </c>
       <c r="B142" s="0">
         <v>1.8624736191727191</v>
@@ -5051,7 +5051,7 @@
     </row>
     <row r="143">
       <c r="A143" s="0">
-        <v>1.1227608361204013</v>
+        <v>0.60386211806615464</v>
       </c>
       <c r="B143" s="0">
         <v>1.8639438966654647</v>
@@ -5062,7 +5062,7 @@
     </row>
     <row r="144">
       <c r="A144" s="0">
-        <v>1.1307236789297659</v>
+        <v>0.60814482812336146</v>
       </c>
       <c r="B144" s="0">
         <v>1.8653600519400513</v>
@@ -5073,7 +5073,7 @@
     </row>
     <row r="145">
       <c r="A145" s="0">
-        <v>1.1386865217391304</v>
+        <v>0.61242753818056817</v>
       </c>
       <c r="B145" s="0">
         <v>1.8667331703717829</v>
@@ -5084,7 +5084,7 @@
     </row>
     <row r="146">
       <c r="A146" s="0">
-        <v>1.146649364548495</v>
+        <v>0.61671024823777498</v>
       </c>
       <c r="B146" s="0">
         <v>1.8680743373359638</v>
@@ -5095,7 +5095,7 @@
     </row>
     <row r="147">
       <c r="A147" s="0">
-        <v>1.1546122073578595</v>
+        <v>0.62099295829498169</v>
       </c>
       <c r="B147" s="0">
         <v>1.8693946382078985</v>
@@ -5106,7 +5106,7 @@
     </row>
     <row r="148">
       <c r="A148" s="0">
-        <v>1.1625750501672241</v>
+        <v>0.62527566835218851</v>
       </c>
       <c r="B148" s="0">
         <v>1.8707051583628911</v>
@@ -5117,7 +5117,7 @@
     </row>
     <row r="149">
       <c r="A149" s="0">
-        <v>1.1705378929765886</v>
+        <v>0.62955837840939533</v>
       </c>
       <c r="B149" s="0">
         <v>1.8720169831762457</v>
@@ -5128,7 +5128,7 @@
     </row>
     <row r="150">
       <c r="A150" s="0">
-        <v>1.1785007357859532</v>
+        <v>0.63384108846660203</v>
       </c>
       <c r="B150" s="0">
         <v>1.8733411980232664</v>
@@ -5139,7 +5139,7 @@
     </row>
     <row r="151">
       <c r="A151" s="0">
-        <v>1.1864635785953177</v>
+        <v>0.63812379852380885</v>
       </c>
       <c r="B151" s="0">
         <v>1.8746888882792578</v>
@@ -5150,7 +5150,7 @@
     </row>
     <row r="152">
       <c r="A152" s="0">
-        <v>1.1944264214046822</v>
+        <v>0.64240650858101556</v>
       </c>
       <c r="B152" s="0">
         <v>1.8760711393195242</v>
@@ -5161,7 +5161,7 @@
     </row>
     <row r="153">
       <c r="A153" s="0">
-        <v>1.2023892642140468</v>
+        <v>0.64668921863822237</v>
       </c>
       <c r="B153" s="0">
         <v>1.8774990365193693</v>
@@ -5172,7 +5172,7 @@
     </row>
     <row r="154">
       <c r="A154" s="0">
-        <v>1.2103521070234113</v>
+        <v>0.65097192869542908</v>
       </c>
       <c r="B154" s="0">
         <v>1.8789836652540979</v>
@@ -5183,7 +5183,7 @@
     </row>
     <row r="155">
       <c r="A155" s="0">
-        <v>1.2183149498327759</v>
+        <v>0.6552546387526359</v>
       </c>
       <c r="B155" s="0">
         <v>1.880536110899014</v>
@@ -5194,7 +5194,7 @@
     </row>
     <row r="156">
       <c r="A156" s="0">
-        <v>1.2262777926421404</v>
+        <v>0.65953734880984272</v>
       </c>
       <c r="B156" s="0">
         <v>1.8821674588294217</v>
@@ -5205,7 +5205,7 @@
     </row>
     <row r="157">
       <c r="A157" s="0">
-        <v>1.234240635451505</v>
+        <v>0.66382005886704942</v>
       </c>
       <c r="B157" s="0">
         <v>1.8838887944206255</v>
@@ -5216,7 +5216,7 @@
     </row>
     <row r="158">
       <c r="A158" s="0">
-        <v>1.2422034782608695</v>
+        <v>0.66810276892425624</v>
       </c>
       <c r="B158" s="0">
         <v>1.8857112030479295</v>
@@ -5227,7 +5227,7 @@
     </row>
     <row r="159">
       <c r="A159" s="0">
-        <v>1.2501663210702341</v>
+        <v>0.67238547898146295</v>
       </c>
       <c r="B159" s="0">
         <v>1.887645770086638</v>
@@ -5238,7 +5238,7 @@
     </row>
     <row r="160">
       <c r="A160" s="0">
-        <v>1.2581291638795986</v>
+        <v>0.67666818903866977</v>
       </c>
       <c r="B160" s="0">
         <v>1.8897035809120553</v>
@@ -5249,7 +5249,7 @@
     </row>
     <row r="161">
       <c r="A161" s="0">
-        <v>1.2660920066889632</v>
+        <v>0.68095089909587647</v>
       </c>
       <c r="B161" s="0">
         <v>1.8918957208994853</v>
@@ -5260,7 +5260,7 @@
     </row>
     <row r="162">
       <c r="A162" s="0">
-        <v>1.2740548494983279</v>
+        <v>0.6852336091530834</v>
       </c>
       <c r="B162" s="0">
         <v>1.8942332754242326</v>
@@ -5271,7 +5271,7 @@
     </row>
     <row r="163">
       <c r="A163" s="0">
-        <v>1.2820176923076922</v>
+        <v>0.68951631921029</v>
       </c>
       <c r="B163" s="0">
         <v>1.8967273298616014</v>
@@ -5282,7 +5282,7 @@
     </row>
     <row r="164">
       <c r="A164" s="0">
-        <v>1.2899805351170568</v>
+        <v>0.69379902926749681</v>
       </c>
       <c r="B164" s="0">
         <v>1.8995307734704847</v>
@@ -5293,7 +5293,7 @@
     </row>
     <row r="165">
       <c r="A165" s="0">
-        <v>1.2979433779264213</v>
+        <v>0.69808173932470363</v>
       </c>
       <c r="B165" s="0">
         <v>1.9032997260576563</v>
@@ -5304,7 +5304,7 @@
     </row>
     <row r="166">
       <c r="A166" s="0">
-        <v>1.3059062207357859</v>
+        <v>0.70236444938191034</v>
       </c>
       <c r="B166" s="0">
         <v>1.9079464169084688</v>
@@ -5315,7 +5315,7 @@
     </row>
     <row r="167">
       <c r="A167" s="0">
-        <v>1.3138690635451507</v>
+        <v>0.70664715943911727</v>
       </c>
       <c r="B167" s="0">
         <v>1.9132728669138197</v>
@@ -5326,7 +5326,7 @@
     </row>
     <row r="168">
       <c r="A168" s="0">
-        <v>1.321831906354515</v>
+        <v>0.71092986949632386</v>
       </c>
       <c r="B168" s="0">
         <v>1.9190810969646066</v>
@@ -5337,7 +5337,7 @@
     </row>
     <row r="169">
       <c r="A169" s="0">
-        <v>1.3297947491638795</v>
+        <v>0.71521257955353068</v>
       </c>
       <c r="B169" s="0">
         <v>1.9251731279517277</v>
@@ -5348,7 +5348,7 @@
     </row>
     <row r="170">
       <c r="A170" s="0">
-        <v>1.3377575919732441</v>
+        <v>0.71949528961073739</v>
       </c>
       <c r="B170" s="0">
         <v>1.9313509807660802</v>
@@ -5359,7 +5359,7 @@
     </row>
     <row r="171">
       <c r="A171" s="0">
-        <v>1.3457204347826086</v>
+        <v>0.72377799966794421</v>
       </c>
       <c r="B171" s="0">
         <v>1.9374166762985625</v>
@@ -5370,7 +5370,7 @@
     </row>
     <row r="172">
       <c r="A172" s="0">
-        <v>1.3536832775919734</v>
+        <v>0.72806070972515113</v>
       </c>
       <c r="B172" s="0">
         <v>1.9431722354400718</v>
@@ -5381,7 +5381,7 @@
     </row>
     <row r="173">
       <c r="A173" s="0">
-        <v>1.3616461204013377</v>
+        <v>0.73234341978235773</v>
       </c>
       <c r="B173" s="0">
         <v>1.9484196790815058</v>
@@ -5392,7 +5392,7 @@
     </row>
     <row r="174">
       <c r="A174" s="0">
-        <v>1.3696089632107022</v>
+        <v>0.73662612983956455</v>
       </c>
       <c r="B174" s="0">
         <v>1.9529610281137626</v>
@@ -5403,7 +5403,7 @@
     </row>
     <row r="175">
       <c r="A175" s="0">
-        <v>1.3775718060200668</v>
+        <v>0.74090883989677125</v>
       </c>
       <c r="B175" s="0">
         <v>1.9565983034277397</v>
@@ -5414,7 +5414,7 @@
     </row>
     <row r="176">
       <c r="A176" s="0">
-        <v>1.3855346488294313</v>
+        <v>0.74519154995397807</v>
       </c>
       <c r="B176" s="0">
         <v>1.9593190151278543</v>
@@ -5425,7 +5425,7 @@
     </row>
     <row r="177">
       <c r="A177" s="0">
-        <v>1.3934974916387961</v>
+        <v>0.74947426001118489</v>
       </c>
       <c r="B177" s="0">
         <v>1.9618309522736916</v>
@@ -5436,7 +5436,7 @@
     </row>
     <row r="178">
       <c r="A178" s="0">
-        <v>1.4014603344481604</v>
+        <v>0.7537569700683916</v>
       </c>
       <c r="B178" s="0">
         <v>1.9642305406402962</v>
@@ -5447,7 +5447,7 @@
     </row>
     <row r="179">
       <c r="A179" s="0">
-        <v>1.409423177257525</v>
+        <v>0.7580396801255983</v>
       </c>
       <c r="B179" s="0">
         <v>1.9665225320198834</v>
@@ -5458,7 +5458,7 @@
     </row>
     <row r="180">
       <c r="A180" s="0">
-        <v>1.4173860200668895</v>
+        <v>0.76232239018280512</v>
       </c>
       <c r="B180" s="0">
         <v>1.968711678204667</v>
@@ -5469,7 +5469,7 @@
     </row>
     <row r="181">
       <c r="A181" s="0">
-        <v>1.4253488628762541</v>
+        <v>0.76660510024001194</v>
       </c>
       <c r="B181" s="0">
         <v>1.9708027309868619</v>
@@ -5480,7 +5480,7 @@
     </row>
     <row r="182">
       <c r="A182" s="0">
-        <v>1.4333117056856188</v>
+        <v>0.77088781029721876</v>
       </c>
       <c r="B182" s="0">
         <v>1.9728004421586824</v>
@@ -5491,7 +5491,7 @@
     </row>
     <row r="183">
       <c r="A183" s="0">
-        <v>1.4412745484949832</v>
+        <v>0.77517052035442546</v>
       </c>
       <c r="B183" s="0">
         <v>1.9747095635123431</v>
@@ -5502,7 +5502,7 @@
     </row>
     <row r="184">
       <c r="A184" s="0">
-        <v>1.4492373913043479</v>
+        <v>0.77945323041163228</v>
       </c>
       <c r="B184" s="0">
         <v>1.9765348468400585</v>
@@ -5513,7 +5513,7 @@
     </row>
     <row r="185">
       <c r="A185" s="0">
-        <v>1.4572002341137125</v>
+        <v>0.7837359404688391</v>
       </c>
       <c r="B185" s="0">
         <v>1.978281043934043</v>
@@ -5524,7 +5524,7 @@
     </row>
     <row r="186">
       <c r="A186" s="0">
-        <v>1.4651630769230768</v>
+        <v>0.78801865052604569</v>
       </c>
       <c r="B186" s="0">
         <v>1.9799529065865114</v>
@@ -5535,7 +5535,7 @@
     </row>
     <row r="187">
       <c r="A187" s="0">
-        <v>1.4731259197324416</v>
+        <v>0.79230136058325262</v>
       </c>
       <c r="B187" s="0">
         <v>1.9815551865896781</v>
@@ -5546,7 +5546,7 @@
     </row>
     <row r="188">
       <c r="A188" s="0">
-        <v>1.4810887625418059</v>
+        <v>0.79658407064045922</v>
       </c>
       <c r="B188" s="0">
         <v>1.9830926357357574</v>
@@ -5557,7 +5557,7 @@
     </row>
     <row r="189">
       <c r="A189" s="0">
-        <v>1.4890516053511706</v>
+        <v>0.80086678069766615</v>
       </c>
       <c r="B189" s="0">
         <v>1.984570005816964</v>
@@ -5568,7 +5568,7 @@
     </row>
     <row r="190">
       <c r="A190" s="0">
-        <v>1.4970144481605352</v>
+        <v>0.80514949075487297</v>
       </c>
       <c r="B190" s="0">
         <v>1.9859920486255125</v>
@@ -5579,7 +5579,7 @@
     </row>
     <row r="191">
       <c r="A191" s="0">
-        <v>1.5049772909698995</v>
+        <v>0.80943220081207956</v>
       </c>
       <c r="B191" s="0">
         <v>1.9873635159536172</v>
@@ -5590,7 +5590,7 @@
     </row>
     <row r="192">
       <c r="A192" s="0">
-        <v>1.5129401337792643</v>
+        <v>0.81371491086928649</v>
       </c>
       <c r="B192" s="0">
         <v>1.9886891595934926</v>
@@ -5601,7 +5601,7 @@
     </row>
     <row r="193">
       <c r="A193" s="0">
-        <v>1.5209029765886286</v>
+        <v>0.81799762092649309</v>
       </c>
       <c r="B193" s="0">
         <v>1.9899737313373533</v>
@@ -5612,7 +5612,7 @@
     </row>
     <row r="194">
       <c r="A194" s="0">
-        <v>1.5288658193979934</v>
+        <v>0.82228033098370001</v>
       </c>
       <c r="B194" s="0">
         <v>1.991221982977414</v>
@@ -5623,7 +5623,7 @@
     </row>
     <row r="195">
       <c r="A195" s="0">
-        <v>1.5368286622073579</v>
+        <v>0.82656304104090672</v>
       </c>
       <c r="B195" s="0">
         <v>1.9924386663058888</v>
@@ -5634,7 +5634,7 @@
     </row>
     <row r="196">
       <c r="A196" s="0">
-        <v>1.5447915050167222</v>
+        <v>0.83084575109811343</v>
       </c>
       <c r="B196" s="0">
         <v>1.9936285331149926</v>
@@ -5645,7 +5645,7 @@
     </row>
     <row r="197">
       <c r="A197" s="0">
-        <v>1.552754347826087</v>
+        <v>0.83512846115532036</v>
       </c>
       <c r="B197" s="0">
         <v>1.9947963351969398</v>
@@ -5656,7 +5656,7 @@
     </row>
     <row r="198">
       <c r="A198" s="0">
-        <v>1.5607171906354513</v>
+        <v>0.83941117121252695</v>
       </c>
       <c r="B198" s="0">
         <v>1.9959468243439447</v>
@@ -5667,7 +5667,7 @@
     </row>
     <row r="199">
       <c r="A199" s="0">
-        <v>1.5686800334448161</v>
+        <v>0.84369388126973388</v>
       </c>
       <c r="B199" s="0">
         <v>1.997084752348222</v>
@@ -5678,7 +5678,7 @@
     </row>
     <row r="200">
       <c r="A200" s="0">
-        <v>1.5766428762541806</v>
+        <v>0.84797659132694059</v>
       </c>
       <c r="B200" s="0">
         <v>1.9982164070860269</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="201">
       <c r="A201" s="0">
-        <v>1.584605719063545</v>
+        <v>0.85225930138414729</v>
       </c>
       <c r="B201" s="0">
         <v>1.9993481975814835</v>
@@ -5700,7 +5700,7 @@
     </row>
     <row r="202">
       <c r="A202" s="0">
-        <v>1.5925685618729097</v>
+        <v>0.85654201144135411</v>
       </c>
       <c r="B202" s="0">
         <v>2.0004778984477838</v>
@@ -5711,7 +5711,7 @@
     </row>
     <row r="203">
       <c r="A203" s="0">
-        <v>1.6005314046822741</v>
+        <v>0.86082472149856082</v>
       </c>
       <c r="B203" s="0">
         <v>2.0016027300789405</v>
@@ -5722,7 +5722,7 @@
     </row>
     <row r="204">
       <c r="A204" s="0">
-        <v>1.6084942474916388</v>
+        <v>0.86510743155576775</v>
       </c>
       <c r="B204" s="0">
         <v>2.0027199128689661</v>
@@ -5733,7 +5733,7 @@
     </row>
     <row r="205">
       <c r="A205" s="0">
-        <v>1.6164570903010034</v>
+        <v>0.86939014161297445</v>
       </c>
       <c r="B205" s="0">
         <v>2.0038266672118725</v>
@@ -5744,7 +5744,7 @@
     </row>
     <row r="206">
       <c r="A206" s="0">
-        <v>1.6244199331103677</v>
+        <v>0.87367285167018116</v>
       </c>
       <c r="B206" s="0">
         <v>2.004920213501673</v>
@@ -5755,7 +5755,7 @@
     </row>
     <row r="207">
       <c r="A207" s="0">
-        <v>1.6323827759197325</v>
+        <v>0.87795556172738798</v>
       </c>
       <c r="B207" s="0">
         <v>2.0059977721323796</v>
@@ -5766,7 +5766,7 @@
     </row>
     <row r="208">
       <c r="A208" s="0">
-        <v>1.640345618729097</v>
+        <v>0.8822382717845948</v>
       </c>
       <c r="B208" s="0">
         <v>2.0070565634980051</v>
@@ -5777,7 +5777,7 @@
     </row>
     <row r="209">
       <c r="A209" s="0">
-        <v>1.6483084615384616</v>
+        <v>0.8865209818418015</v>
       </c>
       <c r="B209" s="0">
         <v>2.0080938079925623</v>
@@ -5788,7 +5788,7 @@
     </row>
     <row r="210">
       <c r="A210" s="0">
-        <v>1.6562713043478261</v>
+        <v>0.89080369189900832</v>
       </c>
       <c r="B210" s="0">
         <v>2.0091067260100628</v>
@@ -5799,7 +5799,7 @@
     </row>
     <row r="211">
       <c r="A211" s="0">
-        <v>1.6642341471571904</v>
+        <v>0.89508640195621492</v>
       </c>
       <c r="B211" s="0">
         <v>2.0100925379445203</v>
@@ -5810,7 +5810,7 @@
     </row>
     <row r="212">
       <c r="A212" s="0">
-        <v>1.6721969899665552</v>
+        <v>0.89936911201342185</v>
       </c>
       <c r="B212" s="0">
         <v>2.0110484641899466</v>
@@ -5821,7 +5821,7 @@
     </row>
     <row r="213">
       <c r="A213" s="0">
-        <v>1.6801598327759197</v>
+        <v>0.90365182207062866</v>
       </c>
       <c r="B213" s="0">
         <v>2.0119717251403539</v>
@@ -5832,7 +5832,7 @@
     </row>
     <row r="214">
       <c r="A214" s="0">
-        <v>1.6881226755852843</v>
+        <v>0.90793453212783537</v>
       </c>
       <c r="B214" s="0">
         <v>2.0128595411897559</v>
@@ -5843,7 +5843,7 @@
     </row>
     <row r="215">
       <c r="A215" s="0">
-        <v>1.6960855183946488</v>
+        <v>0.91221724218504219</v>
       </c>
       <c r="B215" s="0">
         <v>2.0137091327321639</v>
@@ -5854,7 +5854,7 @@
     </row>
     <row r="216">
       <c r="A216" s="0">
-        <v>1.7040483612040134</v>
+        <v>0.91649995224224889</v>
       </c>
       <c r="B216" s="0">
         <v>2.0145177201615914</v>
@@ -5865,7 +5865,7 @@
     </row>
     <row r="217">
       <c r="A217" s="0">
-        <v>1.7120112040133779</v>
+        <v>0.92078266229945571</v>
       </c>
       <c r="B217" s="0">
         <v>2.0152825238720502</v>
@@ -5876,7 +5876,7 @@
     </row>
     <row r="218">
       <c r="A218" s="0">
-        <v>1.7199740468227425</v>
+        <v>0.92506537235666242</v>
       </c>
       <c r="B218" s="0">
         <v>2.0160007642575533</v>
@@ -5887,7 +5887,7 @@
     </row>
     <row r="219">
       <c r="A219" s="0">
-        <v>1.7279368896321072</v>
+        <v>0.92934808241386935</v>
       </c>
       <c r="B219" s="0">
         <v>2.0166696617121129</v>
@@ -5898,7 +5898,7 @@
     </row>
     <row r="220">
       <c r="A220" s="0">
-        <v>1.7358997324414713</v>
+        <v>0.93363079247107583</v>
       </c>
       <c r="B220" s="0">
         <v>2.0172864366297421</v>
@@ -5909,7 +5909,7 @@
     </row>
     <row r="221">
       <c r="A221" s="0">
-        <v>1.7438625752508361</v>
+        <v>0.93791350252828276</v>
       </c>
       <c r="B221" s="0">
         <v>2.0178483094044526</v>
@@ -5920,7 +5920,7 @@
     </row>
     <row r="222">
       <c r="A222" s="0">
-        <v>1.7518254180602006</v>
+        <v>0.94219621258548958</v>
       </c>
       <c r="B222" s="0">
         <v>2.0183525004302574</v>
@@ -5931,7 +5931,7 @@
     </row>
     <row r="223">
       <c r="A223" s="0">
-        <v>1.7597882608695652</v>
+        <v>0.94647892264269629</v>
       </c>
       <c r="B223" s="0">
         <v>2.0187962301011688</v>
@@ -5942,7 +5942,7 @@
     </row>
     <row r="224">
       <c r="A224" s="0">
-        <v>1.76775110367893</v>
+        <v>0.95076163269990321</v>
       </c>
       <c r="B224" s="0">
         <v>2.0191767188111998</v>
@@ -5953,7 +5953,7 @@
     </row>
     <row r="225">
       <c r="A225" s="0">
-        <v>1.7757139464882941</v>
+        <v>0.9550443427571097</v>
       </c>
       <c r="B225" s="0">
         <v>2.0194911869543621</v>
@@ -5964,7 +5964,7 @@
     </row>
     <row r="226">
       <c r="A226" s="0">
-        <v>1.7836767892976588</v>
+        <v>0.95932705281431663</v>
       </c>
       <c r="B226" s="0">
         <v>2.0197551228170942</v>
@@ -5975,7 +5975,7 @@
     </row>
     <row r="227">
       <c r="A227" s="0">
-        <v>1.7916396321070234</v>
+        <v>0.96360976287152333</v>
       </c>
       <c r="B227" s="0">
         <v>2.0200120263279762</v>
@@ -5986,7 +5986,7 @@
     </row>
     <row r="228">
       <c r="A228" s="0">
-        <v>1.7996024749163879</v>
+        <v>0.96789247292873015</v>
       </c>
       <c r="B228" s="0">
         <v>2.0202634345092978</v>
@@ -5997,7 +5997,7 @@
     </row>
     <row r="229">
       <c r="A229" s="0">
-        <v>1.8075653177257527</v>
+        <v>0.97217518298593708</v>
       </c>
       <c r="B229" s="0">
         <v>2.0205088087694367</v>
@@ -6008,7 +6008,7 @@
     </row>
     <row r="230">
       <c r="A230" s="0">
-        <v>1.8155281605351168</v>
+        <v>0.97645789304314357</v>
       </c>
       <c r="B230" s="0">
         <v>2.0207476105167701</v>
@@ -6019,7 +6019,7 @@
     </row>
     <row r="231">
       <c r="A231" s="0">
-        <v>1.8234910033444816</v>
+        <v>0.98074060310035049</v>
       </c>
       <c r="B231" s="0">
         <v>2.0209793011596746</v>
@@ -6030,7 +6030,7 @@
     </row>
     <row r="232">
       <c r="A232" s="0">
-        <v>1.8314538461538461</v>
+        <v>0.9850233131575572</v>
       </c>
       <c r="B232" s="0">
         <v>2.0212033421065279</v>
@@ -6041,7 +6041,7 @@
     </row>
     <row r="233">
       <c r="A233" s="0">
-        <v>1.8394166889632106</v>
+        <v>0.98930602321476402</v>
       </c>
       <c r="B233" s="0">
         <v>2.021419194765707</v>
@@ -6052,7 +6052,7 @@
     </row>
     <row r="234">
       <c r="A234" s="0">
-        <v>1.8473795317725754</v>
+        <v>0.99358873327197084</v>
       </c>
       <c r="B234" s="0">
         <v>2.0216263205455891</v>
@@ -6063,7 +6063,7 @@
     </row>
     <row r="235">
       <c r="A235" s="0">
-        <v>1.8553423745819395</v>
+        <v>0.99787144332917743</v>
       </c>
       <c r="B235" s="0">
         <v>2.0218241808545514</v>
@@ -6074,7 +6074,7 @@
     </row>
     <row r="236">
       <c r="A236" s="0">
-        <v>1.8633052173913043</v>
+        <v>1.0021541533863842</v>
       </c>
       <c r="B236" s="0">
         <v>2.022012237100971</v>
@@ -6085,7 +6085,7 @@
     </row>
     <row r="237">
       <c r="A237" s="0">
-        <v>1.8712680602006688</v>
+        <v>1.0064368634435912</v>
       </c>
       <c r="B237" s="0">
         <v>2.0221899506932246</v>
@@ -6096,7 +6096,7 @@
     </row>
     <row r="238">
       <c r="A238" s="0">
-        <v>1.8792309030100334</v>
+        <v>1.0107195735007979</v>
       </c>
       <c r="B238" s="0">
         <v>2.0223567830396902</v>
@@ -6107,7 +6107,7 @@
     </row>
     <row r="239">
       <c r="A239" s="0">
-        <v>1.8871937458193981</v>
+        <v>1.0150022835580048</v>
       </c>
       <c r="B239" s="0">
         <v>2.0225121955487446</v>
@@ -6118,7 +6118,7 @@
     </row>
     <row r="240">
       <c r="A240" s="0">
-        <v>1.8951565886287627</v>
+        <v>1.0192849936152115</v>
       </c>
       <c r="B240" s="0">
         <v>2.0226556496287649</v>
@@ -6129,7 +6129,7 @@
     </row>
     <row r="241">
       <c r="A241" s="0">
-        <v>1.903119431438127</v>
+        <v>1.0235677036724182</v>
       </c>
       <c r="B241" s="0">
         <v>2.0227866066881282</v>
@@ -6140,7 +6140,7 @@
     </row>
     <row r="242">
       <c r="A242" s="0">
-        <v>1.9110822742474916</v>
+        <v>1.0278504137296249</v>
       </c>
       <c r="B242" s="0">
         <v>2.0229045281352116</v>
@@ -6151,7 +6151,7 @@
     </row>
     <row r="243">
       <c r="A243" s="0">
-        <v>1.9190451170568561</v>
+        <v>1.0321331237868316</v>
       </c>
       <c r="B243" s="0">
         <v>2.0230088753783924</v>
@@ -6162,7 +6162,7 @@
     </row>
     <row r="244">
       <c r="A244" s="0">
-        <v>1.9270079598662209</v>
+        <v>1.0364158338440386</v>
       </c>
       <c r="B244" s="0">
         <v>2.023099109826048</v>
@@ -6173,7 +6173,7 @@
     </row>
     <row r="245">
       <c r="A245" s="0">
-        <v>1.9349708026755854</v>
+        <v>1.0406985439012453</v>
       </c>
       <c r="B245" s="0">
         <v>2.0231746928865553</v>
@@ -6184,7 +6184,7 @@
     </row>
     <row r="246">
       <c r="A246" s="0">
-        <v>1.9429336454849497</v>
+        <v>1.044981253958452</v>
       </c>
       <c r="B246" s="0">
         <v>2.0232350859682913</v>
@@ -6195,7 +6195,7 @@
     </row>
     <row r="247">
       <c r="A247" s="0">
-        <v>1.9508964882943143</v>
+        <v>1.0492639640156587</v>
       </c>
       <c r="B247" s="0">
         <v>2.0232797504796336</v>
@@ -6206,7 +6206,7 @@
     </row>
     <row r="248">
       <c r="A248" s="0">
-        <v>1.9588593311036788</v>
+        <v>1.0535466740728656</v>
       </c>
       <c r="B248" s="0">
         <v>2.023308147828959</v>
@@ -6217,7 +6217,7 @@
     </row>
     <row r="249">
       <c r="A249" s="0">
-        <v>1.9668221739130436</v>
+        <v>1.0578293841300723</v>
       </c>
       <c r="B249" s="0">
         <v>2.0233197394246449</v>
@@ -6228,7 +6228,7 @@
     </row>
     <row r="250">
       <c r="A250" s="0">
-        <v>1.9747850167224081</v>
+        <v>1.0621120941872793</v>
       </c>
       <c r="B250" s="0">
         <v>2.0233189578085056</v>
@@ -6239,7 +6239,7 @@
     </row>
     <row r="251">
       <c r="A251" s="0">
-        <v>1.9827478595317725</v>
+        <v>1.0663948042444857</v>
       </c>
       <c r="B251" s="0">
         <v>2.0233150130833759</v>
@@ -6250,7 +6250,7 @@
     </row>
     <row r="252">
       <c r="A252" s="0">
-        <v>1.990710702341137</v>
+        <v>1.0706775143016927</v>
       </c>
       <c r="B252" s="0">
         <v>2.0233082985842636</v>
@@ -6261,7 +6261,7 @@
     </row>
     <row r="253">
       <c r="A253" s="0">
-        <v>1.9986735451505016</v>
+        <v>1.0749602243588994</v>
       </c>
       <c r="B253" s="0">
         <v>2.0232989935925034</v>
@@ -6272,7 +6272,7 @@
     </row>
     <row r="254">
       <c r="A254" s="0">
-        <v>2.0066363879598663</v>
+        <v>1.0792429344161063</v>
       </c>
       <c r="B254" s="0">
         <v>2.0232872773894313</v>
@@ -6283,7 +6283,7 @@
     </row>
     <row r="255">
       <c r="A255" s="0">
-        <v>2.0145992307692309</v>
+        <v>1.083525644473313</v>
       </c>
       <c r="B255" s="0">
         <v>2.0232733292563823</v>
@@ -6294,7 +6294,7 @@
     </row>
     <row r="256">
       <c r="A256" s="0">
-        <v>2.022562073578595</v>
+        <v>1.0878083545305195</v>
       </c>
       <c r="B256" s="0">
         <v>2.0232573284746915</v>
@@ -6305,7 +6305,7 @@
     </row>
     <row r="257">
       <c r="A257" s="0">
-        <v>2.03052491638796</v>
+        <v>1.0920910645877266</v>
       </c>
       <c r="B257" s="0">
         <v>2.0232394543256951</v>
@@ -6316,7 +6316,7 @@
     </row>
     <row r="258">
       <c r="A258" s="0">
-        <v>2.0384877591973245</v>
+        <v>1.0963737746449334</v>
       </c>
       <c r="B258" s="0">
         <v>2.023219886090728</v>
@@ -6327,7 +6327,7 @@
     </row>
     <row r="259">
       <c r="A259" s="0">
-        <v>2.046450602006689</v>
+        <v>1.1006564847021401</v>
       </c>
       <c r="B259" s="0">
         <v>2.0231988030511259</v>
@@ -6338,7 +6338,7 @@
     </row>
     <row r="260">
       <c r="A260" s="0">
-        <v>2.0544134448160536</v>
+        <v>1.1049391947593468</v>
       </c>
       <c r="B260" s="0">
         <v>2.0231763844882242</v>
@@ -6349,7 +6349,7 @@
     </row>
     <row r="261">
       <c r="A261" s="0">
-        <v>2.0623762876254177</v>
+        <v>1.1092219048165535</v>
       </c>
       <c r="B261" s="0">
         <v>2.0231528096833582</v>
@@ -6360,7 +6360,7 @@
     </row>
     <row r="262">
       <c r="A262" s="0">
-        <v>2.0703391304347827</v>
+        <v>1.1135046148737604</v>
       </c>
       <c r="B262" s="0">
         <v>2.0231282579178633</v>
@@ -6371,7 +6371,7 @@
     </row>
     <row r="263">
       <c r="A263" s="0">
-        <v>2.0783019732441472</v>
+        <v>1.1177873249309671</v>
       </c>
       <c r="B263" s="0">
         <v>2.0231029084730752</v>
@@ -6382,7 +6382,7 @@
     </row>
     <row r="264">
       <c r="A264" s="0">
-        <v>2.0862648160535118</v>
+        <v>1.122070034988174</v>
       </c>
       <c r="B264" s="0">
         <v>2.0230769406303288</v>
@@ -6393,7 +6393,7 @@
     </row>
     <row r="265">
       <c r="A265" s="0">
-        <v>2.0942276588628763</v>
+        <v>1.1263527450453807</v>
       </c>
       <c r="B265" s="0">
         <v>2.0230505336709599</v>
@@ -6404,7 +6404,7 @@
     </row>
     <row r="266">
       <c r="A266" s="0">
-        <v>2.1021905016722404</v>
+        <v>1.1306354551025872</v>
       </c>
       <c r="B266" s="0">
         <v>2.0230238668763039</v>
@@ -6415,7 +6415,7 @@
     </row>
     <row r="267">
       <c r="A267" s="0">
-        <v>2.1101533444816054</v>
+        <v>1.1349181651597942</v>
       </c>
       <c r="B267" s="0">
         <v>2.0229971195276963</v>
@@ -6426,7 +6426,7 @@
     </row>
     <row r="268">
       <c r="A268" s="0">
-        <v>2.11811618729097</v>
+        <v>1.1392008752170011</v>
       </c>
       <c r="B268" s="0">
         <v>2.0229704709064724</v>
@@ -6437,7 +6437,7 @@
     </row>
     <row r="269">
       <c r="A269" s="0">
-        <v>2.1260790301003345</v>
+        <v>1.1434835852742078</v>
       </c>
       <c r="B269" s="0">
         <v>2.0229441002939677</v>
@@ -6448,7 +6448,7 @@
     </row>
     <row r="270">
       <c r="A270" s="0">
-        <v>2.134041872909699</v>
+        <v>1.1477662953314145</v>
       </c>
       <c r="B270" s="0">
         <v>2.0229181869715176</v>
@@ -6459,7 +6459,7 @@
     </row>
     <row r="271">
       <c r="A271" s="0">
-        <v>2.1420047157190631</v>
+        <v>1.152049005388621</v>
       </c>
       <c r="B271" s="0">
         <v>2.0228929102204574</v>
@@ -6470,7 +6470,7 @@
     </row>
     <row r="272">
       <c r="A272" s="0">
-        <v>2.1499675585284281</v>
+        <v>1.1563317154458281</v>
       </c>
       <c r="B272" s="0">
         <v>2.022868449322123</v>
@@ -6481,7 +6481,7 @@
     </row>
     <row r="273">
       <c r="A273" s="0">
-        <v>2.1579304013377927</v>
+        <v>1.1606144255030348</v>
       </c>
       <c r="B273" s="0">
         <v>2.022844983557849</v>
@@ -6492,7 +6492,7 @@
     </row>
     <row r="274">
       <c r="A274" s="0">
-        <v>2.1658932441471572</v>
+        <v>1.1648971355602415</v>
       </c>
       <c r="B274" s="0">
         <v>2.0228226922089712</v>
@@ -6503,7 +6503,7 @@
     </row>
     <row r="275">
       <c r="A275" s="0">
-        <v>2.1738560869565218</v>
+        <v>1.1691798456174485</v>
       </c>
       <c r="B275" s="0">
         <v>2.0228017545568253</v>
@@ -6514,7 +6514,7 @@
     </row>
     <row r="276">
       <c r="A276" s="0">
-        <v>2.1818189297658859</v>
+        <v>1.173462555674655</v>
       </c>
       <c r="B276" s="0">
         <v>2.0227816819079423</v>
@@ -6525,7 +6525,7 @@
     </row>
     <row r="277">
       <c r="A277" s="0">
-        <v>2.1897817725752509</v>
+        <v>1.1777452657318619</v>
       </c>
       <c r="B277" s="0">
         <v>2.0227616150819792</v>
@@ -6536,7 +6536,7 @@
     </row>
     <row r="278">
       <c r="A278" s="0">
-        <v>2.1977446153846154</v>
+        <v>1.1820279757890688</v>
       </c>
       <c r="B278" s="0">
         <v>2.0227415482184852</v>
@@ -6547,7 +6547,7 @@
     </row>
     <row r="279">
       <c r="A279" s="0">
-        <v>2.20570745819398</v>
+        <v>1.1863106858462755</v>
       </c>
       <c r="B279" s="0">
         <v>2.0227214813174603</v>
@@ -6558,7 +6558,7 @@
     </row>
     <row r="280">
       <c r="A280" s="0">
-        <v>2.2136703010033445</v>
+        <v>1.1905933959034822</v>
       </c>
       <c r="B280" s="0">
         <v>2.0227014143789055</v>
@@ -6569,7 +6569,7 @@
     </row>
     <row r="281">
       <c r="A281" s="0">
-        <v>2.221633143812709</v>
+        <v>1.1948761059606889</v>
       </c>
       <c r="B281" s="0">
         <v>2.0226813474028198</v>
@@ -6580,7 +6580,7 @@
     </row>
     <row r="282">
       <c r="A282" s="0">
-        <v>2.2295959866220736</v>
+        <v>1.1991588160178959</v>
       </c>
       <c r="B282" s="0">
         <v>2.0226612803892041</v>
@@ -6591,7 +6591,7 @@
     </row>
     <row r="283">
       <c r="A283" s="0">
-        <v>2.2375588294314381</v>
+        <v>1.2034415260751026</v>
       </c>
       <c r="B283" s="0">
         <v>2.022641213338058</v>
@@ -6602,7 +6602,7 @@
     </row>
     <row r="284">
       <c r="A284" s="0">
-        <v>2.2455216722408027</v>
+        <v>1.2077242361323093</v>
       </c>
       <c r="B284" s="0">
         <v>2.0226211462493824</v>
@@ -6613,7 +6613,7 @@
     </row>
     <row r="285">
       <c r="A285" s="0">
-        <v>2.2534845150501672</v>
+        <v>1.212006946189516</v>
       </c>
       <c r="B285" s="0">
         <v>2.0226010791231772</v>
@@ -6624,7 +6624,7 @@
     </row>
     <row r="286">
       <c r="A286" s="0">
-        <v>2.2614473578595318</v>
+        <v>1.2162896562467229</v>
       </c>
       <c r="B286" s="0">
         <v>2.0225810119594425</v>
@@ -6635,7 +6635,7 @@
     </row>
     <row r="287">
       <c r="A287" s="0">
-        <v>2.2694102006688963</v>
+        <v>1.2205723663039296</v>
       </c>
       <c r="B287" s="0">
         <v>2.0225609447581783</v>
@@ -6646,7 +6646,7 @@
     </row>
     <row r="288">
       <c r="A288" s="0">
-        <v>2.2773730434782609</v>
+        <v>1.2248550763611363</v>
       </c>
       <c r="B288" s="0">
         <v>2.0225408775193849</v>
@@ -6657,7 +6657,7 @@
     </row>
     <row r="289">
       <c r="A289" s="0">
-        <v>2.2853358862876254</v>
+        <v>1.2291377864183433</v>
       </c>
       <c r="B289" s="0">
         <v>2.0225208102430625</v>
@@ -6668,7 +6668,7 @@
     </row>
     <row r="290">
       <c r="A290" s="0">
-        <v>2.29329872909699</v>
+        <v>1.23342049647555</v>
       </c>
       <c r="B290" s="0">
         <v>2.0225007429292114</v>
@@ -6679,7 +6679,7 @@
     </row>
     <row r="291">
       <c r="A291" s="0">
-        <v>2.3012615719063545</v>
+        <v>1.2377032065327567</v>
       </c>
       <c r="B291" s="0">
         <v>2.0224806755778322</v>
@@ -6690,7 +6690,7 @@
     </row>
     <row r="292">
       <c r="A292" s="0">
-        <v>2.309224414715719</v>
+        <v>1.2419859165899634</v>
       </c>
       <c r="B292" s="0">
         <v>2.0224606081889238</v>
@@ -6701,7 +6701,7 @@
     </row>
     <row r="293">
       <c r="A293" s="0">
-        <v>2.3171872575250836</v>
+        <v>1.2462686266471703</v>
       </c>
       <c r="B293" s="0">
         <v>2.0224405407624877</v>
@@ -6712,7 +6712,7 @@
     </row>
     <row r="294">
       <c r="A294" s="0">
-        <v>2.3251501003344481</v>
+        <v>1.250551336704377</v>
       </c>
       <c r="B294" s="0">
         <v>2.0224204732985229</v>
@@ -6723,7 +6723,7 @@
     </row>
     <row r="295">
       <c r="A295" s="0">
-        <v>2.3331129431438127</v>
+        <v>1.2548340467615837</v>
       </c>
       <c r="B295" s="0">
         <v>2.0224004057970304</v>
@@ -6734,7 +6734,7 @@
     </row>
     <row r="296">
       <c r="A296" s="0">
-        <v>2.3410757859531772</v>
+        <v>1.2591167568187907</v>
       </c>
       <c r="B296" s="0">
         <v>2.0223803382580106</v>
@@ -6745,7 +6745,7 @@
     </row>
     <row r="297">
       <c r="A297" s="0">
-        <v>2.3490386287625418</v>
+        <v>1.2633994668759974</v>
       </c>
       <c r="B297" s="0">
         <v>2.022360270681463</v>
@@ -6756,7 +6756,7 @@
     </row>
     <row r="298">
       <c r="A298" s="0">
-        <v>2.3570014715719063</v>
+        <v>1.2676821769332041</v>
       </c>
       <c r="B298" s="0">
         <v>2.0223402030673876</v>
@@ -6767,7 +6767,7 @@
     </row>
     <row r="299">
       <c r="A299" s="0">
-        <v>2.3649643143812709</v>
+        <v>1.2719648869904108</v>
       </c>
       <c r="B299" s="0">
         <v>2.0223201354157854</v>
@@ -6778,7 +6778,7 @@
     </row>
     <row r="300">
       <c r="A300" s="0">
-        <v>2.3729271571906354</v>
+        <v>1.2762475970476177</v>
       </c>
       <c r="B300" s="0">
         <v>2.0223000677266563</v>
@@ -6789,7 +6789,7 @@
     </row>
     <row r="301">
       <c r="A301" s="0">
-        <v>2.38089</v>
+        <v>1.2805303071048244</v>
       </c>
       <c r="B301" s="0">
         <v>2.0222799999999999</v>

--- a/TunnelDataProcessing/BoundaryLayerComparison/BoundaryLayerComparison.xlsx
+++ b/TunnelDataProcessing/BoundaryLayerComparison/BoundaryLayerComparison.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="12" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="24" uniqueCount="3">
   <si>
     <t>Y_over_D</t>
   </si>
@@ -98,7 +98,7 @@
         <v>1.1603657969616621</v>
       </c>
       <c r="C2" s="0">
-        <v>0.57711794681629025</v>
+        <v>0.55480652863735658</v>
       </c>
     </row>
     <row r="3">
@@ -109,7 +109,7 @@
         <v>1.1801272893808017</v>
       </c>
       <c r="C3" s="0">
-        <v>0.58698878725763726</v>
+        <v>0.56425510514526833</v>
       </c>
     </row>
     <row r="4">
@@ -120,7 +120,7 @@
         <v>1.2703880532489977</v>
       </c>
       <c r="C4" s="0">
-        <v>0.63182818934523521</v>
+        <v>0.60741154874692727</v>
       </c>
     </row>
     <row r="5">
@@ -131,7 +131,7 @@
         <v>1.3199692774267098</v>
       </c>
       <c r="C5" s="0">
-        <v>0.65654534958934263</v>
+        <v>0.63111785493386829</v>
       </c>
     </row>
     <row r="6">
@@ -142,7 +142,7 @@
         <v>1.3649038953773749</v>
       </c>
       <c r="C6" s="0">
-        <v>0.6789762211303848</v>
+        <v>0.65260247596124776</v>
       </c>
     </row>
     <row r="7">
@@ -153,7 +153,7 @@
         <v>1.4069184970061013</v>
       </c>
       <c r="C7" s="0">
-        <v>0.69990881958103268</v>
+        <v>0.67269094749561276</v>
       </c>
     </row>
     <row r="8">
@@ -164,7 +164,7 @@
         <v>1.433074383134163</v>
       </c>
       <c r="C8" s="0">
-        <v>0.71308874716967574</v>
+        <v>0.68519688004217794</v>
       </c>
     </row>
     <row r="9">
@@ -175,7 +175,7 @@
         <v>1.4653548246463237</v>
       </c>
       <c r="C9" s="0">
-        <v>0.72895154728431155</v>
+        <v>0.70063115063610415</v>
       </c>
     </row>
     <row r="10">
@@ -186,7 +186,7 @@
         <v>1.4833701477140482</v>
       </c>
       <c r="C10" s="0">
-        <v>0.73809397436543511</v>
+        <v>0.70924482994279858</v>
       </c>
     </row>
     <row r="11">
@@ -197,7 +197,7 @@
         <v>1.5122113345495833</v>
       </c>
       <c r="C11" s="0">
-        <v>0.75247277248299305</v>
+        <v>0.72303468723771624</v>
       </c>
     </row>
     <row r="12">
@@ -208,7 +208,7 @@
         <v>1.5270056304221185</v>
       </c>
       <c r="C12" s="0">
-        <v>0.75978856425996277</v>
+        <v>0.73010829450722314</v>
       </c>
     </row>
     <row r="13">
@@ -219,7 +219,7 @@
         <v>1.5512238889731131</v>
       </c>
       <c r="C13" s="0">
-        <v>0.77170412947024647</v>
+        <v>0.74168778779416911</v>
       </c>
     </row>
     <row r="14">
@@ -230,7 +230,7 @@
         <v>1.5709300764159524</v>
       </c>
       <c r="C14" s="0">
-        <v>0.78162264420204808</v>
+        <v>0.75110992129419674</v>
       </c>
     </row>
     <row r="15">
@@ -241,7 +241,7 @@
         <v>1.5907753810842402</v>
       </c>
       <c r="C15" s="0">
-        <v>0.79137791955947123</v>
+        <v>0.76059857101275374</v>
       </c>
     </row>
     <row r="16">
@@ -252,7 +252,7 @@
         <v>1.6125544390281139</v>
       </c>
       <c r="C16" s="0">
-        <v>0.80235312570807793</v>
+        <v>0.77101180756839116</v>
       </c>
     </row>
     <row r="17">
@@ -263,7 +263,7 @@
         <v>1.6303697885348365</v>
       </c>
       <c r="C17" s="0">
-        <v>0.81104567969113828</v>
+        <v>0.77952987337330093</v>
       </c>
     </row>
     <row r="18">
@@ -274,7 +274,7 @@
         <v>1.6447327293663507</v>
       </c>
       <c r="C18" s="0">
-        <v>0.81815423267522436</v>
+        <v>0.78639723654844917</v>
       </c>
     </row>
     <row r="19">
@@ -285,7 +285,7 @@
         <v>1.6598148970147137</v>
       </c>
       <c r="C19" s="0">
-        <v>0.8255342424173121</v>
+        <v>0.79360848415607876</v>
       </c>
     </row>
     <row r="20">
@@ -296,7 +296,7 @@
         <v>1.6697415726619329</v>
       </c>
       <c r="C20" s="0">
-        <v>0.83065304624521275</v>
+        <v>0.7983547326849163</v>
       </c>
     </row>
     <row r="21">
@@ -307,7 +307,7 @@
         <v>1.6843850017447239</v>
       </c>
       <c r="C21" s="0">
-        <v>0.83782742647799902</v>
+        <v>0.80535620590831136</v>
       </c>
     </row>
     <row r="22">
@@ -318,7 +318,7 @@
         <v>1.7002614123723407</v>
       </c>
       <c r="C22" s="0">
-        <v>0.84570892123892782</v>
+        <v>0.81294720547982002</v>
       </c>
     </row>
     <row r="23">
@@ -329,7 +329,7 @@
         <v>1.713833150061147</v>
       </c>
       <c r="C23" s="0">
-        <v>0.85263669892520311</v>
+        <v>0.81943627013031162</v>
       </c>
     </row>
     <row r="24">
@@ -340,7 +340,7 @@
         <v>1.7239702300810447</v>
       </c>
       <c r="C24" s="0">
-        <v>0.85753695682011299</v>
+        <v>0.82428311945238308</v>
       </c>
     </row>
     <row r="25">
@@ -351,7 +351,7 @@
         <v>1.7363621535622578</v>
       </c>
       <c r="C25" s="0">
-        <v>0.86372992278282312</v>
+        <v>0.8302080786917484</v>
       </c>
     </row>
     <row r="26">
@@ -362,7 +362,7 @@
         <v>1.7504585312760839</v>
       </c>
       <c r="C26" s="0">
-        <v>0.87120431480536631</v>
+        <v>0.83694798985273489</v>
       </c>
     </row>
     <row r="27">
@@ -373,7 +373,7 @@
         <v>1.7637787746447846</v>
       </c>
       <c r="C27" s="0">
-        <v>0.87776312390245903</v>
+        <v>0.84331680734403314</v>
       </c>
     </row>
     <row r="28">
@@ -384,7 +384,7 @@
         <v>1.7699116970299644</v>
       </c>
       <c r="C28" s="0">
-        <v>0.8811015616641642</v>
+        <v>0.84624914591160671</v>
       </c>
     </row>
     <row r="29">
@@ -395,7 +395,7 @@
         <v>1.7845186480742063</v>
       </c>
       <c r="C29" s="0">
-        <v>0.88847707095578965</v>
+        <v>0.85323317786433361</v>
       </c>
     </row>
     <row r="30">
@@ -406,7 +406,7 @@
         <v>1.7996559313864116</v>
       </c>
       <c r="C30" s="0">
-        <v>0.8961917913562697</v>
+        <v>0.86047077796374627</v>
       </c>
     </row>
     <row r="31">
@@ -417,7 +417,7 @@
         <v>1.8042467104192472</v>
       </c>
       <c r="C31" s="0">
-        <v>0.89834015498241082</v>
+        <v>0.86266577042700043</v>
       </c>
     </row>
     <row r="32">
@@ -428,7 +428,7 @@
         <v>1.8182353825519313</v>
       </c>
       <c r="C32" s="0">
-        <v>0.90516585904802416</v>
+        <v>0.86935418424142186</v>
       </c>
     </row>
     <row r="33">
@@ -439,7 +439,7 @@
         <v>1.8302739876195666</v>
       </c>
       <c r="C33" s="0">
-        <v>0.91114224318571335</v>
+        <v>0.87511021109493614</v>
       </c>
     </row>
     <row r="34">
@@ -450,7 +450,7 @@
         <v>1.8361021708613796</v>
       </c>
       <c r="C34" s="0">
-        <v>0.91386533038095963</v>
+        <v>0.87789684451787864</v>
       </c>
     </row>
     <row r="35">
@@ -461,7 +461,7 @@
         <v>1.8446464361359243</v>
       </c>
       <c r="C35" s="0">
-        <v>0.918118283868953</v>
+        <v>0.88198212018624056</v>
       </c>
     </row>
     <row r="36">
@@ -472,7 +472,7 @@
         <v>1.8573114680691525</v>
       </c>
       <c r="C36" s="0">
-        <v>0.9244938828655187</v>
+        <v>0.88803766096515224</v>
       </c>
     </row>
     <row r="37">
@@ -483,7 +483,7 @@
         <v>1.8677466904890905</v>
       </c>
       <c r="C37" s="0">
-        <v>0.9295419239385132</v>
+        <v>0.89302706132624865</v>
       </c>
     </row>
     <row r="38">
@@ -494,7 +494,7 @@
         <v>1.8856764809010658</v>
       </c>
       <c r="C38" s="0">
-        <v>0.93854383475814473</v>
+        <v>0.901599844843059</v>
       </c>
     </row>
     <row r="39">
@@ -505,7 +505,7 @@
         <v>1.891474820100556</v>
       </c>
       <c r="C39" s="0">
-        <v>0.94159952146601156</v>
+        <v>0.90437220891269499</v>
       </c>
     </row>
     <row r="40">
@@ -516,7 +516,7 @@
         <v>1.8944542398949935</v>
       </c>
       <c r="C40" s="0">
-        <v>0.9431877019242535</v>
+        <v>0.90579676103051299</v>
       </c>
     </row>
     <row r="41">
@@ -527,7 +527,7 @@
         <v>1.9007403611013853</v>
       </c>
       <c r="C41" s="0">
-        <v>0.94649118115657627</v>
+        <v>0.90880234866007248</v>
       </c>
     </row>
     <row r="42">
@@ -538,7 +538,7 @@
         <v>1.9214539861382809</v>
       </c>
       <c r="C42" s="0">
-        <v>0.95681857043545127</v>
+        <v>0.9187061690176761</v>
       </c>
     </row>
     <row r="43">
@@ -549,7 +549,7 @@
         <v>1.9202791787202922</v>
       </c>
       <c r="C43" s="0">
-        <v>0.95661113283145649</v>
+        <v>0.91814445750644547</v>
       </c>
     </row>
     <row r="44">
@@ -560,7 +560,7 @@
         <v>1.9274830250897403</v>
       </c>
       <c r="C44" s="0">
-        <v>0.9604068439741329</v>
+        <v>0.92158883772476585</v>
       </c>
     </row>
     <row r="45">
@@ -571,7 +571,7 @@
         <v>1.9421778035683002</v>
       </c>
       <c r="C45" s="0">
-        <v>0.96778737616033739</v>
+        <v>0.92861486267149573</v>
       </c>
     </row>
     <row r="46">
@@ -582,7 +582,7 @@
         <v>1.946322054454416</v>
       </c>
       <c r="C46" s="0">
-        <v>0.97008973517988295</v>
+        <v>0.93059635631250837</v>
       </c>
     </row>
     <row r="47">
@@ -593,7 +593,7 @@
         <v>1.9509668650917373</v>
       </c>
       <c r="C47" s="0">
-        <v>0.97283778418493216</v>
+        <v>0.93281718294547</v>
       </c>
     </row>
     <row r="48">
@@ -604,7 +604,7 @@
         <v>1.9618850638946261</v>
       </c>
       <c r="C48" s="0">
-        <v>0.97826591661294171</v>
+        <v>0.93803750915007234</v>
       </c>
     </row>
     <row r="49">
@@ -615,7 +615,7 @@
         <v>1.9645366119856296</v>
       </c>
       <c r="C49" s="0">
-        <v>0.9797185320783881</v>
+        <v>0.93930529573576504</v>
       </c>
     </row>
     <row r="50">
@@ -626,7 +626,7 @@
         <v>1.9810922636585904</v>
       </c>
       <c r="C50" s="0">
-        <v>0.98749441501862401</v>
+        <v>0.94722106131421924</v>
       </c>
     </row>
     <row r="51">
@@ -637,7 +637,7 @@
         <v>1.9820735124647584</v>
       </c>
       <c r="C51" s="0">
-        <v>0.98745796452973567</v>
+        <v>0.94769022650790646</v>
       </c>
     </row>
     <row r="52">
@@ -648,7 +648,7 @@
         <v>1.994247223365694</v>
       </c>
       <c r="C52" s="0">
-        <v>0.99332203665707786</v>
+        <v>0.95351085161015259</v>
       </c>
     </row>
     <row r="53">
@@ -659,7 +659,7 @@
         <v>2.0011858588976827</v>
       </c>
       <c r="C53" s="0">
-        <v>0.99705115566036029</v>
+        <v>0.95682842638102428</v>
       </c>
     </row>
     <row r="54">
@@ -670,7 +670,7 @@
         <v>2.0074550896397381</v>
       </c>
       <c r="C54" s="0">
-        <v>1.0008414507611003</v>
+        <v>0.95982593816078698</v>
       </c>
     </row>
     <row r="55">
@@ -681,7 +681,7 @@
         <v>2.0107211883721829</v>
       </c>
       <c r="C55" s="0">
-        <v>1.0030009096835921</v>
+        <v>0.96138756028432715</v>
       </c>
     </row>
     <row r="56">
@@ -692,7 +692,7 @@
         <v>2.0160358106010925</v>
       </c>
       <c r="C56" s="0">
-        <v>1.0059564116588409</v>
+        <v>0.96392864441276405</v>
       </c>
     </row>
     <row r="57">
@@ -703,7 +703,7 @@
         <v>2.0233812552390535</v>
       </c>
       <c r="C57" s="0">
-        <v>1.0098227942395508</v>
+        <v>0.96744072711250917</v>
       </c>
     </row>
     <row r="58">
@@ -714,7 +714,7 @@
         <v>2.0239860635023876</v>
       </c>
       <c r="C58" s="0">
-        <v>1.0096790885385358</v>
+        <v>0.96772990452014229</v>
       </c>
     </row>
     <row r="59">
@@ -725,7 +725,7 @@
         <v>2.0332162962056923</v>
       </c>
       <c r="C59" s="0">
-        <v>1.0145627412515961</v>
+        <v>0.97214316228596453</v>
       </c>
     </row>
     <row r="60">
@@ -736,7 +736,7 @@
         <v>2.0377894248150561</v>
       </c>
       <c r="C60" s="0">
-        <v>1.016815824759282</v>
+        <v>0.97432971553961678</v>
       </c>
     </row>
     <row r="61">
@@ -747,7 +747,7 @@
         <v>2.0388522053156368</v>
       </c>
       <c r="C61" s="0">
-        <v>1.0175034434411636</v>
+        <v>0.97483786354068203</v>
       </c>
     </row>
     <row r="62">
@@ -758,7 +758,7 @@
         <v>2.0425296624780596</v>
       </c>
       <c r="C62" s="0">
-        <v>1.0198354756262653</v>
+        <v>0.97659616876463706</v>
       </c>
     </row>
     <row r="63">
@@ -769,7 +769,7 @@
         <v>2.0537170209256859</v>
       </c>
       <c r="C63" s="0">
-        <v>1.0255799891085753</v>
+        <v>0.98194518846273693</v>
       </c>
     </row>
     <row r="64">
@@ -780,7 +780,7 @@
         <v>2.0511956404237117</v>
       </c>
       <c r="C64" s="0">
-        <v>1.0239292613216682</v>
+        <v>0.98073963899950989</v>
       </c>
     </row>
     <row r="65">
@@ -791,7 +791,7 @@
         <v>2.0579376104521154</v>
       </c>
       <c r="C65" s="0">
-        <v>1.0276129878537918</v>
+        <v>0.98396318195245625</v>
       </c>
     </row>
     <row r="66">
@@ -802,7 +802,7 @@
         <v>2.0619459568027794</v>
       </c>
       <c r="C66" s="0">
-        <v>1.0298536490879993</v>
+        <v>0.98587969546070608</v>
       </c>
     </row>
     <row r="67">
@@ -813,7 +813,7 @@
         <v>2.0698774625552594</v>
       </c>
       <c r="C67" s="0">
-        <v>1.0338480522318605</v>
+        <v>0.98967199198040956</v>
       </c>
     </row>
     <row r="68">
@@ -824,7 +824,7 @@
         <v>2.062958675367776</v>
       </c>
       <c r="C68" s="0">
-        <v>1.0307821266076587</v>
+        <v>0.98636390731269585</v>
       </c>
     </row>
     <row r="69">
@@ -835,7 +835,7 @@
         <v>2.0762866300865377</v>
       </c>
       <c r="C69" s="0">
-        <v>1.0371561079558833</v>
+        <v>0.99273641183731542</v>
       </c>
     </row>
     <row r="70">
@@ -846,7 +846,7 @@
         <v>2.077034608690715</v>
       </c>
       <c r="C70" s="0">
-        <v>1.0376666884558037</v>
+        <v>0.99309404338244134</v>
       </c>
     </row>
     <row r="71">
@@ -857,7 +857,7 @@
         <v>2.0789740542092456</v>
       </c>
       <c r="C71" s="0">
-        <v>1.0383926899240417</v>
+        <v>0.99402135185571305</v>
       </c>
     </row>
     <row r="72">
@@ -868,7 +868,7 @@
         <v>2.0812543488510515</v>
       </c>
       <c r="C72" s="0">
-        <v>1.0400342631882669</v>
+        <v>0.99511163076414288</v>
       </c>
     </row>
     <row r="73">
@@ -879,7 +879,7 @@
         <v>2.0804089539163932</v>
       </c>
       <c r="C73" s="0">
-        <v>1.0398018678436343</v>
+        <v>0.99470742147923163</v>
       </c>
     </row>
     <row r="74">
@@ -890,7 +890,7 @@
         <v>2.0790038267260029</v>
       </c>
       <c r="C74" s="0">
-        <v>1.0393230214813669</v>
+        <v>0.99403558701044981</v>
       </c>
     </row>
     <row r="75">
@@ -901,7 +901,7 @@
         <v>2.0790301123714281</v>
       </c>
       <c r="C75" s="0">
-        <v>1.0395578458896277</v>
+        <v>0.99404815498490184</v>
       </c>
     </row>
     <row r="76">
@@ -912,7 +912,7 @@
         <v>2.0786896581288801</v>
       </c>
       <c r="C76" s="0">
-        <v>1.0394165605313461</v>
+        <v>0.99388537335434834</v>
       </c>
     </row>
     <row r="77">
@@ -923,7 +923,7 @@
         <v>2.076683596976634</v>
       </c>
       <c r="C77" s="0">
-        <v>1.0388233047660373</v>
+        <v>0.99292621390047087</v>
       </c>
     </row>
     <row r="78">
@@ -934,7 +934,7 @@
         <v>2.0749784870930008</v>
       </c>
       <c r="C78" s="0">
-        <v>1.0379138229091884</v>
+        <v>0.99211094849195847</v>
       </c>
     </row>
     <row r="79">
@@ -945,7 +945,7 @@
         <v>2.0762344313246754</v>
       </c>
       <c r="C79" s="0">
-        <v>1.0388503453419435</v>
+        <v>0.99271145400596283</v>
       </c>
     </row>
     <row r="80">
@@ -956,7 +956,7 @@
         <v>2.0782855312316246</v>
       </c>
       <c r="C80" s="0">
-        <v>1.0397276092808685</v>
+        <v>0.99369214787184768</v>
       </c>
     </row>
     <row r="81">
@@ -967,7 +967,7 @@
         <v>2.0774722259440317</v>
       </c>
       <c r="C81" s="0">
-        <v>1.0392345028422367</v>
+        <v>0.99330328163284498</v>
       </c>
     </row>
     <row r="82">
@@ -978,7 +978,7 @@
         <v>2.0789847234394747</v>
       </c>
       <c r="C82" s="0">
-        <v>1.0402402587544863</v>
+        <v>0.99402645314239535</v>
       </c>
     </row>
     <row r="83">
@@ -989,7 +989,7 @@
         <v>2.0810170329842466</v>
       </c>
       <c r="C83" s="0">
-        <v>1.0415205390063011</v>
+        <v>0.99499816275896957</v>
       </c>
     </row>
     <row r="84">
@@ -1000,7 +1000,7 @@
         <v>2.0806476034369767</v>
       </c>
       <c r="C84" s="0">
-        <v>1.0412491030444502</v>
+        <v>0.99482152714524019</v>
       </c>
     </row>
     <row r="85">
@@ -1011,7 +1011,7 @@
         <v>2.0812655843253434</v>
       </c>
       <c r="C85" s="0">
-        <v>1.0419512046596278</v>
+        <v>0.99511700278950399</v>
       </c>
     </row>
     <row r="86">
@@ -1022,7 +1022,7 @@
         <v>2.083783165031635</v>
       </c>
       <c r="C86" s="0">
-        <v>1.042868878281602</v>
+        <v>0.99632073545370303</v>
       </c>
     </row>
     <row r="87">
@@ -1033,7 +1033,7 @@
         <v>2.084183588990745</v>
       </c>
       <c r="C87" s="0">
-        <v>1.0434305466703853</v>
+        <v>0.9965121904477392</v>
       </c>
     </row>
     <row r="88">
@@ -1044,7 +1044,7 @@
         <v>2.0847598317312452</v>
       </c>
       <c r="C88" s="0">
-        <v>1.0437658271846129</v>
+        <v>0.99678770980150377</v>
       </c>
     </row>
     <row r="89">
@@ -1055,7 +1055,7 @@
         <v>2.0863662512352565</v>
       </c>
       <c r="C89" s="0">
-        <v>1.0447192815482274</v>
+        <v>0.99755578830820357</v>
       </c>
     </row>
     <row r="90">
@@ -1066,7 +1066,7 @@
         <v>2.0866615922173031</v>
       </c>
       <c r="C90" s="0">
-        <v>1.0445991796668874</v>
+        <v>0.99769699990323912</v>
       </c>
     </row>
     <row r="91">
@@ -1077,7 +1077,7 @@
         <v>2.0872585326684021</v>
       </c>
       <c r="C91" s="0">
-        <v>1.045057693229932</v>
+        <v>0.99798241546817956</v>
       </c>
     </row>
     <row r="92">
@@ -1088,7 +1088,7 @@
         <v>2.0889936832896634</v>
       </c>
       <c r="C92" s="0">
-        <v>1.0460407380619188</v>
+        <v>0.99881204427606551</v>
       </c>
     </row>
     <row r="93">
@@ -1099,7 +1099,7 @@
         <v>2.0895626095608311</v>
       </c>
       <c r="C93" s="0">
-        <v>1.0464186141886198</v>
+        <v>0.99908406540111383</v>
       </c>
     </row>
     <row r="94">
@@ -1110,7 +1110,7 @@
         <v>2.0900664475671347</v>
       </c>
       <c r="C94" s="0">
-        <v>1.0468418154483854</v>
+        <v>0.99932496582751806</v>
       </c>
     </row>
     <row r="95">
@@ -1121,7 +1121,7 @@
         <v>2.0899826434458921</v>
       </c>
       <c r="C95" s="0">
-        <v>1.0475436413495329</v>
+        <v>0.99928489650307417</v>
       </c>
     </row>
     <row r="96">
@@ -1132,7 +1132,7 @@
         <v>2.0882875471414692</v>
       </c>
       <c r="C96" s="0">
-        <v>1.0469336474630886</v>
+        <v>0.9984744188943534</v>
       </c>
     </row>
     <row r="97">
@@ -1143,7 +1143,7 @@
         <v>2.0891972778324335</v>
       </c>
       <c r="C97" s="0">
-        <v>1.0475660448288369</v>
+        <v>0.99890938908045357</v>
       </c>
     </row>
     <row r="98">
@@ -1154,7 +1154,7 @@
         <v>2.0890097169373272</v>
       </c>
       <c r="C98" s="0">
-        <v>1.0473574184522145</v>
+        <v>0.99881971045549367</v>
       </c>
     </row>
     <row r="99">
@@ -1165,7 +1165,7 @@
         <v>2.0908557023832333</v>
       </c>
       <c r="C99" s="0">
-        <v>1.048252852837626</v>
+        <v>0.99970233279737919</v>
       </c>
     </row>
     <row r="100">
@@ -1176,7 +1176,7 @@
         <v>2.0913515235657063</v>
       </c>
       <c r="C100" s="0">
-        <v>1.0489758609360076</v>
+        <v>0.99993940013407001</v>
       </c>
     </row>
     <row r="101">
@@ -1187,7 +1187,7 @@
         <v>2.0930225097939967</v>
       </c>
       <c r="C101" s="0">
-        <v>1.049625937434675</v>
+        <v>1.000738349974841</v>
       </c>
     </row>
     <row r="102">
@@ -1198,7 +1198,7 @@
         <v>2.093151881661107</v>
       </c>
       <c r="C102" s="0">
-        <v>1.0499647888323158</v>
+        <v>1.0008002066382162</v>
       </c>
     </row>
   </sheetData>
@@ -1234,7 +1234,7 @@
         <v>0.54130912771519346</v>
       </c>
       <c r="C2" s="0">
-        <v>0.27158094972863578</v>
+        <v>0.25932384607386133</v>
       </c>
     </row>
     <row r="3">
@@ -1245,7 +1245,7 @@
         <v>0.54342481564007938</v>
       </c>
       <c r="C3" s="0">
-        <v>0.27264722792543883</v>
+        <v>0.2603374043193859</v>
       </c>
     </row>
     <row r="4">
@@ -1256,7 +1256,7 @@
         <v>0.95787796605385633</v>
       </c>
       <c r="C4" s="0">
-        <v>0.48064573356874729</v>
+        <v>0.45888861929035873</v>
       </c>
     </row>
     <row r="5">
@@ -1267,7 +1267,7 @@
         <v>1.1442788844265042</v>
       </c>
       <c r="C5" s="0">
-        <v>0.57395645262496897</v>
+        <v>0.54818732235883494</v>
       </c>
     </row>
     <row r="6">
@@ -1278,7 +1278,7 @@
         <v>1.2153701708161071</v>
       </c>
       <c r="C6" s="0">
-        <v>0.60988509321332096</v>
+        <v>0.58224487813422909</v>
       </c>
     </row>
     <row r="7">
@@ -1289,7 +1289,7 @@
         <v>1.2684796319446261</v>
       </c>
       <c r="C7" s="0">
-        <v>0.63651032961654752</v>
+        <v>0.60768791801218247</v>
       </c>
     </row>
     <row r="8">
@@ -1300,7 +1300,7 @@
         <v>1.3162243217368683</v>
       </c>
       <c r="C8" s="0">
-        <v>0.66026535236014883</v>
+        <v>0.63056086796369704</v>
       </c>
     </row>
     <row r="9">
@@ -1311,7 +1311,7 @@
         <v>1.3574896818881461</v>
       </c>
       <c r="C9" s="0">
-        <v>0.68082386303089382</v>
+        <v>0.65032977884318022</v>
       </c>
     </row>
     <row r="10">
@@ -1322,7 +1322,7 @@
         <v>1.3960349284979801</v>
       </c>
       <c r="C10" s="0">
-        <v>0.70018331767266617</v>
+        <v>0.66879557054508332</v>
       </c>
     </row>
     <row r="11">
@@ -1333,7 +1333,7 @@
         <v>1.4266616169728561</v>
       </c>
       <c r="C11" s="0">
-        <v>0.71579764322371131</v>
+        <v>0.68346783495217756</v>
       </c>
     </row>
     <row r="12">
@@ -1344,7 +1344,7 @@
         <v>1.4547397750330797</v>
       </c>
       <c r="C12" s="0">
-        <v>0.72978842000592548</v>
+        <v>0.69691918015594434</v>
       </c>
     </row>
     <row r="13">
@@ -1355,7 +1355,7 @@
         <v>1.4797212709756193</v>
       </c>
       <c r="C13" s="0">
-        <v>0.74233116771255436</v>
+        <v>0.70888701383324093</v>
       </c>
     </row>
     <row r="14">
@@ -1366,7 +1366,7 @@
         <v>1.5051348409401275</v>
       </c>
       <c r="C14" s="0">
-        <v>0.75515027950984681</v>
+        <v>0.72106184032005916</v>
       </c>
     </row>
     <row r="15">
@@ -1377,7 +1377,7 @@
         <v>1.5199390535343353</v>
       </c>
       <c r="C15" s="0">
-        <v>0.76270091819646291</v>
+        <v>0.72815406387858195</v>
       </c>
     </row>
     <row r="16">
@@ -1388,7 +1388,7 @@
         <v>1.5477706346571014</v>
       </c>
       <c r="C16" s="0">
-        <v>0.7763696238951614</v>
+        <v>0.74148728197807379</v>
       </c>
     </row>
     <row r="17">
@@ -1399,7 +1399,7 @@
         <v>1.5641142860431971</v>
       </c>
       <c r="C17" s="0">
-        <v>0.78467342296568765</v>
+        <v>0.74931700129986334</v>
       </c>
     </row>
     <row r="18">
@@ -1410,7 +1410,7 @@
         <v>1.5837147348579532</v>
       </c>
       <c r="C18" s="0">
-        <v>0.79467851643507692</v>
+        <v>0.75870694784089188</v>
       </c>
     </row>
     <row r="19">
@@ -1421,7 +1421,7 @@
         <v>1.596412437583469</v>
       </c>
       <c r="C19" s="0">
-        <v>0.80066171093143701</v>
+        <v>0.76479001006631908</v>
       </c>
     </row>
     <row r="20">
@@ -1432,7 +1432,7 @@
         <v>1.6146002490234277</v>
       </c>
       <c r="C20" s="0">
-        <v>0.80984892327010816</v>
+        <v>0.77350320733713596</v>
       </c>
     </row>
     <row r="21">
@@ -1443,7 +1443,7 @@
         <v>1.6362267190936306</v>
       </c>
       <c r="C21" s="0">
-        <v>0.82071353726440188</v>
+        <v>0.7838637556975121</v>
       </c>
     </row>
     <row r="22">
@@ -1454,7 +1454,7 @@
         <v>1.6434510694586038</v>
       </c>
       <c r="C22" s="0">
-        <v>0.82422067797945575</v>
+        <v>0.78732471030941298</v>
       </c>
     </row>
     <row r="23">
@@ -1465,7 +1465,7 @@
         <v>1.6689867395243676</v>
       </c>
       <c r="C23" s="0">
-        <v>0.83724953003380465</v>
+        <v>0.7995580310396172</v>
       </c>
     </row>
     <row r="24">
@@ -1476,7 +1476,7 @@
         <v>1.676201284926365</v>
       </c>
       <c r="C24" s="0">
-        <v>0.84093016624726602</v>
+        <v>0.80301428840815137</v>
       </c>
     </row>
     <row r="25">
@@ -1487,7 +1487,7 @@
         <v>1.6874219921690372</v>
       </c>
       <c r="C25" s="0">
-        <v>0.84679873134106753</v>
+        <v>0.80838976945743746</v>
       </c>
     </row>
     <row r="26">
@@ -1498,7 +1498,7 @@
         <v>1.701661435915589</v>
       </c>
       <c r="C26" s="0">
-        <v>0.85383872712029829</v>
+        <v>0.81521143037029586</v>
       </c>
     </row>
     <row r="27">
@@ -1509,7 +1509,7 @@
         <v>1.7157523002003863</v>
       </c>
       <c r="C27" s="0">
-        <v>0.86067772599572812</v>
+        <v>0.82196191162721088</v>
       </c>
     </row>
     <row r="28">
@@ -1520,7 +1520,7 @@
         <v>1.7268351046621127</v>
       </c>
       <c r="C28" s="0">
-        <v>0.86617129218881195</v>
+        <v>0.82727132787598245</v>
       </c>
     </row>
     <row r="29">
@@ -1531,7 +1531,7 @@
         <v>1.7339042370987565</v>
       </c>
       <c r="C29" s="0">
-        <v>0.86983116114984416</v>
+        <v>0.83065792255546567</v>
       </c>
     </row>
     <row r="30">
@@ -1542,7 +1542,7 @@
         <v>1.7536929322619588</v>
       </c>
       <c r="C30" s="0">
-        <v>0.87958311985312332</v>
+        <v>0.84013805188593738</v>
       </c>
     </row>
     <row r="31">
@@ -1553,7 +1553,7 @@
         <v>1.7680875566839407</v>
       </c>
       <c r="C31" s="0">
-        <v>0.88705565306968492</v>
+        <v>0.84703405488454386</v>
       </c>
     </row>
     <row r="32">
@@ -1564,7 +1564,7 @@
         <v>1.7794782787063641</v>
       </c>
       <c r="C32" s="0">
-        <v>0.89273546996886166</v>
+        <v>0.85249098456330452</v>
       </c>
     </row>
     <row r="33">
@@ -1575,7 +1575,7 @@
         <v>1.7876330500223203</v>
       </c>
       <c r="C33" s="0">
-        <v>0.89688540272187545</v>
+        <v>0.85639767401898137</v>
       </c>
     </row>
     <row r="34">
@@ -1586,7 +1586,7 @@
         <v>1.7953218844312575</v>
       </c>
       <c r="C34" s="0">
-        <v>0.90081643014173773</v>
+        <v>0.8600811480427184</v>
       </c>
     </row>
     <row r="35">
@@ -1597,7 +1597,7 @@
         <v>1.8059876724927291</v>
       </c>
       <c r="C35" s="0">
-        <v>0.90616325124491448</v>
+        <v>0.86519078510571046</v>
       </c>
     </row>
     <row r="36">
@@ -1608,7 +1608,7 @@
         <v>1.8135998702381615</v>
       </c>
       <c r="C36" s="0">
-        <v>0.90991050729096079</v>
+        <v>0.86883754496130805</v>
       </c>
     </row>
     <row r="37">
@@ -1619,7 +1619,7 @@
         <v>1.8251284801403713</v>
       </c>
       <c r="C37" s="0">
-        <v>0.91575857255277637</v>
+        <v>0.87436053230191546</v>
       </c>
     </row>
     <row r="38">
@@ -1630,7 +1630,7 @@
         <v>1.8330010011429358</v>
       </c>
       <c r="C38" s="0">
-        <v>0.91961266616267656</v>
+        <v>0.87813200468276997</v>
       </c>
     </row>
     <row r="39">
@@ -1641,7 +1641,7 @@
         <v>1.8517029845433384</v>
       </c>
       <c r="C39" s="0">
-        <v>0.92904361618646047</v>
+        <v>0.88709152525297108</v>
       </c>
     </row>
     <row r="40">
@@ -1652,7 +1652,7 @@
         <v>1.8539005330462288</v>
       </c>
       <c r="C40" s="0">
-        <v>0.92980378446388812</v>
+        <v>0.88814430027656766</v>
       </c>
     </row>
     <row r="41">
@@ -1663,7 +1663,7 @@
         <v>1.8673111593981089</v>
       </c>
       <c r="C41" s="0">
-        <v>0.93675410330309816</v>
+        <v>0.89456890135157252</v>
       </c>
     </row>
     <row r="42">
@@ -1674,7 +1674,7 @@
         <v>1.8781528854502467</v>
       </c>
       <c r="C42" s="0">
-        <v>0.94217224867233851</v>
+        <v>0.89976282466446156</v>
       </c>
     </row>
     <row r="43">
@@ -1685,7 +1685,7 @@
         <v>1.881763369351126</v>
       </c>
       <c r="C43" s="0">
-        <v>0.94392106321054625</v>
+        <v>0.90149249173162471</v>
       </c>
     </row>
     <row r="44">
@@ -1696,7 +1696,7 @@
         <v>1.8930050499758488</v>
       </c>
       <c r="C44" s="0">
-        <v>0.94975481704376208</v>
+        <v>0.90687802045574217</v>
       </c>
     </row>
     <row r="45">
@@ -1707,7 +1707,7 @@
         <v>1.9034270327155363</v>
       </c>
       <c r="C45" s="0">
-        <v>0.95471871736065173</v>
+        <v>0.91187085820665692</v>
       </c>
     </row>
     <row r="46">
@@ -1718,7 +1718,7 @@
         <v>1.9142516596871049</v>
       </c>
       <c r="C46" s="0">
-        <v>0.96010553673889498</v>
+        <v>0.91705658989832528</v>
       </c>
     </row>
     <row r="47">
@@ -1729,7 +1729,7 @@
         <v>1.9173841218405794</v>
       </c>
       <c r="C47" s="0">
-        <v>0.9617654179947227</v>
+        <v>0.91855725207401873</v>
       </c>
     </row>
     <row r="48">
@@ -1740,7 +1740,7 @@
         <v>1.9297464739706887</v>
       </c>
       <c r="C48" s="0">
-        <v>0.96814025121011238</v>
+        <v>0.92447965858216474</v>
       </c>
     </row>
     <row r="49">
@@ -1751,7 +1751,7 @@
         <v>1.9329769335998661</v>
       </c>
       <c r="C49" s="0">
-        <v>0.9694408923074197</v>
+        <v>0.92602726820618986</v>
       </c>
     </row>
     <row r="50">
@@ -1762,7 +1762,7 @@
         <v>1.9428356525090114</v>
       </c>
       <c r="C50" s="0">
-        <v>0.97467240429077362</v>
+        <v>0.93075026431688124</v>
       </c>
     </row>
     <row r="51">
@@ -1773,7 +1773,7 @@
         <v>1.9517599346046777</v>
       </c>
       <c r="C51" s="0">
-        <v>0.97897042762594477</v>
+        <v>0.93502560171284321</v>
       </c>
     </row>
     <row r="52">
@@ -1784,7 +1784,7 @@
         <v>1.9531201422496405</v>
       </c>
       <c r="C52" s="0">
-        <v>0.97970538798854667</v>
+        <v>0.93567723358064425</v>
       </c>
     </row>
     <row r="53">
@@ -1795,7 +1795,7 @@
         <v>1.9654175029724239</v>
       </c>
       <c r="C53" s="0">
-        <v>0.98602136432055221</v>
+        <v>0.94156850478948251</v>
       </c>
     </row>
     <row r="54">
@@ -1806,7 +1806,7 @@
         <v>1.9759989057674308</v>
       </c>
       <c r="C54" s="0">
-        <v>0.99111065231618534</v>
+        <v>0.94663771557711518</v>
       </c>
     </row>
     <row r="55">
@@ -1817,7 +1817,7 @@
         <v>1.9771480086852162</v>
       </c>
       <c r="C55" s="0">
-        <v>0.99186999396145092</v>
+        <v>0.94718821393917418</v>
       </c>
     </row>
     <row r="56">
@@ -1828,7 +1828,7 @@
         <v>1.978694287109332</v>
       </c>
       <c r="C56" s="0">
-        <v>0.99259902930009447</v>
+        <v>0.94792898635092948</v>
       </c>
     </row>
     <row r="57">
@@ -1839,7 +1839,7 @@
         <v>1.9906113553395421</v>
       </c>
       <c r="C57" s="0">
-        <v>0.99878452285038444</v>
+        <v>0.95363807162061054</v>
       </c>
     </row>
     <row r="58">
@@ -1850,7 +1850,7 @@
         <v>1.9975749726654961</v>
       </c>
       <c r="C58" s="0">
-        <v>1.0024092067323802</v>
+        <v>0.95697411739389204</v>
       </c>
     </row>
     <row r="59">
@@ -1861,7 +1861,7 @@
         <v>2.0033787731399566</v>
       </c>
       <c r="C59" s="0">
-        <v>1.0050373168971889</v>
+        <v>0.95975453210301598</v>
       </c>
     </row>
     <row r="60">
@@ -1872,7 +1872,7 @@
         <v>2.0064809784889892</v>
       </c>
       <c r="C60" s="0">
-        <v>1.0066298407191359</v>
+        <v>0.96124069921388233</v>
       </c>
     </row>
     <row r="61">
@@ -1883,7 +1883,7 @@
         <v>2.0079171298935381</v>
       </c>
       <c r="C61" s="0">
-        <v>1.0074213118342144</v>
+        <v>0.96192871330177321</v>
       </c>
     </row>
     <row r="62">
@@ -1894,7 +1894,7 @@
         <v>2.0206405743721558</v>
       </c>
       <c r="C62" s="0">
-        <v>1.0135425249422971</v>
+        <v>0.96802410757570534</v>
       </c>
     </row>
     <row r="63">
@@ -1905,7 +1905,7 @@
         <v>2.0223844980510957</v>
       </c>
       <c r="C63" s="0">
-        <v>1.0145640602087427</v>
+        <v>0.96885956549157459</v>
       </c>
     </row>
     <row r="64">
@@ -1916,7 +1916,7 @@
         <v>2.0243615727227504</v>
       </c>
       <c r="C64" s="0">
-        <v>1.0155525941207535</v>
+        <v>0.969806718572094</v>
       </c>
     </row>
     <row r="65">
@@ -1927,7 +1927,7 @@
         <v>2.0300084416355344</v>
       </c>
       <c r="C65" s="0">
-        <v>1.0182641983232465</v>
+        <v>0.97251195240201116</v>
       </c>
     </row>
     <row r="66">
@@ -1938,7 +1938,7 @@
         <v>2.0342028945281339</v>
       </c>
       <c r="C66" s="0">
-        <v>1.0202494647802565</v>
+        <v>0.97452138028820934</v>
       </c>
     </row>
     <row r="67">
@@ -1949,7 +1949,7 @@
         <v>2.0371051635690631</v>
       </c>
       <c r="C67" s="0">
-        <v>1.0218030102802642</v>
+        <v>0.97591176432479787</v>
       </c>
     </row>
     <row r="68">
@@ -1960,7 +1960,7 @@
         <v>2.0445219475083123</v>
       </c>
       <c r="C68" s="0">
-        <v>1.0259138834453805</v>
+        <v>0.97946490769177408</v>
       </c>
     </row>
     <row r="69">
@@ -1971,7 +1971,7 @@
         <v>2.0474547043216558</v>
       </c>
       <c r="C69" s="0">
-        <v>1.0270604740816696</v>
+        <v>0.98086989744253938</v>
       </c>
     </row>
     <row r="70">
@@ -1982,7 +1982,7 @@
         <v>2.0535524674209058</v>
       </c>
       <c r="C70" s="0">
-        <v>1.0303011500842845</v>
+        <v>0.98379114021932257</v>
       </c>
     </row>
     <row r="71">
@@ -1993,7 +1993,7 @@
         <v>2.0517316649346187</v>
       </c>
       <c r="C71" s="0">
-        <v>1.0294377253446163</v>
+        <v>0.98291885213196328</v>
       </c>
     </row>
     <row r="72">
@@ -2004,7 +2004,7 @@
         <v>2.0598859333364405</v>
       </c>
       <c r="C72" s="0">
-        <v>1.0336827277525582</v>
+        <v>0.98682530065760421</v>
       </c>
     </row>
     <row r="73">
@@ -2015,7 +2015,7 @@
         <v>2.0578476372508243</v>
       </c>
       <c r="C73" s="0">
-        <v>1.0326735644538418</v>
+        <v>0.98584881836071336</v>
       </c>
     </row>
     <row r="74">
@@ -2026,7 +2026,7 @@
         <v>2.0650769646030835</v>
       </c>
       <c r="C74" s="0">
-        <v>1.0360132604939867</v>
+        <v>0.98931215728763644</v>
       </c>
     </row>
     <row r="75">
@@ -2037,7 +2037,7 @@
         <v>2.0644988294153213</v>
       </c>
       <c r="C75" s="0">
-        <v>1.0360026429968057</v>
+        <v>0.98903519125701744</v>
       </c>
     </row>
     <row r="76">
@@ -2048,7 +2048,7 @@
         <v>2.0650897870508658</v>
       </c>
       <c r="C76" s="0">
-        <v>1.0361592805717152</v>
+        <v>0.98931830011121868</v>
       </c>
     </row>
     <row r="77">
@@ -2059,7 +2059,7 @@
         <v>2.0647331054455802</v>
       </c>
       <c r="C77" s="0">
-        <v>1.0361253812417708</v>
+        <v>0.98914742539108069</v>
       </c>
     </row>
     <row r="78">
@@ -2070,7 +2070,7 @@
         <v>2.069428282002141</v>
       </c>
       <c r="C78" s="0">
-        <v>1.0380979717028433</v>
+        <v>0.99139673392903649</v>
       </c>
     </row>
     <row r="79">
@@ -2081,7 +2081,7 @@
         <v>2.0660035485054853</v>
       </c>
       <c r="C79" s="0">
-        <v>1.0367287137940679</v>
+        <v>0.98975605392447163</v>
       </c>
     </row>
     <row r="80">
@@ -2092,7 +2092,7 @@
         <v>2.0653133565979962</v>
       </c>
       <c r="C80" s="0">
-        <v>1.036499628783355</v>
+        <v>0.9894254051125172</v>
       </c>
     </row>
     <row r="81">
@@ -2103,7 +2103,7 @@
         <v>2.0659131580717265</v>
       </c>
       <c r="C81" s="0">
-        <v>1.0365874099697601</v>
+        <v>0.98971275076601661</v>
       </c>
     </row>
     <row r="82">
@@ -2114,7 +2114,7 @@
         <v>2.0664753490187824</v>
       </c>
       <c r="C82" s="0">
-        <v>1.037241961346997</v>
+        <v>0.98998207842216346</v>
       </c>
     </row>
     <row r="83">
@@ -2125,7 +2125,7 @@
         <v>2.0672910757448002</v>
       </c>
       <c r="C83" s="0">
-        <v>1.0375469364038163</v>
+        <v>0.9903728669404156</v>
       </c>
     </row>
     <row r="84">
@@ -2136,7 +2136,7 @@
         <v>2.0692764391864471</v>
       </c>
       <c r="C84" s="0">
-        <v>1.038572129635194</v>
+        <v>0.99132399090485979</v>
       </c>
     </row>
     <row r="85">
@@ -2147,7 +2147,7 @@
         <v>2.0684558919353186</v>
       </c>
       <c r="C85" s="0">
-        <v>1.0380054609412488</v>
+        <v>0.99093089302759674</v>
       </c>
     </row>
     <row r="86">
@@ -2158,7 +2158,7 @@
         <v>2.0701221395948761</v>
       </c>
       <c r="C86" s="0">
-        <v>1.0387224710756235</v>
+        <v>0.99172913885325253</v>
       </c>
     </row>
     <row r="87">
@@ -2169,7 +2169,7 @@
         <v>2.0729183123798931</v>
       </c>
       <c r="C87" s="0">
-        <v>1.0401465720555834</v>
+        <v>0.99306869557559763</v>
       </c>
     </row>
     <row r="88">
@@ -2180,7 +2180,7 @@
         <v>2.0704643298225101</v>
       </c>
       <c r="C88" s="0">
-        <v>1.0390806865947602</v>
+        <v>0.99189307121902193</v>
       </c>
     </row>
     <row r="89">
@@ -2191,7 +2191,7 @@
         <v>2.071367220881247</v>
       </c>
       <c r="C89" s="0">
-        <v>1.0397199987958805</v>
+        <v>0.99232561737416558</v>
       </c>
     </row>
     <row r="90">
@@ -2202,7 +2202,7 @@
         <v>2.0765510660637023</v>
       </c>
       <c r="C90" s="0">
-        <v>1.0421576219120381</v>
+        <v>0.99480903138168453</v>
       </c>
     </row>
     <row r="91">
@@ -2213,7 +2213,7 @@
         <v>2.0775355260697501</v>
       </c>
       <c r="C91" s="0">
-        <v>1.0427838099533207</v>
+        <v>0.99528065460398596</v>
       </c>
     </row>
     <row r="92">
@@ -2224,7 +2224,7 @@
         <v>2.0776246871578468</v>
       </c>
       <c r="C92" s="0">
-        <v>1.0427518605169377</v>
+        <v>0.99532336882235306</v>
       </c>
     </row>
     <row r="93">
@@ -2235,7 +2235,7 @@
         <v>2.0786311785282723</v>
       </c>
       <c r="C93" s="0">
-        <v>1.0434218412374552</v>
+        <v>0.99580554656489473</v>
       </c>
     </row>
     <row r="94">
@@ -2246,7 +2246,7 @@
         <v>2.0801140823208719</v>
       </c>
       <c r="C94" s="0">
-        <v>1.0438045254045869</v>
+        <v>0.99651595822279082</v>
       </c>
     </row>
     <row r="95">
@@ -2257,7 +2257,7 @@
         <v>2.0811707011919842</v>
       </c>
       <c r="C95" s="0">
-        <v>1.0445835241528301</v>
+        <v>0.997022150443579</v>
       </c>
     </row>
     <row r="96">
@@ -2268,7 +2268,7 @@
         <v>2.0822410738333499</v>
       </c>
       <c r="C96" s="0">
-        <v>1.0452205005141468</v>
+        <v>0.99753493165468254</v>
       </c>
     </row>
     <row r="97">
@@ -2279,7 +2279,7 @@
         <v>2.0840956497977299</v>
       </c>
       <c r="C97" s="0">
-        <v>1.0458698813654583</v>
+        <v>0.9984233995324534</v>
       </c>
     </row>
     <row r="98">
@@ -2290,7 +2290,7 @@
         <v>2.08491970627193</v>
       </c>
       <c r="C98" s="0">
-        <v>1.0463562847368042</v>
+        <v>0.99881817856596733</v>
       </c>
     </row>
     <row r="99">
@@ -2301,7 +2301,7 @@
         <v>2.0868185312295591</v>
       </c>
       <c r="C99" s="0">
-        <v>1.0474886105809356</v>
+        <v>0.99972784471756504</v>
       </c>
     </row>
     <row r="100">
@@ -2312,7 +2312,7 @@
         <v>2.0875521451159416</v>
       </c>
       <c r="C100" s="0">
-        <v>1.0476839275334631</v>
+        <v>1.0000792956072866</v>
       </c>
     </row>
     <row r="101">
@@ -2323,7 +2323,7 @@
         <v>2.0884255393293722</v>
       </c>
       <c r="C101" s="0">
-        <v>1.048259624251503</v>
+        <v>1.0004977107696569</v>
       </c>
     </row>
     <row r="102">
@@ -2334,7 +2334,7 @@
         <v>2.0892172006827363</v>
       </c>
       <c r="C102" s="0">
-        <v>1.0485908939571678</v>
+        <v>1.0008769703395242</v>
       </c>
     </row>
   </sheetData>
@@ -2370,7 +2370,7 @@
         <v>0.54672817077449887</v>
       </c>
       <c r="C2" s="0">
-        <v>0.2743583411659945</v>
+        <v>0.2621605866782965</v>
       </c>
     </row>
     <row r="3">
@@ -2381,7 +2381,7 @@
         <v>0.55022162793262885</v>
       </c>
       <c r="C3" s="0">
-        <v>0.27608273287001739</v>
+        <v>0.26383572768449975</v>
       </c>
     </row>
     <row r="4">
@@ -2392,7 +2392,7 @@
         <v>0.97345960599107384</v>
       </c>
       <c r="C4" s="0">
-        <v>0.48834587086311176</v>
+        <v>0.46678176661853971</v>
       </c>
     </row>
     <row r="5">
@@ -2403,7 +2403,7 @@
         <v>1.1396262655815841</v>
       </c>
       <c r="C5" s="0">
-        <v>0.57178405318594383</v>
+        <v>0.54646002593140852</v>
       </c>
     </row>
     <row r="6">
@@ -2414,7 +2414,7 @@
         <v>1.2203277269898152</v>
       </c>
       <c r="C6" s="0">
-        <v>0.61222376470172291</v>
+        <v>0.5851570304018513</v>
       </c>
     </row>
     <row r="7">
@@ -2425,7 +2425,7 @@
         <v>1.271283732146518</v>
       </c>
       <c r="C7" s="0">
-        <v>0.63791641383908149</v>
+        <v>0.60959084764550919</v>
       </c>
     </row>
     <row r="8">
@@ -2436,7 +2436,7 @@
         <v>1.3163319118340238</v>
       </c>
       <c r="C8" s="0">
-        <v>0.66049708099343252</v>
+        <v>0.63119181472012675</v>
       </c>
     </row>
     <row r="9">
@@ -2447,7 +2447,7 @@
         <v>1.3606932970784156</v>
       </c>
       <c r="C9" s="0">
-        <v>0.68274047285144335</v>
+        <v>0.65246345829586716</v>
       </c>
     </row>
     <row r="10">
@@ -2458,7 +2458,7 @@
         <v>1.3916707364970806</v>
       </c>
       <c r="C10" s="0">
-        <v>0.69822626353657047</v>
+        <v>0.66731739143101965</v>
       </c>
     </row>
     <row r="11">
@@ -2469,7 +2469,7 @@
         <v>1.4265856769385599</v>
       </c>
       <c r="C11" s="0">
-        <v>0.71578495776148621</v>
+        <v>0.68405938820248524</v>
       </c>
     </row>
     <row r="12">
@@ -2480,7 +2480,7 @@
         <v>1.4531586129944851</v>
       </c>
       <c r="C12" s="0">
-        <v>0.72910931695089576</v>
+        <v>0.69680132629636038</v>
       </c>
     </row>
     <row r="13">
@@ -2491,7 +2491,7 @@
         <v>1.4804802764378551</v>
       </c>
       <c r="C13" s="0">
-        <v>0.74275321230806335</v>
+        <v>0.70990228523760923</v>
       </c>
     </row>
     <row r="14">
@@ -2502,7 +2502,7 @@
         <v>1.5060787325393334</v>
       </c>
       <c r="C14" s="0">
-        <v>0.75575131733813805</v>
+        <v>0.72217695229951584</v>
       </c>
     </row>
     <row r="15">
@@ -2513,7 +2513,7 @@
         <v>1.5245716154185167</v>
       </c>
       <c r="C15" s="0">
-        <v>0.76482317968913016</v>
+        <v>0.7310444394423713</v>
       </c>
     </row>
     <row r="16">
@@ -2524,7 +2524,7 @@
         <v>1.5469238427387362</v>
       </c>
       <c r="C16" s="0">
-        <v>0.77615970137322732</v>
+        <v>0.74176251350746703</v>
       </c>
     </row>
     <row r="17">
@@ -2535,7 +2535,7 @@
         <v>1.5669150781876708</v>
       </c>
       <c r="C17" s="0">
-        <v>0.78620948107363298</v>
+        <v>0.75134847284497897</v>
       </c>
     </row>
     <row r="18">
@@ -2546,7 +2546,7 @@
         <v>1.5799461235773449</v>
       </c>
       <c r="C18" s="0">
-        <v>0.79281342396473231</v>
+        <v>0.75759696466779658</v>
       </c>
     </row>
     <row r="19">
@@ -2557,7 +2557,7 @@
         <v>1.5965470472081567</v>
       </c>
       <c r="C19" s="0">
-        <v>0.80104555084648588</v>
+        <v>0.76555724202517139</v>
       </c>
     </row>
     <row r="20">
@@ -2568,7 +2568,7 @@
         <v>1.6154303702695589</v>
       </c>
       <c r="C20" s="0">
-        <v>0.81064712573512832</v>
+        <v>0.77461194839817604</v>
       </c>
     </row>
     <row r="21">
@@ -2579,7 +2579,7 @@
         <v>1.6310848057741159</v>
       </c>
       <c r="C21" s="0">
-        <v>0.81854667522414848</v>
+        <v>0.78211837703194931</v>
       </c>
     </row>
     <row r="22">
@@ -2590,7 +2590,7 @@
         <v>1.6474247616726454</v>
       </c>
       <c r="C22" s="0">
-        <v>0.82654072386030608</v>
+        <v>0.78995351824771598</v>
       </c>
     </row>
     <row r="23">
@@ -2601,7 +2601,7 @@
         <v>1.6601031599459797</v>
       </c>
       <c r="C23" s="0">
-        <v>0.83313007099105774</v>
+        <v>0.7960329129216176</v>
       </c>
     </row>
     <row r="24">
@@ -2612,7 +2612,7 @@
         <v>1.6750050794432789</v>
       </c>
       <c r="C24" s="0">
-        <v>0.84036042554244161</v>
+        <v>0.80317850403412683</v>
       </c>
     </row>
     <row r="25">
@@ -2623,7 +2623,7 @@
         <v>1.6852363943960962</v>
       </c>
       <c r="C25" s="0">
-        <v>0.84557517433334817</v>
+        <v>0.80808450243315078</v>
       </c>
     </row>
     <row r="26">
@@ -2634,7 +2634,7 @@
         <v>1.7013384085791208</v>
       </c>
       <c r="C26" s="0">
-        <v>0.8538761915693075</v>
+        <v>0.81580554866887711</v>
       </c>
     </row>
     <row r="27">
@@ -2645,7 +2645,7 @@
         <v>1.709802408757813</v>
       </c>
       <c r="C27" s="0">
-        <v>0.85814429256007907</v>
+        <v>0.81986410531750897</v>
       </c>
     </row>
     <row r="28">
@@ -2656,7 +2656,7 @@
         <v>1.7302111635211372</v>
       </c>
       <c r="C28" s="0">
-        <v>0.86822256313867041</v>
+        <v>0.82965026854840151</v>
       </c>
     </row>
     <row r="29">
@@ -2667,7 +2667,7 @@
         <v>1.7310128459042906</v>
       </c>
       <c r="C29" s="0">
-        <v>0.86869128604268531</v>
+        <v>0.83003468174518158</v>
       </c>
     </row>
     <row r="30">
@@ -2678,7 +2678,7 @@
         <v>1.7523860856693019</v>
       </c>
       <c r="C30" s="0">
-        <v>0.87917522035477524</v>
+        <v>0.84028332334722977</v>
       </c>
     </row>
     <row r="31">
@@ -2689,7 +2689,7 @@
         <v>1.7594101346477633</v>
       </c>
       <c r="C31" s="0">
-        <v>0.88312847743594114</v>
+        <v>0.84365141173097258</v>
       </c>
     </row>
     <row r="32">
@@ -2700,7 +2700,7 @@
         <v>1.7783119873010516</v>
       </c>
       <c r="C32" s="0">
-        <v>0.89234656238427923</v>
+        <v>0.85271500319338622</v>
       </c>
     </row>
     <row r="33">
@@ -2711,7 +2711,7 @@
         <v>1.7856148369744718</v>
       </c>
       <c r="C33" s="0">
-        <v>0.89605831032291872</v>
+        <v>0.8562167787687972</v>
       </c>
     </row>
     <row r="34">
@@ -2722,7 +2722,7 @@
         <v>1.7976888293157787</v>
       </c>
       <c r="C34" s="0">
-        <v>0.90205370708453669</v>
+        <v>0.86200635590227881</v>
       </c>
     </row>
     <row r="35">
@@ -2733,7 +2733,7 @@
         <v>1.8035087230425404</v>
       </c>
       <c r="C35" s="0">
-        <v>0.9051688963979756</v>
+        <v>0.86479704208852715</v>
       </c>
     </row>
     <row r="36">
@@ -2744,7 +2744,7 @@
         <v>1.8142976617370148</v>
       </c>
       <c r="C36" s="0">
-        <v>0.91073044870230102</v>
+        <v>0.86997042558872761</v>
       </c>
     </row>
     <row r="37">
@@ -2755,7 +2755,7 @@
         <v>1.8263740159121082</v>
       </c>
       <c r="C37" s="0">
-        <v>0.91673125812818868</v>
+        <v>0.87576113524064192</v>
       </c>
     </row>
     <row r="38">
@@ -2766,7 +2766,7 @@
         <v>1.8302218752844301</v>
       </c>
       <c r="C38" s="0">
-        <v>0.91858677193457805</v>
+        <v>0.87760621497939861</v>
       </c>
     </row>
     <row r="39">
@@ -2777,7 +2777,7 @@
         <v>1.8440214219002558</v>
       </c>
       <c r="C39" s="0">
-        <v>0.92547480995193199</v>
+        <v>0.88422320936542864</v>
       </c>
     </row>
     <row r="40">
@@ -2788,7 +2788,7 @@
         <v>1.8534210137322913</v>
       </c>
       <c r="C40" s="0">
-        <v>0.93016746986992338</v>
+        <v>0.88873038979063368</v>
       </c>
     </row>
     <row r="41">
@@ -2799,7 +2799,7 @@
         <v>1.8662127278733327</v>
       </c>
       <c r="C41" s="0">
-        <v>0.93686601415701987</v>
+        <v>0.89486412034102014</v>
       </c>
     </row>
     <row r="42">
@@ -2810,7 +2810,7 @@
         <v>1.8796019338083763</v>
       </c>
       <c r="C42" s="0">
-        <v>0.94351533267580057</v>
+        <v>0.90128435304663523</v>
       </c>
     </row>
     <row r="43">
@@ -2821,7 +2821,7 @@
         <v>1.8871007933343615</v>
       </c>
       <c r="C43" s="0">
-        <v>0.94699356635553267</v>
+        <v>0.90488011693413628</v>
       </c>
     </row>
     <row r="44">
@@ -2832,7 +2832,7 @@
         <v>1.8938611513936354</v>
       </c>
       <c r="C44" s="0">
-        <v>0.95063054884358966</v>
+        <v>0.90812176338609052</v>
       </c>
     </row>
     <row r="45">
@@ -2843,7 +2843,7 @@
         <v>1.9034126828989011</v>
       </c>
       <c r="C45" s="0">
-        <v>0.95519251820510376</v>
+        <v>0.91270180011540236</v>
       </c>
     </row>
     <row r="46">
@@ -2854,7 +2854,7 @@
         <v>1.9102777588568298</v>
       </c>
       <c r="C46" s="0">
-        <v>0.95885121289234687</v>
+        <v>0.91599365964803281</v>
       </c>
     </row>
     <row r="47">
@@ -2865,7 +2865,7 @@
         <v>1.9227301810457671</v>
       </c>
       <c r="C47" s="0">
-        <v>0.96499903400678799</v>
+        <v>0.92196469695893835</v>
       </c>
     </row>
     <row r="48">
@@ -2876,7 +2876,7 @@
         <v>1.9168388139072805</v>
       </c>
       <c r="C48" s="0">
-        <v>0.96194378962876859</v>
+        <v>0.91913973869279486</v>
       </c>
     </row>
     <row r="49">
@@ -2887,7 +2887,7 @@
         <v>1.927327009949376</v>
       </c>
       <c r="C49" s="0">
-        <v>0.96754350876016171</v>
+        <v>0.92416891365500264</v>
       </c>
     </row>
     <row r="50">
@@ -2898,7 +2898,7 @@
         <v>1.9363025147809552</v>
       </c>
       <c r="C50" s="0">
-        <v>0.97193824334298373</v>
+        <v>0.92847274092815624</v>
       </c>
     </row>
     <row r="51">
@@ -2909,7 +2909,7 @@
         <v>1.9451553607177954</v>
       </c>
       <c r="C51" s="0">
-        <v>0.97635277919192898</v>
+        <v>0.93271775226767961</v>
       </c>
     </row>
     <row r="52">
@@ -2920,7 +2920,7 @@
         <v>1.9500108066957691</v>
       </c>
       <c r="C52" s="0">
-        <v>0.97876056966469061</v>
+        <v>0.9350459779458391</v>
       </c>
     </row>
     <row r="53">
@@ -2931,7 +2931,7 @@
         <v>1.9578644926326771</v>
       </c>
       <c r="C53" s="0">
-        <v>0.98295381289872374</v>
+        <v>0.93881188397166215</v>
       </c>
     </row>
     <row r="54">
@@ -2942,7 +2942,7 @@
         <v>1.9729131363973691</v>
       </c>
       <c r="C54" s="0">
-        <v>0.99029968758336506</v>
+        <v>0.94602783055893169</v>
       </c>
     </row>
     <row r="55">
@@ -2953,7 +2953,7 @@
         <v>1.9749017631929549</v>
       </c>
       <c r="C55" s="0">
-        <v>0.99150207854239125</v>
+        <v>0.94698139321636055</v>
       </c>
     </row>
     <row r="56">
@@ -2964,7 +2964,7 @@
         <v>1.9858528637561035</v>
       </c>
       <c r="C56" s="0">
-        <v>0.99705448872302782</v>
+        <v>0.95223253464618851</v>
       </c>
     </row>
     <row r="57">
@@ -2975,7 +2975,7 @@
         <v>1.9913987847635966</v>
       </c>
       <c r="C57" s="0">
-        <v>0.9997793335449342</v>
+        <v>0.95489184869422128</v>
       </c>
     </row>
     <row r="58">
@@ -2986,7 +2986,7 @@
         <v>1.9893710871277019</v>
       </c>
       <c r="C58" s="0">
-        <v>0.99842886607660863</v>
+        <v>0.95391955125236949</v>
       </c>
     </row>
     <row r="59">
@@ -2997,7 +2997,7 @@
         <v>1.9997050412674184</v>
       </c>
       <c r="C59" s="0">
-        <v>1.0039631449041009</v>
+        <v>0.9588747659729443</v>
       </c>
     </row>
     <row r="60">
@@ -3008,7 +3008,7 @@
         <v>2.003141360415615</v>
       </c>
       <c r="C60" s="0">
-        <v>1.0055573672253231</v>
+        <v>0.9605225088405358</v>
       </c>
     </row>
     <row r="61">
@@ -3019,7 +3019,7 @@
         <v>2.0136767260782289</v>
       </c>
       <c r="C61" s="0">
-        <v>1.0110758040610079</v>
+        <v>0.96557430201788141</v>
       </c>
     </row>
     <row r="62">
@@ -3030,7 +3030,7 @@
         <v>2.0195381269848847</v>
       </c>
       <c r="C62" s="0">
-        <v>1.0138674771849332</v>
+        <v>0.96838489123311933</v>
       </c>
     </row>
     <row r="63">
@@ -3041,7 +3041,7 @@
         <v>2.021898314193554</v>
       </c>
       <c r="C63" s="0">
-        <v>1.015282683851042</v>
+        <v>0.96951662011846074</v>
       </c>
     </row>
     <row r="64">
@@ -3052,7 +3052,7 @@
         <v>2.0256200650527045</v>
       </c>
       <c r="C64" s="0">
-        <v>1.0168987265384182</v>
+        <v>0.971301229803605</v>
       </c>
     </row>
     <row r="65">
@@ -3063,7 +3063,7 @@
         <v>2.0305655810895065</v>
       </c>
       <c r="C65" s="0">
-        <v>1.0196120006773763</v>
+        <v>0.97367264480458848</v>
       </c>
     </row>
     <row r="66">
@@ -3074,7 +3074,7 @@
         <v>2.0337027818117144</v>
       </c>
       <c r="C66" s="0">
-        <v>1.0210110268018111</v>
+        <v>0.97517695796389858</v>
       </c>
     </row>
     <row r="67">
@@ -3085,7 +3085,7 @@
         <v>2.0342729895826017</v>
       </c>
       <c r="C67" s="0">
-        <v>1.0216320098071741</v>
+        <v>0.97545037720902839</v>
       </c>
     </row>
     <row r="68">
@@ -3096,7 +3096,7 @@
         <v>2.042405207993597</v>
       </c>
       <c r="C68" s="0">
-        <v>1.025582490313337</v>
+        <v>0.97934984181243889</v>
       </c>
     </row>
     <row r="69">
@@ -3107,7 +3107,7 @@
         <v>2.0454120980756429</v>
       </c>
       <c r="C69" s="0">
-        <v>1.0270918024157856</v>
+        <v>0.98079166996420508</v>
       </c>
     </row>
     <row r="70">
@@ -3118,7 +3118,7 @@
         <v>2.0502461981425788</v>
       </c>
       <c r="C70" s="0">
-        <v>1.029527777750139</v>
+        <v>0.98310966010510858</v>
       </c>
     </row>
     <row r="71">
@@ -3129,7 +3129,7 @@
         <v>2.0543554536555186</v>
       </c>
       <c r="C71" s="0">
-        <v>1.0316269722950235</v>
+        <v>0.98508008141074066</v>
       </c>
     </row>
     <row r="72">
@@ -3140,7 +3140,7 @@
         <v>2.0531331487915017</v>
       </c>
       <c r="C72" s="0">
-        <v>1.0310696535999986</v>
+        <v>0.98449397632711844</v>
       </c>
     </row>
     <row r="73">
@@ -3151,7 +3151,7 @@
         <v>2.0615400849797427</v>
       </c>
       <c r="C73" s="0">
-        <v>1.034977637187535</v>
+        <v>0.98852517033008003</v>
       </c>
     </row>
     <row r="74">
@@ -3162,7 +3162,7 @@
         <v>2.0637579363125038</v>
       </c>
       <c r="C74" s="0">
-        <v>1.036114407921052</v>
+        <v>0.9895886480099263</v>
       </c>
     </row>
     <row r="75">
@@ -3173,7 +3173,7 @@
         <v>2.065171080326726</v>
       </c>
       <c r="C75" s="0">
-        <v>1.0369912558202052</v>
+        <v>0.99026626201197165</v>
       </c>
     </row>
     <row r="76">
@@ -3184,7 +3184,7 @@
         <v>2.0624133525333175</v>
       </c>
       <c r="C76" s="0">
-        <v>1.0354149402156083</v>
+        <v>0.98894390919595543</v>
       </c>
     </row>
     <row r="77">
@@ -3195,7 +3195,7 @@
         <v>2.0625081611608787</v>
       </c>
       <c r="C77" s="0">
-        <v>1.0356342169955275</v>
+        <v>0.98898937070087189</v>
       </c>
     </row>
     <row r="78">
@@ -3206,7 +3206,7 @@
         <v>2.0652875179873575</v>
       </c>
       <c r="C78" s="0">
-        <v>1.036912941604673</v>
+        <v>0.99032209481345201</v>
       </c>
     </row>
     <row r="79">
@@ -3217,7 +3217,7 @@
         <v>2.0674265943402204</v>
       </c>
       <c r="C79" s="0">
-        <v>1.0380077080669265</v>
+        <v>0.99134779925231742</v>
       </c>
     </row>
     <row r="80">
@@ -3228,7 +3228,7 @@
         <v>2.0670009948720707</v>
       </c>
       <c r="C80" s="0">
-        <v>1.0380486627209131</v>
+        <v>0.99114372085975533</v>
       </c>
     </row>
     <row r="81">
@@ -3239,7 +3239,7 @@
         <v>2.0665671699638559</v>
       </c>
       <c r="C81" s="0">
-        <v>1.0374946202407895</v>
+        <v>0.99093569830205153</v>
       </c>
     </row>
     <row r="82">
@@ -3250,7 +3250,7 @@
         <v>2.0635460082962624</v>
       </c>
       <c r="C82" s="0">
-        <v>1.0364055465410238</v>
+        <v>0.98948702680940781</v>
       </c>
     </row>
     <row r="83">
@@ -3261,7 +3261,7 @@
         <v>2.0637208100735145</v>
       </c>
       <c r="C83" s="0">
-        <v>1.036465133331071</v>
+        <v>0.98957084567758846</v>
       </c>
     </row>
     <row r="84">
@@ -3272,7 +3272,7 @@
         <v>2.0669297151754202</v>
       </c>
       <c r="C84" s="0">
-        <v>1.0382214704000812</v>
+        <v>0.99110954166780763</v>
       </c>
     </row>
     <row r="85">
@@ -3283,7 +3283,7 @@
         <v>2.0682162216853066</v>
       </c>
       <c r="C85" s="0">
-        <v>1.0388881193279402</v>
+        <v>0.9917264319606921</v>
       </c>
     </row>
     <row r="86">
@@ -3294,7 +3294,7 @@
         <v>2.0690265318398326</v>
       </c>
       <c r="C86" s="0">
-        <v>1.0390345325535675</v>
+        <v>0.99211498224373496</v>
       </c>
     </row>
     <row r="87">
@@ -3305,7 +3305,7 @@
         <v>2.0695056488224632</v>
       </c>
       <c r="C87" s="0">
-        <v>1.0391825047399823</v>
+        <v>0.99234472271801122</v>
       </c>
     </row>
     <row r="88">
@@ -3316,7 +3316,7 @@
         <v>2.0730494425838288</v>
       </c>
       <c r="C88" s="0">
-        <v>1.0408217176422878</v>
+        <v>0.99404400053321951</v>
       </c>
     </row>
     <row r="89">
@@ -3327,7 +3327,7 @@
         <v>2.0723771618701052</v>
       </c>
       <c r="C89" s="0">
-        <v>1.0409111046593555</v>
+        <v>0.9937216364851541</v>
       </c>
     </row>
     <row r="90">
@@ -3338,7 +3338,7 @@
         <v>2.0710651445750892</v>
       </c>
       <c r="C90" s="0">
-        <v>1.0401014861101328</v>
+        <v>0.99309251356414885</v>
       </c>
     </row>
     <row r="91">
@@ -3349,7 +3349,7 @@
         <v>2.0752023919162217</v>
       </c>
       <c r="C91" s="0">
-        <v>1.0422103986748625</v>
+        <v>0.99507635717814824</v>
       </c>
     </row>
     <row r="92">
@@ -3360,7 +3360,7 @@
         <v>2.0778049986388383</v>
       </c>
       <c r="C92" s="0">
-        <v>1.0434706644685887</v>
+        <v>0.99632432818415562</v>
       </c>
     </row>
     <row r="93">
@@ -3371,7 +3371,7 @@
         <v>2.0797469177498513</v>
       </c>
       <c r="C93" s="0">
-        <v>1.0443079425553865</v>
+        <v>0.99725549412847447</v>
       </c>
     </row>
     <row r="94">
@@ -3382,7 +3382,7 @@
         <v>2.0786398212008041</v>
       </c>
       <c r="C94" s="0">
-        <v>1.0440414685412143</v>
+        <v>0.99672463236512954</v>
       </c>
     </row>
     <row r="95">
@@ -3393,7 +3393,7 @@
         <v>2.0794829213568939</v>
       </c>
       <c r="C95" s="0">
-        <v>1.0443775139358227</v>
+        <v>0.99712890571953883</v>
       </c>
     </row>
     <row r="96">
@@ -3404,7 +3404,7 @@
         <v>2.0823110496785411</v>
       </c>
       <c r="C96" s="0">
-        <v>1.0456545211858639</v>
+        <v>0.99848501615912744</v>
       </c>
     </row>
     <row r="97">
@@ -3415,7 +3415,7 @@
         <v>2.0813744149440301</v>
       </c>
       <c r="C97" s="0">
-        <v>1.0450977714184855</v>
+        <v>0.99803589221668487</v>
       </c>
     </row>
     <row r="98">
@@ -3426,7 +3426,7 @@
         <v>2.082433775628497</v>
       </c>
       <c r="C98" s="0">
-        <v>1.0459178250057029</v>
+        <v>0.9985438642462775</v>
       </c>
     </row>
     <row r="99">
@@ -3437,7 +3437,7 @@
         <v>2.0855004566131905</v>
       </c>
       <c r="C99" s="0">
-        <v>1.0474878949870536</v>
+        <v>1.0000143626202016</v>
       </c>
     </row>
     <row r="100">
@@ -3448,7 +3448,7 @@
         <v>2.0846662077458666</v>
       </c>
       <c r="C100" s="0">
-        <v>1.0470539377437031</v>
+        <v>0.99961433353045581</v>
       </c>
     </row>
     <row r="101">
@@ -3459,7 +3459,7 @@
         <v>2.0866882354905574</v>
       </c>
       <c r="C101" s="0">
-        <v>1.0478947022022385</v>
+        <v>1.000583912213546</v>
       </c>
     </row>
     <row r="102">
@@ -3470,7 +3470,7 @@
         <v>2.0880638434839023</v>
       </c>
       <c r="C102" s="0">
-        <v>1.0486436652861224</v>
+        <v>1.0012435273895188</v>
       </c>
     </row>
   </sheetData>
@@ -3506,7 +3506,7 @@
         <v>0.87603299999999995</v>
       </c>
       <c r="C2" s="0">
-        <v>0.43662356168234295</v>
+        <v>0.43318215779725949</v>
       </c>
     </row>
     <row r="3">
@@ -3517,7 +3517,7 @@
         <v>0.98544772386602164</v>
       </c>
       <c r="C3" s="0">
-        <v>0.49115694847812857</v>
+        <v>0.48728572031040063</v>
       </c>
     </row>
     <row r="4">
@@ -3528,7 +3528,7 @@
         <v>1.0754073156353341</v>
       </c>
       <c r="C4" s="0">
-        <v>0.53599370390378809</v>
+        <v>0.53176907890213332</v>
       </c>
     </row>
     <row r="5">
@@ -3539,7 +3539,7 @@
         <v>1.1405801993434901</v>
       </c>
       <c r="C5" s="0">
-        <v>0.5684765174619123</v>
+        <v>0.56399586761279707</v>
       </c>
     </row>
     <row r="6">
@@ -3550,7 +3550,7 @@
         <v>1.1756363078411047</v>
       </c>
       <c r="C6" s="0">
-        <v>0.5859488306635281</v>
+        <v>0.5813304665639456</v>
       </c>
     </row>
     <row r="7">
@@ -3561,7 +3561,7 @@
         <v>1.1882246666541769</v>
       </c>
       <c r="C7" s="0">
-        <v>0.59222299392073297</v>
+        <v>0.58755517777205402</v>
       </c>
     </row>
     <row r="8">
@@ -3572,7 +3572,7 @@
         <v>1.1989258770929192</v>
       </c>
       <c r="C8" s="0">
-        <v>0.59755658365545283</v>
+        <v>0.59284672892240664</v>
       </c>
     </row>
     <row r="9">
@@ -3583,7 +3583,7 @@
         <v>1.2161768923540177</v>
       </c>
       <c r="C9" s="0">
-        <v>0.60615466126889583</v>
+        <v>0.60137703772926221</v>
       </c>
     </row>
     <row r="10">
@@ -3594,7 +3594,7 @@
         <v>1.2372276289176045</v>
       </c>
       <c r="C10" s="0">
-        <v>0.6166465577778516</v>
+        <v>0.61178623862447534</v>
       </c>
     </row>
     <row r="11">
@@ -3605,7 +3605,7 @@
         <v>1.2596903805621178</v>
       </c>
       <c r="C11" s="0">
-        <v>0.62784221664939333</v>
+        <v>0.62289365492892301</v>
       </c>
     </row>
     <row r="12">
@@ -3616,7 +3616,7 @@
         <v>1.2811818809192341</v>
       </c>
       <c r="C12" s="0">
-        <v>0.63855379421761438</v>
+        <v>0.63352080538900413</v>
       </c>
     </row>
     <row r="13">
@@ -3627,7 +3627,7 @@
         <v>1.3027791017068797</v>
       </c>
       <c r="C13" s="0">
-        <v>0.64931806390008273</v>
+        <v>0.64420023265169413</v>
       </c>
     </row>
     <row r="14">
@@ -3638,7 +3638,7 @@
         <v>1.3212218633896358</v>
       </c>
       <c r="C14" s="0">
-        <v>0.65851011978517338</v>
+        <v>0.65331983807920302</v>
       </c>
     </row>
     <row r="15">
@@ -3649,7 +3649,7 @@
         <v>1.3335465841302176</v>
       </c>
       <c r="C15" s="0">
-        <v>0.66465288320446592</v>
+        <v>0.65941418512395344</v>
       </c>
     </row>
     <row r="16">
@@ -3660,7 +3660,7 @@
         <v>1.34330917042303</v>
       </c>
       <c r="C16" s="0">
-        <v>0.6695186533277363</v>
+        <v>0.66424160394950271</v>
       </c>
     </row>
     <row r="17">
@@ -3671,7 +3671,7 @@
         <v>1.3528885770730126</v>
       </c>
       <c r="C17" s="0">
-        <v>0.67429312489481075</v>
+        <v>0.66897844382089677</v>
       </c>
     </row>
     <row r="18">
@@ -3682,7 +3682,7 @@
         <v>1.3646748555964048</v>
       </c>
       <c r="C18" s="0">
-        <v>0.68016752335681341</v>
+        <v>0.67480654112221128</v>
       </c>
     </row>
     <row r="19">
@@ -3693,7 +3693,7 @@
         <v>1.3822774607054451</v>
       </c>
       <c r="C19" s="0">
-        <v>0.68894083684796847</v>
+        <v>0.68351070462288666</v>
       </c>
     </row>
     <row r="20">
@@ -3704,7 +3704,7 @@
         <v>1.3975555116290648</v>
       </c>
       <c r="C20" s="0">
-        <v>0.6965555694092247</v>
+        <v>0.69106541896130769</v>
       </c>
     </row>
     <row r="21">
@@ -3715,7 +3715,7 @@
         <v>1.4062997747264605</v>
       </c>
       <c r="C21" s="0">
-        <v>0.700913797121962</v>
+        <v>0.69538929575233821</v>
       </c>
     </row>
     <row r="22">
@@ -3726,7 +3726,7 @@
         <v>1.4130616913692964</v>
       </c>
       <c r="C22" s="0">
-        <v>0.70428400364202937</v>
+        <v>0.69873293879111509</v>
       </c>
     </row>
     <row r="23">
@@ -3737,7 +3737,7 @@
         <v>1.4190493379174101</v>
       </c>
       <c r="C23" s="0">
-        <v>0.70726830624470793</v>
+        <v>0.70169371955147375</v>
       </c>
     </row>
     <row r="24">
@@ -3748,7 +3748,7 @@
         <v>1.4254640386677579</v>
       </c>
       <c r="C24" s="0">
-        <v>0.71046545690997209</v>
+        <v>0.7048656707367138</v>
       </c>
     </row>
     <row r="25">
@@ -3759,7 +3759,7 @@
         <v>1.4319802569440785</v>
       </c>
       <c r="C25" s="0">
-        <v>0.7137132049200432</v>
+        <v>0.70808782046579299</v>
       </c>
     </row>
     <row r="26">
@@ -3770,7 +3770,7 @@
         <v>1.4382717422584212</v>
       </c>
       <c r="C26" s="0">
-        <v>0.71684894378629649</v>
+        <v>0.71119884389095711</v>
       </c>
     </row>
     <row r="27">
@@ -3781,7 +3781,7 @@
         <v>1.4450207081516659</v>
       </c>
       <c r="C27" s="0">
-        <v>0.72021269552393785</v>
+        <v>0.71453608302297134</v>
       </c>
     </row>
     <row r="28">
@@ -3792,7 +3792,7 @@
         <v>1.4529318416461383</v>
       </c>
       <c r="C28" s="0">
-        <v>0.72415568315488443</v>
+        <v>0.71844799259459446</v>
       </c>
     </row>
     <row r="29">
@@ -3803,7 +3803,7 @@
         <v>1.4643058380160126</v>
       </c>
       <c r="C29" s="0">
-        <v>0.72982459609032924</v>
+        <v>0.72407222397660898</v>
       </c>
     </row>
     <row r="30">
@@ -3814,7 +3814,7 @@
         <v>1.474049151810628</v>
       </c>
       <c r="C30" s="0">
-        <v>0.73468076060878196</v>
+        <v>0.72889011290733108</v>
       </c>
     </row>
     <row r="31">
@@ -3825,7 +3825,7 @@
         <v>1.4791447358590264</v>
       </c>
       <c r="C31" s="0">
-        <v>0.73722045038766404</v>
+        <v>0.73140978521798894</v>
       </c>
     </row>
     <row r="32">
@@ -3836,7 +3836,7 @@
         <v>1.4827199143060805</v>
       </c>
       <c r="C32" s="0">
-        <v>0.73900235489035149</v>
+        <v>0.73317764500661009</v>
       </c>
     </row>
     <row r="33">
@@ -3847,7 +3847,7 @@
         <v>1.4867149836946894</v>
       </c>
       <c r="C33" s="0">
-        <v>0.74099353721524386</v>
+        <v>0.73515313311985164</v>
       </c>
     </row>
     <row r="34">
@@ -3858,7 +3858,7 @@
         <v>1.4931734883575623</v>
       </c>
       <c r="C34" s="0">
-        <v>0.74421252018625705</v>
+        <v>0.73834674453175853</v>
       </c>
     </row>
     <row r="35">
@@ -3869,7 +3869,7 @@
         <v>1.509833339997235</v>
       </c>
       <c r="C35" s="0">
-        <v>0.75251595597008403</v>
+        <v>0.74658473383336654</v>
       </c>
     </row>
     <row r="36">
@@ -3880,7 +3880,7 @@
         <v>1.5248789902532451</v>
       </c>
       <c r="C36" s="0">
-        <v>0.76001485772675992</v>
+        <v>0.75402453032888828</v>
       </c>
     </row>
     <row r="37">
@@ -3891,7 +3891,7 @@
         <v>1.5329642254314313</v>
       </c>
       <c r="C37" s="0">
-        <v>0.76404461936877455</v>
+        <v>0.75802252997135033</v>
       </c>
     </row>
     <row r="38">
@@ -3902,7 +3902,7 @@
         <v>1.5395805702127974</v>
       </c>
       <c r="C38" s="0">
-        <v>0.76734227142498523</v>
+        <v>0.76129419041008128</v>
       </c>
     </row>
     <row r="39">
@@ -3913,7 +3913,7 @@
         <v>1.5451029243134944</v>
       </c>
       <c r="C39" s="0">
-        <v>0.77009466764329826</v>
+        <v>0.76402489263871942</v>
       </c>
     </row>
     <row r="40">
@@ -3924,7 +3924,7 @@
         <v>1.5499061874496738</v>
       </c>
       <c r="C40" s="0">
-        <v>0.77248866177162012</v>
+        <v>0.76640001765090293</v>
       </c>
     </row>
     <row r="41">
@@ -3935,7 +3935,7 @@
         <v>1.5543652593374868</v>
       </c>
       <c r="C41" s="0">
-        <v>0.7747111075578571</v>
+        <v>0.76860494644027044</v>
       </c>
     </row>
     <row r="42">
@@ -3946,7 +3946,7 @@
         <v>1.5588473185845522</v>
       </c>
       <c r="C42" s="0">
-        <v>0.77694501047261599</v>
+        <v>0.77082124205472669</v>
       </c>
     </row>
     <row r="43">
@@ -3957,7 +3957,7 @@
         <v>1.5631373236617419</v>
       </c>
       <c r="C43" s="0">
-        <v>0.77908319167861839</v>
+        <v>0.77294257042511705</v>
       </c>
     </row>
     <row r="44">
@@ -3968,7 +3968,7 @@
         <v>1.567052100027293</v>
       </c>
       <c r="C44" s="0">
-        <v>0.78103435516209074</v>
+        <v>0.77487835511966985</v>
       </c>
     </row>
     <row r="45">
@@ -3979,7 +3979,7 @@
         <v>1.570699917277663</v>
       </c>
       <c r="C45" s="0">
-        <v>0.78285246356693716</v>
+        <v>0.77668213345651937</v>
       </c>
     </row>
     <row r="46">
@@ -3990,7 +3990,7 @@
         <v>1.574189045009309</v>
       </c>
       <c r="C46" s="0">
-        <v>0.78459147953706154</v>
+        <v>0.77840744275380014</v>
       </c>
     </row>
     <row r="47">
@@ -4001,7 +4001,7 @@
         <v>1.5776277528186882</v>
       </c>
       <c r="C47" s="0">
-        <v>0.78630536571636755</v>
+        <v>0.78010782032964621</v>
       </c>
     </row>
     <row r="48">
@@ -4012,7 +4012,7 @@
         <v>1.5811243103022576</v>
       </c>
       <c r="C48" s="0">
-        <v>0.7880480847487592</v>
+        <v>0.78183680350219187</v>
       </c>
     </row>
     <row r="49">
@@ -4023,7 +4023,7 @@
         <v>1.5847869870564746</v>
       </c>
       <c r="C49" s="0">
-        <v>0.78987359927814038</v>
+        <v>0.78364792958957163</v>
       </c>
     </row>
     <row r="50">
@@ -4034,7 +4034,7 @@
         <v>1.5887237996240766</v>
       </c>
       <c r="C50" s="0">
-        <v>0.79183574582392369</v>
+        <v>0.78559461077952364</v>
       </c>
     </row>
     <row r="51">
@@ -4045,7 +4045,7 @@
         <v>1.592978308038639</v>
       </c>
       <c r="C51" s="0">
-        <v>0.79395623514016378</v>
+        <v>0.78769838670507297</v>
       </c>
     </row>
     <row r="52">
@@ -4056,7 +4056,7 @@
         <v>1.5974464971735054</v>
       </c>
       <c r="C52" s="0">
-        <v>0.79618322505302741</v>
+        <v>0.78990782380491709</v>
       </c>
     </row>
     <row r="53">
@@ -4067,7 +4067,7 @@
         <v>1.6020039513511992</v>
       </c>
       <c r="C53" s="0">
-        <v>0.798454705551215</v>
+        <v>0.79216140082171382</v>
       </c>
     </row>
     <row r="54">
@@ -4078,7 +4078,7 @@
         <v>1.6065262548942443</v>
       </c>
       <c r="C54" s="0">
-        <v>0.80070866662342688</v>
+        <v>0.79439759649812147</v>
       </c>
     </row>
     <row r="55">
@@ -4089,7 +4089,7 @@
         <v>1.6108889921251641</v>
       </c>
       <c r="C55" s="0">
-        <v>0.80288309825836346</v>
+        <v>0.7965548895767981</v>
       </c>
     </row>
     <row r="56">
@@ -4100,7 +4100,7 @@
         <v>1.614971500463384</v>
       </c>
       <c r="C56" s="0">
-        <v>0.8049178610255554</v>
+        <v>0.79857361463758392</v>
       </c>
     </row>
     <row r="57">
@@ -4111,7 +4111,7 @@
         <v>1.6188339488628898</v>
       </c>
       <c r="C57" s="0">
-        <v>0.80684294373020971</v>
+        <v>0.80048352411825252</v>
       </c>
     </row>
     <row r="58">
@@ -4122,7 +4122,7 @@
         <v>1.6225621330925475</v>
       </c>
       <c r="C58" s="0">
-        <v>0.80870110783699689</v>
+        <v>0.80232704244378228</v>
       </c>
     </row>
     <row r="59">
@@ -4133,7 +4133,7 @@
         <v>1.6261806898596503</v>
       </c>
       <c r="C59" s="0">
-        <v>0.81050463252590943</v>
+        <v>0.80411635201144172</v>
       </c>
     </row>
     <row r="60">
@@ -4144,7 +4144,7 @@
         <v>1.6297142558714908</v>
       </c>
       <c r="C60" s="0">
-        <v>0.81226579697693979</v>
+        <v>0.80586363521849913</v>
       </c>
     </row>
     <row r="61">
@@ -4155,7 +4155,7 @@
         <v>1.6331874678353617</v>
       </c>
       <c r="C61" s="0">
-        <v>0.81399688037008033</v>
+        <v>0.80758107446222271</v>
       </c>
     </row>
     <row r="62">
@@ -4166,7 +4166,7 @@
         <v>1.636627982686762</v>
       </c>
       <c r="C62" s="0">
-        <v>0.81571166719710553</v>
+        <v>0.80928234558701262</v>
       </c>
     </row>
     <row r="63">
@@ -4177,7 +4177,7 @@
         <v>1.6401300810629214</v>
       </c>
       <c r="C63" s="0">
-        <v>0.81745714786548296</v>
+        <v>0.81101406862872794</v>
       </c>
     </row>
     <row r="64">
@@ -4188,7 +4188,7 @@
         <v>1.6436542335389974</v>
       </c>
       <c r="C64" s="0">
-        <v>0.81921362051664559</v>
+        <v>0.81275669701600695</v>
       </c>
     </row>
     <row r="65">
@@ -4199,7 +4199,7 @@
         <v>1.6470989757883827</v>
       </c>
       <c r="C65" s="0">
-        <v>0.82093051432087927</v>
+        <v>0.81446005851111514</v>
       </c>
     </row>
     <row r="66">
@@ -4210,7 +4210,7 @@
         <v>1.6503628434844706</v>
       </c>
       <c r="C66" s="0">
-        <v>0.82255725844847016</v>
+        <v>0.81607398087631844</v>
       </c>
     </row>
     <row r="67">
@@ -4221,7 +4221,7 @@
         <v>1.6533443723006538</v>
       </c>
       <c r="C67" s="0">
-        <v>0.82404328206970412</v>
+        <v>0.81754829187388234</v>
       </c>
     </row>
     <row r="68">
@@ -4232,7 +4232,7 @@
         <v>1.655942381895193</v>
       </c>
       <c r="C68" s="0">
-        <v>0.82533815589575021</v>
+        <v>0.81883295969135106</v>
       </c>
     </row>
     <row r="69">
@@ -4243,7 +4243,7 @@
         <v>1.6581065539638267</v>
       </c>
       <c r="C69" s="0">
-        <v>0.82641680078321478</v>
+        <v>0.8199031028555186</v>
       </c>
     </row>
     <row r="70">
@@ -4254,7 +4254,7 @@
         <v>1.6598957259701834</v>
       </c>
       <c r="C70" s="0">
-        <v>0.82730854190926584</v>
+        <v>0.82078781540673995</v>
       </c>
     </row>
     <row r="71">
@@ -4265,7 +4265,7 @@
         <v>1.6613828537146031</v>
       </c>
       <c r="C71" s="0">
-        <v>0.82804974117053243</v>
+        <v>0.82152317264242392</v>
       </c>
     </row>
     <row r="72">
@@ -4276,7 +4276,7 @@
         <v>1.6626408929974259</v>
       </c>
       <c r="C72" s="0">
-        <v>0.82867676046364391</v>
+        <v>0.8221452498599795</v>
       </c>
     </row>
     <row r="73">
@@ -4287,7 +4287,7 @@
         <v>1.6637427996189922</v>
       </c>
       <c r="C73" s="0">
-        <v>0.82922596168522988</v>
+        <v>0.82269012235681604</v>
       </c>
     </row>
     <row r="74">
@@ -4298,7 +4298,7 @@
         <v>1.6647615293796418</v>
       </c>
       <c r="C74" s="0">
-        <v>0.8297337067319196</v>
+        <v>0.82319386543034234</v>
       </c>
     </row>
     <row r="75">
@@ -4309,7 +4309,7 @@
         <v>1.6657700380797149</v>
       </c>
       <c r="C75" s="0">
-        <v>0.83023635750034208</v>
+        <v>0.82369255437796751</v>
       </c>
     </row>
     <row r="76">
@@ -4320,7 +4320,7 @@
         <v>1.6668412815195519</v>
       </c>
       <c r="C76" s="0">
-        <v>0.83077027588712715</v>
+        <v>0.8242222644971009</v>
       </c>
     </row>
     <row r="77">
@@ -4331,7 +4331,7 @@
         <v>1.6680482154994924</v>
       </c>
       <c r="C77" s="0">
-        <v>0.83137182378890384</v>
+        <v>0.82481907108515118</v>
       </c>
     </row>
     <row r="78">
@@ -4342,7 +4342,7 @@
         <v>1.6694637958198768</v>
       </c>
       <c r="C78" s="0">
-        <v>0.8320773631023014</v>
+        <v>0.82551904943952759</v>
       </c>
     </row>
     <row r="79">
@@ -4353,7 +4353,7 @@
         <v>1.6711609782810453</v>
       </c>
       <c r="C79" s="0">
-        <v>0.83292325572394943</v>
+        <v>0.82635827485763935</v>
       </c>
     </row>
     <row r="80">
@@ -4364,7 +4364,7 @@
         <v>1.6732127186833377</v>
       </c>
       <c r="C80" s="0">
-        <v>0.83394586355047706</v>
+        <v>0.82737282263689516</v>
       </c>
     </row>
     <row r="81">
@@ -4375,7 +4375,7 @@
         <v>1.6756919728270945</v>
       </c>
       <c r="C81" s="0">
-        <v>0.83518154847851378</v>
+        <v>0.82859876807470445</v>
       </c>
     </row>
     <row r="82">
@@ -4386,7 +4386,7 @@
         <v>1.6786716965126554</v>
       </c>
       <c r="C82" s="0">
-        <v>0.83666667240468873</v>
+        <v>0.83007218646847591</v>
       </c>
     </row>
     <row r="83">
@@ -4397,7 +4397,7 @@
         <v>1.6822248455403608</v>
       </c>
       <c r="C83" s="0">
-        <v>0.83843759722563149</v>
+        <v>0.831829153115619</v>
       </c>
     </row>
     <row r="84">
@@ -4408,7 +4408,7 @@
         <v>1.687953584151594</v>
       </c>
       <c r="C84" s="0">
-        <v>0.84129285753703964</v>
+        <v>0.83466190867741918</v>
       </c>
     </row>
     <row r="85">
@@ -4419,7 +4419,7 @@
         <v>1.712304110600176</v>
       </c>
       <c r="C85" s="0">
-        <v>0.8534294021498795</v>
+        <v>0.84670279479757216</v>
       </c>
     </row>
     <row r="86">
@@ -4430,7 +4430,7 @@
         <v>1.7265298847914845</v>
       </c>
       <c r="C86" s="0">
-        <v>0.86051966952005599</v>
+        <v>0.85373717770384117</v>
       </c>
     </row>
     <row r="87">
@@ -4441,7 +4441,7 @@
         <v>1.7313470261748305</v>
       </c>
       <c r="C87" s="0">
-        <v>0.8629205807048218</v>
+        <v>0.8561191652532284</v>
       </c>
     </row>
     <row r="88">
@@ -4452,7 +4452,7 @@
         <v>1.7353945125776127</v>
       </c>
       <c r="C88" s="0">
-        <v>0.86493788819100514</v>
+        <v>0.85812057261301078</v>
       </c>
     </row>
     <row r="89">
@@ -4463,7 +4463,7 @@
         <v>1.7387730393685694</v>
       </c>
       <c r="C89" s="0">
-        <v>0.86662177955206887</v>
+        <v>0.85979119178544205</v>
       </c>
     </row>
     <row r="90">
@@ -4474,7 +4474,7 @@
         <v>1.7415833019164395</v>
       </c>
       <c r="C90" s="0">
-        <v>0.86802244236147619</v>
+        <v>0.86118081477277608</v>
       </c>
     </row>
     <row r="91">
@@ -4485,7 +4485,7 @@
         <v>1.7439259955899609</v>
       </c>
       <c r="C91" s="0">
-        <v>0.86919006419268985</v>
+        <v>0.86233923357726627</v>
       </c>
     </row>
     <row r="92">
@@ -4496,7 +4496,7 @@
         <v>1.7459018157578723</v>
       </c>
       <c r="C92" s="0">
-        <v>0.87017483261917294</v>
+        <v>0.8633162402011666</v>
       </c>
     </row>
     <row r="93">
@@ -4507,7 +4507,7 @@
         <v>1.7476114577889119</v>
       </c>
       <c r="C93" s="0">
-        <v>0.87102693521438834</v>
+        <v>0.86416162664673046</v>
       </c>
     </row>
     <row r="94">
@@ -4518,7 +4518,7 @@
         <v>1.7491556170518183</v>
       </c>
       <c r="C94" s="0">
-        <v>0.87179655955179913</v>
+        <v>0.86492518491621162</v>
       </c>
     </row>
     <row r="95">
@@ -4529,7 +4529,7 @@
         <v>1.7506349889153299</v>
       </c>
       <c r="C95" s="0">
-        <v>0.87253389320486829</v>
+        <v>0.86565670701186381</v>
       </c>
     </row>
     <row r="96">
@@ -4540,7 +4540,7 @@
         <v>1.7521502687481851</v>
       </c>
       <c r="C96" s="0">
-        <v>0.87328912374705869</v>
+        <v>0.86640598493594079</v>
       </c>
     </row>
     <row r="97">
@@ -4551,7 +4551,7 @@
         <v>1.7538021519191223</v>
       </c>
       <c r="C97" s="0">
-        <v>0.8741124387518332</v>
+        <v>0.86722281069069607</v>
       </c>
     </row>
     <row r="98">
@@ -4562,7 +4562,7 @@
         <v>1.7556913337968798</v>
       </c>
       <c r="C98" s="0">
-        <v>0.87505402579265501</v>
+        <v>0.8681569762783834</v>
       </c>
     </row>
     <row r="99">
@@ -4573,7 +4573,7 @@
         <v>1.7579185097501961</v>
       </c>
       <c r="C99" s="0">
-        <v>0.876164072442987</v>
+        <v>0.86925827370125641</v>
       </c>
     </row>
     <row r="100">
@@ -4584,7 +4584,7 @@
         <v>1.7605655683309591</v>
       </c>
       <c r="C100" s="0">
-        <v>0.87748339277168985</v>
+        <v>0.87056719533757676</v>
       </c>
     </row>
     <row r="101">
@@ -4595,7 +4595,7 @@
         <v>1.763440965390344</v>
       </c>
       <c r="C101" s="0">
-        <v>0.87891651926957237</v>
+        <v>0.87198902613927975</v>
       </c>
     </row>
     <row r="102">
@@ -4606,7 +4606,7 @@
         <v>1.7664454494121249</v>
       </c>
       <c r="C102" s="0">
-        <v>0.88041398399362691</v>
+        <v>0.87347468806254336</v>
       </c>
     </row>
     <row r="103">
@@ -4617,7 +4617,7 @@
         <v>1.7695501069065942</v>
       </c>
       <c r="C103" s="0">
-        <v>0.88196137617296144</v>
+        <v>0.87500988392009171</v>
       </c>
     </row>
     <row r="104">
@@ -4628,7 +4628,7 @@
         <v>1.7727260243840448</v>
       </c>
       <c r="C104" s="0">
-        <v>0.88354428503668425</v>
+        <v>0.87658031652464896</v>
       </c>
     </row>
     <row r="105">
@@ -4639,7 +4639,7 @@
         <v>1.7759442883547691</v>
       </c>
       <c r="C105" s="0">
-        <v>0.88514829981390342</v>
+        <v>0.87817168868893902</v>
       </c>
     </row>
     <row r="106">
@@ -4650,7 +4650,7 @@
         <v>1.7791759853290601</v>
       </c>
       <c r="C106" s="0">
-        <v>0.88675900973372712</v>
+        <v>0.87976970322568626</v>
       </c>
     </row>
     <row r="107">
@@ -4661,7 +4661,7 @@
         <v>1.7823922018172103</v>
       </c>
       <c r="C107" s="0">
-        <v>0.88836200402526366</v>
+        <v>0.88136006294761449</v>
       </c>
     </row>
     <row r="108">
@@ -4672,7 +4672,7 @@
         <v>1.7855640243295121</v>
       </c>
       <c r="C108" s="0">
-        <v>0.889942871917621</v>
+        <v>0.88292847066744795</v>
       </c>
     </row>
     <row r="109">
@@ -4683,7 +4683,7 @@
         <v>1.7886625393762585</v>
       </c>
       <c r="C109" s="0">
-        <v>0.89148720263990744</v>
+        <v>0.88446062919791069</v>
       </c>
     </row>
     <row r="110">
@@ -4694,7 +4694,7 @@
         <v>1.7916588334677419</v>
       </c>
       <c r="C110" s="0">
-        <v>0.89298058542123104</v>
+        <v>0.88594224135172683</v>
       </c>
     </row>
     <row r="111">
@@ -4705,7 +4705,7 @@
         <v>1.7945239931142551</v>
       </c>
       <c r="C111" s="0">
-        <v>0.8944086094907</v>
+        <v>0.88735900994162042</v>
       </c>
     </row>
     <row r="112">
@@ -4716,7 +4716,7 @@
         <v>1.7972360437806132</v>
       </c>
       <c r="C112" s="0">
-        <v>0.89576032252138293</v>
+        <v>0.88870006896531983</v>
       </c>
     </row>
     <row r="113">
@@ -4727,7 +4727,7 @@
         <v>1.7998533110661301</v>
       </c>
       <c r="C113" s="0">
-        <v>0.89706479457218125</v>
+        <v>0.88999425935571874</v>
       </c>
     </row>
     <row r="114">
@@ -4738,7 +4738,7 @@
         <v>1.8024017013484004</v>
       </c>
       <c r="C114" s="0">
-        <v>0.8983349376393962</v>
+        <v>0.89125439133862738</v>
       </c>
     </row>
     <row r="115">
@@ -4749,7 +4749,7 @@
         <v>1.8048887016228576</v>
       </c>
       <c r="C115" s="0">
-        <v>0.89957448331602996</v>
+        <v>0.89248416709517053</v>
       </c>
     </row>
     <row r="116">
@@ -4760,7 +4760,7 @@
         <v>1.8073217988849353</v>
       </c>
       <c r="C116" s="0">
-        <v>0.90078716319508467</v>
+        <v>0.89368728880647297</v>
       </c>
     </row>
     <row r="117">
@@ -4771,7 +4771,7 @@
         <v>1.8097084801300671</v>
       </c>
       <c r="C117" s="0">
-        <v>0.9019767088695626</v>
+        <v>0.89486745865365969</v>
       </c>
     </row>
     <row r="118">
@@ -4782,7 +4782,7 @@
         <v>1.8120562323536868</v>
       </c>
       <c r="C118" s="0">
-        <v>0.90314685193246602</v>
+        <v>0.89602837881785546</v>
       </c>
     </row>
     <row r="119">
@@ -4793,7 +4793,7 @@
         <v>1.814372542551228</v>
       </c>
       <c r="C119" s="0">
-        <v>0.90430132397679719</v>
+        <v>0.89717375148018508</v>
       </c>
     </row>
     <row r="120">
@@ -4804,7 +4804,7 @@
         <v>1.8166648977181241</v>
       </c>
       <c r="C120" s="0">
-        <v>0.90544385659555826</v>
+        <v>0.89830727882177352</v>
       </c>
     </row>
     <row r="121">
@@ -4815,7 +4815,7 @@
         <v>1.8189407848498091</v>
       </c>
       <c r="C121" s="0">
-        <v>0.90657818138175161</v>
+        <v>0.8994326630237458</v>
       </c>
     </row>
     <row r="122">
@@ -4826,7 +4826,7 @@
         <v>1.8212076909417161</v>
       </c>
       <c r="C122" s="0">
-        <v>0.90770802992837918</v>
+        <v>0.90055360626722636</v>
       </c>
     </row>
     <row r="123">
@@ -4837,7 +4837,7 @@
         <v>1.8234731029892792</v>
       </c>
       <c r="C123" s="0">
-        <v>0.90883713382844356</v>
+        <v>0.90167381073334041</v>
       </c>
     </row>
     <row r="124">
@@ -4848,7 +4848,7 @@
         <v>1.8257439720725368</v>
       </c>
       <c r="C124" s="0">
-        <v>0.90996895756938279</v>
+        <v>0.90279671360293623</v>
       </c>
     </row>
     <row r="125">
@@ -4859,7 +4859,7 @@
         <v>1.8280189886946592</v>
       </c>
       <c r="C125" s="0">
-        <v>0.9111028484849506</v>
+        <v>0.90392166735398849</v>
       </c>
     </row>
     <row r="126">
@@ -4870,7 +4870,7 @@
         <v>1.8302931112465</v>
       </c>
       <c r="C126" s="0">
-        <v>0.91223629378699611</v>
+        <v>0.90504617900378004</v>
       </c>
     </row>
     <row r="127">
@@ -4881,7 +4881,7 @@
         <v>1.8325617304425572</v>
       </c>
       <c r="C127" s="0">
-        <v>0.91336699616177364</v>
+        <v>0.90616796934566024</v>
       </c>
     </row>
     <row r="128">
@@ -4892,7 +4892,7 @@
         <v>1.8348202369973285</v>
       </c>
       <c r="C128" s="0">
-        <v>0.91449265829553705</v>
+        <v>0.90728475917297846</v>
       </c>
     </row>
     <row r="129">
@@ -4903,7 +4903,7 @@
         <v>1.8370640216253116</v>
       </c>
       <c r="C129" s="0">
-        <v>0.91561098287454046</v>
+        <v>0.90839426927908407</v>
       </c>
     </row>
     <row r="130">
@@ -4914,7 +4914,7 @@
         <v>1.8392884750410048</v>
       </c>
       <c r="C130" s="0">
-        <v>0.91671967258503817</v>
+        <v>0.90949422045732675</v>
       </c>
     </row>
     <row r="131">
@@ -4925,7 +4925,7 @@
         <v>1.8414889879589054</v>
       </c>
       <c r="C131" s="0">
-        <v>0.91781643011328395</v>
+        <v>0.91058233350105566</v>
       </c>
     </row>
     <row r="132">
@@ -4936,7 +4936,7 @@
         <v>1.8436609510935114</v>
       </c>
       <c r="C132" s="0">
-        <v>0.91889895814553202</v>
+        <v>0.91165632920362016</v>
       </c>
     </row>
     <row r="133">
@@ -4947,7 +4947,7 @@
         <v>1.8457997551593206</v>
       </c>
       <c r="C133" s="0">
-        <v>0.91996495936803657</v>
+        <v>0.91271392835836984</v>
       </c>
     </row>
     <row r="134">
@@ -4958,7 +4958,7 @@
         <v>1.8479007908708309</v>
       </c>
       <c r="C134" s="0">
-        <v>0.9210121364670516</v>
+        <v>0.91375285175865395</v>
       </c>
     </row>
     <row r="135">
@@ -4969,7 +4969,7 @@
         <v>1.8499594489425402</v>
       </c>
       <c r="C135" s="0">
-        <v>0.9220381921288312</v>
+        <v>0.91477082019782208</v>
       </c>
     </row>
     <row r="136">
@@ -4980,7 +4980,7 @@
         <v>1.8519711200889462</v>
       </c>
       <c r="C136" s="0">
-        <v>0.92304082903962958</v>
+        <v>0.91576555446922359</v>
       </c>
     </row>
     <row r="137">
@@ -4991,7 +4991,7 @@
         <v>1.8539311950245467</v>
       </c>
       <c r="C137" s="0">
-        <v>0.92401774988570062</v>
+        <v>0.91673477536620784</v>
       </c>
     </row>
     <row r="138">
@@ -5002,7 +5002,7 @@
         <v>1.8558295795140607</v>
       </c>
       <c r="C138" s="0">
-        <v>0.92496392359976631</v>
+        <v>0.91767349147564259</v>
       </c>
     </row>
     <row r="139">
@@ -5013,7 +5013,7 @@
         <v>1.8576271996324851</v>
       </c>
       <c r="C139" s="0">
-        <v>0.9258598753489109</v>
+        <v>0.91856238146243407</v>
       </c>
     </row>
     <row r="140">
@@ -5024,7 +5024,7 @@
         <v>1.8593263560315336</v>
       </c>
       <c r="C140" s="0">
-        <v>0.92670675180083439</v>
+        <v>0.91940258295641297</v>
       </c>
     </row>
     <row r="141">
@@ -5035,7 +5035,7 @@
         <v>1.8609381340865101</v>
       </c>
       <c r="C141" s="0">
-        <v>0.92751007801686192</v>
+        <v>0.92019957747116865</v>
       </c>
     </row>
     <row r="142">
@@ -5046,7 +5046,7 @@
         <v>1.8624736191727191</v>
       </c>
       <c r="C142" s="0">
-        <v>0.92827537905831892</v>
+        <v>0.9209588465202907</v>
       </c>
     </row>
     <row r="143">
@@ -5057,7 +5057,7 @@
         <v>1.8639438966654647</v>
       </c>
       <c r="C143" s="0">
-        <v>0.9290081799865304</v>
+        <v>0.92168587161736837</v>
       </c>
     </row>
     <row r="144">
@@ -5068,7 +5068,7 @@
         <v>1.8653600519400513</v>
       </c>
       <c r="C144" s="0">
-        <v>0.92971400586282194</v>
+        <v>0.92238613427599137</v>
       </c>
     </row>
     <row r="145">
@@ -5079,7 +5079,7 @@
         <v>1.8667331703717829</v>
       </c>
       <c r="C145" s="0">
-        <v>0.93039838174851841</v>
+        <v>0.92306511600974872</v>
       </c>
     </row>
     <row r="146">
@@ -5090,7 +5090,7 @@
         <v>1.8680743373359638</v>
       </c>
       <c r="C146" s="0">
-        <v>0.93106683270494517</v>
+        <v>0.92372829833223002</v>
       </c>
     </row>
     <row r="147">
@@ -5101,7 +5101,7 @@
         <v>1.8693946382078985</v>
       </c>
       <c r="C147" s="0">
-        <v>0.93172488379342744</v>
+        <v>0.92438116275702487</v>
       </c>
     </row>
     <row r="148">
@@ -5112,7 +5112,7 @@
         <v>1.8707051583628911</v>
       </c>
       <c r="C148" s="0">
-        <v>0.93237806007529045</v>
+        <v>0.9250291907977225</v>
       </c>
     </row>
     <row r="149">
@@ -5123,7 +5123,7 @@
         <v>1.8720169831762457</v>
       </c>
       <c r="C149" s="0">
-        <v>0.93303188661185954</v>
+        <v>0.9256778639679123</v>
       </c>
     </row>
     <row r="150">
@@ -5134,7 +5134,7 @@
         <v>1.8733411980232664</v>
       </c>
       <c r="C150" s="0">
-        <v>0.93369188846445961</v>
+        <v>0.92633266378118373</v>
       </c>
     </row>
     <row r="151">
@@ -5145,7 +5145,7 @@
         <v>1.8746888882792578</v>
       </c>
       <c r="C151" s="0">
-        <v>0.93436359069441621</v>
+        <v>0.92699907175112639</v>
       </c>
     </row>
     <row r="152">
@@ -5156,7 +5156,7 @@
         <v>1.8760711393195242</v>
       </c>
       <c r="C152" s="0">
-        <v>0.93505251836305447</v>
+        <v>0.92768256939132954</v>
       </c>
     </row>
     <row r="153">
@@ -5167,7 +5167,7 @@
         <v>1.8774990365193693</v>
       </c>
       <c r="C153" s="0">
-        <v>0.93576419653169951</v>
+        <v>0.92838863821538242</v>
       </c>
     </row>
     <row r="154">
@@ -5178,7 +5178,7 @@
         <v>1.8789836652540979</v>
       </c>
       <c r="C154" s="0">
-        <v>0.93650415026167677</v>
+        <v>0.92912275973687486</v>
       </c>
     </row>
     <row r="155">
@@ -5189,7 +5189,7 @@
         <v>1.880536110899014</v>
       </c>
       <c r="C155" s="0">
-        <v>0.93727790461431137</v>
+        <v>0.92989041546939599</v>
       </c>
     </row>
     <row r="156">
@@ -5200,7 +5200,7 @@
         <v>1.8821674588294217</v>
       </c>
       <c r="C156" s="0">
-        <v>0.93809098465092844</v>
+        <v>0.9306970869265353</v>
       </c>
     </row>
     <row r="157">
@@ -5211,7 +5211,7 @@
         <v>1.8838887944206255</v>
       </c>
       <c r="C157" s="0">
-        <v>0.93894891543285319</v>
+        <v>0.93154825562188226</v>
       </c>
     </row>
     <row r="158">
@@ -5222,7 +5222,7 @@
         <v>1.8857112030479295</v>
       </c>
       <c r="C158" s="0">
-        <v>0.93985722202141109</v>
+        <v>0.93244940306902624</v>
       </c>
     </row>
     <row r="159">
@@ -5233,7 +5233,7 @@
         <v>1.887645770086638</v>
       </c>
       <c r="C159" s="0">
-        <v>0.94082142947792724</v>
+        <v>0.93340601078155672</v>
       </c>
     </row>
     <row r="160">
@@ -5244,7 +5244,7 @@
         <v>1.8897035809120553</v>
       </c>
       <c r="C160" s="0">
-        <v>0.94184706286372677</v>
+        <v>0.93442356027306306</v>
       </c>
     </row>
     <row r="161">
@@ -5255,7 +5255,7 @@
         <v>1.8918957208994853</v>
       </c>
       <c r="C161" s="0">
-        <v>0.94293964724013501</v>
+        <v>0.93550753305713474</v>
       </c>
     </row>
     <row r="162">
@@ -5266,7 +5266,7 @@
         <v>1.8942332754242326</v>
       </c>
       <c r="C162" s="0">
-        <v>0.94410470766847709</v>
+        <v>0.93666341064736103</v>
       </c>
     </row>
     <row r="163">
@@ -5277,7 +5277,7 @@
         <v>1.8967273298616014</v>
       </c>
       <c r="C163" s="0">
-        <v>0.94534776921007846</v>
+        <v>0.93789667455733161</v>
       </c>
     </row>
     <row r="164">
@@ -5288,7 +5288,7 @@
         <v>1.8995307734704847</v>
       </c>
       <c r="C164" s="0">
-        <v>0.94674503339246219</v>
+        <v>0.93928292570512972</v>
       </c>
     </row>
     <row r="165">
@@ -5299,7 +5299,7 @@
         <v>1.9032997260576563</v>
       </c>
       <c r="C165" s="0">
-        <v>0.94862351685418422</v>
+        <v>0.941146603231372</v>
       </c>
     </row>
     <row r="166">
@@ -5310,7 +5310,7 @@
         <v>1.9079464169084688</v>
       </c>
       <c r="C166" s="0">
-        <v>0.95093947379795063</v>
+        <v>0.94344430613682384</v>
       </c>
     </row>
     <row r="167">
@@ -5321,7 +5321,7 @@
         <v>1.9132728669138197</v>
       </c>
       <c r="C167" s="0">
-        <v>0.95359422946635497</v>
+        <v>0.94607813740427282</v>
       </c>
     </row>
     <row r="168">
@@ -5332,7 +5332,7 @@
         <v>1.9190810969646066</v>
       </c>
       <c r="C168" s="0">
-        <v>0.95648910910199081</v>
+        <v>0.94895020001650632</v>
       </c>
     </row>
     <row r="169">
@@ -5343,7 +5343,7 @@
         <v>1.9251731279517277</v>
       </c>
       <c r="C169" s="0">
-        <v>0.95952543794745215</v>
+        <v>0.95196259695631213</v>
       </c>
     </row>
     <row r="170">
@@ -5354,7 +5354,7 @@
         <v>1.9313509807660802</v>
       </c>
       <c r="C170" s="0">
-        <v>0.96260454124533235</v>
+        <v>0.95501743120647753</v>
       </c>
     </row>
     <row r="171">
@@ -5365,7 +5365,7 @@
         <v>1.9374166762985625</v>
       </c>
       <c r="C171" s="0">
-        <v>0.96562774423822539</v>
+        <v>0.9580168057497902</v>
       </c>
     </row>
     <row r="172">
@@ -5376,7 +5376,7 @@
         <v>1.9431722354400718</v>
       </c>
       <c r="C172" s="0">
-        <v>0.96849637216872475</v>
+        <v>0.96086282356903763</v>
       </c>
     </row>
     <row r="173">
@@ -5387,7 +5387,7 @@
         <v>1.9484196790815058</v>
       </c>
       <c r="C173" s="0">
-        <v>0.97111175027942409</v>
+        <v>0.96345758764700717</v>
       </c>
     </row>
     <row r="174">
@@ -5398,7 +5398,7 @@
         <v>1.9529610281137626</v>
       </c>
       <c r="C174" s="0">
-        <v>0.97337520381291731</v>
+        <v>0.96570320096648654</v>
       </c>
     </row>
     <row r="175">
@@ -5409,7 +5409,7 @@
         <v>1.9565983034277397</v>
       </c>
       <c r="C175" s="0">
-        <v>0.97518805801179786</v>
+        <v>0.96750176651026321</v>
       </c>
     </row>
     <row r="176">
@@ -5420,7 +5420,7 @@
         <v>1.9593190151278543</v>
       </c>
       <c r="C176" s="0">
-        <v>0.97654408778786206</v>
+        <v>0.96884710825538001</v>
       </c>
     </row>
     <row r="177">
@@ -5431,7 +5431,7 @@
         <v>1.9618309522736916</v>
       </c>
       <c r="C177" s="0">
-        <v>0.9777960622492553</v>
+        <v>0.97008921483479527</v>
       </c>
     </row>
     <row r="178">
@@ -5442,7 +5442,7 @@
         <v>1.9642305406402962</v>
       </c>
       <c r="C178" s="0">
-        <v>0.97899204096147097</v>
+        <v>0.97127576701544482</v>
       </c>
     </row>
     <row r="179">
@@ -5453,7 +5453,7 @@
         <v>1.9665225320198834</v>
       </c>
       <c r="C179" s="0">
-        <v>0.98013439226501842</v>
+        <v>0.97240911447091993</v>
       </c>
     </row>
     <row r="180">
@@ -5464,7 +5464,7 @@
         <v>1.968711678204667</v>
       </c>
       <c r="C180" s="0">
-        <v>0.98122548450040625</v>
+        <v>0.9734916068748114</v>
       </c>
     </row>
     <row r="181">
@@ -5475,7 +5475,7 @@
         <v>1.9708027309868619</v>
       </c>
       <c r="C181" s="0">
-        <v>0.98226768600814363</v>
+        <v>0.97452559390071014</v>
       </c>
     </row>
     <row r="182">
@@ -5486,7 +5486,7 @@
         <v>1.9728004421586824</v>
       </c>
       <c r="C182" s="0">
-        <v>0.98326336512873946</v>
+        <v>0.97551342522220708</v>
       </c>
     </row>
     <row r="183">
@@ -5497,7 +5497,7 @@
         <v>1.9747095635123431</v>
       </c>
       <c r="C183" s="0">
-        <v>0.98421489020270247</v>
+        <v>0.97645745051289312</v>
       </c>
     </row>
     <row r="184">
@@ -5508,7 +5508,7 @@
         <v>1.9765348468400585</v>
       </c>
       <c r="C184" s="0">
-        <v>0.98512462957054203</v>
+        <v>0.9773600194463592</v>
       </c>
     </row>
     <row r="185">
@@ -5519,7 +5519,7 @@
         <v>1.978281043934043</v>
       </c>
       <c r="C185" s="0">
-        <v>0.98599495157276662</v>
+        <v>0.97822348169619633</v>
       </c>
     </row>
     <row r="186">
@@ -5530,7 +5530,7 @@
         <v>1.9799529065865114</v>
       </c>
       <c r="C186" s="0">
-        <v>0.98682822454988561</v>
+        <v>0.97905018693599533</v>
       </c>
     </row>
     <row r="187">
@@ -5541,7 +5541,7 @@
         <v>1.9815551865896781</v>
       </c>
       <c r="C187" s="0">
-        <v>0.98762681684240772</v>
+        <v>0.97984248483934733</v>
       </c>
     </row>
     <row r="188">
@@ -5552,7 +5552,7 @@
         <v>1.9830926357357574</v>
       </c>
       <c r="C188" s="0">
-        <v>0.98839309679084186</v>
+        <v>0.98060272507984303</v>
       </c>
     </row>
     <row r="189">
@@ -5563,7 +5563,7 @@
         <v>1.984570005816964</v>
       </c>
       <c r="C189" s="0">
-        <v>0.98912943273569709</v>
+        <v>0.98133325733107346</v>
       </c>
     </row>
     <row r="190">
@@ -5574,7 +5574,7 @@
         <v>1.9859920486255125</v>
       </c>
       <c r="C190" s="0">
-        <v>0.98983819301748233</v>
+        <v>0.98203643126662976</v>
       </c>
     </row>
     <row r="191">
@@ -5585,7 +5585,7 @@
         <v>1.9873635159536172</v>
       </c>
       <c r="C191" s="0">
-        <v>0.9905217459767065</v>
+        <v>0.98271459656010252</v>
       </c>
     </row>
     <row r="192">
@@ -5596,7 +5596,7 @@
         <v>1.9886891595934926</v>
       </c>
       <c r="C192" s="0">
-        <v>0.99118245995387855</v>
+        <v>0.98337010288508275</v>
       </c>
     </row>
     <row r="193">
@@ -5607,7 +5607,7 @@
         <v>1.9899737313373533</v>
       </c>
       <c r="C193" s="0">
-        <v>0.9918227032895075</v>
+        <v>0.9840052999151615</v>
       </c>
     </row>
     <row r="194">
@@ -5618,7 +5618,7 @@
         <v>1.991221982977414</v>
       </c>
       <c r="C194" s="0">
-        <v>0.99244484432410218</v>
+        <v>0.98462253732392979</v>
       </c>
     </row>
     <row r="195">
@@ -5629,7 +5629,7 @@
         <v>1.9924386663058888</v>
       </c>
       <c r="C195" s="0">
-        <v>0.99305125139817152</v>
+        <v>0.98522416478497821</v>
       </c>
     </row>
     <row r="196">
@@ -5640,7 +5640,7 @@
         <v>1.9936285331149926</v>
       </c>
       <c r="C196" s="0">
-        <v>0.99364429285222466</v>
+        <v>0.985812531971898</v>
       </c>
     </row>
     <row r="197">
@@ -5651,7 +5651,7 @@
         <v>1.9947963351969398</v>
       </c>
       <c r="C197" s="0">
-        <v>0.99422633702677043</v>
+        <v>0.98638998855828008</v>
       </c>
     </row>
     <row r="198">
@@ -5662,7 +5662,7 @@
         <v>1.9959468243439447</v>
       </c>
       <c r="C198" s="0">
-        <v>0.99479975226231765</v>
+        <v>0.98695888421771516</v>
       </c>
     </row>
     <row r="199">
@@ -5673,7 +5673,7 @@
         <v>1.997084752348222</v>
       </c>
       <c r="C199" s="0">
-        <v>0.99536690689937546</v>
+        <v>0.98752156862379437</v>
       </c>
     </row>
     <row r="200">
@@ -5684,7 +5684,7 @@
         <v>1.9982164070860269</v>
       </c>
       <c r="C200" s="0">
-        <v>0.99593093487801898</v>
+        <v>0.98808115101532967</v>
       </c>
     </row>
     <row r="201">
@@ -5695,7 +5695,7 @@
         <v>1.9993481975814835</v>
       </c>
       <c r="C201" s="0">
-        <v>0.99649503051962673</v>
+        <v>0.98864080053651926</v>
       </c>
     </row>
     <row r="202">
@@ -5706,7 +5706,7 @@
         <v>2.0004778984477838</v>
       </c>
       <c r="C202" s="0">
-        <v>0.99705808466927592</v>
+        <v>0.98919941677463974</v>
       </c>
     </row>
     <row r="203">
@@ -5717,7 +5717,7 @@
         <v>2.0016027300789405</v>
       </c>
       <c r="C203" s="0">
-        <v>0.997618711943692</v>
+        <v>0.9897556252658074</v>
       </c>
     </row>
     <row r="204">
@@ -5728,7 +5728,7 @@
         <v>2.0027199128689661</v>
       </c>
       <c r="C204" s="0">
-        <v>0.99817552695960032</v>
+        <v>0.99030805154613843</v>
       </c>
     </row>
     <row r="205">
@@ -5739,7 +5739,7 @@
         <v>2.0038266672118725</v>
       </c>
       <c r="C205" s="0">
-        <v>0.99872714433372578</v>
+        <v>0.99085532115174879</v>
       </c>
     </row>
     <row r="206">
@@ -5750,7 +5750,7 @@
         <v>2.004920213501673</v>
       </c>
       <c r="C206" s="0">
-        <v>0.99927217868279394</v>
+        <v>0.99139605961875521</v>
       </c>
     </row>
     <row r="207">
@@ -5761,7 +5761,7 @@
         <v>2.0059977721323796</v>
       </c>
       <c r="C207" s="0">
-        <v>0.99980924462352971</v>
+        <v>0.99192889248327343</v>
       </c>
     </row>
     <row r="208">
@@ -5772,7 +5772,7 @@
         <v>2.0070565634980051</v>
       </c>
       <c r="C208" s="0">
-        <v>1.0003369567726588</v>
+        <v>0.99245244528142007</v>
       </c>
     </row>
     <row r="209">
@@ -5783,7 +5783,7 @@
         <v>2.0080938079925623</v>
       </c>
       <c r="C209" s="0">
-        <v>1.0008539297469063</v>
+        <v>0.99296534354931132</v>
       </c>
     </row>
     <row r="210">
@@ -5794,7 +5794,7 @@
         <v>2.0091067260100628</v>
       </c>
       <c r="C210" s="0">
-        <v>1.0013587781629971</v>
+        <v>0.99346621282306313</v>
       </c>
     </row>
     <row r="211">
@@ -5805,7 +5805,7 @@
         <v>2.0100925379445203</v>
       </c>
       <c r="C211" s="0">
-        <v>1.001850116637657</v>
+        <v>0.99395367863879214</v>
       </c>
     </row>
     <row r="212">
@@ -5816,7 +5816,7 @@
         <v>2.0110484641899466</v>
       </c>
       <c r="C212" s="0">
-        <v>1.002326559787611</v>
+        <v>0.99442636653261451</v>
       </c>
     </row>
     <row r="213">
@@ -5827,7 +5827,7 @@
         <v>2.0119717251403539</v>
       </c>
       <c r="C213" s="0">
-        <v>1.0027867222295841</v>
+        <v>0.994882902040646</v>
       </c>
     </row>
     <row r="214">
@@ -5838,7 +5838,7 @@
         <v>2.0128595411897559</v>
       </c>
       <c r="C214" s="0">
-        <v>1.0032292185803022</v>
+        <v>0.99532191069900355</v>
       </c>
     </row>
     <row r="215">
@@ -5849,7 +5849,7 @@
         <v>2.0137091327321639</v>
       </c>
       <c r="C215" s="0">
-        <v>1.00365266345649</v>
+        <v>0.99574201804380291</v>
       </c>
     </row>
     <row r="216">
@@ -5860,7 +5860,7 @@
         <v>2.0145177201615914</v>
       </c>
       <c r="C216" s="0">
-        <v>1.0040556714748732</v>
+        <v>0.9961418496111607</v>
       </c>
     </row>
     <row r="217">
@@ -5871,7 +5871,7 @@
         <v>2.0152825238720502</v>
       </c>
       <c r="C217" s="0">
-        <v>1.0044368572521765</v>
+        <v>0.99652003093719288</v>
       </c>
     </row>
     <row r="218">
@@ -5882,7 +5882,7 @@
         <v>2.0160007642575533</v>
       </c>
       <c r="C218" s="0">
-        <v>1.0047948354051255</v>
+        <v>0.99687518755801574</v>
       </c>
     </row>
     <row r="219">
@@ -5893,7 +5893,7 @@
         <v>2.0166696617121129</v>
       </c>
       <c r="C219" s="0">
-        <v>1.0051282205504455</v>
+        <v>0.99720594500974558</v>
       </c>
     </row>
     <row r="220">
@@ -5904,7 +5904,7 @@
         <v>2.0172864366297421</v>
       </c>
       <c r="C220" s="0">
-        <v>1.0054356273048619</v>
+        <v>0.99751092882849879</v>
       </c>
     </row>
     <row r="221">
@@ -5915,7 +5915,7 @@
         <v>2.0178483094044526</v>
       </c>
       <c r="C221" s="0">
-        <v>1.0057156702850993</v>
+        <v>0.99778876455039123</v>
       </c>
     </row>
     <row r="222">
@@ -5926,7 +5926,7 @@
         <v>2.0183525004302574</v>
       </c>
       <c r="C222" s="0">
-        <v>1.0059669641078837</v>
+        <v>0.99803807771153952</v>
       </c>
     </row>
     <row r="223">
@@ -5937,7 +5937,7 @@
         <v>2.0187962301011688</v>
       </c>
       <c r="C223" s="0">
-        <v>1.0061881233899399</v>
+        <v>0.99825749384805951</v>
       </c>
     </row>
     <row r="224">
@@ -5948,7 +5948,7 @@
         <v>2.0191767188111998</v>
       </c>
       <c r="C224" s="0">
-        <v>1.0063777627479933</v>
+        <v>0.99844563849606793</v>
       </c>
     </row>
     <row r="225">
@@ -5959,7 +5959,7 @@
         <v>2.0194911869543621</v>
       </c>
       <c r="C225" s="0">
-        <v>1.0065344967987691</v>
+        <v>0.99860113719168042</v>
       </c>
     </row>
     <row r="226">
@@ -5970,7 +5970,7 @@
         <v>2.0197551228170942</v>
       </c>
       <c r="C226" s="0">
-        <v>1.0066660450583</v>
+        <v>0.9987316486068194</v>
       </c>
     </row>
     <row r="227">
@@ -5981,7 +5981,7 @@
         <v>2.0200120263279762</v>
       </c>
       <c r="C227" s="0">
-        <v>1.0067940883237134</v>
+        <v>0.99885868265369837</v>
       </c>
     </row>
     <row r="228">
@@ -5992,7 +5992,7 @@
         <v>2.0202634345092978</v>
       </c>
       <c r="C228" s="0">
-        <v>1.0069193926622084</v>
+        <v>0.99898299936148538</v>
       </c>
     </row>
     <row r="229">
@@ -6003,7 +6003,7 @@
         <v>2.0205088087694367</v>
       </c>
       <c r="C229" s="0">
-        <v>1.0070416896343626</v>
+        <v>0.99910433240655883</v>
       </c>
     </row>
     <row r="230">
@@ -6014,7 +6014,7 @@
         <v>2.0207476105167701</v>
       </c>
       <c r="C230" s="0">
-        <v>1.0071607108007532</v>
+        <v>0.99922241546529711</v>
       </c>
     </row>
     <row r="231">
@@ -6025,7 +6025,7 @@
         <v>2.0209793011596746</v>
       </c>
       <c r="C231" s="0">
-        <v>1.0072761877219576</v>
+        <v>0.99933698221407807</v>
       </c>
     </row>
     <row r="232">
@@ -6036,7 +6036,7 @@
         <v>2.0212033421065279</v>
       </c>
       <c r="C232" s="0">
-        <v>1.0073878519585533</v>
+        <v>0.99944776632928012</v>
       </c>
     </row>
     <row r="233">
@@ -6047,7 +6047,7 @@
         <v>2.021419194765707</v>
       </c>
       <c r="C233" s="0">
-        <v>1.0074954350711181</v>
+        <v>0.99955450148728153</v>
       </c>
     </row>
     <row r="234">
@@ -6058,7 +6058,7 @@
         <v>2.0216263205455891</v>
       </c>
       <c r="C234" s="0">
-        <v>1.007598668620229</v>
+        <v>0.9996569213644606</v>
       </c>
     </row>
     <row r="235">
@@ -6069,7 +6069,7 @@
         <v>2.0218241808545514</v>
       </c>
       <c r="C235" s="0">
-        <v>1.0076972841664638</v>
+        <v>0.99975475963719551</v>
       </c>
     </row>
     <row r="236">
@@ -6080,7 +6080,7 @@
         <v>2.022012237100971</v>
       </c>
       <c r="C236" s="0">
-        <v>1.0077910132703998</v>
+        <v>0.99984774998186432</v>
       </c>
     </row>
     <row r="237">
@@ -6091,7 +6091,7 @@
         <v>2.0221899506932246</v>
       </c>
       <c r="C237" s="0">
-        <v>1.0078795874926141</v>
+        <v>0.99993562607484521</v>
       </c>
     </row>
     <row r="238">
@@ -6102,7 +6102,7 @@
         <v>2.0223567830396902</v>
       </c>
       <c r="C238" s="0">
-        <v>1.0079627383936849</v>
+        <v>1.0000181215925168</v>
       </c>
     </row>
     <row r="239">
@@ -6113,7 +6113,7 @@
         <v>2.0225121955487446</v>
       </c>
       <c r="C239" s="0">
-        <v>1.0080401975341891</v>
+        <v>1.0000949702112569</v>
       </c>
     </row>
     <row r="240">
@@ -6124,7 +6124,7 @@
         <v>2.0226556496287649</v>
       </c>
       <c r="C240" s="0">
-        <v>1.0081116964747041</v>
+        <v>1.0001659056074441</v>
       </c>
     </row>
     <row r="241">
@@ -6135,7 +6135,7 @@
         <v>2.0227866066881282</v>
       </c>
       <c r="C241" s="0">
-        <v>1.0081769667758078</v>
+        <v>1.0002306614574563</v>
       </c>
     </row>
     <row r="242">
@@ -6146,7 +6146,7 @@
         <v>2.0229045281352116</v>
       </c>
       <c r="C242" s="0">
-        <v>1.008235739998077</v>
+        <v>1.0002889714376719</v>
       </c>
     </row>
     <row r="243">
@@ -6157,7 +6157,7 @@
         <v>2.0230088753783924</v>
       </c>
       <c r="C243" s="0">
-        <v>1.0082877477020897</v>
+        <v>1.0003405692244691</v>
       </c>
     </row>
     <row r="244">
@@ -6168,7 +6168,7 @@
         <v>2.023099109826048</v>
       </c>
       <c r="C244" s="0">
-        <v>1.0083327214484232</v>
+        <v>1.0003851884942261</v>
       </c>
     </row>
     <row r="245">
@@ -6179,7 +6179,7 @@
         <v>2.0231746928865553</v>
       </c>
       <c r="C245" s="0">
-        <v>1.0083703927976551</v>
+        <v>1.0004225629233212</v>
       </c>
     </row>
     <row r="246">
@@ -6190,7 +6190,7 @@
         <v>2.0232350859682913</v>
       </c>
       <c r="C246" s="0">
-        <v>1.0084004933103625</v>
+        <v>1.0004524261881325</v>
       </c>
     </row>
     <row r="247">
@@ -6201,7 +6201,7 @@
         <v>2.0232797504796336</v>
       </c>
       <c r="C247" s="0">
-        <v>1.0084227545471229</v>
+        <v>1.0004745119650384</v>
       </c>
     </row>
     <row r="248">
@@ -6212,7 +6212,7 @@
         <v>2.023308147828959</v>
       </c>
       <c r="C248" s="0">
-        <v>1.008436908068514</v>
+        <v>1.0004885539304169</v>
       </c>
     </row>
     <row r="249">
@@ -6223,7 +6223,7 @@
         <v>2.0233197394246449</v>
       </c>
       <c r="C249" s="0">
-        <v>1.0084426854351132</v>
+        <v>1.0004942857606467</v>
       </c>
     </row>
     <row r="250">
@@ -6234,7 +6234,7 @@
         <v>2.0233189578085056</v>
       </c>
       <c r="C250" s="0">
-        <v>1.0084422958698542</v>
+        <v>1.0004938992658847</v>
       </c>
     </row>
     <row r="251">
@@ -6245,7 +6245,7 @@
         <v>2.0233150130833759</v>
       </c>
       <c r="C251" s="0">
-        <v>1.0084403297796087</v>
+        <v>1.0004919486720787</v>
       </c>
     </row>
     <row r="252">
@@ -6256,7 +6256,7 @@
         <v>2.0233082985842636</v>
       </c>
       <c r="C252" s="0">
-        <v>1.0084369832064577</v>
+        <v>1.0004886284761341</v>
       </c>
     </row>
     <row r="253">
@@ -6267,7 +6267,7 @@
         <v>2.0232989935925034</v>
       </c>
       <c r="C253" s="0">
-        <v>1.0084323455060014</v>
+        <v>1.0004840273293634</v>
       </c>
     </row>
     <row r="254">
@@ -6278,7 +6278,7 @@
         <v>2.0232872773894313</v>
       </c>
       <c r="C254" s="0">
-        <v>1.0084265060338413</v>
+        <v>1.00047823388308</v>
       </c>
     </row>
     <row r="255">
@@ -6289,7 +6289,7 @@
         <v>2.0232733292563823</v>
       </c>
       <c r="C255" s="0">
-        <v>1.0084195541455783</v>
+        <v>1.0004713367885967</v>
       </c>
     </row>
     <row r="256">
@@ -6300,7 +6300,7 @@
         <v>2.0232573284746915</v>
       </c>
       <c r="C256" s="0">
-        <v>1.0084115791968133</v>
+        <v>1.0004634246972266</v>
       </c>
     </row>
     <row r="257">
@@ -6311,7 +6311,7 @@
         <v>2.0232394543256951</v>
       </c>
       <c r="C257" s="0">
-        <v>1.0084026705431475</v>
+        <v>1.0004545862602829</v>
       </c>
     </row>
     <row r="258">
@@ -6322,7 +6322,7 @@
         <v>2.023219886090728</v>
       </c>
       <c r="C258" s="0">
-        <v>1.0083929175401816</v>
+        <v>1.0004449101290787</v>
       </c>
     </row>
     <row r="259">
@@ -6333,7 +6333,7 @@
         <v>2.0231988030511259</v>
       </c>
       <c r="C259" s="0">
-        <v>1.008382409543517</v>
+        <v>1.0004344849549267</v>
       </c>
     </row>
     <row r="260">
@@ -6344,7 +6344,7 @@
         <v>2.0231763844882242</v>
       </c>
       <c r="C260" s="0">
-        <v>1.0083712359087544</v>
+        <v>1.0004233993891405</v>
       </c>
     </row>
     <row r="261">
@@ -6355,7 +6355,7 @@
         <v>2.0231528096833582</v>
       </c>
       <c r="C261" s="0">
-        <v>1.0083594859914948</v>
+        <v>1.0004117420830327</v>
       </c>
     </row>
     <row r="262">
@@ -6366,7 +6366,7 @@
         <v>2.0231282579178633</v>
       </c>
       <c r="C262" s="0">
-        <v>1.0083472491473395</v>
+        <v>1.0003996016879166</v>
       </c>
     </row>
     <row r="263">
@@ -6377,7 +6377,7 @@
         <v>2.0231029084730752</v>
       </c>
       <c r="C263" s="0">
-        <v>1.0083346147318892</v>
+        <v>1.0003870668551051</v>
       </c>
     </row>
     <row r="264">
@@ -6388,7 +6388,7 @@
         <v>2.0230769406303288</v>
       </c>
       <c r="C264" s="0">
-        <v>1.0083216721007451</v>
+        <v>1.0003742262359114</v>
       </c>
     </row>
     <row r="265">
@@ -6399,7 +6399,7 @@
         <v>2.0230505336709599</v>
       </c>
       <c r="C265" s="0">
-        <v>1.0083085106095082</v>
+        <v>1.0003611684816482</v>
       </c>
     </row>
     <row r="266">
@@ -6410,7 +6410,7 @@
         <v>2.0230238668763039</v>
       </c>
       <c r="C266" s="0">
-        <v>1.0082952196137793</v>
+        <v>1.0003479822436292</v>
       </c>
     </row>
     <row r="267">
@@ -6421,7 +6421,7 @@
         <v>2.0229971195276963</v>
       </c>
       <c r="C267" s="0">
-        <v>1.0082818884691596</v>
+        <v>1.000334756173167</v>
       </c>
     </row>
     <row r="268">
@@ -6432,7 +6432,7 @@
         <v>2.0229704709064724</v>
       </c>
       <c r="C268" s="0">
-        <v>1.0082686065312501</v>
+        <v>1.0003215789215747</v>
       </c>
     </row>
     <row r="269">
@@ -6443,7 +6443,7 @@
         <v>2.0229441002939677</v>
       </c>
       <c r="C269" s="0">
-        <v>1.0082554631556517</v>
+        <v>1.0003085391401656</v>
       </c>
     </row>
     <row r="270">
@@ -6454,7 +6454,7 @@
         <v>2.0229181869715176</v>
       </c>
       <c r="C270" s="0">
-        <v>1.0082425476979655</v>
+        <v>1.0002957254802525</v>
       </c>
     </row>
     <row r="271">
@@ -6465,7 +6465,7 @@
         <v>2.0228929102204574</v>
       </c>
       <c r="C271" s="0">
-        <v>1.0082299495137925</v>
+        <v>1.0002832265931485</v>
       </c>
     </row>
     <row r="272">
@@ -6476,7 +6476,7 @@
         <v>2.022868449322123</v>
       </c>
       <c r="C272" s="0">
-        <v>1.0082177579587337</v>
+        <v>1.0002711311301669</v>
       </c>
     </row>
     <row r="273">
@@ -6487,7 +6487,7 @@
         <v>2.022844983557849</v>
       </c>
       <c r="C273" s="0">
-        <v>1.0082060623883902</v>
+        <v>1.0002595277426205</v>
       </c>
     </row>
     <row r="274">
@@ -6498,7 +6498,7 @@
         <v>2.0228226922089712</v>
       </c>
       <c r="C274" s="0">
-        <v>1.0081949521583624</v>
+        <v>1.0002485050818222</v>
       </c>
     </row>
     <row r="275">
@@ -6509,7 +6509,7 @@
         <v>2.0228017545568253</v>
       </c>
       <c r="C275" s="0">
-        <v>1.0081845166242522</v>
+        <v>1.0002381517990853</v>
       </c>
     </row>
     <row r="276">
@@ -6520,7 +6520,7 @@
         <v>2.0227816819079423</v>
       </c>
       <c r="C276" s="0">
-        <v>1.008174512216373</v>
+        <v>1.0002282262445048</v>
       </c>
     </row>
     <row r="277">
@@ -6531,7 +6531,7 @@
         <v>2.0227616150819792</v>
       </c>
       <c r="C277" s="0">
-        <v>1.0081645107106949</v>
+        <v>1.0002183035692507</v>
       </c>
     </row>
     <row r="278">
@@ -6542,7 +6542,7 @@
         <v>2.0227415482184852</v>
       </c>
       <c r="C278" s="0">
-        <v>1.0081545091863111</v>
+        <v>1.0002083808754383</v>
       </c>
     </row>
     <row r="279">
@@ -6553,7 +6553,7 @@
         <v>2.0227214813174603</v>
       </c>
       <c r="C279" s="0">
-        <v>1.0081445076432216</v>
+        <v>1.0001984581630676</v>
       </c>
     </row>
     <row r="280">
@@ -6564,7 +6564,7 @@
         <v>2.0227014143789055</v>
       </c>
       <c r="C280" s="0">
-        <v>1.0081345060814266</v>
+        <v>1.0001885354321389</v>
       </c>
     </row>
     <row r="281">
@@ -6575,7 +6575,7 @@
         <v>2.0226813474028198</v>
       </c>
       <c r="C281" s="0">
-        <v>1.0081245045009259</v>
+        <v>1.0001786126826522</v>
       </c>
     </row>
     <row r="282">
@@ -6586,7 +6586,7 @@
         <v>2.0226612803892041</v>
       </c>
       <c r="C282" s="0">
-        <v>1.00811450290172</v>
+        <v>1.0001686899146074</v>
       </c>
     </row>
     <row r="283">
@@ -6597,7 +6597,7 @@
         <v>2.022641213338058</v>
       </c>
       <c r="C283" s="0">
-        <v>1.0081045012838086</v>
+        <v>1.0001587671280043</v>
       </c>
     </row>
     <row r="284">
@@ -6608,7 +6608,7 @@
         <v>2.0226211462493824</v>
       </c>
       <c r="C284" s="0">
-        <v>1.0080944996471919</v>
+        <v>1.0001488443228439</v>
       </c>
     </row>
     <row r="285">
@@ -6619,7 +6619,7 @@
         <v>2.0226010791231772</v>
       </c>
       <c r="C285" s="0">
-        <v>1.0080844979918702</v>
+        <v>1.0001389214991256</v>
       </c>
     </row>
     <row r="286">
@@ -6630,7 +6630,7 @@
         <v>2.0225810119594425</v>
       </c>
       <c r="C286" s="0">
-        <v>1.0080744963178434</v>
+        <v>1.0001289986568498</v>
       </c>
     </row>
     <row r="287">
@@ -6641,7 +6641,7 @@
         <v>2.0225609447581783</v>
       </c>
       <c r="C287" s="0">
-        <v>1.0080644946251116</v>
+        <v>1.0001190757960161</v>
       </c>
     </row>
     <row r="288">
@@ -6652,7 +6652,7 @@
         <v>2.0225408775193849</v>
       </c>
       <c r="C288" s="0">
-        <v>1.0080544929136748</v>
+        <v>1.0001091529166253</v>
       </c>
     </row>
     <row r="289">
@@ -6663,7 +6663,7 @@
         <v>2.0225208102430625</v>
       </c>
       <c r="C289" s="0">
-        <v>1.0080444911835331</v>
+        <v>1.0000992300186768</v>
       </c>
     </row>
     <row r="290">
@@ -6674,7 +6674,7 @@
         <v>2.0225007429292114</v>
       </c>
       <c r="C290" s="0">
-        <v>1.0080344894346869</v>
+        <v>1.000089307102171</v>
       </c>
     </row>
     <row r="291">
@@ -6685,7 +6685,7 @@
         <v>2.0224806755778322</v>
       </c>
       <c r="C291" s="0">
-        <v>1.0080244876671363</v>
+        <v>1.0000793841671085</v>
       </c>
     </row>
     <row r="292">
@@ -6696,7 +6696,7 @@
         <v>2.0224606081889238</v>
       </c>
       <c r="C292" s="0">
-        <v>1.0080144858808806</v>
+        <v>1.0000694612134884</v>
       </c>
     </row>
     <row r="293">
@@ -6707,7 +6707,7 @@
         <v>2.0224405407624877</v>
       </c>
       <c r="C293" s="0">
-        <v>1.0080044840759208</v>
+        <v>1.0000595382413116</v>
       </c>
     </row>
     <row r="294">
@@ -6718,7 +6718,7 @@
         <v>2.0224204732985229</v>
       </c>
       <c r="C294" s="0">
-        <v>1.0079944822522564</v>
+        <v>1.0000496152505773</v>
       </c>
     </row>
     <row r="295">
@@ -6729,7 +6729,7 @@
         <v>2.0224004057970304</v>
       </c>
       <c r="C295" s="0">
-        <v>1.0079844804098876</v>
+        <v>1.0000396922412864</v>
       </c>
     </row>
     <row r="296">
@@ -6740,7 +6740,7 @@
         <v>2.0223803382580106</v>
       </c>
       <c r="C296" s="0">
-        <v>1.0079744785488152</v>
+        <v>1.000029769213439</v>
       </c>
     </row>
     <row r="297">
@@ -6751,7 +6751,7 @@
         <v>2.022360270681463</v>
       </c>
       <c r="C297" s="0">
-        <v>1.0079644766690383</v>
+        <v>1.0000198461670347</v>
       </c>
     </row>
     <row r="298">
@@ -6762,7 +6762,7 @@
         <v>2.0223402030673876</v>
       </c>
       <c r="C298" s="0">
-        <v>1.0079544747705571</v>
+        <v>1.0000099231020738</v>
       </c>
     </row>
     <row r="299">
@@ -6773,7 +6773,7 @@
         <v>2.0223201354157854</v>
       </c>
       <c r="C299" s="0">
-        <v>1.0079444728533724</v>
+        <v>1.0000000000185563</v>
       </c>
     </row>
     <row r="300">
@@ -6784,7 +6784,7 @@
         <v>2.0223000677266563</v>
       </c>
       <c r="C300" s="0">
-        <v>1.0079344709174838</v>
+        <v>0.99999007691648267</v>
       </c>
     </row>
     <row r="301">
@@ -6795,7 +6795,7 @@
         <v>2.0222799999999999</v>
       </c>
       <c r="C301" s="0">
-        <v>1.0079244689628912</v>
+        <v>0.99998015379585237</v>
       </c>
     </row>
   </sheetData>

--- a/TunnelDataProcessing/BoundaryLayerComparison/BoundaryLayerComparison.xlsx
+++ b/TunnelDataProcessing/BoundaryLayerComparison/BoundaryLayerComparison.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Excel_2" sheetId="3" r:id="rId5"/>
     <sheet name="Excel_3" sheetId="4" r:id="rId6"/>
     <sheet name="CSV" sheetId="5" r:id="rId7"/>
+    <sheet name="zone2" sheetId="6" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
@@ -17,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="24" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="15" uniqueCount="3">
   <si>
     <t>Y_over_D</t>
   </si>
@@ -6800,4 +6801,2889 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C261"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14.5546875" customWidth="true"/>
+    <col min="2" max="2" width="8.5546875" customWidth="true"/>
+    <col min="3" max="3" width="12.5546875" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0">
+        <v>0</v>
+      </c>
+      <c r="B2" s="0">
+        <v>0</v>
+      </c>
+      <c r="C2" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0">
+        <v>0.0054439544885404763</v>
+      </c>
+      <c r="B3" s="0">
+        <v>0.91806900000000002</v>
+      </c>
+      <c r="C3" s="0">
+        <v>0.4603788061138524</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0">
+        <v>0.010887908977080953</v>
+      </c>
+      <c r="B4" s="0">
+        <v>1.08047</v>
+      </c>
+      <c r="C4" s="0">
+        <v>0.54181710594937216</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0">
+        <v>0.016331863465621425</v>
+      </c>
+      <c r="B5" s="0">
+        <v>1.1706300000000001</v>
+      </c>
+      <c r="C5" s="0">
+        <v>0.58702912504513172</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0">
+        <v>0.021775817954161905</v>
+      </c>
+      <c r="B6" s="0">
+        <v>1.23393</v>
+      </c>
+      <c r="C6" s="0">
+        <v>0.61877181369599221</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0">
+        <v>0.027219772442702381</v>
+      </c>
+      <c r="B7" s="0">
+        <v>1.2831900000000001</v>
+      </c>
+      <c r="C7" s="0">
+        <v>0.64347394391623536</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0">
+        <v>0.032663726931242851</v>
+      </c>
+      <c r="B8" s="0">
+        <v>1.3238000000000001</v>
+      </c>
+      <c r="C8" s="0">
+        <v>0.66383840815180328</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0">
+        <v>0.038107681419783331</v>
+      </c>
+      <c r="B9" s="0">
+        <v>1.3586100000000001</v>
+      </c>
+      <c r="C9" s="0">
+        <v>0.68129437958839811</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0">
+        <v>0.04355163590832381</v>
+      </c>
+      <c r="B10" s="0">
+        <v>1.3892199999999999</v>
+      </c>
+      <c r="C10" s="0">
+        <v>0.69664420106711589</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0">
+        <v>0.048995590396864283</v>
+      </c>
+      <c r="B11" s="0">
+        <v>1.4166700000000001</v>
+      </c>
+      <c r="C11" s="0">
+        <v>0.71040939543466919</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0">
+        <v>0.054439544885404763</v>
+      </c>
+      <c r="B12" s="0">
+        <v>1.4416599999999999</v>
+      </c>
+      <c r="C12" s="0">
+        <v>0.72294098768403725</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0">
+        <v>0.059883499373945236</v>
+      </c>
+      <c r="B13" s="0">
+        <v>1.4645600000000001</v>
+      </c>
+      <c r="C13" s="0">
+        <v>0.73442451959722388</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0">
+        <v>0.065327453862485702</v>
+      </c>
+      <c r="B14" s="0">
+        <v>1.48586</v>
+      </c>
+      <c r="C14" s="0">
+        <v>0.74510570866931436</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0">
+        <v>0.070771408351026188</v>
+      </c>
+      <c r="B15" s="0">
+        <v>1.5057199999999999</v>
+      </c>
+      <c r="C15" s="0">
+        <v>0.75506478918441844</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0">
+        <v>0.076215362839566661</v>
+      </c>
+      <c r="B16" s="0">
+        <v>1.5245599999999999</v>
+      </c>
+      <c r="C16" s="0">
+        <v>0.76451237613832379</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0">
+        <v>0.081659317328107134</v>
+      </c>
+      <c r="B17" s="0">
+        <v>1.5423100000000001</v>
+      </c>
+      <c r="C17" s="0">
+        <v>0.77341336703173258</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0">
+        <v>0.087103271816647621</v>
+      </c>
+      <c r="B18" s="0">
+        <v>1.5592299999999999</v>
+      </c>
+      <c r="C18" s="0">
+        <v>0.78189814257632273</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0">
+        <v>0.092547226305188079</v>
+      </c>
+      <c r="B19" s="0">
+        <v>1.57545</v>
+      </c>
+      <c r="C19" s="0">
+        <v>0.79003189312793354</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0">
+        <v>0.097991180793728566</v>
+      </c>
+      <c r="B20" s="0">
+        <v>1.5908899999999999</v>
+      </c>
+      <c r="C20" s="0">
+        <v>0.79777450154450991</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0">
+        <v>0.10343513528226904</v>
+      </c>
+      <c r="B21" s="0">
+        <v>1.6057399999999999</v>
+      </c>
+      <c r="C21" s="0">
+        <v>0.80522124603843215</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0">
+        <v>0.10887908977080953</v>
+      </c>
+      <c r="B22" s="0">
+        <v>1.6201300000000001</v>
+      </c>
+      <c r="C22" s="0">
+        <v>0.81243731696553934</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0">
+        <v>0.11432304425934998</v>
+      </c>
+      <c r="B23" s="0">
+        <v>1.6340399999999999</v>
+      </c>
+      <c r="C23" s="0">
+        <v>0.81941268504031761</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0">
+        <v>0.11976699874789047</v>
+      </c>
+      <c r="B24" s="0">
+        <v>1.64747</v>
+      </c>
+      <c r="C24" s="0">
+        <v>0.8261473502627672</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0">
+        <v>0.12521095323643094</v>
+      </c>
+      <c r="B25" s="0">
+        <v>1.6604699999999999</v>
+      </c>
+      <c r="C25" s="0">
+        <v>0.83266638584667219</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0">
+        <v>0.1306549077249714</v>
+      </c>
+      <c r="B26" s="0">
+        <v>1.6731199999999999</v>
+      </c>
+      <c r="C26" s="0">
+        <v>0.83900990893408744</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0">
+        <v>0.13609886221351189</v>
+      </c>
+      <c r="B27" s="0">
+        <v>1.6854899999999999</v>
+      </c>
+      <c r="C27" s="0">
+        <v>0.84521302202431092</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0">
+        <v>0.14154281670205238</v>
+      </c>
+      <c r="B28" s="0">
+        <v>1.69739</v>
+      </c>
+      <c r="C28" s="0">
+        <v>0.85118044690496242</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0">
+        <v>0.14698677119059286</v>
+      </c>
+      <c r="B29" s="0">
+        <v>1.7092000000000001</v>
+      </c>
+      <c r="C29" s="0">
+        <v>0.85710274000080233</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0">
+        <v>0.15243072567913332</v>
+      </c>
+      <c r="B30" s="0">
+        <v>1.72058</v>
+      </c>
+      <c r="C30" s="0">
+        <v>0.86280940345809753</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0">
+        <v>0.15787468016767378</v>
+      </c>
+      <c r="B31" s="0">
+        <v>1.7318199999999999</v>
+      </c>
+      <c r="C31" s="0">
+        <v>0.86844586191679696</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0">
+        <v>0.16331863465621427</v>
+      </c>
+      <c r="B32" s="0">
+        <v>1.7427900000000001</v>
+      </c>
+      <c r="C32" s="0">
+        <v>0.87394692502106142</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0">
+        <v>0.16876258914475475</v>
+      </c>
+      <c r="B33" s="0">
+        <v>1.75342</v>
+      </c>
+      <c r="C33" s="0">
+        <v>0.87927749027159297</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0">
+        <v>0.17420654363329524</v>
+      </c>
+      <c r="B34" s="0">
+        <v>1.76389</v>
+      </c>
+      <c r="C34" s="0">
+        <v>0.88452782123801488</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0">
+        <v>0.1796504981218357</v>
+      </c>
+      <c r="B35" s="0">
+        <v>1.77413</v>
+      </c>
+      <c r="C35" s="0">
+        <v>0.88966281542102932</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0">
+        <v>0.18509445261037616</v>
+      </c>
+      <c r="B36" s="0">
+        <v>1.7841899999999999</v>
+      </c>
+      <c r="C36" s="0">
+        <v>0.89470754603442038</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0">
+        <v>0.19053840709891665</v>
+      </c>
+      <c r="B37" s="0">
+        <v>1.7941100000000001</v>
+      </c>
+      <c r="C37" s="0">
+        <v>0.89968207164921565</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0">
+        <v>0.19598236158745713</v>
+      </c>
+      <c r="B38" s="0">
+        <v>1.80365</v>
+      </c>
+      <c r="C38" s="0">
+        <v>0.90446604083925053</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0">
+        <v>0.20142631607599762</v>
+      </c>
+      <c r="B39" s="0">
+        <v>1.8129900000000001</v>
+      </c>
+      <c r="C39" s="0">
+        <v>0.9091497171741485</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0">
+        <v>0.20687027056453808</v>
+      </c>
+      <c r="B40" s="0">
+        <v>1.8224199999999999</v>
+      </c>
+      <c r="C40" s="0">
+        <v>0.91387852529385794</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0">
+        <v>0.21231422505307854</v>
+      </c>
+      <c r="B41" s="0">
+        <v>1.8315300000000001</v>
+      </c>
+      <c r="C41" s="0">
+        <v>0.91844686484534843</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0">
+        <v>0.21775817954161905</v>
+      </c>
+      <c r="B42" s="0">
+        <v>1.8403799999999999</v>
+      </c>
+      <c r="C42" s="0">
+        <v>0.92288482368516056</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0">
+        <v>0.22320213403015954</v>
+      </c>
+      <c r="B43" s="0">
+        <v>1.84904</v>
+      </c>
+      <c r="C43" s="0">
+        <v>0.92722750431259271</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0">
+        <v>0.22864608851869997</v>
+      </c>
+      <c r="B44" s="0">
+        <v>1.8575999999999999</v>
+      </c>
+      <c r="C44" s="0">
+        <v>0.93152003851245624</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0">
+        <v>0.23409004300724046</v>
+      </c>
+      <c r="B45" s="0">
+        <v>1.86595</v>
+      </c>
+      <c r="C45" s="0">
+        <v>0.93570726521442604</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0">
+        <v>0.23953399749578094</v>
+      </c>
+      <c r="B46" s="0">
+        <v>1.87412</v>
+      </c>
+      <c r="C46" s="0">
+        <v>0.93980422834677246</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0">
+        <v>0.2449779519843214</v>
+      </c>
+      <c r="B47" s="0">
+        <v>1.88205</v>
+      </c>
+      <c r="C47" s="0">
+        <v>0.94378084005295459</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0">
+        <v>0.25042190647286189</v>
+      </c>
+      <c r="B48" s="0">
+        <v>1.88988</v>
+      </c>
+      <c r="C48" s="0">
+        <v>0.94770730533156811</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="0">
+        <v>0.25586586096140235</v>
+      </c>
+      <c r="B49" s="0">
+        <v>1.89747</v>
+      </c>
+      <c r="C49" s="0">
+        <v>0.95151341918401722</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0">
+        <v>0.26130981544994281</v>
+      </c>
+      <c r="B50" s="0">
+        <v>1.9049199999999999</v>
+      </c>
+      <c r="C50" s="0">
+        <v>0.95524932803787044</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="0">
+        <v>0.26675376993848332</v>
+      </c>
+      <c r="B51" s="0">
+        <v>1.91215</v>
+      </c>
+      <c r="C51" s="0">
+        <v>0.95887491475107312</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="0">
+        <v>0.27219772442702378</v>
+      </c>
+      <c r="B52" s="0">
+        <v>1.9191</v>
+      </c>
+      <c r="C52" s="0">
+        <v>0.96236009146708379</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="0">
+        <v>0.27764167891556429</v>
+      </c>
+      <c r="B53" s="0">
+        <v>1.9258599999999999</v>
+      </c>
+      <c r="C53" s="0">
+        <v>0.96574998997071437</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="0">
+        <v>0.28308563340410475</v>
+      </c>
+      <c r="B54" s="0">
+        <v>1.93255</v>
+      </c>
+      <c r="C54" s="0">
+        <v>0.96910478597504701</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="0">
+        <v>0.28852958789264521</v>
+      </c>
+      <c r="B55" s="0">
+        <v>1.9389799999999999</v>
+      </c>
+      <c r="C55" s="0">
+        <v>0.97232920126770161</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="0">
+        <v>0.29397354238118573</v>
+      </c>
+      <c r="B56" s="0">
+        <v>1.9451700000000001</v>
+      </c>
+      <c r="C56" s="0">
+        <v>0.97543326513419182</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="0">
+        <v>0.29941749686972613</v>
+      </c>
+      <c r="B57" s="0">
+        <v>1.95112</v>
+      </c>
+      <c r="C57" s="0">
+        <v>0.97841697757451751</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="0">
+        <v>0.30486145135826664</v>
+      </c>
+      <c r="B58" s="0">
+        <v>1.9569099999999999</v>
+      </c>
+      <c r="C58" s="0">
+        <v>0.98132045573073368</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="0">
+        <v>0.31030540584680716</v>
+      </c>
+      <c r="B59" s="0">
+        <v>1.96245</v>
+      </c>
+      <c r="C59" s="0">
+        <v>0.98409856781802862</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="0">
+        <v>0.31574936033534756</v>
+      </c>
+      <c r="B60" s="0">
+        <v>1.9678599999999999</v>
+      </c>
+      <c r="C60" s="0">
+        <v>0.98681148954948439</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="0">
+        <v>0.32119331482388808</v>
+      </c>
+      <c r="B61" s="0">
+        <v>1.97299</v>
+      </c>
+      <c r="C61" s="0">
+        <v>0.98938400128374848</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="0">
+        <v>0.32663726931242854</v>
+      </c>
+      <c r="B62" s="0">
+        <v>1.9779800000000001</v>
+      </c>
+      <c r="C62" s="0">
+        <v>0.99188630801941668</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="0">
+        <v>0.33208122380096905</v>
+      </c>
+      <c r="B63" s="0">
+        <v>1.98272</v>
+      </c>
+      <c r="C63" s="0">
+        <v>0.99426324868616356</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="0">
+        <v>0.33752517828950951</v>
+      </c>
+      <c r="B64" s="0">
+        <v>1.9873099999999999</v>
+      </c>
+      <c r="C64" s="0">
+        <v>0.99656496971155761</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="0">
+        <v>0.34296913277804997</v>
+      </c>
+      <c r="B65" s="0">
+        <v>1.9914799999999999</v>
+      </c>
+      <c r="C65" s="0">
+        <v>0.99865607574116411</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="0">
+        <v>0.34841308726659048</v>
+      </c>
+      <c r="B66" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C66" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="0">
+        <v>0.35385704175513089</v>
+      </c>
+      <c r="B67" s="0">
+        <v>1.9942299999999999</v>
+      </c>
+      <c r="C67" s="0">
+        <v>1.0000351024992979</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="0">
+        <v>0.3593009962436714</v>
+      </c>
+      <c r="B68" s="0">
+        <v>1.9942299999999999</v>
+      </c>
+      <c r="C68" s="0">
+        <v>1.0000351024992979</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="0">
+        <v>0.36474495073221191</v>
+      </c>
+      <c r="B69" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C69" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="0">
+        <v>0.37018890522075232</v>
+      </c>
+      <c r="B70" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C70" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="0">
+        <v>0.37563285970929283</v>
+      </c>
+      <c r="B71" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C71" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="0">
+        <v>0.38107681419783329</v>
+      </c>
+      <c r="B72" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C72" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="0">
+        <v>0.38652076868637381</v>
+      </c>
+      <c r="B73" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C73" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="0">
+        <v>0.39196472317491426</v>
+      </c>
+      <c r="B74" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C74" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="0">
+        <v>0.39740867766345472</v>
+      </c>
+      <c r="B75" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C75" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="0">
+        <v>0.40285263215199524</v>
+      </c>
+      <c r="B76" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C76" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="0">
+        <v>0.4082965866405357</v>
+      </c>
+      <c r="B77" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C77" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="0">
+        <v>0.41374054112907616</v>
+      </c>
+      <c r="B78" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C78" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="0">
+        <v>0.41918449561761667</v>
+      </c>
+      <c r="B79" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C79" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="0">
+        <v>0.42462845010615707</v>
+      </c>
+      <c r="B80" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C80" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="0">
+        <v>0.43007240459469764</v>
+      </c>
+      <c r="B81" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C81" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="0">
+        <v>0.4355163590832381</v>
+      </c>
+      <c r="B82" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C82" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="0">
+        <v>0.44096031357177851</v>
+      </c>
+      <c r="B83" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C83" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="0">
+        <v>0.44640426806031908</v>
+      </c>
+      <c r="B84" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C84" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="0">
+        <v>0.45184822254885948</v>
+      </c>
+      <c r="B85" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C85" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="0">
+        <v>0.45729217703739994</v>
+      </c>
+      <c r="B86" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C86" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="0">
+        <v>0.46273613152594045</v>
+      </c>
+      <c r="B87" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C87" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="0">
+        <v>0.46818008601448091</v>
+      </c>
+      <c r="B88" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C88" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="0">
+        <v>0.47362404050302137</v>
+      </c>
+      <c r="B89" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C89" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="0">
+        <v>0.47906799499156189</v>
+      </c>
+      <c r="B90" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C90" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="0">
+        <v>0.48451194948010234</v>
+      </c>
+      <c r="B91" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C91" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="0">
+        <v>0.4899559039686428</v>
+      </c>
+      <c r="B92" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C92" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="0">
+        <v>0.49539985845718332</v>
+      </c>
+      <c r="B93" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C93" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="0">
+        <v>0.50084381294572378</v>
+      </c>
+      <c r="B94" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C94" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="0">
+        <v>0.50628776743426418</v>
+      </c>
+      <c r="B95" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C95" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="0">
+        <v>0.51173172192280469</v>
+      </c>
+      <c r="B96" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C96" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="0">
+        <v>0.51717567641134521</v>
+      </c>
+      <c r="B97" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C97" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="0">
+        <v>0.52261963089988561</v>
+      </c>
+      <c r="B98" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C98" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="0">
+        <v>0.52806358538842613</v>
+      </c>
+      <c r="B99" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C99" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="0">
+        <v>0.53350753987696664</v>
+      </c>
+      <c r="B100" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C100" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="0">
+        <v>0.53895149436550716</v>
+      </c>
+      <c r="B101" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C101" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="0">
+        <v>0.54439544885404756</v>
+      </c>
+      <c r="B102" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C102" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="0">
+        <v>0.54983940334258807</v>
+      </c>
+      <c r="B103" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C103" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="0">
+        <v>0.55528335783112859</v>
+      </c>
+      <c r="B104" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C104" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="0">
+        <v>0.56072731231966899</v>
+      </c>
+      <c r="B105" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C105" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="0">
+        <v>0.56617126680820951</v>
+      </c>
+      <c r="B106" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C106" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="0">
+        <v>0.57161522129675002</v>
+      </c>
+      <c r="B107" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C107" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="0">
+        <v>0.57705917578529042</v>
+      </c>
+      <c r="B108" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C108" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="0">
+        <v>0.58250313027383094</v>
+      </c>
+      <c r="B109" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C109" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="0">
+        <v>0.58794708476237145</v>
+      </c>
+      <c r="B110" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C110" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="0">
+        <v>0.59339103925091186</v>
+      </c>
+      <c r="B111" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C111" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="0">
+        <v>0.59883499373945226</v>
+      </c>
+      <c r="B112" s="0">
+        <v>1.9942200000000001</v>
+      </c>
+      <c r="C112" s="0">
+        <v>1.0000300878565411</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="0">
+        <v>0.60427894822799288</v>
+      </c>
+      <c r="B113" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C113" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="0">
+        <v>0.60972290271653329</v>
+      </c>
+      <c r="B114" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C114" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="0">
+        <v>0.61516685720507369</v>
+      </c>
+      <c r="B115" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C115" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="0">
+        <v>0.62061081169361432</v>
+      </c>
+      <c r="B116" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C116" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="0">
+        <v>0.62605476618215472</v>
+      </c>
+      <c r="B117" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C117" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="0">
+        <v>0.63149872067069512</v>
+      </c>
+      <c r="B118" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C118" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="0">
+        <v>0.63694267515923564</v>
+      </c>
+      <c r="B119" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C119" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="0">
+        <v>0.64238662964777615</v>
+      </c>
+      <c r="B120" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C120" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="0">
+        <v>0.64783058413631667</v>
+      </c>
+      <c r="B121" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C121" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="0">
+        <v>0.65327453862485707</v>
+      </c>
+      <c r="B122" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C122" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="0">
+        <v>0.65871849311339759</v>
+      </c>
+      <c r="B123" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C123" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="0">
+        <v>0.6641624476019381</v>
+      </c>
+      <c r="B124" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C124" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="0">
+        <v>0.6696064020904785</v>
+      </c>
+      <c r="B125" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C125" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="0">
+        <v>0.67505035657901902</v>
+      </c>
+      <c r="B126" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C126" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="0">
+        <v>0.68049431106755953</v>
+      </c>
+      <c r="B127" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C127" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="0">
+        <v>0.68593826555609994</v>
+      </c>
+      <c r="B128" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C128" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="0">
+        <v>0.69138222004464045</v>
+      </c>
+      <c r="B129" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C129" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="0">
+        <v>0.69682617453318096</v>
+      </c>
+      <c r="B130" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C130" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="0">
+        <v>0.70227012902172137</v>
+      </c>
+      <c r="B131" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C131" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="0">
+        <v>0.70771408351026177</v>
+      </c>
+      <c r="B132" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C132" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="0">
+        <v>0.7131580379988024</v>
+      </c>
+      <c r="B133" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C133" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="0">
+        <v>0.7186019924873428</v>
+      </c>
+      <c r="B134" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C134" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="0">
+        <v>0.7240459469758832</v>
+      </c>
+      <c r="B135" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C135" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="0">
+        <v>0.72948990146442383</v>
+      </c>
+      <c r="B136" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C136" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="0">
+        <v>0.73493385595296423</v>
+      </c>
+      <c r="B137" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C137" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="0">
+        <v>0.74037781044150464</v>
+      </c>
+      <c r="B138" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C138" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="0">
+        <v>0.74582176493004526</v>
+      </c>
+      <c r="B139" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C139" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="0">
+        <v>0.75126571941858566</v>
+      </c>
+      <c r="B140" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C140" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="0">
+        <v>0.75670967390712607</v>
+      </c>
+      <c r="B141" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C141" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="0">
+        <v>0.76215362839566658</v>
+      </c>
+      <c r="B142" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C142" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="0">
+        <v>0.7675975828842071</v>
+      </c>
+      <c r="B143" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C143" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="0">
+        <v>0.77304153737274761</v>
+      </c>
+      <c r="B144" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C144" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="0">
+        <v>0.77848549186128801</v>
+      </c>
+      <c r="B145" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C145" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="0">
+        <v>0.78392944634982853</v>
+      </c>
+      <c r="B146" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C146" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="0">
+        <v>0.78937340083836904</v>
+      </c>
+      <c r="B147" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C147" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="0">
+        <v>0.79481735532690945</v>
+      </c>
+      <c r="B148" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C148" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="0">
+        <v>0.80026130981544996</v>
+      </c>
+      <c r="B149" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C149" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="0">
+        <v>0.80570526430399048</v>
+      </c>
+      <c r="B150" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C150" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="0">
+        <v>0.81114921879253088</v>
+      </c>
+      <c r="B151" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C151" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="0">
+        <v>0.81659317328107139</v>
+      </c>
+      <c r="B152" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C152" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="0">
+        <v>0.82203712776961191</v>
+      </c>
+      <c r="B153" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C153" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="0">
+        <v>0.82748108225815231</v>
+      </c>
+      <c r="B154" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C154" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="0">
+        <v>0.83292503674669272</v>
+      </c>
+      <c r="B155" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C155" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="0">
+        <v>0.83836899123523334</v>
+      </c>
+      <c r="B156" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C156" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="0">
+        <v>0.84381294572377374</v>
+      </c>
+      <c r="B157" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C157" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="0">
+        <v>0.84925690021231415</v>
+      </c>
+      <c r="B158" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C158" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="0">
+        <v>0.85470085470085466</v>
+      </c>
+      <c r="B159" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C159" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="0">
+        <v>0.86014480918939529</v>
+      </c>
+      <c r="B160" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C160" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="0">
+        <v>0.86558876367793569</v>
+      </c>
+      <c r="B161" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C161" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="0">
+        <v>0.87103271816647621</v>
+      </c>
+      <c r="B162" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C162" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="0">
+        <v>0.87647667265501661</v>
+      </c>
+      <c r="B163" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C163" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="0">
+        <v>0.88192062714355701</v>
+      </c>
+      <c r="B164" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C164" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="0">
+        <v>0.88736458163209753</v>
+      </c>
+      <c r="B165" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C165" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="0">
+        <v>0.89280853612063815</v>
+      </c>
+      <c r="B166" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C166" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="0">
+        <v>0.89825249060917856</v>
+      </c>
+      <c r="B167" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C167" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="0">
+        <v>0.90369644509771896</v>
+      </c>
+      <c r="B168" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C168" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="0">
+        <v>0.90914039958625947</v>
+      </c>
+      <c r="B169" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C169" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="0">
+        <v>0.91458435407479988</v>
+      </c>
+      <c r="B170" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C170" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="0">
+        <v>0.92002830856334028</v>
+      </c>
+      <c r="B171" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C171" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="0">
+        <v>0.92547226305188091</v>
+      </c>
+      <c r="B172" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C172" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="0">
+        <v>0.93091621754042142</v>
+      </c>
+      <c r="B173" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C173" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="0">
+        <v>0.93636017202896182</v>
+      </c>
+      <c r="B174" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C174" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="0">
+        <v>0.94180412651750234</v>
+      </c>
+      <c r="B175" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C175" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="0">
+        <v>0.94724808100604274</v>
+      </c>
+      <c r="B176" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C176" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="0">
+        <v>0.95269203549458337</v>
+      </c>
+      <c r="B177" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C177" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="0">
+        <v>0.95813598998312377</v>
+      </c>
+      <c r="B178" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C178" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="0">
+        <v>0.96357994447166428</v>
+      </c>
+      <c r="B179" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C179" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="0">
+        <v>0.96902389896020469</v>
+      </c>
+      <c r="B180" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C180" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="0">
+        <v>0.97446785344874509</v>
+      </c>
+      <c r="B181" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C181" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="0">
+        <v>0.97991180793728561</v>
+      </c>
+      <c r="B182" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C182" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="0">
+        <v>0.98535576242582623</v>
+      </c>
+      <c r="B183" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C183" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="0">
+        <v>0.99079971691436663</v>
+      </c>
+      <c r="B184" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C184" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="0">
+        <v>0.99624367140290704</v>
+      </c>
+      <c r="B185" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C185" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="0">
+        <v>1.0016876258914476</v>
+      </c>
+      <c r="B186" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C186" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="0">
+        <v>1.0071315803799881</v>
+      </c>
+      <c r="B187" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C187" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="0">
+        <v>1.0125755348685284</v>
+      </c>
+      <c r="B188" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C188" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="0">
+        <v>1.0180194893570691</v>
+      </c>
+      <c r="B189" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C189" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="0">
+        <v>1.0234634438456094</v>
+      </c>
+      <c r="B190" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C190" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="0">
+        <v>1.0289073983341499</v>
+      </c>
+      <c r="B191" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C191" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="0">
+        <v>1.0343513528226904</v>
+      </c>
+      <c r="B192" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C192" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="0">
+        <v>1.0397953073112309</v>
+      </c>
+      <c r="B193" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C193" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="0">
+        <v>1.0452392617997712</v>
+      </c>
+      <c r="B194" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C194" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="0">
+        <v>1.050683216288312</v>
+      </c>
+      <c r="B195" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C195" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="0">
+        <v>1.0561271707768523</v>
+      </c>
+      <c r="B196" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C196" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="0">
+        <v>1.0615711252653928</v>
+      </c>
+      <c r="B197" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C197" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="0">
+        <v>1.0670150797539333</v>
+      </c>
+      <c r="B198" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C198" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="0">
+        <v>1.0724590342424736</v>
+      </c>
+      <c r="B199" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C199" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="0">
+        <v>1.0779029887310143</v>
+      </c>
+      <c r="B200" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C200" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="0">
+        <v>1.0833469432195548</v>
+      </c>
+      <c r="B201" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C201" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="0">
+        <v>1.0887908977080951</v>
+      </c>
+      <c r="B202" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C202" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="0">
+        <v>1.0942348521966356</v>
+      </c>
+      <c r="B203" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C203" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="0">
+        <v>1.0996788066851761</v>
+      </c>
+      <c r="B204" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C204" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="0">
+        <v>1.1051227611737164</v>
+      </c>
+      <c r="B205" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C205" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="0">
+        <v>1.1105667156622572</v>
+      </c>
+      <c r="B206" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C206" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="0">
+        <v>1.1160106701507977</v>
+      </c>
+      <c r="B207" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C207" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="0">
+        <v>1.121454624639338</v>
+      </c>
+      <c r="B208" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C208" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="0">
+        <v>1.1268985791278785</v>
+      </c>
+      <c r="B209" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C209" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="0">
+        <v>1.132342533616419</v>
+      </c>
+      <c r="B210" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C210" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="0">
+        <v>1.1377864881049593</v>
+      </c>
+      <c r="B211" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C211" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="0">
+        <v>1.1432304425935</v>
+      </c>
+      <c r="B212" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C212" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="0">
+        <v>1.1486743970820403</v>
+      </c>
+      <c r="B213" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C213" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="0">
+        <v>1.1541183515705808</v>
+      </c>
+      <c r="B214" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C214" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="0">
+        <v>1.1595623060591214</v>
+      </c>
+      <c r="B215" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C215" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="0">
+        <v>1.1650062605476619</v>
+      </c>
+      <c r="B216" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C216" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="0">
+        <v>1.1704502150362022</v>
+      </c>
+      <c r="B217" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C217" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="0">
+        <v>1.1758941695247429</v>
+      </c>
+      <c r="B218" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C218" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="0">
+        <v>1.1813381240132832</v>
+      </c>
+      <c r="B219" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C219" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="0">
+        <v>1.1867820785018237</v>
+      </c>
+      <c r="B220" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C220" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="0">
+        <v>1.1922260329903642</v>
+      </c>
+      <c r="B221" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C221" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="0">
+        <v>1.1976699874789045</v>
+      </c>
+      <c r="B222" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C222" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="0">
+        <v>1.2031139419674453</v>
+      </c>
+      <c r="B223" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C223" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="0">
+        <v>1.2085578964559858</v>
+      </c>
+      <c r="B224" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C224" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="0">
+        <v>1.2140018509445261</v>
+      </c>
+      <c r="B225" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C225" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="0">
+        <v>1.2194458054330666</v>
+      </c>
+      <c r="B226" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C226" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="0">
+        <v>1.2248897599216071</v>
+      </c>
+      <c r="B227" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C227" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="0">
+        <v>1.2303337144101474</v>
+      </c>
+      <c r="B228" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C228" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="0">
+        <v>1.2357776688986881</v>
+      </c>
+      <c r="B229" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C229" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="0">
+        <v>1.2412216233872286</v>
+      </c>
+      <c r="B230" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C230" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="0">
+        <v>1.2466655778757689</v>
+      </c>
+      <c r="B231" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C231" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="0">
+        <v>1.2521095323643094</v>
+      </c>
+      <c r="B232" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C232" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="0">
+        <v>1.25755348685285</v>
+      </c>
+      <c r="B233" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C233" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="0">
+        <v>1.2629974413413902</v>
+      </c>
+      <c r="B234" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C234" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="0">
+        <v>1.268441395829931</v>
+      </c>
+      <c r="B235" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C235" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="0">
+        <v>1.2738853503184713</v>
+      </c>
+      <c r="B236" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C236" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="0">
+        <v>1.2793293048070118</v>
+      </c>
+      <c r="B237" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C237" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="0">
+        <v>1.2847732592955523</v>
+      </c>
+      <c r="B238" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C238" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="0">
+        <v>1.2902172137840926</v>
+      </c>
+      <c r="B239" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C239" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="0">
+        <v>1.2956611682726333</v>
+      </c>
+      <c r="B240" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C240" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="0">
+        <v>1.3011051227611738</v>
+      </c>
+      <c r="B241" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C241" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="0">
+        <v>1.3065490772497141</v>
+      </c>
+      <c r="B242" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C242" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="0">
+        <v>1.3119930317382547</v>
+      </c>
+      <c r="B243" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C243" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="0">
+        <v>1.3174369862267952</v>
+      </c>
+      <c r="B244" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C244" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="0">
+        <v>1.3228809407153355</v>
+      </c>
+      <c r="B245" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C245" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="0">
+        <v>1.3283248952038762</v>
+      </c>
+      <c r="B246" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C246" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="0">
+        <v>1.3337688496924167</v>
+      </c>
+      <c r="B247" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C247" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="0">
+        <v>1.339212804180957</v>
+      </c>
+      <c r="B248" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C248" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="0">
+        <v>1.3446567586694975</v>
+      </c>
+      <c r="B249" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C249" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="0">
+        <v>1.350100713158038</v>
+      </c>
+      <c r="B250" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C250" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="0">
+        <v>1.3555446676465783</v>
+      </c>
+      <c r="B251" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C251" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="0">
+        <v>1.3609886221351191</v>
+      </c>
+      <c r="B252" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C252" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="0">
+        <v>1.3664325766236596</v>
+      </c>
+      <c r="B253" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C253" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="0">
+        <v>1.3718765311121999</v>
+      </c>
+      <c r="B254" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C254" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="0">
+        <v>1.3773204856007404</v>
+      </c>
+      <c r="B255" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C255" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="0">
+        <v>1.3827644400892809</v>
+      </c>
+      <c r="B256" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C256" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="0">
+        <v>1.3882083945778212</v>
+      </c>
+      <c r="B257" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C257" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="0">
+        <v>1.3936523490663619</v>
+      </c>
+      <c r="B258" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C258" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="0">
+        <v>1.3990963035549022</v>
+      </c>
+      <c r="B259" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C259" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="0">
+        <v>1.4045402580434427</v>
+      </c>
+      <c r="B260" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C260" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="0">
+        <v>1.4099842125319832</v>
+      </c>
+      <c r="B261" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C261" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/TunnelDataProcessing/BoundaryLayerComparison/BoundaryLayerComparison.xlsx
+++ b/TunnelDataProcessing/BoundaryLayerComparison/BoundaryLayerComparison.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="15" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="105" uniqueCount="3">
   <si>
     <t>Y_over_D</t>
   </si>
@@ -75,9 +75,9 @@
   <dimension ref="A1:C102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" customWidth="true"/>
-    <col min="2" max="2" width="11.5546875" customWidth="true"/>
-    <col min="3" max="3" width="12.5546875" customWidth="true"/>
+    <col min="1" max="1" width="13.7109375" customWidth="true"/>
+    <col min="2" max="2" width="11.7109375" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3483,9 +3483,9 @@
   <dimension ref="A1:C301"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" customWidth="true"/>
-    <col min="2" max="2" width="12.5546875" customWidth="true"/>
-    <col min="3" max="3" width="12.5546875" customWidth="true"/>
+    <col min="1" max="1" width="14.7109375" customWidth="true"/>
+    <col min="2" max="2" width="12.7109375" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6805,12 +6805,12 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C261"/>
+  <dimension ref="A1:C520"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" customWidth="true"/>
-    <col min="2" max="2" width="8.5546875" customWidth="true"/>
-    <col min="3" max="3" width="12.5546875" customWidth="true"/>
+    <col min="1" max="1" width="14.7109375" customWidth="true"/>
+    <col min="2" max="2" width="8.7109375" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6837,2850 +6837,5699 @@
     </row>
     <row r="3">
       <c r="A3" s="0">
-        <v>0.0054439544885404763</v>
+        <v>0.0027219772442702381</v>
       </c>
       <c r="B3" s="0">
-        <v>0.91806900000000002</v>
+        <v>0.72908399999999995</v>
       </c>
       <c r="C3" s="0">
-        <v>0.4603788061138524</v>
+        <v>0.36560957997352261</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>0.010887908977080953</v>
+        <v>0.0054439544885404763</v>
       </c>
       <c r="B4" s="0">
-        <v>1.08047</v>
+        <v>0.91806900000000002</v>
       </c>
       <c r="C4" s="0">
-        <v>0.54181710594937216</v>
+        <v>0.4603788061138524</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>0.016331863465621425</v>
+        <v>0.0081659317328107127</v>
       </c>
       <c r="B5" s="0">
-        <v>1.1706300000000001</v>
+        <v>1.01471</v>
       </c>
       <c r="C5" s="0">
-        <v>0.58702912504513172</v>
+        <v>0.50884081518032653</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>0.021775817954161905</v>
+        <v>0.010887908977080953</v>
       </c>
       <c r="B6" s="0">
-        <v>1.23393</v>
+        <v>1.08047</v>
       </c>
       <c r="C6" s="0">
-        <v>0.61877181369599221</v>
+        <v>0.54181710594937216</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0">
-        <v>0.027219772442702381</v>
+        <v>0.013609886221351191</v>
       </c>
       <c r="B7" s="0">
-        <v>1.2831900000000001</v>
+        <v>1.1303799999999999</v>
       </c>
       <c r="C7" s="0">
-        <v>0.64347394391623536</v>
+        <v>0.56684518794881045</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0">
-        <v>0.032663726931242851</v>
+        <v>0.016331863465621425</v>
       </c>
       <c r="B8" s="0">
-        <v>1.3238000000000001</v>
+        <v>1.1706300000000001</v>
       </c>
       <c r="C8" s="0">
-        <v>0.66383840815180328</v>
+        <v>0.58702912504513172</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0">
-        <v>0.038107681419783331</v>
+        <v>0.019053840709891665</v>
       </c>
       <c r="B9" s="0">
-        <v>1.3586100000000001</v>
+        <v>1.2045300000000001</v>
       </c>
       <c r="C9" s="0">
-        <v>0.68129437958839811</v>
+        <v>0.60402876399085326</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0">
-        <v>0.04355163590832381</v>
+        <v>0.021775817954161905</v>
       </c>
       <c r="B10" s="0">
-        <v>1.3892199999999999</v>
+        <v>1.23393</v>
       </c>
       <c r="C10" s="0">
-        <v>0.69664420106711589</v>
+        <v>0.61877181369599221</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0">
-        <v>0.048995590396864283</v>
+        <v>0.024497795198432142</v>
       </c>
       <c r="B11" s="0">
-        <v>1.4166700000000001</v>
+        <v>1.2599400000000001</v>
       </c>
       <c r="C11" s="0">
-        <v>0.71040939543466919</v>
+        <v>0.63181489950655911</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0">
-        <v>0.054439544885404763</v>
+        <v>0.027219772442702381</v>
       </c>
       <c r="B12" s="0">
-        <v>1.4416599999999999</v>
+        <v>1.2831900000000001</v>
       </c>
       <c r="C12" s="0">
-        <v>0.72294098768403725</v>
+        <v>0.64347394391623536</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0">
-        <v>0.059883499373945236</v>
+        <v>0.029941749686972618</v>
       </c>
       <c r="B13" s="0">
-        <v>1.4645600000000001</v>
+        <v>1.30443</v>
       </c>
       <c r="C13" s="0">
-        <v>0.73442451959722388</v>
+        <v>0.65412504513178471</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0">
-        <v>0.065327453862485702</v>
+        <v>0.032663726931242851</v>
       </c>
       <c r="B14" s="0">
-        <v>1.48586</v>
+        <v>1.3238000000000001</v>
       </c>
       <c r="C14" s="0">
-        <v>0.74510570866931436</v>
+        <v>0.66383840815180328</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0">
-        <v>0.070771408351026188</v>
+        <v>0.035385704175513094</v>
       </c>
       <c r="B15" s="0">
-        <v>1.5057199999999999</v>
+        <v>1.3418000000000001</v>
       </c>
       <c r="C15" s="0">
-        <v>0.75506478918441844</v>
+        <v>0.67286476511413329</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0">
-        <v>0.076215362839566661</v>
+        <v>0.038107681419783331</v>
       </c>
       <c r="B16" s="0">
-        <v>1.5245599999999999</v>
+        <v>1.3586100000000001</v>
       </c>
       <c r="C16" s="0">
-        <v>0.76451237613832379</v>
+        <v>0.68129437958839811</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0">
-        <v>0.081659317328107134</v>
+        <v>0.040829658664053567</v>
       </c>
       <c r="B17" s="0">
-        <v>1.5423100000000001</v>
+        <v>1.3743700000000001</v>
       </c>
       <c r="C17" s="0">
-        <v>0.77341336703173258</v>
+        <v>0.68919745657319376</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0">
-        <v>0.087103271816647621</v>
+        <v>0.04355163590832381</v>
       </c>
       <c r="B18" s="0">
-        <v>1.5592299999999999</v>
+        <v>1.3892199999999999</v>
       </c>
       <c r="C18" s="0">
-        <v>0.78189814257632273</v>
+        <v>0.69664420106711589</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0">
-        <v>0.092547226305188079</v>
+        <v>0.04627361315259404</v>
       </c>
       <c r="B19" s="0">
-        <v>1.57545</v>
+        <v>1.4033100000000001</v>
       </c>
       <c r="C19" s="0">
-        <v>0.79003189312793354</v>
+        <v>0.70370983271151766</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0">
-        <v>0.097991180793728566</v>
+        <v>0.048995590396864283</v>
       </c>
       <c r="B20" s="0">
-        <v>1.5908899999999999</v>
+        <v>1.4166700000000001</v>
       </c>
       <c r="C20" s="0">
-        <v>0.79777450154450991</v>
+        <v>0.71040939543466919</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0">
-        <v>0.10343513528226904</v>
+        <v>0.051717567641134519</v>
       </c>
       <c r="B21" s="0">
-        <v>1.6057399999999999</v>
+        <v>1.4294199999999999</v>
       </c>
       <c r="C21" s="0">
-        <v>0.80522124603843215</v>
+        <v>0.71680306494965285</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0">
-        <v>0.10887908977080953</v>
+        <v>0.054439544885404763</v>
       </c>
       <c r="B22" s="0">
-        <v>1.6201300000000001</v>
+        <v>1.4416599999999999</v>
       </c>
       <c r="C22" s="0">
-        <v>0.81243731696553934</v>
+        <v>0.72294098768403725</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0">
-        <v>0.11432304425934998</v>
+        <v>0.057161522129674992</v>
       </c>
       <c r="B23" s="0">
-        <v>1.6340399999999999</v>
+        <v>1.45333</v>
       </c>
       <c r="C23" s="0">
-        <v>0.81941268504031761</v>
+        <v>0.72879307578128127</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0">
-        <v>0.11976699874789047</v>
+        <v>0.059883499373945236</v>
       </c>
       <c r="B24" s="0">
-        <v>1.64747</v>
+        <v>1.4645600000000001</v>
       </c>
       <c r="C24" s="0">
-        <v>0.8261473502627672</v>
+        <v>0.73442451959722388</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0">
-        <v>0.12521095323643094</v>
+        <v>0.062605476618215472</v>
       </c>
       <c r="B25" s="0">
-        <v>1.6604699999999999</v>
+        <v>1.4753700000000001</v>
       </c>
       <c r="C25" s="0">
-        <v>0.83266638584667219</v>
+        <v>0.7398453484173787</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0">
-        <v>0.1306549077249714</v>
+        <v>0.065327453862485702</v>
       </c>
       <c r="B26" s="0">
-        <v>1.6731199999999999</v>
+        <v>1.48586</v>
       </c>
       <c r="C26" s="0">
-        <v>0.83900990893408744</v>
+        <v>0.74510570866931436</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0">
-        <v>0.13609886221351189</v>
+        <v>0.068049431106755945</v>
       </c>
       <c r="B27" s="0">
-        <v>1.6854899999999999</v>
+        <v>1.4959199999999999</v>
       </c>
       <c r="C27" s="0">
-        <v>0.84521302202431092</v>
+        <v>0.75015043928270542</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0">
-        <v>0.14154281670205238</v>
+        <v>0.070771408351026188</v>
       </c>
       <c r="B28" s="0">
-        <v>1.69739</v>
+        <v>1.5057199999999999</v>
       </c>
       <c r="C28" s="0">
-        <v>0.85118044690496242</v>
+        <v>0.75506478918441844</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0">
-        <v>0.14698677119059286</v>
+        <v>0.073493385595296432</v>
       </c>
       <c r="B29" s="0">
-        <v>1.7092000000000001</v>
+        <v>1.5153300000000001</v>
       </c>
       <c r="C29" s="0">
-        <v>0.85710274000080233</v>
+        <v>0.75988386087375137</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0">
-        <v>0.15243072567913332</v>
+        <v>0.076215362839566661</v>
       </c>
       <c r="B30" s="0">
-        <v>1.72058</v>
+        <v>1.5245599999999999</v>
       </c>
       <c r="C30" s="0">
-        <v>0.86280940345809753</v>
+        <v>0.76451237613832379</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0">
-        <v>0.15787468016767378</v>
+        <v>0.07893734008383689</v>
       </c>
       <c r="B31" s="0">
-        <v>1.7318199999999999</v>
+        <v>1.53352</v>
       </c>
       <c r="C31" s="0">
-        <v>0.86844586191679696</v>
+        <v>0.76900549604846147</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0">
-        <v>0.16331863465621427</v>
+        <v>0.081659317328107134</v>
       </c>
       <c r="B32" s="0">
-        <v>1.7427900000000001</v>
+        <v>1.5423100000000001</v>
       </c>
       <c r="C32" s="0">
-        <v>0.87394692502106142</v>
+        <v>0.77341336703173258</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0">
-        <v>0.16876258914475475</v>
+        <v>0.084381294572377377</v>
       </c>
       <c r="B33" s="0">
-        <v>1.75342</v>
+        <v>1.5508900000000001</v>
       </c>
       <c r="C33" s="0">
-        <v>0.87927749027159297</v>
+        <v>0.77771593051710997</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0">
-        <v>0.17420654363329524</v>
+        <v>0.087103271816647621</v>
       </c>
       <c r="B34" s="0">
-        <v>1.76389</v>
+        <v>1.5592299999999999</v>
       </c>
       <c r="C34" s="0">
-        <v>0.88452782123801488</v>
+        <v>0.78189814257632273</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0">
-        <v>0.1796504981218357</v>
+        <v>0.08982524906091785</v>
       </c>
       <c r="B35" s="0">
-        <v>1.77413</v>
+        <v>1.56742</v>
       </c>
       <c r="C35" s="0">
-        <v>0.88966281542102932</v>
+        <v>0.78600513499418301</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0">
-        <v>0.18509445261037616</v>
+        <v>0.092547226305188079</v>
       </c>
       <c r="B36" s="0">
-        <v>1.7841899999999999</v>
+        <v>1.57545</v>
       </c>
       <c r="C36" s="0">
-        <v>0.89470754603442038</v>
+        <v>0.79003189312793354</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0">
-        <v>0.19053840709891665</v>
+        <v>0.095269203549458323</v>
       </c>
       <c r="B37" s="0">
-        <v>1.7941100000000001</v>
+        <v>1.58328</v>
       </c>
       <c r="C37" s="0">
-        <v>0.89968207164921565</v>
+        <v>0.79395835840654705</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0">
-        <v>0.19598236158745713</v>
+        <v>0.097991180793728566</v>
       </c>
       <c r="B38" s="0">
-        <v>1.80365</v>
+        <v>1.5908899999999999</v>
       </c>
       <c r="C38" s="0">
-        <v>0.90446604083925053</v>
+        <v>0.79777450154450991</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0">
-        <v>0.20142631607599762</v>
+        <v>0.10071315803799881</v>
       </c>
       <c r="B39" s="0">
-        <v>1.8129900000000001</v>
+        <v>1.59839</v>
       </c>
       <c r="C39" s="0">
-        <v>0.9091497171741485</v>
+        <v>0.80153548361214744</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0">
-        <v>0.20687027056453808</v>
+        <v>0.10343513528226904</v>
       </c>
       <c r="B40" s="0">
-        <v>1.8224199999999999</v>
+        <v>1.6057399999999999</v>
       </c>
       <c r="C40" s="0">
-        <v>0.91387852529385794</v>
+        <v>0.80522124603843215</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0">
-        <v>0.21231422505307854</v>
+        <v>0.10615711252653927</v>
       </c>
       <c r="B41" s="0">
-        <v>1.8315300000000001</v>
+        <v>1.61303</v>
       </c>
       <c r="C41" s="0">
-        <v>0.91844686484534843</v>
+        <v>0.80887692060817584</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0">
-        <v>0.21775817954161905</v>
+        <v>0.10887908977080953</v>
       </c>
       <c r="B42" s="0">
-        <v>1.8403799999999999</v>
+        <v>1.6201300000000001</v>
       </c>
       <c r="C42" s="0">
-        <v>0.92288482368516056</v>
+        <v>0.81243731696553934</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0">
-        <v>0.22320213403015954</v>
+        <v>0.11160106701507977</v>
       </c>
       <c r="B43" s="0">
-        <v>1.84904</v>
+        <v>1.6270800000000001</v>
       </c>
       <c r="C43" s="0">
-        <v>0.92722750431259271</v>
+        <v>0.81592249368155012</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0">
-        <v>0.22864608851869997</v>
+        <v>0.11432304425934998</v>
       </c>
       <c r="B44" s="0">
-        <v>1.8575999999999999</v>
+        <v>1.6340399999999999</v>
       </c>
       <c r="C44" s="0">
-        <v>0.93152003851245624</v>
+        <v>0.81941268504031761</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0">
-        <v>0.23409004300724046</v>
+        <v>0.11704502150362023</v>
       </c>
       <c r="B45" s="0">
-        <v>1.86595</v>
+        <v>1.6407799999999999</v>
       </c>
       <c r="C45" s="0">
-        <v>0.93570726521442604</v>
+        <v>0.82279255425843456</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0">
-        <v>0.23953399749578094</v>
+        <v>0.11976699874789047</v>
       </c>
       <c r="B46" s="0">
-        <v>1.87412</v>
+        <v>1.64747</v>
       </c>
       <c r="C46" s="0">
-        <v>0.93980422834677246</v>
+        <v>0.8261473502627672</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0">
-        <v>0.2449779519843214</v>
+        <v>0.1224889759921607</v>
       </c>
       <c r="B47" s="0">
-        <v>1.88205</v>
+        <v>1.65405</v>
       </c>
       <c r="C47" s="0">
-        <v>0.94378084005295459</v>
+        <v>0.82944698519677451</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0">
-        <v>0.25042190647286189</v>
+        <v>0.12521095323643094</v>
       </c>
       <c r="B48" s="0">
-        <v>1.88988</v>
+        <v>1.6604699999999999</v>
       </c>
       <c r="C48" s="0">
-        <v>0.94770730533156811</v>
+        <v>0.83266638584667219</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0">
-        <v>0.25586586096140235</v>
+        <v>0.12793293048070117</v>
       </c>
       <c r="B49" s="0">
-        <v>1.89747</v>
+        <v>1.66686</v>
       </c>
       <c r="C49" s="0">
-        <v>0.95151341918401722</v>
+        <v>0.83587074256829941</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0">
-        <v>0.26130981544994281</v>
+        <v>0.1306549077249714</v>
       </c>
       <c r="B50" s="0">
-        <v>1.9049199999999999</v>
+        <v>1.6731199999999999</v>
       </c>
       <c r="C50" s="0">
-        <v>0.95524932803787044</v>
+        <v>0.83900990893408744</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0">
-        <v>0.26675376993848332</v>
+        <v>0.13337688496924166</v>
       </c>
       <c r="B51" s="0">
-        <v>1.91215</v>
+        <v>1.67933</v>
       </c>
       <c r="C51" s="0">
-        <v>0.95887491475107312</v>
+        <v>0.84212400208609128</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0">
-        <v>0.27219772442702378</v>
+        <v>0.13609886221351189</v>
       </c>
       <c r="B52" s="0">
-        <v>1.9191</v>
+        <v>1.6854899999999999</v>
       </c>
       <c r="C52" s="0">
-        <v>0.96236009146708379</v>
+        <v>0.84521302202431092</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0">
-        <v>0.27764167891556429</v>
+        <v>0.13882083945778215</v>
       </c>
       <c r="B53" s="0">
-        <v>1.9258599999999999</v>
+        <v>1.6914899999999999</v>
       </c>
       <c r="C53" s="0">
-        <v>0.96574998997071437</v>
+        <v>0.84822180767842092</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0">
-        <v>0.28308563340410475</v>
+        <v>0.14154281670205238</v>
       </c>
       <c r="B54" s="0">
-        <v>1.93255</v>
+        <v>1.69739</v>
       </c>
       <c r="C54" s="0">
-        <v>0.96910478597504701</v>
+        <v>0.85118044690496242</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0">
-        <v>0.28852958789264521</v>
+        <v>0.14426479394632261</v>
       </c>
       <c r="B55" s="0">
-        <v>1.9389799999999999</v>
+        <v>1.7033</v>
       </c>
       <c r="C55" s="0">
-        <v>0.97232920126770161</v>
+        <v>0.85414410077426084</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0">
-        <v>0.29397354238118573</v>
+        <v>0.14698677119059286</v>
       </c>
       <c r="B56" s="0">
-        <v>1.9451700000000001</v>
+        <v>1.7092000000000001</v>
       </c>
       <c r="C56" s="0">
-        <v>0.97543326513419182</v>
+        <v>0.85710274000080233</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0">
-        <v>0.29941749686972613</v>
+        <v>0.14970874843486306</v>
       </c>
       <c r="B57" s="0">
-        <v>1.95112</v>
+        <v>1.7149700000000001</v>
       </c>
       <c r="C57" s="0">
-        <v>0.97841697757451751</v>
+        <v>0.85999618887150475</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0">
-        <v>0.30486145135826664</v>
+        <v>0.15243072567913332</v>
       </c>
       <c r="B58" s="0">
-        <v>1.9569099999999999</v>
+        <v>1.72058</v>
       </c>
       <c r="C58" s="0">
-        <v>0.98132045573073368</v>
+        <v>0.86280940345809753</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0">
-        <v>0.31030540584680716</v>
+        <v>0.15515270292340358</v>
       </c>
       <c r="B59" s="0">
-        <v>1.96245</v>
+        <v>1.7262200000000001</v>
       </c>
       <c r="C59" s="0">
-        <v>0.98409856781802862</v>
+        <v>0.86563766197296099</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0">
-        <v>0.31574936033534756</v>
+        <v>0.15787468016767378</v>
       </c>
       <c r="B60" s="0">
-        <v>1.9678599999999999</v>
+        <v>1.7318199999999999</v>
       </c>
       <c r="C60" s="0">
-        <v>0.98681148954948439</v>
+        <v>0.86844586191679696</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0">
-        <v>0.32119331482388808</v>
+        <v>0.16059665741194404</v>
       </c>
       <c r="B61" s="0">
-        <v>1.97299</v>
+        <v>1.73733</v>
       </c>
       <c r="C61" s="0">
-        <v>0.98938400128374848</v>
+        <v>0.87120893007582134</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0">
-        <v>0.32663726931242854</v>
+        <v>0.16331863465621427</v>
       </c>
       <c r="B62" s="0">
-        <v>1.9779800000000001</v>
+        <v>1.7427900000000001</v>
       </c>
       <c r="C62" s="0">
-        <v>0.99188630801941668</v>
+        <v>0.87394692502106142</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0">
-        <v>0.33208122380096905</v>
+        <v>0.16604061190048452</v>
       </c>
       <c r="B63" s="0">
-        <v>1.98272</v>
+        <v>1.74813</v>
       </c>
       <c r="C63" s="0">
-        <v>0.99426324868616356</v>
+        <v>0.87662474425321935</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0">
-        <v>0.33752517828950951</v>
+        <v>0.16876258914475475</v>
       </c>
       <c r="B64" s="0">
-        <v>1.9873099999999999</v>
+        <v>1.75342</v>
       </c>
       <c r="C64" s="0">
-        <v>0.99656496971155761</v>
+        <v>0.87927749027159297</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0">
-        <v>0.34296913277804997</v>
+        <v>0.17148456638902498</v>
       </c>
       <c r="B65" s="0">
-        <v>1.9914799999999999</v>
+        <v>1.7586999999999999</v>
       </c>
       <c r="C65" s="0">
-        <v>0.99865607574116411</v>
+        <v>0.88192522164720977</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0">
-        <v>0.34841308726659048</v>
+        <v>0.17420654363329524</v>
       </c>
       <c r="B66" s="0">
-        <v>1.9941599999999999</v>
+        <v>1.76389</v>
       </c>
       <c r="C66" s="0">
-        <v>0.99999999999999989</v>
+        <v>0.88452782123801488</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0">
-        <v>0.35385704175513089</v>
+        <v>0.17692852087756544</v>
       </c>
       <c r="B67" s="0">
-        <v>1.9942299999999999</v>
+        <v>1.76901</v>
       </c>
       <c r="C67" s="0">
-        <v>1.0000351024992979</v>
+        <v>0.88709531832952215</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0">
-        <v>0.3593009962436714</v>
+        <v>0.1796504981218357</v>
       </c>
       <c r="B68" s="0">
-        <v>1.9942299999999999</v>
+        <v>1.77413</v>
       </c>
       <c r="C68" s="0">
-        <v>1.0000351024992979</v>
+        <v>0.88966281542102932</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="0">
-        <v>0.36474495073221191</v>
+        <v>0.18237247536610596</v>
       </c>
       <c r="B69" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.77925</v>
       </c>
       <c r="C69" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.89223031251253648</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="0">
-        <v>0.37018890522075232</v>
+        <v>0.18509445261037616</v>
       </c>
       <c r="B70" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.7841899999999999</v>
       </c>
       <c r="C70" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.89470754603442038</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="0">
-        <v>0.37563285970929283</v>
+        <v>0.18781642985464642</v>
       </c>
       <c r="B71" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.78915</v>
       </c>
       <c r="C71" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.89719480884181801</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0">
-        <v>0.38107681419783329</v>
+        <v>0.19053840709891665</v>
       </c>
       <c r="B72" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.7941100000000001</v>
       </c>
       <c r="C72" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.89968207164921565</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0">
-        <v>0.38652076868637381</v>
+        <v>0.1932603843431869</v>
       </c>
       <c r="B73" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.7989599999999999</v>
       </c>
       <c r="C73" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.90211417338628785</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0">
-        <v>0.39196472317491426</v>
+        <v>0.19598236158745713</v>
       </c>
       <c r="B74" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.80365</v>
       </c>
       <c r="C74" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.90446604083925053</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0">
-        <v>0.39740867766345472</v>
+        <v>0.19870433883172736</v>
       </c>
       <c r="B75" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.80829</v>
       </c>
       <c r="C75" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.90679283507842889</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0">
-        <v>0.40285263215199524</v>
+        <v>0.20142631607599762</v>
       </c>
       <c r="B76" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.8129900000000001</v>
       </c>
       <c r="C76" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.9091497171741485</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0">
-        <v>0.4082965866405357</v>
+        <v>0.20414829332026785</v>
       </c>
       <c r="B77" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.81776</v>
       </c>
       <c r="C77" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.91154170176916594</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0">
-        <v>0.41374054112907616</v>
+        <v>0.20687027056453808</v>
       </c>
       <c r="B78" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.8224199999999999</v>
       </c>
       <c r="C78" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.91387852529385794</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0">
-        <v>0.41918449561761667</v>
+        <v>0.20959224780880834</v>
       </c>
       <c r="B79" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.82698</v>
       </c>
       <c r="C79" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.91616520239098165</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0">
-        <v>0.42462845010615707</v>
+        <v>0.21231422505307854</v>
       </c>
       <c r="B80" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.8315300000000001</v>
       </c>
       <c r="C80" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.91844686484534843</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0">
-        <v>0.43007240459469764</v>
+        <v>0.21503620229734882</v>
       </c>
       <c r="B81" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.8359700000000001</v>
       </c>
       <c r="C81" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.92067336622938978</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0">
-        <v>0.4355163590832381</v>
+        <v>0.21775817954161905</v>
       </c>
       <c r="B82" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.8403799999999999</v>
       </c>
       <c r="C82" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.92288482368516056</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0">
-        <v>0.44096031357177851</v>
+        <v>0.22048015678588925</v>
       </c>
       <c r="B83" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.84473</v>
       </c>
       <c r="C83" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.92506619328439033</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0">
-        <v>0.44640426806031908</v>
+        <v>0.22320213403015954</v>
       </c>
       <c r="B84" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.84904</v>
       </c>
       <c r="C84" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.92722750431259271</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0">
-        <v>0.45184822254885948</v>
+        <v>0.22592411127442974</v>
       </c>
       <c r="B85" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.8533500000000001</v>
       </c>
       <c r="C85" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.92938881534079509</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0">
-        <v>0.45729217703739994</v>
+        <v>0.22864608851869997</v>
       </c>
       <c r="B86" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.8575999999999999</v>
       </c>
       <c r="C86" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.93152003851245624</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0">
-        <v>0.46273613152594045</v>
+        <v>0.23136806576297023</v>
       </c>
       <c r="B87" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.86182</v>
       </c>
       <c r="C87" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.93363621775584704</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0">
-        <v>0.46818008601448091</v>
+        <v>0.23409004300724046</v>
       </c>
       <c r="B88" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.86595</v>
       </c>
       <c r="C88" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.93570726521442604</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0">
-        <v>0.47362404050302137</v>
+        <v>0.23681202025151069</v>
       </c>
       <c r="B89" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.87008</v>
       </c>
       <c r="C89" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.93777831267300504</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0">
-        <v>0.47906799499156189</v>
+        <v>0.23953399749578094</v>
       </c>
       <c r="B90" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.87412</v>
       </c>
       <c r="C90" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.93980422834677246</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0">
-        <v>0.48451194948010234</v>
+        <v>0.24225597474005117</v>
       </c>
       <c r="B91" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.8781099999999999</v>
       </c>
       <c r="C91" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.94180507080675557</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0">
-        <v>0.4899559039686428</v>
+        <v>0.2449779519843214</v>
       </c>
       <c r="B92" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.88205</v>
       </c>
       <c r="C92" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.94378084005295459</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0">
-        <v>0.49539985845718332</v>
+        <v>0.24769992922859166</v>
       </c>
       <c r="B93" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.8859900000000001</v>
       </c>
       <c r="C93" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.94575660929915351</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0">
-        <v>0.50084381294572378</v>
+        <v>0.25042190647286189</v>
       </c>
       <c r="B94" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.88988</v>
       </c>
       <c r="C94" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.94770730533156811</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0">
-        <v>0.50628776743426418</v>
+        <v>0.25314388371713209</v>
       </c>
       <c r="B95" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.8936900000000001</v>
       </c>
       <c r="C95" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.94961788422192805</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0">
-        <v>0.51173172192280469</v>
+        <v>0.25586586096140235</v>
       </c>
       <c r="B96" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.89747</v>
       </c>
       <c r="C96" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.95151341918401722</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0">
-        <v>0.51717567641134521</v>
+        <v>0.2585878382056726</v>
       </c>
       <c r="B97" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.90126</v>
       </c>
       <c r="C97" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.95341396878886342</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0">
-        <v>0.52261963089988561</v>
+        <v>0.26130981544994281</v>
       </c>
       <c r="B98" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.9049199999999999</v>
       </c>
       <c r="C98" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.95524932803787044</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0">
-        <v>0.52806358538842613</v>
+        <v>0.26403179269421306</v>
       </c>
       <c r="B99" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.9085300000000001</v>
       </c>
       <c r="C99" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.95705961407309337</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0">
-        <v>0.53350753987696664</v>
+        <v>0.26675376993848332</v>
       </c>
       <c r="B100" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.91215</v>
       </c>
       <c r="C100" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.95887491475107312</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0">
-        <v>0.53895149436550716</v>
+        <v>0.26947574718275358</v>
       </c>
       <c r="B101" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.9156500000000001</v>
       </c>
       <c r="C101" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.96063003971597061</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="0">
-        <v>0.54439544885404756</v>
+        <v>0.27219772442702378</v>
       </c>
       <c r="B102" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.9191</v>
       </c>
       <c r="C102" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.96236009146708379</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="0">
-        <v>0.54983940334258807</v>
+        <v>0.27491970167129404</v>
       </c>
       <c r="B103" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.9224699999999999</v>
       </c>
       <c r="C103" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.96405002607614221</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="0">
-        <v>0.55528335783112859</v>
+        <v>0.27764167891556429</v>
       </c>
       <c r="B104" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.9258599999999999</v>
       </c>
       <c r="C104" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.96574998997071437</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="0">
-        <v>0.56072731231966899</v>
+        <v>0.2803636561598345</v>
       </c>
       <c r="B105" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.9292499999999999</v>
       </c>
       <c r="C105" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.96744995386528654</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="0">
-        <v>0.56617126680820951</v>
+        <v>0.28308563340410475</v>
       </c>
       <c r="B106" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.93255</v>
       </c>
       <c r="C106" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.96910478597504701</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="0">
-        <v>0.57161522129675002</v>
+        <v>0.28580761064837501</v>
       </c>
       <c r="B107" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.9357899999999999</v>
       </c>
       <c r="C107" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.97072953022826636</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="0">
-        <v>0.57705917578529042</v>
+        <v>0.28852958789264521</v>
       </c>
       <c r="B108" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.9389799999999999</v>
       </c>
       <c r="C108" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.97232920126770161</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="0">
-        <v>0.58250313027383094</v>
+        <v>0.29125156513691547</v>
       </c>
       <c r="B109" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.9420900000000001</v>
       </c>
       <c r="C109" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.973888755165082</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="0">
-        <v>0.58794708476237145</v>
+        <v>0.29397354238118573</v>
       </c>
       <c r="B110" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.9451700000000001</v>
       </c>
       <c r="C110" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.97543326513419182</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="0">
-        <v>0.59339103925091186</v>
+        <v>0.29669551962545593</v>
       </c>
       <c r="B111" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.94817</v>
       </c>
       <c r="C111" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.97693765796124676</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0">
-        <v>0.59883499373945226</v>
+        <v>0.29941749686972613</v>
       </c>
       <c r="B112" s="0">
-        <v>1.9942200000000001</v>
+        <v>1.95112</v>
       </c>
       <c r="C112" s="0">
-        <v>1.0000300878565411</v>
+        <v>0.97841697757451751</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0">
-        <v>0.60427894822799288</v>
+        <v>0.30213947411399644</v>
       </c>
       <c r="B113" s="0">
-        <v>1.99421</v>
+        <v>1.9540500000000001</v>
       </c>
       <c r="C113" s="0">
-        <v>1.0000250732137841</v>
+        <v>0.97988626790227462</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0">
-        <v>0.60972290271653329</v>
+        <v>0.30486145135826664</v>
       </c>
       <c r="B114" s="0">
-        <v>1.99421</v>
+        <v>1.9569099999999999</v>
       </c>
       <c r="C114" s="0">
-        <v>1.0000250732137841</v>
+        <v>0.98132045573073368</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0">
-        <v>0.61516685720507369</v>
+        <v>0.30758342860253685</v>
       </c>
       <c r="B115" s="0">
-        <v>1.99421</v>
+        <v>1.9596899999999999</v>
       </c>
       <c r="C115" s="0">
-        <v>1.0000250732137841</v>
+        <v>0.98271452641713797</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0">
-        <v>0.62061081169361432</v>
+        <v>0.31030540584680716</v>
       </c>
       <c r="B116" s="0">
-        <v>1.99421</v>
+        <v>1.96245</v>
       </c>
       <c r="C116" s="0">
-        <v>1.0000250732137841</v>
+        <v>0.98409856781802862</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0">
-        <v>0.62605476618215472</v>
+        <v>0.31302738309107736</v>
       </c>
       <c r="B117" s="0">
-        <v>1.99421</v>
+        <v>1.96519</v>
       </c>
       <c r="C117" s="0">
-        <v>1.0000250732137841</v>
+        <v>0.98547257993340542</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0">
-        <v>0.63149872067069512</v>
+        <v>0.31574936033534756</v>
       </c>
       <c r="B118" s="0">
-        <v>1.99421</v>
+        <v>1.9678599999999999</v>
       </c>
       <c r="C118" s="0">
-        <v>1.0000250732137841</v>
+        <v>0.98681148954948439</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0">
-        <v>0.63694267515923564</v>
+        <v>0.31847133757961782</v>
       </c>
       <c r="B119" s="0">
-        <v>1.99421</v>
+        <v>1.9704299999999999</v>
       </c>
       <c r="C119" s="0">
-        <v>1.0000250732137841</v>
+        <v>0.98810025273799484</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0">
-        <v>0.64238662964777615</v>
+        <v>0.32119331482388808</v>
       </c>
       <c r="B120" s="0">
-        <v>1.99421</v>
+        <v>1.97299</v>
       </c>
       <c r="C120" s="0">
-        <v>1.0000250732137841</v>
+        <v>0.98938400128374848</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0">
-        <v>0.64783058413631667</v>
+        <v>0.32391529206815833</v>
       </c>
       <c r="B121" s="0">
-        <v>1.99421</v>
+        <v>1.9755100000000001</v>
       </c>
       <c r="C121" s="0">
-        <v>1.0000250732137841</v>
+        <v>0.99064769125847474</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0">
-        <v>0.65327453862485707</v>
+        <v>0.32663726931242854</v>
       </c>
       <c r="B122" s="0">
-        <v>1.99421</v>
+        <v>1.9779800000000001</v>
       </c>
       <c r="C122" s="0">
-        <v>1.0000250732137841</v>
+        <v>0.99188630801941668</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0">
-        <v>0.65871849311339759</v>
+        <v>0.32935924655669879</v>
       </c>
       <c r="B123" s="0">
-        <v>1.99421</v>
+        <v>1.9803599999999999</v>
       </c>
       <c r="C123" s="0">
-        <v>1.0000250732137841</v>
+        <v>0.99307979299554683</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0">
-        <v>0.6641624476019381</v>
+        <v>0.33208122380096905</v>
       </c>
       <c r="B124" s="0">
-        <v>1.99421</v>
+        <v>1.98272</v>
       </c>
       <c r="C124" s="0">
-        <v>1.0000250732137841</v>
+        <v>0.99426324868616356</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0">
-        <v>0.6696064020904785</v>
+        <v>0.33480320104523925</v>
       </c>
       <c r="B125" s="0">
-        <v>1.99421</v>
+        <v>1.98506</v>
       </c>
       <c r="C125" s="0">
-        <v>1.0000250732137841</v>
+        <v>0.99543667509126643</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0">
-        <v>0.67505035657901902</v>
+        <v>0.33752517828950951</v>
       </c>
       <c r="B126" s="0">
-        <v>1.99421</v>
+        <v>1.9873099999999999</v>
       </c>
       <c r="C126" s="0">
-        <v>1.0000250732137841</v>
+        <v>0.99656496971155761</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0">
-        <v>0.68049431106755953</v>
+        <v>0.34024715553377977</v>
       </c>
       <c r="B127" s="0">
-        <v>1.99421</v>
+        <v>1.98949</v>
       </c>
       <c r="C127" s="0">
-        <v>1.0000250732137841</v>
+        <v>0.99765816183255096</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0">
-        <v>0.68593826555609994</v>
+        <v>0.34296913277804997</v>
       </c>
       <c r="B128" s="0">
-        <v>1.99421</v>
+        <v>1.9914799999999999</v>
       </c>
       <c r="C128" s="0">
-        <v>1.0000250732137841</v>
+        <v>0.99865607574116411</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0">
-        <v>0.69138222004464045</v>
+        <v>0.34569111002232022</v>
       </c>
       <c r="B129" s="0">
-        <v>1.99421</v>
+        <v>1.9933399999999999</v>
       </c>
       <c r="C129" s="0">
-        <v>1.0000250732137841</v>
+        <v>0.99958879929393818</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0">
-        <v>0.69682617453318096</v>
+        <v>0.34841308726659048</v>
       </c>
       <c r="B130" s="0">
-        <v>1.99421</v>
+        <v>1.9941599999999999</v>
       </c>
       <c r="C130" s="0">
-        <v>1.0000250732137841</v>
+        <v>0.99999999999999989</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0">
-        <v>0.70227012902172137</v>
+        <v>0.35113506451086068</v>
       </c>
       <c r="B131" s="0">
-        <v>1.99421</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C131" s="0">
-        <v>1.0000250732137841</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0">
-        <v>0.70771408351026177</v>
+        <v>0.35385704175513089</v>
       </c>
       <c r="B132" s="0">
-        <v>1.99421</v>
+        <v>1.9942299999999999</v>
       </c>
       <c r="C132" s="0">
-        <v>1.0000250732137841</v>
+        <v>1.0000351024992979</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0">
-        <v>0.7131580379988024</v>
+        <v>0.3565790189994012</v>
       </c>
       <c r="B133" s="0">
-        <v>1.99421</v>
+        <v>1.9942299999999999</v>
       </c>
       <c r="C133" s="0">
-        <v>1.0000250732137841</v>
+        <v>1.0000351024992979</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0">
-        <v>0.7186019924873428</v>
+        <v>0.3593009962436714</v>
       </c>
       <c r="B134" s="0">
-        <v>1.99421</v>
+        <v>1.9942299999999999</v>
       </c>
       <c r="C134" s="0">
-        <v>1.0000250732137841</v>
+        <v>1.0000351024992979</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0">
-        <v>0.7240459469758832</v>
+        <v>0.3620229734879416</v>
       </c>
       <c r="B135" s="0">
-        <v>1.99421</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C135" s="0">
-        <v>1.0000250732137841</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0">
-        <v>0.72948990146442383</v>
+        <v>0.36474495073221191</v>
       </c>
       <c r="B136" s="0">
-        <v>1.99421</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C136" s="0">
-        <v>1.0000250732137841</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0">
-        <v>0.73493385595296423</v>
+        <v>0.36746692797648212</v>
       </c>
       <c r="B137" s="0">
-        <v>1.99421</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C137" s="0">
-        <v>1.0000250732137841</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0">
-        <v>0.74037781044150464</v>
+        <v>0.37018890522075232</v>
       </c>
       <c r="B138" s="0">
-        <v>1.99421</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C138" s="0">
-        <v>1.0000250732137841</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0">
-        <v>0.74582176493004526</v>
+        <v>0.37291088246502263</v>
       </c>
       <c r="B139" s="0">
-        <v>1.99421</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C139" s="0">
-        <v>1.0000250732137841</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0">
-        <v>0.75126571941858566</v>
+        <v>0.37563285970929283</v>
       </c>
       <c r="B140" s="0">
-        <v>1.99421</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C140" s="0">
-        <v>1.0000250732137841</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0">
-        <v>0.75670967390712607</v>
+        <v>0.37835483695356303</v>
       </c>
       <c r="B141" s="0">
-        <v>1.9942</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C141" s="0">
-        <v>1.0000200585710273</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0">
-        <v>0.76215362839566658</v>
+        <v>0.38107681419783329</v>
       </c>
       <c r="B142" s="0">
-        <v>1.9942</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C142" s="0">
-        <v>1.0000200585710273</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0">
-        <v>0.7675975828842071</v>
+        <v>0.38379879144210355</v>
       </c>
       <c r="B143" s="0">
-        <v>1.9942</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C143" s="0">
-        <v>1.0000200585710273</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0">
-        <v>0.77304153737274761</v>
+        <v>0.38652076868637381</v>
       </c>
       <c r="B144" s="0">
-        <v>1.9942</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C144" s="0">
-        <v>1.0000200585710273</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0">
-        <v>0.77848549186128801</v>
+        <v>0.38924274593064401</v>
       </c>
       <c r="B145" s="0">
-        <v>1.9942</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C145" s="0">
-        <v>1.0000200585710273</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0">
-        <v>0.78392944634982853</v>
+        <v>0.39196472317491426</v>
       </c>
       <c r="B146" s="0">
-        <v>1.9942</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C146" s="0">
-        <v>1.0000200585710273</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0">
-        <v>0.78937340083836904</v>
+        <v>0.39468670041918452</v>
       </c>
       <c r="B147" s="0">
-        <v>1.9942</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C147" s="0">
-        <v>1.0000200585710273</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0">
-        <v>0.79481735532690945</v>
+        <v>0.39740867766345472</v>
       </c>
       <c r="B148" s="0">
-        <v>1.9942</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C148" s="0">
-        <v>1.0000200585710273</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="0">
-        <v>0.80026130981544996</v>
+        <v>0.40013065490772498</v>
       </c>
       <c r="B149" s="0">
-        <v>1.9942</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C149" s="0">
-        <v>1.0000200585710273</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0">
-        <v>0.80570526430399048</v>
+        <v>0.40285263215199524</v>
       </c>
       <c r="B150" s="0">
-        <v>1.9942</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C150" s="0">
-        <v>1.0000200585710273</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0">
-        <v>0.81114921879253088</v>
+        <v>0.40557460939626544</v>
       </c>
       <c r="B151" s="0">
-        <v>1.9942</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C151" s="0">
-        <v>1.0000200585710273</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="0">
-        <v>0.81659317328107139</v>
+        <v>0.4082965866405357</v>
       </c>
       <c r="B152" s="0">
-        <v>1.9942</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C152" s="0">
-        <v>1.0000200585710273</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="0">
-        <v>0.82203712776961191</v>
+        <v>0.41101856388480595</v>
       </c>
       <c r="B153" s="0">
-        <v>1.9942</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C153" s="0">
-        <v>1.0000200585710273</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0">
-        <v>0.82748108225815231</v>
+        <v>0.41374054112907616</v>
       </c>
       <c r="B154" s="0">
-        <v>1.9942</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C154" s="0">
-        <v>1.0000200585710273</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="0">
-        <v>0.83292503674669272</v>
+        <v>0.41646251837334636</v>
       </c>
       <c r="B155" s="0">
-        <v>1.9942</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C155" s="0">
-        <v>1.0000200585710273</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0">
-        <v>0.83836899123523334</v>
+        <v>0.41918449561761667</v>
       </c>
       <c r="B156" s="0">
-        <v>1.9942</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C156" s="0">
-        <v>1.0000200585710273</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0">
-        <v>0.84381294572377374</v>
+        <v>0.42190647286188687</v>
       </c>
       <c r="B157" s="0">
-        <v>1.9942</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C157" s="0">
-        <v>1.0000200585710273</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0">
-        <v>0.84925690021231415</v>
+        <v>0.42462845010615707</v>
       </c>
       <c r="B158" s="0">
-        <v>1.9942</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C158" s="0">
-        <v>1.0000200585710273</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0">
-        <v>0.85470085470085466</v>
+        <v>0.42735042735042733</v>
       </c>
       <c r="B159" s="0">
-        <v>1.9942</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C159" s="0">
-        <v>1.0000200585710273</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="0">
-        <v>0.86014480918939529</v>
+        <v>0.43007240459469764</v>
       </c>
       <c r="B160" s="0">
-        <v>1.9942</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C160" s="0">
-        <v>1.0000200585710273</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0">
-        <v>0.86558876367793569</v>
+        <v>0.43279438183896785</v>
       </c>
       <c r="B161" s="0">
-        <v>1.9942</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C161" s="0">
-        <v>1.0000200585710273</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0">
-        <v>0.87103271816647621</v>
+        <v>0.4355163590832381</v>
       </c>
       <c r="B162" s="0">
-        <v>1.9942</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C162" s="0">
-        <v>1.0000200585710273</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="0">
-        <v>0.87647667265501661</v>
+        <v>0.4382383363275083</v>
       </c>
       <c r="B163" s="0">
-        <v>1.9942</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C163" s="0">
-        <v>1.0000200585710273</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0">
-        <v>0.88192062714355701</v>
+        <v>0.44096031357177851</v>
       </c>
       <c r="B164" s="0">
-        <v>1.9942</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C164" s="0">
-        <v>1.0000200585710273</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="0">
-        <v>0.88736458163209753</v>
+        <v>0.44368229081604876</v>
       </c>
       <c r="B165" s="0">
-        <v>1.9942</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C165" s="0">
-        <v>1.0000200585710273</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="0">
-        <v>0.89280853612063815</v>
+        <v>0.44640426806031908</v>
       </c>
       <c r="B166" s="0">
-        <v>1.9941899999999999</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C166" s="0">
-        <v>1.0000150439282705</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="0">
-        <v>0.89825249060917856</v>
+        <v>0.44912624530458928</v>
       </c>
       <c r="B167" s="0">
-        <v>1.9941899999999999</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C167" s="0">
-        <v>1.0000150439282705</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="0">
-        <v>0.90369644509771896</v>
+        <v>0.45184822254885948</v>
       </c>
       <c r="B168" s="0">
-        <v>1.9941899999999999</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C168" s="0">
-        <v>1.0000150439282705</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0">
-        <v>0.90914039958625947</v>
+        <v>0.45457019979312974</v>
       </c>
       <c r="B169" s="0">
-        <v>1.9941899999999999</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C169" s="0">
-        <v>1.0000150439282705</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0">
-        <v>0.91458435407479988</v>
+        <v>0.45729217703739994</v>
       </c>
       <c r="B170" s="0">
-        <v>1.9941899999999999</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C170" s="0">
-        <v>1.0000150439282705</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="0">
-        <v>0.92002830856334028</v>
+        <v>0.46001415428167014</v>
       </c>
       <c r="B171" s="0">
-        <v>1.9941899999999999</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C171" s="0">
-        <v>1.0000150439282705</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0">
-        <v>0.92547226305188091</v>
+        <v>0.46273613152594045</v>
       </c>
       <c r="B172" s="0">
-        <v>1.9941899999999999</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C172" s="0">
-        <v>1.0000150439282705</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0">
-        <v>0.93091621754042142</v>
+        <v>0.46545810877021071</v>
       </c>
       <c r="B173" s="0">
-        <v>1.9941899999999999</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C173" s="0">
-        <v>1.0000150439282705</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="0">
-        <v>0.93636017202896182</v>
+        <v>0.46818008601448091</v>
       </c>
       <c r="B174" s="0">
-        <v>1.9941899999999999</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C174" s="0">
-        <v>1.0000150439282705</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="0">
-        <v>0.94180412651750234</v>
+        <v>0.47090206325875117</v>
       </c>
       <c r="B175" s="0">
-        <v>1.9941899999999999</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C175" s="0">
-        <v>1.0000150439282705</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0">
-        <v>0.94724808100604274</v>
+        <v>0.47362404050302137</v>
       </c>
       <c r="B176" s="0">
-        <v>1.9941899999999999</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C176" s="0">
-        <v>1.0000150439282705</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="0">
-        <v>0.95269203549458337</v>
+        <v>0.47634601774729168</v>
       </c>
       <c r="B177" s="0">
-        <v>1.9941899999999999</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C177" s="0">
-        <v>1.0000150439282705</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="0">
-        <v>0.95813598998312377</v>
+        <v>0.47906799499156189</v>
       </c>
       <c r="B178" s="0">
-        <v>1.9941899999999999</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C178" s="0">
-        <v>1.0000150439282705</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="0">
-        <v>0.96357994447166428</v>
+        <v>0.48178997223583214</v>
       </c>
       <c r="B179" s="0">
-        <v>1.9941899999999999</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C179" s="0">
-        <v>1.0000150439282705</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="0">
-        <v>0.96902389896020469</v>
+        <v>0.48451194948010234</v>
       </c>
       <c r="B180" s="0">
-        <v>1.9941899999999999</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C180" s="0">
-        <v>1.0000150439282705</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="0">
-        <v>0.97446785344874509</v>
+        <v>0.48723392672437255</v>
       </c>
       <c r="B181" s="0">
-        <v>1.9941899999999999</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C181" s="0">
-        <v>1.0000150439282705</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="0">
-        <v>0.97991180793728561</v>
+        <v>0.4899559039686428</v>
       </c>
       <c r="B182" s="0">
-        <v>1.9941899999999999</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C182" s="0">
-        <v>1.0000150439282705</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="0">
-        <v>0.98535576242582623</v>
+        <v>0.49267788121291312</v>
       </c>
       <c r="B183" s="0">
-        <v>1.9941899999999999</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C183" s="0">
-        <v>1.0000150439282705</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="0">
-        <v>0.99079971691436663</v>
+        <v>0.49539985845718332</v>
       </c>
       <c r="B184" s="0">
-        <v>1.9941899999999999</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C184" s="0">
-        <v>1.0000150439282705</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="0">
-        <v>0.99624367140290704</v>
+        <v>0.49812183570145352</v>
       </c>
       <c r="B185" s="0">
-        <v>1.9941899999999999</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C185" s="0">
-        <v>1.0000150439282705</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="0">
-        <v>1.0016876258914476</v>
+        <v>0.50084381294572378</v>
       </c>
       <c r="B186" s="0">
-        <v>1.9941899999999999</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C186" s="0">
-        <v>1.0000150439282705</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="0">
-        <v>1.0071315803799881</v>
+        <v>0.50356579018999403</v>
       </c>
       <c r="B187" s="0">
-        <v>1.9941899999999999</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C187" s="0">
-        <v>1.0000150439282705</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="0">
-        <v>1.0125755348685284</v>
+        <v>0.50628776743426418</v>
       </c>
       <c r="B188" s="0">
-        <v>1.9941899999999999</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C188" s="0">
-        <v>1.0000150439282705</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="0">
-        <v>1.0180194893570691</v>
+        <v>0.50900974467853455</v>
       </c>
       <c r="B189" s="0">
-        <v>1.9941899999999999</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C189" s="0">
-        <v>1.0000150439282705</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="0">
-        <v>1.0234634438456094</v>
+        <v>0.51173172192280469</v>
       </c>
       <c r="B190" s="0">
-        <v>1.9941899999999999</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C190" s="0">
-        <v>1.0000150439282705</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="0">
-        <v>1.0289073983341499</v>
+        <v>0.51445369916707495</v>
       </c>
       <c r="B191" s="0">
-        <v>1.9941800000000001</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C191" s="0">
-        <v>1.0000100292855136</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="0">
-        <v>1.0343513528226904</v>
+        <v>0.51717567641134521</v>
       </c>
       <c r="B192" s="0">
-        <v>1.9941800000000001</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C192" s="0">
-        <v>1.0000100292855136</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="0">
-        <v>1.0397953073112309</v>
+        <v>0.51989765365561547</v>
       </c>
       <c r="B193" s="0">
-        <v>1.9941800000000001</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C193" s="0">
-        <v>1.0000100292855136</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="0">
-        <v>1.0452392617997712</v>
+        <v>0.52261963089988561</v>
       </c>
       <c r="B194" s="0">
-        <v>1.9941800000000001</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C194" s="0">
-        <v>1.0000100292855136</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="0">
-        <v>1.050683216288312</v>
+        <v>0.52534160814415598</v>
       </c>
       <c r="B195" s="0">
-        <v>1.9941800000000001</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C195" s="0">
-        <v>1.0000100292855136</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="0">
-        <v>1.0561271707768523</v>
+        <v>0.52806358538842613</v>
       </c>
       <c r="B196" s="0">
-        <v>1.9941800000000001</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C196" s="0">
-        <v>1.0000100292855136</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="0">
-        <v>1.0615711252653928</v>
+        <v>0.53078556263269638</v>
       </c>
       <c r="B197" s="0">
-        <v>1.9941800000000001</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C197" s="0">
-        <v>1.0000100292855136</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="0">
-        <v>1.0670150797539333</v>
+        <v>0.53350753987696664</v>
       </c>
       <c r="B198" s="0">
-        <v>1.9941800000000001</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C198" s="0">
-        <v>1.0000100292855136</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="0">
-        <v>1.0724590342424736</v>
+        <v>0.53622951712123679</v>
       </c>
       <c r="B199" s="0">
-        <v>1.9941800000000001</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C199" s="0">
-        <v>1.0000100292855136</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="0">
-        <v>1.0779029887310143</v>
+        <v>0.53895149436550716</v>
       </c>
       <c r="B200" s="0">
-        <v>1.9941800000000001</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C200" s="0">
-        <v>1.0000100292855136</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="0">
-        <v>1.0833469432195548</v>
+        <v>0.54167347160977741</v>
       </c>
       <c r="B201" s="0">
-        <v>1.9941800000000001</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C201" s="0">
-        <v>1.0000100292855136</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="0">
-        <v>1.0887908977080951</v>
+        <v>0.54439544885404756</v>
       </c>
       <c r="B202" s="0">
-        <v>1.9941800000000001</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C202" s="0">
-        <v>1.0000100292855136</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="0">
-        <v>1.0942348521966356</v>
+        <v>0.54711742609831782</v>
       </c>
       <c r="B203" s="0">
-        <v>1.9941800000000001</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C203" s="0">
-        <v>1.0000100292855136</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="0">
-        <v>1.0996788066851761</v>
+        <v>0.54983940334258807</v>
       </c>
       <c r="B204" s="0">
-        <v>1.9941800000000001</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C204" s="0">
-        <v>1.0000100292855136</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="0">
-        <v>1.1051227611737164</v>
+        <v>0.55256138058685822</v>
       </c>
       <c r="B205" s="0">
-        <v>1.9941800000000001</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C205" s="0">
-        <v>1.0000100292855136</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="0">
-        <v>1.1105667156622572</v>
+        <v>0.55528335783112859</v>
       </c>
       <c r="B206" s="0">
-        <v>1.9941800000000001</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C206" s="0">
-        <v>1.0000100292855136</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="0">
-        <v>1.1160106701507977</v>
+        <v>0.55800533507539885</v>
       </c>
       <c r="B207" s="0">
-        <v>1.9941800000000001</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C207" s="0">
-        <v>1.0000100292855136</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="0">
-        <v>1.121454624639338</v>
+        <v>0.56072731231966899</v>
       </c>
       <c r="B208" s="0">
-        <v>1.9941800000000001</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C208" s="0">
-        <v>1.0000100292855136</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="0">
-        <v>1.1268985791278785</v>
+        <v>0.56344928956393925</v>
       </c>
       <c r="B209" s="0">
-        <v>1.9941800000000001</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C209" s="0">
-        <v>1.0000100292855136</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="0">
-        <v>1.132342533616419</v>
+        <v>0.56617126680820951</v>
       </c>
       <c r="B210" s="0">
-        <v>1.9941800000000001</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C210" s="0">
-        <v>1.0000100292855136</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="0">
-        <v>1.1377864881049593</v>
+        <v>0.56889324405247965</v>
       </c>
       <c r="B211" s="0">
-        <v>1.9941800000000001</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C211" s="0">
-        <v>1.0000100292855136</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="0">
-        <v>1.1432304425935</v>
+        <v>0.57161522129675002</v>
       </c>
       <c r="B212" s="0">
-        <v>1.9941800000000001</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C212" s="0">
-        <v>1.0000100292855136</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="0">
-        <v>1.1486743970820403</v>
+        <v>0.57433719854102017</v>
       </c>
       <c r="B213" s="0">
-        <v>1.9941800000000001</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C213" s="0">
-        <v>1.0000100292855136</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="0">
-        <v>1.1541183515705808</v>
+        <v>0.57705917578529042</v>
       </c>
       <c r="B214" s="0">
-        <v>1.9941800000000001</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C214" s="0">
-        <v>1.0000100292855136</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="0">
-        <v>1.1595623060591214</v>
+        <v>0.57978115302956068</v>
       </c>
       <c r="B215" s="0">
-        <v>1.99417</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C215" s="0">
-        <v>1.0000050146427568</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="0">
-        <v>1.1650062605476619</v>
+        <v>0.58250313027383094</v>
       </c>
       <c r="B216" s="0">
-        <v>1.99417</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C216" s="0">
-        <v>1.0000050146427568</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="0">
-        <v>1.1704502150362022</v>
+        <v>0.58522510751810108</v>
       </c>
       <c r="B217" s="0">
-        <v>1.99417</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C217" s="0">
-        <v>1.0000050146427568</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="0">
-        <v>1.1758941695247429</v>
+        <v>0.58794708476237145</v>
       </c>
       <c r="B218" s="0">
-        <v>1.99417</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C218" s="0">
-        <v>1.0000050146427568</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="0">
-        <v>1.1813381240132832</v>
+        <v>0.5906690620066416</v>
       </c>
       <c r="B219" s="0">
-        <v>1.99417</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C219" s="0">
-        <v>1.0000050146427568</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="0">
-        <v>1.1867820785018237</v>
+        <v>0.59339103925091186</v>
       </c>
       <c r="B220" s="0">
-        <v>1.99417</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C220" s="0">
-        <v>1.0000050146427568</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="0">
-        <v>1.1922260329903642</v>
+        <v>0.59611301649518211</v>
       </c>
       <c r="B221" s="0">
-        <v>1.99417</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C221" s="0">
-        <v>1.0000050146427568</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="0">
-        <v>1.1976699874789045</v>
+        <v>0.59883499373945226</v>
       </c>
       <c r="B222" s="0">
-        <v>1.99417</v>
+        <v>1.9942200000000001</v>
       </c>
       <c r="C222" s="0">
-        <v>1.0000050146427568</v>
+        <v>1.0000300878565411</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="0">
-        <v>1.2031139419674453</v>
+        <v>0.60155697098372263</v>
       </c>
       <c r="B223" s="0">
-        <v>1.99417</v>
+        <v>1.99421</v>
       </c>
       <c r="C223" s="0">
-        <v>1.0000050146427568</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="0">
-        <v>1.2085578964559858</v>
+        <v>0.60427894822799288</v>
       </c>
       <c r="B224" s="0">
-        <v>1.99417</v>
+        <v>1.99421</v>
       </c>
       <c r="C224" s="0">
-        <v>1.0000050146427568</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="0">
-        <v>1.2140018509445261</v>
+        <v>0.60700092547226303</v>
       </c>
       <c r="B225" s="0">
-        <v>1.99417</v>
+        <v>1.99421</v>
       </c>
       <c r="C225" s="0">
-        <v>1.0000050146427568</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="0">
-        <v>1.2194458054330666</v>
+        <v>0.60972290271653329</v>
       </c>
       <c r="B226" s="0">
-        <v>1.99417</v>
+        <v>1.99421</v>
       </c>
       <c r="C226" s="0">
-        <v>1.0000050146427568</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="0">
-        <v>1.2248897599216071</v>
+        <v>0.61244487996080355</v>
       </c>
       <c r="B227" s="0">
-        <v>1.99417</v>
+        <v>1.99421</v>
       </c>
       <c r="C227" s="0">
-        <v>1.0000050146427568</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="0">
-        <v>1.2303337144101474</v>
+        <v>0.61516685720507369</v>
       </c>
       <c r="B228" s="0">
-        <v>1.99417</v>
+        <v>1.99421</v>
       </c>
       <c r="C228" s="0">
-        <v>1.0000050146427568</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="0">
-        <v>1.2357776688986881</v>
+        <v>0.61788883444934406</v>
       </c>
       <c r="B229" s="0">
-        <v>1.99417</v>
+        <v>1.99421</v>
       </c>
       <c r="C229" s="0">
-        <v>1.0000050146427568</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="0">
-        <v>1.2412216233872286</v>
+        <v>0.62061081169361432</v>
       </c>
       <c r="B230" s="0">
-        <v>1.99417</v>
+        <v>1.99421</v>
       </c>
       <c r="C230" s="0">
-        <v>1.0000050146427568</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="0">
-        <v>1.2466655778757689</v>
+        <v>0.62333278893788446</v>
       </c>
       <c r="B231" s="0">
-        <v>1.99417</v>
+        <v>1.99421</v>
       </c>
       <c r="C231" s="0">
-        <v>1.0000050146427568</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="0">
-        <v>1.2521095323643094</v>
+        <v>0.62605476618215472</v>
       </c>
       <c r="B232" s="0">
-        <v>1.99417</v>
+        <v>1.99421</v>
       </c>
       <c r="C232" s="0">
-        <v>1.0000050146427568</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="0">
-        <v>1.25755348685285</v>
+        <v>0.62877674342642498</v>
       </c>
       <c r="B233" s="0">
-        <v>1.99417</v>
+        <v>1.99421</v>
       </c>
       <c r="C233" s="0">
-        <v>1.0000050146427568</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="0">
-        <v>1.2629974413413902</v>
+        <v>0.63149872067069512</v>
       </c>
       <c r="B234" s="0">
-        <v>1.99417</v>
+        <v>1.99421</v>
       </c>
       <c r="C234" s="0">
-        <v>1.0000050146427568</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="0">
-        <v>1.268441395829931</v>
+        <v>0.63422069791496549</v>
       </c>
       <c r="B235" s="0">
-        <v>1.99417</v>
+        <v>1.99421</v>
       </c>
       <c r="C235" s="0">
-        <v>1.0000050146427568</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="0">
-        <v>1.2738853503184713</v>
+        <v>0.63694267515923564</v>
       </c>
       <c r="B236" s="0">
-        <v>1.99417</v>
+        <v>1.99421</v>
       </c>
       <c r="C236" s="0">
-        <v>1.0000050146427568</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="0">
-        <v>1.2793293048070118</v>
+        <v>0.6396646524035059</v>
       </c>
       <c r="B237" s="0">
-        <v>1.99417</v>
+        <v>1.99421</v>
       </c>
       <c r="C237" s="0">
-        <v>1.0000050146427568</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="0">
-        <v>1.2847732592955523</v>
+        <v>0.64238662964777615</v>
       </c>
       <c r="B238" s="0">
-        <v>1.99417</v>
+        <v>1.99421</v>
       </c>
       <c r="C238" s="0">
-        <v>1.0000050146427568</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="0">
-        <v>1.2902172137840926</v>
+        <v>0.6451086068920463</v>
       </c>
       <c r="B239" s="0">
-        <v>1.99417</v>
+        <v>1.99421</v>
       </c>
       <c r="C239" s="0">
-        <v>1.0000050146427568</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="0">
-        <v>1.2956611682726333</v>
+        <v>0.64783058413631667</v>
       </c>
       <c r="B240" s="0">
-        <v>1.9941599999999999</v>
+        <v>1.99421</v>
       </c>
       <c r="C240" s="0">
-        <v>0.99999999999999989</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="0">
-        <v>1.3011051227611738</v>
+        <v>0.65055256138058692</v>
       </c>
       <c r="B241" s="0">
-        <v>1.9941599999999999</v>
+        <v>1.99421</v>
       </c>
       <c r="C241" s="0">
-        <v>0.99999999999999989</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="0">
-        <v>1.3065490772497141</v>
+        <v>0.65327453862485707</v>
       </c>
       <c r="B242" s="0">
-        <v>1.9941599999999999</v>
+        <v>1.99421</v>
       </c>
       <c r="C242" s="0">
-        <v>0.99999999999999989</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="0">
-        <v>1.3119930317382547</v>
+        <v>0.65599651586912733</v>
       </c>
       <c r="B243" s="0">
-        <v>1.9941599999999999</v>
+        <v>1.99421</v>
       </c>
       <c r="C243" s="0">
-        <v>0.99999999999999989</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="0">
-        <v>1.3174369862267952</v>
+        <v>0.65871849311339759</v>
       </c>
       <c r="B244" s="0">
-        <v>1.9941599999999999</v>
+        <v>1.99421</v>
       </c>
       <c r="C244" s="0">
-        <v>0.99999999999999989</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="0">
-        <v>1.3228809407153355</v>
+        <v>0.66144047035766773</v>
       </c>
       <c r="B245" s="0">
-        <v>1.9941599999999999</v>
+        <v>1.99421</v>
       </c>
       <c r="C245" s="0">
-        <v>0.99999999999999989</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="0">
-        <v>1.3283248952038762</v>
+        <v>0.6641624476019381</v>
       </c>
       <c r="B246" s="0">
-        <v>1.9941599999999999</v>
+        <v>1.99421</v>
       </c>
       <c r="C246" s="0">
-        <v>0.99999999999999989</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="0">
-        <v>1.3337688496924167</v>
+        <v>0.66688442484620836</v>
       </c>
       <c r="B247" s="0">
-        <v>1.9941599999999999</v>
+        <v>1.99421</v>
       </c>
       <c r="C247" s="0">
-        <v>0.99999999999999989</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="0">
-        <v>1.339212804180957</v>
+        <v>0.6696064020904785</v>
       </c>
       <c r="B248" s="0">
-        <v>1.9941599999999999</v>
+        <v>1.99421</v>
       </c>
       <c r="C248" s="0">
-        <v>0.99999999999999989</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="0">
-        <v>1.3446567586694975</v>
+        <v>0.67232837933474876</v>
       </c>
       <c r="B249" s="0">
-        <v>1.9941599999999999</v>
+        <v>1.99421</v>
       </c>
       <c r="C249" s="0">
-        <v>0.99999999999999989</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="0">
-        <v>1.350100713158038</v>
+        <v>0.67505035657901902</v>
       </c>
       <c r="B250" s="0">
-        <v>1.9941599999999999</v>
+        <v>1.99421</v>
       </c>
       <c r="C250" s="0">
-        <v>0.99999999999999989</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="0">
-        <v>1.3555446676465783</v>
+        <v>0.67777233382328916</v>
       </c>
       <c r="B251" s="0">
-        <v>1.9941599999999999</v>
+        <v>1.99421</v>
       </c>
       <c r="C251" s="0">
-        <v>0.99999999999999989</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="0">
-        <v>1.3609886221351191</v>
+        <v>0.68049431106755953</v>
       </c>
       <c r="B252" s="0">
-        <v>1.9941599999999999</v>
+        <v>1.99421</v>
       </c>
       <c r="C252" s="0">
-        <v>0.99999999999999989</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="0">
-        <v>1.3664325766236596</v>
+        <v>0.68321628831182979</v>
       </c>
       <c r="B253" s="0">
-        <v>1.9941599999999999</v>
+        <v>1.99421</v>
       </c>
       <c r="C253" s="0">
-        <v>0.99999999999999989</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="0">
-        <v>1.3718765311121999</v>
+        <v>0.68593826555609994</v>
       </c>
       <c r="B254" s="0">
-        <v>1.9941599999999999</v>
+        <v>1.99421</v>
       </c>
       <c r="C254" s="0">
-        <v>0.99999999999999989</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="0">
-        <v>1.3773204856007404</v>
+        <v>0.68866024280037019</v>
       </c>
       <c r="B255" s="0">
-        <v>1.9941599999999999</v>
+        <v>1.99421</v>
       </c>
       <c r="C255" s="0">
-        <v>0.99999999999999989</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="0">
-        <v>1.3827644400892809</v>
+        <v>0.69138222004464045</v>
       </c>
       <c r="B256" s="0">
-        <v>1.9941599999999999</v>
+        <v>1.99421</v>
       </c>
       <c r="C256" s="0">
-        <v>0.99999999999999989</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="0">
-        <v>1.3882083945778212</v>
+        <v>0.6941041972889106</v>
       </c>
       <c r="B257" s="0">
-        <v>1.9941599999999999</v>
+        <v>1.99421</v>
       </c>
       <c r="C257" s="0">
-        <v>0.99999999999999989</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="0">
-        <v>1.3936523490663619</v>
+        <v>0.69682617453318096</v>
       </c>
       <c r="B258" s="0">
-        <v>1.9941599999999999</v>
+        <v>1.99421</v>
       </c>
       <c r="C258" s="0">
-        <v>0.99999999999999989</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="0">
-        <v>1.3990963035549022</v>
+        <v>0.69954815177745111</v>
       </c>
       <c r="B259" s="0">
-        <v>1.9941599999999999</v>
+        <v>1.99421</v>
       </c>
       <c r="C259" s="0">
-        <v>0.99999999999999989</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="0">
-        <v>1.4045402580434427</v>
+        <v>0.70227012902172137</v>
       </c>
       <c r="B260" s="0">
-        <v>1.9941599999999999</v>
+        <v>1.99421</v>
       </c>
       <c r="C260" s="0">
-        <v>0.99999999999999989</v>
+        <v>1.0000250732137841</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="0">
+        <v>0.70499210626599162</v>
+      </c>
+      <c r="B261" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C261" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="0">
+        <v>0.70771408351026177</v>
+      </c>
+      <c r="B262" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C262" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="0">
+        <v>0.71043606075453214</v>
+      </c>
+      <c r="B263" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C263" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="0">
+        <v>0.7131580379988024</v>
+      </c>
+      <c r="B264" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C264" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="0">
+        <v>0.71588001524307254</v>
+      </c>
+      <c r="B265" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C265" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="0">
+        <v>0.7186019924873428</v>
+      </c>
+      <c r="B266" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C266" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="0">
+        <v>0.72132396973161306</v>
+      </c>
+      <c r="B267" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C267" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="0">
+        <v>0.7240459469758832</v>
+      </c>
+      <c r="B268" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C268" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="0">
+        <v>0.72676792422015357</v>
+      </c>
+      <c r="B269" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C269" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="0">
+        <v>0.72948990146442383</v>
+      </c>
+      <c r="B270" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C270" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="0">
+        <v>0.73221187870869398</v>
+      </c>
+      <c r="B271" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C271" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="0">
+        <v>0.73493385595296423</v>
+      </c>
+      <c r="B272" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C272" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="0">
+        <v>0.73765583319723449</v>
+      </c>
+      <c r="B273" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C273" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="0">
+        <v>0.74037781044150464</v>
+      </c>
+      <c r="B274" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C274" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="0">
+        <v>0.743099787685775</v>
+      </c>
+      <c r="B275" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C275" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="0">
+        <v>0.74582176493004526</v>
+      </c>
+      <c r="B276" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C276" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="0">
+        <v>0.74854374217431541</v>
+      </c>
+      <c r="B277" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C277" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="0">
+        <v>0.75126571941858566</v>
+      </c>
+      <c r="B278" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C278" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="0">
+        <v>0.75398769666285592</v>
+      </c>
+      <c r="B279" s="0">
+        <v>1.99421</v>
+      </c>
+      <c r="C279" s="0">
+        <v>1.0000250732137841</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="0">
+        <v>0.75670967390712607</v>
+      </c>
+      <c r="B280" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C280" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="0">
+        <v>0.75943165115139644</v>
+      </c>
+      <c r="B281" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C281" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="0">
+        <v>0.76215362839566658</v>
+      </c>
+      <c r="B282" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C282" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="0">
+        <v>0.76487560563993684</v>
+      </c>
+      <c r="B283" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C283" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="0">
+        <v>0.7675975828842071</v>
+      </c>
+      <c r="B284" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C284" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="0">
+        <v>0.77031956012847724</v>
+      </c>
+      <c r="B285" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C285" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="0">
+        <v>0.77304153737274761</v>
+      </c>
+      <c r="B286" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C286" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="0">
+        <v>0.77576351461701787</v>
+      </c>
+      <c r="B287" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C287" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="0">
+        <v>0.77848549186128801</v>
+      </c>
+      <c r="B288" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C288" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="0">
+        <v>0.78120746910555827</v>
+      </c>
+      <c r="B289" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C289" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="0">
+        <v>0.78392944634982853</v>
+      </c>
+      <c r="B290" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C290" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="0">
+        <v>0.78665142359409868</v>
+      </c>
+      <c r="B291" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C291" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="0">
+        <v>0.78937340083836904</v>
+      </c>
+      <c r="B292" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C292" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="0">
+        <v>0.7920953780826393</v>
+      </c>
+      <c r="B293" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C293" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="0">
+        <v>0.79481735532690945</v>
+      </c>
+      <c r="B294" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C294" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="0">
+        <v>0.7975393325711797</v>
+      </c>
+      <c r="B295" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C295" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="0">
+        <v>0.80026130981544996</v>
+      </c>
+      <c r="B296" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C296" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="0">
+        <v>0.80298328705972011</v>
+      </c>
+      <c r="B297" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C297" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="0">
+        <v>0.80570526430399048</v>
+      </c>
+      <c r="B298" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C298" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="0">
+        <v>0.80842724154826073</v>
+      </c>
+      <c r="B299" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C299" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="0">
+        <v>0.81114921879253088</v>
+      </c>
+      <c r="B300" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C300" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="0">
+        <v>0.81387119603680114</v>
+      </c>
+      <c r="B301" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C301" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="0">
+        <v>0.81659317328107139</v>
+      </c>
+      <c r="B302" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C302" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="0">
+        <v>0.81931515052534154</v>
+      </c>
+      <c r="B303" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C303" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="0">
+        <v>0.82203712776961191</v>
+      </c>
+      <c r="B304" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C304" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="0">
+        <v>0.82475910501388205</v>
+      </c>
+      <c r="B305" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C305" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="0">
+        <v>0.82748108225815231</v>
+      </c>
+      <c r="B306" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C306" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="0">
+        <v>0.83020305950242257</v>
+      </c>
+      <c r="B307" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C307" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="0">
+        <v>0.83292503674669272</v>
+      </c>
+      <c r="B308" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C308" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="0">
+        <v>0.83564701399096308</v>
+      </c>
+      <c r="B309" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C309" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="0">
+        <v>0.83836899123523334</v>
+      </c>
+      <c r="B310" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C310" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="0">
+        <v>0.84109096847950349</v>
+      </c>
+      <c r="B311" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C311" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="0">
+        <v>0.84381294572377374</v>
+      </c>
+      <c r="B312" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C312" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="0">
+        <v>0.846534922968044</v>
+      </c>
+      <c r="B313" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C313" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="0">
+        <v>0.84925690021231415</v>
+      </c>
+      <c r="B314" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C314" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="0">
+        <v>0.85197887745658452</v>
+      </c>
+      <c r="B315" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C315" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="0">
+        <v>0.85470085470085466</v>
+      </c>
+      <c r="B316" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C316" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="0">
+        <v>0.85742283194512492</v>
+      </c>
+      <c r="B317" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C317" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="0">
+        <v>0.86014480918939529</v>
+      </c>
+      <c r="B318" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C318" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="0">
+        <v>0.86286678643366543</v>
+      </c>
+      <c r="B319" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C319" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="0">
+        <v>0.86558876367793569</v>
+      </c>
+      <c r="B320" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C320" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="0">
+        <v>0.86831074092220584</v>
+      </c>
+      <c r="B321" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C321" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="0">
+        <v>0.87103271816647621</v>
+      </c>
+      <c r="B322" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C322" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="0">
+        <v>0.87375469541074624</v>
+      </c>
+      <c r="B323" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C323" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="0">
+        <v>0.87647667265501661</v>
+      </c>
+      <c r="B324" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C324" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="0">
+        <v>0.87919864989928687</v>
+      </c>
+      <c r="B325" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C325" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="0">
+        <v>0.88192062714355701</v>
+      </c>
+      <c r="B326" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C326" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="0">
+        <v>0.88464260438782738</v>
+      </c>
+      <c r="B327" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C327" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="0">
+        <v>0.88736458163209753</v>
+      </c>
+      <c r="B328" s="0">
+        <v>1.9942</v>
+      </c>
+      <c r="C328" s="0">
+        <v>1.0000200585710273</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="0">
+        <v>0.89008655887636778</v>
+      </c>
+      <c r="B329" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C329" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="0">
+        <v>0.89280853612063815</v>
+      </c>
+      <c r="B330" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C330" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="0">
+        <v>0.89553051336490819</v>
+      </c>
+      <c r="B331" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C331" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="0">
+        <v>0.89825249060917856</v>
+      </c>
+      <c r="B332" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C332" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="0">
+        <v>0.9009744678534487</v>
+      </c>
+      <c r="B333" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C333" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="0">
+        <v>0.90369644509771896</v>
+      </c>
+      <c r="B334" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C334" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="0">
+        <v>0.90641842234198933</v>
+      </c>
+      <c r="B335" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C335" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="0">
+        <v>0.90914039958625947</v>
+      </c>
+      <c r="B336" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C336" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="0">
+        <v>0.91186237683052973</v>
+      </c>
+      <c r="B337" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C337" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="0">
+        <v>0.91458435407479988</v>
+      </c>
+      <c r="B338" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C338" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="0">
+        <v>0.91730633131907025</v>
+      </c>
+      <c r="B339" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C339" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="0">
+        <v>0.92002830856334028</v>
+      </c>
+      <c r="B340" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C340" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="0">
+        <v>0.92275028580761065</v>
+      </c>
+      <c r="B341" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C341" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="0">
+        <v>0.92547226305188091</v>
+      </c>
+      <c r="B342" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C342" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="0">
+        <v>0.92819424029615105</v>
+      </c>
+      <c r="B343" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C343" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="0">
+        <v>0.93091621754042142</v>
+      </c>
+      <c r="B344" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C344" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="0">
+        <v>0.93363819478469157</v>
+      </c>
+      <c r="B345" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C345" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="0">
+        <v>0.93636017202896182</v>
+      </c>
+      <c r="B346" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C346" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="0">
+        <v>0.93908214927323219</v>
+      </c>
+      <c r="B347" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C347" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="0">
+        <v>0.94180412651750234</v>
+      </c>
+      <c r="B348" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C348" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="0">
+        <v>0.9445261037617726</v>
+      </c>
+      <c r="B349" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C349" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="0">
+        <v>0.94724808100604274</v>
+      </c>
+      <c r="B350" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C350" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="0">
+        <v>0.949970058250313</v>
+      </c>
+      <c r="B351" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C351" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="0">
+        <v>0.95269203549458337</v>
+      </c>
+      <c r="B352" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C352" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="0">
+        <v>0.95541401273885351</v>
+      </c>
+      <c r="B353" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C353" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="0">
+        <v>0.95813598998312377</v>
+      </c>
+      <c r="B354" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C354" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="0">
+        <v>0.96085796722739392</v>
+      </c>
+      <c r="B355" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C355" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="0">
+        <v>0.96357994447166428</v>
+      </c>
+      <c r="B356" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C356" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="0">
+        <v>0.96630192171593432</v>
+      </c>
+      <c r="B357" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C357" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="0">
+        <v>0.96902389896020469</v>
+      </c>
+      <c r="B358" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C358" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="0">
+        <v>0.97174587620447506</v>
+      </c>
+      <c r="B359" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C359" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="0">
+        <v>0.97446785344874509</v>
+      </c>
+      <c r="B360" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C360" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="0">
+        <v>0.97718983069301546</v>
+      </c>
+      <c r="B361" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C361" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="0">
+        <v>0.97991180793728561</v>
+      </c>
+      <c r="B362" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C362" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="0">
+        <v>0.98263378518155586</v>
+      </c>
+      <c r="B363" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C363" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="0">
+        <v>0.98535576242582623</v>
+      </c>
+      <c r="B364" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C364" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="0">
+        <v>0.98807773967009638</v>
+      </c>
+      <c r="B365" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C365" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="0">
+        <v>0.99079971691436663</v>
+      </c>
+      <c r="B366" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C366" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="0">
+        <v>0.99352169415863678</v>
+      </c>
+      <c r="B367" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C367" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="0">
+        <v>0.99624367140290704</v>
+      </c>
+      <c r="B368" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C368" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="0">
+        <v>0.99896564864717741</v>
+      </c>
+      <c r="B369" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C369" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="0">
+        <v>1.0016876258914476</v>
+      </c>
+      <c r="B370" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C370" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="0">
+        <v>1.0044096031357179</v>
+      </c>
+      <c r="B371" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C371" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="0">
+        <v>1.0071315803799881</v>
+      </c>
+      <c r="B372" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C372" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="0">
+        <v>1.0098535576242582</v>
+      </c>
+      <c r="B373" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C373" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="0">
+        <v>1.0125755348685284</v>
+      </c>
+      <c r="B374" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C374" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="0">
+        <v>1.0152975121127987</v>
+      </c>
+      <c r="B375" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C375" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="0">
+        <v>1.0180194893570691</v>
+      </c>
+      <c r="B376" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C376" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="0">
+        <v>1.0207414666013392</v>
+      </c>
+      <c r="B377" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C377" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="0">
+        <v>1.0234634438456094</v>
+      </c>
+      <c r="B378" s="0">
+        <v>1.9941899999999999</v>
+      </c>
+      <c r="C378" s="0">
+        <v>1.0000150439282705</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="0">
+        <v>1.0261854210898795</v>
+      </c>
+      <c r="B379" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C379" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="0">
+        <v>1.0289073983341499</v>
+      </c>
+      <c r="B380" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C380" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="0">
+        <v>1.0316293755784203</v>
+      </c>
+      <c r="B381" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C381" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="0">
+        <v>1.0343513528226904</v>
+      </c>
+      <c r="B382" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C382" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="0">
+        <v>1.0370733300669608</v>
+      </c>
+      <c r="B383" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C383" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="0">
+        <v>1.0397953073112309</v>
+      </c>
+      <c r="B384" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C384" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="0">
+        <v>1.0425172845555011</v>
+      </c>
+      <c r="B385" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C385" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="0">
+        <v>1.0452392617997712</v>
+      </c>
+      <c r="B386" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C386" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="0">
+        <v>1.0479612390440416</v>
+      </c>
+      <c r="B387" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C387" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="0">
+        <v>1.050683216288312</v>
+      </c>
+      <c r="B388" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C388" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="0">
+        <v>1.0534051935325821</v>
+      </c>
+      <c r="B389" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C389" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="0">
+        <v>1.0561271707768523</v>
+      </c>
+      <c r="B390" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C390" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="0">
+        <v>1.0588491480211224</v>
+      </c>
+      <c r="B391" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C391" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="0">
+        <v>1.0615711252653928</v>
+      </c>
+      <c r="B392" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C392" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="0">
+        <v>1.0642931025096631</v>
+      </c>
+      <c r="B393" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C393" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="0">
+        <v>1.0670150797539333</v>
+      </c>
+      <c r="B394" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C394" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="0">
+        <v>1.0697370569982037</v>
+      </c>
+      <c r="B395" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C395" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="0">
+        <v>1.0724590342424736</v>
+      </c>
+      <c r="B396" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C396" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="0">
+        <v>1.0751810114867439</v>
+      </c>
+      <c r="B397" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C397" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="0">
+        <v>1.0779029887310143</v>
+      </c>
+      <c r="B398" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C398" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="0">
+        <v>1.0806249659752845</v>
+      </c>
+      <c r="B399" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C399" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="0">
+        <v>1.0833469432195548</v>
+      </c>
+      <c r="B400" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C400" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="0">
+        <v>1.086068920463825</v>
+      </c>
+      <c r="B401" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C401" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="0">
+        <v>1.0887908977080951</v>
+      </c>
+      <c r="B402" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C402" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="0">
+        <v>1.0915128749523653</v>
+      </c>
+      <c r="B403" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C403" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="0">
+        <v>1.0942348521966356</v>
+      </c>
+      <c r="B404" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C404" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="0">
+        <v>1.096956829440906</v>
+      </c>
+      <c r="B405" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C405" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="0">
+        <v>1.0996788066851761</v>
+      </c>
+      <c r="B406" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C406" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="0">
+        <v>1.1024007839294463</v>
+      </c>
+      <c r="B407" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C407" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="0">
+        <v>1.1051227611737164</v>
+      </c>
+      <c r="B408" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C408" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="0">
+        <v>1.1078447384179868</v>
+      </c>
+      <c r="B409" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C409" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="0">
+        <v>1.1105667156622572</v>
+      </c>
+      <c r="B410" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C410" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="0">
+        <v>1.1132886929065273</v>
+      </c>
+      <c r="B411" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C411" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="0">
+        <v>1.1160106701507977</v>
+      </c>
+      <c r="B412" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C412" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="0">
+        <v>1.1187326473950676</v>
+      </c>
+      <c r="B413" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C413" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="0">
+        <v>1.121454624639338</v>
+      </c>
+      <c r="B414" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C414" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="0">
+        <v>1.1241766018836084</v>
+      </c>
+      <c r="B415" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C415" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="0">
+        <v>1.1268985791278785</v>
+      </c>
+      <c r="B416" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C416" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="0">
+        <v>1.1296205563721489</v>
+      </c>
+      <c r="B417" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C417" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="0">
+        <v>1.132342533616419</v>
+      </c>
+      <c r="B418" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C418" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="0">
+        <v>1.1350645108606892</v>
+      </c>
+      <c r="B419" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C419" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="0">
+        <v>1.1377864881049593</v>
+      </c>
+      <c r="B420" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C420" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="0">
+        <v>1.1405084653492297</v>
+      </c>
+      <c r="B421" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C421" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="0">
+        <v>1.1432304425935</v>
+      </c>
+      <c r="B422" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C422" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="0">
+        <v>1.1459524198377702</v>
+      </c>
+      <c r="B423" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C423" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="0">
+        <v>1.1486743970820403</v>
+      </c>
+      <c r="B424" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C424" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="0">
+        <v>1.1513963743263105</v>
+      </c>
+      <c r="B425" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C425" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="0">
+        <v>1.1541183515705808</v>
+      </c>
+      <c r="B426" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C426" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="0">
+        <v>1.1568403288148512</v>
+      </c>
+      <c r="B427" s="0">
+        <v>1.9941800000000001</v>
+      </c>
+      <c r="C427" s="0">
+        <v>1.0000100292855136</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="0">
+        <v>1.1595623060591214</v>
+      </c>
+      <c r="B428" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C428" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="0">
+        <v>1.1622842833033917</v>
+      </c>
+      <c r="B429" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C429" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="0">
+        <v>1.1650062605476619</v>
+      </c>
+      <c r="B430" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C430" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="0">
+        <v>1.167728237791932</v>
+      </c>
+      <c r="B431" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C431" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="0">
+        <v>1.1704502150362022</v>
+      </c>
+      <c r="B432" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C432" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="0">
+        <v>1.1731721922804725</v>
+      </c>
+      <c r="B433" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C433" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="0">
+        <v>1.1758941695247429</v>
+      </c>
+      <c r="B434" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C434" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="0">
+        <v>1.1786161467690131</v>
+      </c>
+      <c r="B435" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C435" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="0">
+        <v>1.1813381240132832</v>
+      </c>
+      <c r="B436" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C436" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="0">
+        <v>1.1840601012575533</v>
+      </c>
+      <c r="B437" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C437" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="0">
+        <v>1.1867820785018237</v>
+      </c>
+      <c r="B438" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C438" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="0">
+        <v>1.1895040557460941</v>
+      </c>
+      <c r="B439" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C439" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="0">
+        <v>1.1922260329903642</v>
+      </c>
+      <c r="B440" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C440" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="0">
+        <v>1.1949480102346346</v>
+      </c>
+      <c r="B441" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C441" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="0">
+        <v>1.1976699874789045</v>
+      </c>
+      <c r="B442" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C442" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="0">
+        <v>1.2003919647231749</v>
+      </c>
+      <c r="B443" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C443" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="0">
+        <v>1.2031139419674453</v>
+      </c>
+      <c r="B444" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C444" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="0">
+        <v>1.2058359192117154</v>
+      </c>
+      <c r="B445" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C445" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="0">
+        <v>1.2085578964559858</v>
+      </c>
+      <c r="B446" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C446" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="0">
+        <v>1.2112798737002559</v>
+      </c>
+      <c r="B447" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C447" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="0">
+        <v>1.2140018509445261</v>
+      </c>
+      <c r="B448" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C448" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="0">
+        <v>1.2167238281887962</v>
+      </c>
+      <c r="B449" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C449" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="0">
+        <v>1.2194458054330666</v>
+      </c>
+      <c r="B450" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C450" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="0">
+        <v>1.2221677826773369</v>
+      </c>
+      <c r="B451" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C451" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="0">
+        <v>1.2248897599216071</v>
+      </c>
+      <c r="B452" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C452" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="0">
+        <v>1.2276117371658772</v>
+      </c>
+      <c r="B453" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C453" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="0">
+        <v>1.2303337144101474</v>
+      </c>
+      <c r="B454" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C454" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="0">
+        <v>1.2330556916544178</v>
+      </c>
+      <c r="B455" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C455" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="0">
+        <v>1.2357776688986881</v>
+      </c>
+      <c r="B456" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C456" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="0">
+        <v>1.2384996461429583</v>
+      </c>
+      <c r="B457" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C457" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="0">
+        <v>1.2412216233872286</v>
+      </c>
+      <c r="B458" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C458" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="0">
+        <v>1.2439436006314986</v>
+      </c>
+      <c r="B459" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C459" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="0">
+        <v>1.2466655778757689</v>
+      </c>
+      <c r="B460" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C460" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="0">
+        <v>1.2493875551200393</v>
+      </c>
+      <c r="B461" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C461" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="0">
+        <v>1.2521095323643094</v>
+      </c>
+      <c r="B462" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C462" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="0">
+        <v>1.2548315096085798</v>
+      </c>
+      <c r="B463" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C463" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="0">
+        <v>1.25755348685285</v>
+      </c>
+      <c r="B464" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C464" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="0">
+        <v>1.2602754640971201</v>
+      </c>
+      <c r="B465" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C465" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="0">
+        <v>1.2629974413413902</v>
+      </c>
+      <c r="B466" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C466" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="0">
+        <v>1.2657194185856606</v>
+      </c>
+      <c r="B467" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C467" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="0">
+        <v>1.268441395829931</v>
+      </c>
+      <c r="B468" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C468" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="0">
+        <v>1.2711633730742011</v>
+      </c>
+      <c r="B469" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C469" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="0">
+        <v>1.2738853503184713</v>
+      </c>
+      <c r="B470" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C470" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="0">
+        <v>1.2766073275627414</v>
+      </c>
+      <c r="B471" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C471" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="0">
+        <v>1.2793293048070118</v>
+      </c>
+      <c r="B472" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C472" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="0">
+        <v>1.2820512820512822</v>
+      </c>
+      <c r="B473" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C473" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="0">
+        <v>1.2847732592955523</v>
+      </c>
+      <c r="B474" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C474" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="0">
+        <v>1.2874952365398227</v>
+      </c>
+      <c r="B475" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C475" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="0">
+        <v>1.2902172137840926</v>
+      </c>
+      <c r="B476" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C476" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="0">
+        <v>1.292939191028363</v>
+      </c>
+      <c r="B477" s="0">
+        <v>1.99417</v>
+      </c>
+      <c r="C477" s="0">
+        <v>1.0000050146427568</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="0">
+        <v>1.2956611682726333</v>
+      </c>
+      <c r="B478" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C478" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="0">
+        <v>1.2983831455169035</v>
+      </c>
+      <c r="B479" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C479" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="0">
+        <v>1.3011051227611738</v>
+      </c>
+      <c r="B480" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C480" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="0">
+        <v>1.303827100005444</v>
+      </c>
+      <c r="B481" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C481" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="0">
+        <v>1.3065490772497141</v>
+      </c>
+      <c r="B482" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C482" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="0">
+        <v>1.3092710544939843</v>
+      </c>
+      <c r="B483" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C483" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="0">
+        <v>1.3119930317382547</v>
+      </c>
+      <c r="B484" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C484" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="0">
+        <v>1.314715008982525</v>
+      </c>
+      <c r="B485" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C485" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="0">
+        <v>1.3174369862267952</v>
+      </c>
+      <c r="B486" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C486" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="0">
+        <v>1.3201589634710655</v>
+      </c>
+      <c r="B487" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C487" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="0">
+        <v>1.3228809407153355</v>
+      </c>
+      <c r="B488" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C488" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="0">
+        <v>1.3256029179596058</v>
+      </c>
+      <c r="B489" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C489" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="0">
+        <v>1.3283248952038762</v>
+      </c>
+      <c r="B490" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C490" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="0">
+        <v>1.3310468724481463</v>
+      </c>
+      <c r="B491" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C491" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="0">
+        <v>1.3337688496924167</v>
+      </c>
+      <c r="B492" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C492" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="0">
+        <v>1.3364908269366869</v>
+      </c>
+      <c r="B493" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C493" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="0">
+        <v>1.339212804180957</v>
+      </c>
+      <c r="B494" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C494" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="0">
+        <v>1.3419347814252272</v>
+      </c>
+      <c r="B495" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C495" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="0">
+        <v>1.3446567586694975</v>
+      </c>
+      <c r="B496" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C496" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="0">
+        <v>1.3473787359137679</v>
+      </c>
+      <c r="B497" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C497" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="0">
+        <v>1.350100713158038</v>
+      </c>
+      <c r="B498" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C498" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="0">
+        <v>1.3528226904023082</v>
+      </c>
+      <c r="B499" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C499" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="0">
+        <v>1.3555446676465783</v>
+      </c>
+      <c r="B500" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C500" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="0">
+        <v>1.3582666448908487</v>
+      </c>
+      <c r="B501" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C501" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="0">
+        <v>1.3609886221351191</v>
+      </c>
+      <c r="B502" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C502" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="0">
+        <v>1.3637105993793892</v>
+      </c>
+      <c r="B503" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C503" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="0">
+        <v>1.3664325766236596</v>
+      </c>
+      <c r="B504" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C504" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="0">
+        <v>1.3691545538679295</v>
+      </c>
+      <c r="B505" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C505" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="0">
+        <v>1.3718765311121999</v>
+      </c>
+      <c r="B506" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C506" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="0">
+        <v>1.3745985083564702</v>
+      </c>
+      <c r="B507" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C507" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="0">
+        <v>1.3773204856007404</v>
+      </c>
+      <c r="B508" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C508" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="0">
+        <v>1.3800424628450108</v>
+      </c>
+      <c r="B509" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C509" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="0">
+        <v>1.3827644400892809</v>
+      </c>
+      <c r="B510" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C510" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="0">
+        <v>1.385486417333551</v>
+      </c>
+      <c r="B511" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C511" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="0">
+        <v>1.3882083945778212</v>
+      </c>
+      <c r="B512" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C512" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="0">
+        <v>1.3909303718220916</v>
+      </c>
+      <c r="B513" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C513" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="0">
+        <v>1.3936523490663619</v>
+      </c>
+      <c r="B514" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C514" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="0">
+        <v>1.3963743263106321</v>
+      </c>
+      <c r="B515" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C515" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="0">
+        <v>1.3990963035549022</v>
+      </c>
+      <c r="B516" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C516" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="0">
+        <v>1.4018182807991724</v>
+      </c>
+      <c r="B517" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C517" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="0">
+        <v>1.4045402580434427</v>
+      </c>
+      <c r="B518" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C518" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="0">
+        <v>1.4072622352877131</v>
+      </c>
+      <c r="B519" s="0">
+        <v>1.9941599999999999</v>
+      </c>
+      <c r="C519" s="0">
+        <v>0.99999999999999989</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="0">
         <v>1.4099842125319832</v>
       </c>
-      <c r="B261" s="0">
+      <c r="B520" s="0">
         <v>1.9941599999999999</v>
       </c>
-      <c r="C261" s="0">
+      <c r="C520" s="0">
         <v>0.99999999999999989</v>
       </c>
     </row>

--- a/TunnelDataProcessing/BoundaryLayerComparison/BoundaryLayerComparison.xlsx
+++ b/TunnelDataProcessing/BoundaryLayerComparison/BoundaryLayerComparison.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -18,7 +18,88 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="105" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="30">
+  <si>
+    <t>Y_over_D</t>
+  </si>
+  <si>
+    <t>Mach</t>
+  </si>
+  <si>
+    <t>Mach_nd</t>
+  </si>
+  <si>
+    <t>Y_over_D</t>
+  </si>
+  <si>
+    <t>Mach</t>
+  </si>
+  <si>
+    <t>Mach_nd</t>
+  </si>
+  <si>
+    <t>Y_over_D</t>
+  </si>
+  <si>
+    <t>Mach</t>
+  </si>
+  <si>
+    <t>Mach_nd</t>
+  </si>
+  <si>
+    <t>Y_over_D</t>
+  </si>
+  <si>
+    <t>Mach</t>
+  </si>
+  <si>
+    <t>Mach_nd</t>
+  </si>
+  <si>
+    <t>Y_over_D</t>
+  </si>
+  <si>
+    <t>Mach</t>
+  </si>
+  <si>
+    <t>Mach_nd</t>
+  </si>
+  <si>
+    <t>Y_over_D</t>
+  </si>
+  <si>
+    <t>Mach</t>
+  </si>
+  <si>
+    <t>Mach_nd</t>
+  </si>
+  <si>
+    <t>Y_over_D</t>
+  </si>
+  <si>
+    <t>Mach</t>
+  </si>
+  <si>
+    <t>Mach_nd</t>
+  </si>
+  <si>
+    <t>Y_over_D</t>
+  </si>
+  <si>
+    <t>Mach</t>
+  </si>
+  <si>
+    <t>Mach_nd</t>
+  </si>
+  <si>
+    <t>Y_over_D</t>
+  </si>
+  <si>
+    <t>Mach</t>
+  </si>
+  <si>
+    <t>Mach_nd</t>
+  </si>
   <si>
     <t>Y_over_D</t>
   </si>
@@ -32,7 +113,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -82,13 +163,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2">
@@ -3490,13 +3571,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
@@ -6815,13 +6896,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">

--- a/TunnelDataProcessing/BoundaryLayerComparison/BoundaryLayerComparison.xlsx
+++ b/TunnelDataProcessing/BoundaryLayerComparison/BoundaryLayerComparison.xlsx
@@ -18,7 +18,151 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="78">
+  <si>
+    <t>Y_over_D</t>
+  </si>
+  <si>
+    <t>Mach</t>
+  </si>
+  <si>
+    <t>Mach_nd</t>
+  </si>
+  <si>
+    <t>Y_over_D</t>
+  </si>
+  <si>
+    <t>Mach</t>
+  </si>
+  <si>
+    <t>Mach_nd</t>
+  </si>
+  <si>
+    <t>Y_over_D</t>
+  </si>
+  <si>
+    <t>Mach</t>
+  </si>
+  <si>
+    <t>Mach_nd</t>
+  </si>
+  <si>
+    <t>Y_over_D</t>
+  </si>
+  <si>
+    <t>Mach</t>
+  </si>
+  <si>
+    <t>Mach_nd</t>
+  </si>
+  <si>
+    <t>Y_over_D</t>
+  </si>
+  <si>
+    <t>Mach</t>
+  </si>
+  <si>
+    <t>Mach_nd</t>
+  </si>
+  <si>
+    <t>Y_over_D</t>
+  </si>
+  <si>
+    <t>Mach</t>
+  </si>
+  <si>
+    <t>Mach_nd</t>
+  </si>
+  <si>
+    <t>Y_over_D</t>
+  </si>
+  <si>
+    <t>Mach</t>
+  </si>
+  <si>
+    <t>Mach_nd</t>
+  </si>
+  <si>
+    <t>Y_over_D</t>
+  </si>
+  <si>
+    <t>Mach</t>
+  </si>
+  <si>
+    <t>Mach_nd</t>
+  </si>
+  <si>
+    <t>Y_over_D</t>
+  </si>
+  <si>
+    <t>Mach</t>
+  </si>
+  <si>
+    <t>Mach_nd</t>
+  </si>
+  <si>
+    <t>Y_over_D</t>
+  </si>
+  <si>
+    <t>Mach</t>
+  </si>
+  <si>
+    <t>Mach_nd</t>
+  </si>
+  <si>
+    <t>Y_over_D</t>
+  </si>
+  <si>
+    <t>Mach</t>
+  </si>
+  <si>
+    <t>Mach_nd</t>
+  </si>
+  <si>
+    <t>Y_over_D</t>
+  </si>
+  <si>
+    <t>Mach</t>
+  </si>
+  <si>
+    <t>Mach_nd</t>
+  </si>
+  <si>
+    <t>Y_over_D</t>
+  </si>
+  <si>
+    <t>Mach</t>
+  </si>
+  <si>
+    <t>Mach_nd</t>
+  </si>
+  <si>
+    <t>Y_over_D</t>
+  </si>
+  <si>
+    <t>Mach</t>
+  </si>
+  <si>
+    <t>Mach_nd</t>
+  </si>
+  <si>
+    <t>Y_over_D</t>
+  </si>
+  <si>
+    <t>Mach</t>
+  </si>
+  <si>
+    <t>Mach_nd</t>
+  </si>
+  <si>
+    <t>Y_over_D</t>
+  </si>
+  <si>
+    <t>Mach</t>
+  </si>
+  <si>
+    <t>Mach_nd</t>
+  </si>
   <si>
     <t>Y_over_D</t>
   </si>
@@ -163,13 +307,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2">
@@ -1292,20 +1436,20 @@
   <dimension ref="A1:C102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" customWidth="true"/>
-    <col min="2" max="2" width="12.5546875" customWidth="true"/>
-    <col min="3" max="3" width="12.5546875" customWidth="true"/>
+    <col min="1" max="1" width="13.7109375" customWidth="true"/>
+    <col min="2" max="2" width="12.7109375" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>2</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2">
@@ -2428,20 +2572,20 @@
   <dimension ref="A1:C102"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" customWidth="true"/>
-    <col min="2" max="2" width="12.5546875" customWidth="true"/>
-    <col min="3" max="3" width="12.5546875" customWidth="true"/>
+    <col min="1" max="1" width="13.7109375" customWidth="true"/>
+    <col min="2" max="2" width="12.7109375" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>2</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2">
@@ -3571,13 +3715,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2">
@@ -6896,13 +7040,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>27</v>
+        <v>75</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>29</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2">
